--- a/actions_fetch/out/kookmin(2026-2).xlsx
+++ b/actions_fetch/out/kookmin(2026-2).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4873" uniqueCount="1409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5065" uniqueCount="1453">
   <si>
     <t>campusCode</t>
   </si>
@@ -4108,10 +4108,142 @@
     <t>소프트웨어융합대학원</t>
   </si>
   <si>
+    <t>7147801</t>
+  </si>
+  <si>
+    <t>자료구조</t>
+  </si>
+  <si>
+    <t>한진섭</t>
+  </si>
+  <si>
     <t>7175701</t>
   </si>
   <si>
     <t>알고리즘특론</t>
+  </si>
+  <si>
+    <t>이지나</t>
+  </si>
+  <si>
+    <t>7241701</t>
+  </si>
+  <si>
+    <t>사용자경험과AI코딩</t>
+  </si>
+  <si>
+    <t>윤종영</t>
+  </si>
+  <si>
+    <t>36296</t>
+  </si>
+  <si>
+    <t>인공지능전공</t>
+  </si>
+  <si>
+    <t>710010a</t>
+  </si>
+  <si>
+    <t>인공지능과비즈니스</t>
+  </si>
+  <si>
+    <t>711610b</t>
+  </si>
+  <si>
+    <t>인공지능자연어처리</t>
+  </si>
+  <si>
+    <t>7142401</t>
+  </si>
+  <si>
+    <t>딥러닝개론</t>
+  </si>
+  <si>
+    <t>7176401</t>
+  </si>
+  <si>
+    <t>인공지능추천시스템</t>
+  </si>
+  <si>
+    <t>36322</t>
+  </si>
+  <si>
+    <t>소프트웨어전공</t>
+  </si>
+  <si>
+    <t>710040b</t>
+  </si>
+  <si>
+    <t>블록체인응용개발</t>
+  </si>
+  <si>
+    <t>7147701</t>
+  </si>
+  <si>
+    <t>소프트웨어공학</t>
+  </si>
+  <si>
+    <t>7175901</t>
+  </si>
+  <si>
+    <t>파이썬매시업프로젝트</t>
+  </si>
+  <si>
+    <t>7176201</t>
+  </si>
+  <si>
+    <t>IoT 기초</t>
+  </si>
+  <si>
+    <t>허대영</t>
+  </si>
+  <si>
+    <t>7264301</t>
+  </si>
+  <si>
+    <t>정보보호개론</t>
+  </si>
+  <si>
+    <t>이수미</t>
+  </si>
+  <si>
+    <t>7264401</t>
+  </si>
+  <si>
+    <t>컴퓨터네트워크의실제</t>
+  </si>
+  <si>
+    <t>36346</t>
+  </si>
+  <si>
+    <t>인공지능응용전공</t>
+  </si>
+  <si>
+    <t>714200b</t>
+  </si>
+  <si>
+    <t>프로그래밍특론</t>
+  </si>
+  <si>
+    <t>714250c</t>
+  </si>
+  <si>
+    <t>데이터분석</t>
+  </si>
+  <si>
+    <t>이정미</t>
+  </si>
+  <si>
+    <t>714270b</t>
+  </si>
+  <si>
+    <t>인공지능수학</t>
+  </si>
+  <si>
+    <t>7264701</t>
+  </si>
+  <si>
+    <t>LLM및프롬프트엔지니어링</t>
   </si>
   <si>
     <t>36379</t>
@@ -4614,7 +4746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M406"/>
+  <dimension ref="A1:M422"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -20838,10 +20970,10 @@
         <v>2</v>
       </c>
       <c r="I396" t="s">
-        <v>166</v>
+        <v>1367</v>
       </c>
       <c r="J396" t="s">
-        <v>166</v>
+        <v>1104</v>
       </c>
       <c r="K396" t="s">
         <v>21</v>
@@ -20855,40 +20987,40 @@
     </row>
     <row r="397" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B397" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C397" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="D397" t="s">
         <v>15</v>
       </c>
       <c r="E397" t="s">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="F397" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G397" t="s">
         <v>1369</v>
       </c>
-      <c r="G397" t="s">
+      <c r="H397">
+        <v>2</v>
+      </c>
+      <c r="I397" t="s">
         <v>1370</v>
       </c>
-      <c r="H397">
-        <v>2</v>
-      </c>
-      <c r="I397" t="s">
-        <v>1371</v>
-      </c>
       <c r="J397" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="K397" t="s">
         <v>21</v>
       </c>
       <c r="L397" t="s">
-        <v>1372</v>
+        <v>166</v>
       </c>
       <c r="M397" t="s">
         <v>23</v>
@@ -20896,40 +21028,40 @@
     </row>
     <row r="398" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B398" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C398" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D398" t="s">
+        <v>15</v>
+      </c>
+      <c r="E398" t="s">
+        <v>36</v>
+      </c>
+      <c r="F398" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G398" t="s">
+        <v>1372</v>
+      </c>
+      <c r="H398">
+        <v>2</v>
+      </c>
+      <c r="I398" t="s">
         <v>1373</v>
       </c>
-      <c r="D398" t="s">
-        <v>1374</v>
-      </c>
-      <c r="E398" t="s">
-        <v>36</v>
-      </c>
-      <c r="F398" t="s">
-        <v>1375</v>
-      </c>
-      <c r="G398" t="s">
-        <v>1376</v>
-      </c>
-      <c r="H398">
-        <v>2</v>
-      </c>
-      <c r="I398" t="s">
-        <v>1377</v>
-      </c>
       <c r="J398" t="s">
-        <v>1378</v>
+        <v>1097</v>
       </c>
       <c r="K398" t="s">
         <v>21</v>
       </c>
       <c r="L398" t="s">
-        <v>1379</v>
+        <v>166</v>
       </c>
       <c r="M398" t="s">
         <v>23</v>
@@ -20937,40 +21069,40 @@
     </row>
     <row r="399" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B399" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C399" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="D399" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="E399" t="s">
         <v>36</v>
       </c>
       <c r="F399" t="s">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="G399" t="s">
-        <v>1383</v>
+        <v>1377</v>
       </c>
       <c r="H399">
         <v>2</v>
       </c>
       <c r="I399" t="s">
-        <v>674</v>
+        <v>166</v>
       </c>
       <c r="J399" t="s">
-        <v>248</v>
+        <v>166</v>
       </c>
       <c r="K399" t="s">
         <v>21</v>
       </c>
       <c r="L399" t="s">
-        <v>1384</v>
+        <v>166</v>
       </c>
       <c r="M399" t="s">
         <v>23</v>
@@ -20978,40 +21110,40 @@
     </row>
     <row r="400" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B400" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C400" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="D400" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="E400" t="s">
         <v>36</v>
       </c>
       <c r="F400" t="s">
-        <v>1385</v>
+        <v>1378</v>
       </c>
       <c r="G400" t="s">
-        <v>1386</v>
+        <v>1379</v>
       </c>
       <c r="H400">
         <v>2</v>
       </c>
       <c r="I400" t="s">
-        <v>1387</v>
+        <v>166</v>
       </c>
       <c r="J400" t="s">
-        <v>767</v>
+        <v>166</v>
       </c>
       <c r="K400" t="s">
         <v>21</v>
       </c>
       <c r="L400" t="s">
-        <v>1379</v>
+        <v>166</v>
       </c>
       <c r="M400" t="s">
         <v>23</v>
@@ -21019,40 +21151,40 @@
     </row>
     <row r="401" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B401" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C401" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D401" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E401" t="s">
+        <v>36</v>
+      </c>
+      <c r="F401" t="s">
         <v>1380</v>
       </c>
-      <c r="D401" t="s">
+      <c r="G401" t="s">
         <v>1381</v>
       </c>
-      <c r="E401" t="s">
-        <v>36</v>
-      </c>
-      <c r="F401" t="s">
-        <v>1388</v>
-      </c>
-      <c r="G401" t="s">
-        <v>1389</v>
-      </c>
       <c r="H401">
         <v>2</v>
       </c>
       <c r="I401" t="s">
-        <v>1390</v>
+        <v>166</v>
       </c>
       <c r="J401" t="s">
-        <v>1378</v>
+        <v>166</v>
       </c>
       <c r="K401" t="s">
         <v>21</v>
       </c>
       <c r="L401" t="s">
-        <v>1372</v>
+        <v>166</v>
       </c>
       <c r="M401" t="s">
         <v>23</v>
@@ -21060,40 +21192,40 @@
     </row>
     <row r="402" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B402" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C402" t="s">
-        <v>1380</v>
+        <v>1374</v>
       </c>
       <c r="D402" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="E402" t="s">
         <v>36</v>
       </c>
       <c r="F402" t="s">
-        <v>1391</v>
+        <v>1382</v>
       </c>
       <c r="G402" t="s">
-        <v>1392</v>
+        <v>1383</v>
       </c>
       <c r="H402">
         <v>2</v>
       </c>
       <c r="I402" t="s">
-        <v>1393</v>
+        <v>166</v>
       </c>
       <c r="J402" t="s">
-        <v>308</v>
+        <v>166</v>
       </c>
       <c r="K402" t="s">
         <v>21</v>
       </c>
       <c r="L402" t="s">
-        <v>1394</v>
+        <v>166</v>
       </c>
       <c r="M402" t="s">
         <v>23</v>
@@ -21101,40 +21233,40 @@
     </row>
     <row r="403" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B403" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C403" t="s">
-        <v>1395</v>
+        <v>1384</v>
       </c>
       <c r="D403" t="s">
-        <v>1396</v>
+        <v>1385</v>
       </c>
       <c r="E403" t="s">
         <v>36</v>
       </c>
       <c r="F403" t="s">
-        <v>1397</v>
+        <v>1386</v>
       </c>
       <c r="G403" t="s">
-        <v>1398</v>
+        <v>1387</v>
       </c>
       <c r="H403">
         <v>2</v>
       </c>
       <c r="I403" t="s">
-        <v>1399</v>
+        <v>166</v>
       </c>
       <c r="J403" t="s">
-        <v>1400</v>
+        <v>166</v>
       </c>
       <c r="K403" t="s">
         <v>21</v>
       </c>
       <c r="L403" t="s">
-        <v>1372</v>
+        <v>166</v>
       </c>
       <c r="M403" t="s">
         <v>23</v>
@@ -21142,40 +21274,40 @@
     </row>
     <row r="404" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B404" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C404" t="s">
-        <v>1395</v>
+        <v>1384</v>
       </c>
       <c r="D404" t="s">
-        <v>1396</v>
+        <v>1385</v>
       </c>
       <c r="E404" t="s">
         <v>36</v>
       </c>
       <c r="F404" t="s">
-        <v>1401</v>
+        <v>1388</v>
       </c>
       <c r="G404" t="s">
-        <v>1402</v>
+        <v>1389</v>
       </c>
       <c r="H404">
         <v>2</v>
       </c>
       <c r="I404" t="s">
-        <v>1399</v>
+        <v>1370</v>
       </c>
       <c r="J404" t="s">
-        <v>248</v>
+        <v>166</v>
       </c>
       <c r="K404" t="s">
         <v>21</v>
       </c>
       <c r="L404" t="s">
-        <v>1394</v>
+        <v>166</v>
       </c>
       <c r="M404" t="s">
         <v>23</v>
@@ -21183,40 +21315,40 @@
     </row>
     <row r="405" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B405" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C405" t="s">
-        <v>1395</v>
+        <v>1384</v>
       </c>
       <c r="D405" t="s">
-        <v>1396</v>
+        <v>1385</v>
       </c>
       <c r="E405" t="s">
         <v>36</v>
       </c>
       <c r="F405" t="s">
-        <v>1403</v>
+        <v>1390</v>
       </c>
       <c r="G405" t="s">
-        <v>1404</v>
+        <v>1391</v>
       </c>
       <c r="H405">
         <v>2</v>
       </c>
       <c r="I405" t="s">
-        <v>1371</v>
+        <v>166</v>
       </c>
       <c r="J405" t="s">
-        <v>1405</v>
+        <v>166</v>
       </c>
       <c r="K405" t="s">
         <v>21</v>
       </c>
       <c r="L405" t="s">
-        <v>1379</v>
+        <v>166</v>
       </c>
       <c r="M405" t="s">
         <v>23</v>
@@ -21224,42 +21356,698 @@
     </row>
     <row r="406" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B406" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="C406" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D406" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E406" t="s">
+        <v>36</v>
+      </c>
+      <c r="F406" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G406" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H406">
+        <v>2</v>
+      </c>
+      <c r="I406" t="s">
+        <v>1394</v>
+      </c>
+      <c r="J406" t="s">
+        <v>166</v>
+      </c>
+      <c r="K406" t="s">
+        <v>21</v>
+      </c>
+      <c r="L406" t="s">
+        <v>166</v>
+      </c>
+      <c r="M406" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="407" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B407" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C407" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D407" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E407" t="s">
+        <v>36</v>
+      </c>
+      <c r="F407" t="s">
         <v>1395</v>
       </c>
-      <c r="D406" t="s">
+      <c r="G407" t="s">
         <v>1396</v>
       </c>
-      <c r="E406" t="s">
-        <v>36</v>
-      </c>
-      <c r="F406" t="s">
+      <c r="H407">
+        <v>2</v>
+      </c>
+      <c r="I407" t="s">
+        <v>1397</v>
+      </c>
+      <c r="J407" t="s">
+        <v>166</v>
+      </c>
+      <c r="K407" t="s">
+        <v>21</v>
+      </c>
+      <c r="L407" t="s">
+        <v>166</v>
+      </c>
+      <c r="M407" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="408" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B408" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C408" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D408" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E408" t="s">
+        <v>36</v>
+      </c>
+      <c r="F408" t="s">
+        <v>1398</v>
+      </c>
+      <c r="G408" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H408">
+        <v>2</v>
+      </c>
+      <c r="I408" t="s">
+        <v>166</v>
+      </c>
+      <c r="J408" t="s">
+        <v>166</v>
+      </c>
+      <c r="K408" t="s">
+        <v>21</v>
+      </c>
+      <c r="L408" t="s">
+        <v>166</v>
+      </c>
+      <c r="M408" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="409" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B409" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C409" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D409" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E409" t="s">
+        <v>36</v>
+      </c>
+      <c r="F409" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G409" t="s">
+        <v>1403</v>
+      </c>
+      <c r="H409">
+        <v>2</v>
+      </c>
+      <c r="I409" t="s">
+        <v>166</v>
+      </c>
+      <c r="J409" t="s">
+        <v>166</v>
+      </c>
+      <c r="K409" t="s">
+        <v>21</v>
+      </c>
+      <c r="L409" t="s">
+        <v>166</v>
+      </c>
+      <c r="M409" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B410" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C410" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D410" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E410" t="s">
+        <v>36</v>
+      </c>
+      <c r="F410" t="s">
+        <v>1404</v>
+      </c>
+      <c r="G410" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H410">
+        <v>2</v>
+      </c>
+      <c r="I410" t="s">
         <v>1406</v>
       </c>
-      <c r="G406" t="s">
+      <c r="J410" t="s">
+        <v>166</v>
+      </c>
+      <c r="K410" t="s">
+        <v>21</v>
+      </c>
+      <c r="L410" t="s">
+        <v>166</v>
+      </c>
+      <c r="M410" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B411" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C411" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D411" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E411" t="s">
+        <v>36</v>
+      </c>
+      <c r="F411" t="s">
         <v>1407</v>
       </c>
-      <c r="H406">
-        <v>2</v>
-      </c>
-      <c r="I406" t="s">
+      <c r="G411" t="s">
         <v>1408</v>
       </c>
-      <c r="J406" t="s">
+      <c r="H411">
+        <v>2</v>
+      </c>
+      <c r="I411" t="s">
+        <v>166</v>
+      </c>
+      <c r="J411" t="s">
+        <v>166</v>
+      </c>
+      <c r="K411" t="s">
+        <v>21</v>
+      </c>
+      <c r="L411" t="s">
+        <v>166</v>
+      </c>
+      <c r="M411" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B412" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C412" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D412" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E412" t="s">
+        <v>36</v>
+      </c>
+      <c r="F412" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G412" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H412">
+        <v>2</v>
+      </c>
+      <c r="I412" t="s">
+        <v>166</v>
+      </c>
+      <c r="J412" t="s">
+        <v>166</v>
+      </c>
+      <c r="K412" t="s">
+        <v>21</v>
+      </c>
+      <c r="L412" t="s">
+        <v>166</v>
+      </c>
+      <c r="M412" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="413" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B413" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C413" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D413" t="s">
+        <v>15</v>
+      </c>
+      <c r="E413" t="s">
+        <v>95</v>
+      </c>
+      <c r="F413" t="s">
+        <v>1413</v>
+      </c>
+      <c r="G413" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H413">
+        <v>2</v>
+      </c>
+      <c r="I413" t="s">
+        <v>1415</v>
+      </c>
+      <c r="J413" t="s">
+        <v>775</v>
+      </c>
+      <c r="K413" t="s">
+        <v>21</v>
+      </c>
+      <c r="L413" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M413" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="414" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B414" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C414" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D414" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E414" t="s">
+        <v>36</v>
+      </c>
+      <c r="F414" t="s">
+        <v>1419</v>
+      </c>
+      <c r="G414" t="s">
+        <v>1420</v>
+      </c>
+      <c r="H414">
+        <v>2</v>
+      </c>
+      <c r="I414" t="s">
+        <v>1421</v>
+      </c>
+      <c r="J414" t="s">
+        <v>1422</v>
+      </c>
+      <c r="K414" t="s">
+        <v>21</v>
+      </c>
+      <c r="L414" t="s">
+        <v>1423</v>
+      </c>
+      <c r="M414" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="415" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B415" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C415" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D415" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E415" t="s">
+        <v>36</v>
+      </c>
+      <c r="F415" t="s">
+        <v>1426</v>
+      </c>
+      <c r="G415" t="s">
+        <v>1427</v>
+      </c>
+      <c r="H415">
+        <v>2</v>
+      </c>
+      <c r="I415" t="s">
+        <v>674</v>
+      </c>
+      <c r="J415" t="s">
+        <v>248</v>
+      </c>
+      <c r="K415" t="s">
+        <v>21</v>
+      </c>
+      <c r="L415" t="s">
+        <v>1428</v>
+      </c>
+      <c r="M415" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="416" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B416" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C416" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D416" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E416" t="s">
+        <v>36</v>
+      </c>
+      <c r="F416" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G416" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H416">
+        <v>2</v>
+      </c>
+      <c r="I416" t="s">
+        <v>1431</v>
+      </c>
+      <c r="J416" t="s">
         <v>767</v>
       </c>
-      <c r="K406" t="s">
-        <v>21</v>
-      </c>
-      <c r="L406" t="s">
-        <v>1372</v>
-      </c>
-      <c r="M406" t="s">
+      <c r="K416" t="s">
+        <v>21</v>
+      </c>
+      <c r="L416" t="s">
+        <v>1423</v>
+      </c>
+      <c r="M416" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B417" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C417" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D417" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E417" t="s">
+        <v>36</v>
+      </c>
+      <c r="F417" t="s">
+        <v>1432</v>
+      </c>
+      <c r="G417" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H417">
+        <v>2</v>
+      </c>
+      <c r="I417" t="s">
+        <v>1434</v>
+      </c>
+      <c r="J417" t="s">
+        <v>1422</v>
+      </c>
+      <c r="K417" t="s">
+        <v>21</v>
+      </c>
+      <c r="L417" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M417" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="418" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B418" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C418" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D418" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E418" t="s">
+        <v>36</v>
+      </c>
+      <c r="F418" t="s">
+        <v>1435</v>
+      </c>
+      <c r="G418" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H418">
+        <v>2</v>
+      </c>
+      <c r="I418" t="s">
+        <v>1437</v>
+      </c>
+      <c r="J418" t="s">
+        <v>308</v>
+      </c>
+      <c r="K418" t="s">
+        <v>21</v>
+      </c>
+      <c r="L418" t="s">
+        <v>1438</v>
+      </c>
+      <c r="M418" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="419" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B419" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C419" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D419" t="s">
+        <v>1440</v>
+      </c>
+      <c r="E419" t="s">
+        <v>36</v>
+      </c>
+      <c r="F419" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G419" t="s">
+        <v>1442</v>
+      </c>
+      <c r="H419">
+        <v>2</v>
+      </c>
+      <c r="I419" t="s">
+        <v>1443</v>
+      </c>
+      <c r="J419" t="s">
+        <v>1444</v>
+      </c>
+      <c r="K419" t="s">
+        <v>21</v>
+      </c>
+      <c r="L419" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M419" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="420" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B420" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C420" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D420" t="s">
+        <v>1440</v>
+      </c>
+      <c r="E420" t="s">
+        <v>36</v>
+      </c>
+      <c r="F420" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G420" t="s">
+        <v>1446</v>
+      </c>
+      <c r="H420">
+        <v>2</v>
+      </c>
+      <c r="I420" t="s">
+        <v>1443</v>
+      </c>
+      <c r="J420" t="s">
+        <v>248</v>
+      </c>
+      <c r="K420" t="s">
+        <v>21</v>
+      </c>
+      <c r="L420" t="s">
+        <v>1438</v>
+      </c>
+      <c r="M420" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="421" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B421" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C421" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D421" t="s">
+        <v>1440</v>
+      </c>
+      <c r="E421" t="s">
+        <v>36</v>
+      </c>
+      <c r="F421" t="s">
+        <v>1447</v>
+      </c>
+      <c r="G421" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H421">
+        <v>2</v>
+      </c>
+      <c r="I421" t="s">
+        <v>1415</v>
+      </c>
+      <c r="J421" t="s">
+        <v>1449</v>
+      </c>
+      <c r="K421" t="s">
+        <v>21</v>
+      </c>
+      <c r="L421" t="s">
+        <v>1423</v>
+      </c>
+      <c r="M421" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="422" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C422" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D422" t="s">
+        <v>1440</v>
+      </c>
+      <c r="E422" t="s">
+        <v>36</v>
+      </c>
+      <c r="F422" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G422" t="s">
+        <v>1451</v>
+      </c>
+      <c r="H422">
+        <v>2</v>
+      </c>
+      <c r="I422" t="s">
+        <v>1452</v>
+      </c>
+      <c r="J422" t="s">
+        <v>767</v>
+      </c>
+      <c r="K422" t="s">
+        <v>21</v>
+      </c>
+      <c r="L422" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M422" t="s">
         <v>23</v>
       </c>
     </row>

--- a/actions_fetch/out/kookmin(2026-2).xlsx
+++ b/actions_fetch/out/kookmin(2026-2).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12085" uniqueCount="2957">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12085" uniqueCount="2961">
   <si>
     <t>campusCode</t>
   </si>
@@ -8545,6 +8545,9 @@
     <t>한진섭</t>
   </si>
   <si>
+    <t>미래관4층47호실</t>
+  </si>
+  <si>
     <t>7175701</t>
   </si>
   <si>
@@ -8560,12 +8563,18 @@
     <t>논문/프로젝트I</t>
   </si>
   <si>
+    <t>미래관4층45호실</t>
+  </si>
+  <si>
     <t>7223501</t>
   </si>
   <si>
     <t>논문/프로젝트II</t>
   </si>
   <si>
+    <t>미래관4층24호실</t>
+  </si>
+  <si>
     <t>김준호</t>
   </si>
   <si>
@@ -8729,6 +8738,9 @@
   </si>
   <si>
     <t>이창우</t>
+  </si>
+  <si>
+    <t>미래관6층11호실</t>
   </si>
   <si>
     <t>7208601</t>
@@ -48943,7 +48955,7 @@
         <v>21</v>
       </c>
       <c r="L968" t="s">
-        <v>116</v>
+        <v>2844</v>
       </c>
       <c r="M968" t="s">
         <v>23</v>
@@ -48966,16 +48978,16 @@
         <v>16</v>
       </c>
       <c r="F969" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="G969" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="H969">
         <v>2</v>
       </c>
       <c r="I969" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="J969" t="s">
         <v>2209</v>
@@ -48984,7 +48996,7 @@
         <v>21</v>
       </c>
       <c r="L969" t="s">
-        <v>116</v>
+        <v>2844</v>
       </c>
       <c r="M969" t="s">
         <v>23</v>
@@ -49007,10 +49019,10 @@
         <v>16</v>
       </c>
       <c r="F970" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="G970" t="s">
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="H970">
         <v>2</v>
@@ -49025,7 +49037,7 @@
         <v>21</v>
       </c>
       <c r="L970" t="s">
-        <v>116</v>
+        <v>2850</v>
       </c>
       <c r="M970" t="s">
         <v>23</v>
@@ -49048,10 +49060,10 @@
         <v>16</v>
       </c>
       <c r="F971" t="s">
-        <v>2849</v>
+        <v>2851</v>
       </c>
       <c r="G971" t="s">
-        <v>2850</v>
+        <v>2852</v>
       </c>
       <c r="H971">
         <v>2</v>
@@ -49066,7 +49078,7 @@
         <v>21</v>
       </c>
       <c r="L971" t="s">
-        <v>116</v>
+        <v>2853</v>
       </c>
       <c r="M971" t="s">
         <v>23</v>
@@ -49089,10 +49101,10 @@
         <v>16</v>
       </c>
       <c r="F972" t="s">
-        <v>2849</v>
+        <v>2851</v>
       </c>
       <c r="G972" t="s">
-        <v>2850</v>
+        <v>2852</v>
       </c>
       <c r="H972">
         <v>2</v>
@@ -49107,7 +49119,7 @@
         <v>21</v>
       </c>
       <c r="L972" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="M972" t="s">
         <v>623</v>
@@ -49130,16 +49142,16 @@
         <v>16</v>
       </c>
       <c r="F973" t="s">
-        <v>2849</v>
+        <v>2851</v>
       </c>
       <c r="G973" t="s">
-        <v>2850</v>
+        <v>2852</v>
       </c>
       <c r="H973">
         <v>2</v>
       </c>
       <c r="I973" t="s">
-        <v>2851</v>
+        <v>2854</v>
       </c>
       <c r="J973" t="s">
         <v>2218</v>
@@ -49148,7 +49160,7 @@
         <v>21</v>
       </c>
       <c r="L973" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="M973" t="s">
         <v>624</v>
@@ -49171,16 +49183,16 @@
         <v>16</v>
       </c>
       <c r="F974" t="s">
-        <v>2849</v>
+        <v>2851</v>
       </c>
       <c r="G974" t="s">
-        <v>2850</v>
+        <v>2852</v>
       </c>
       <c r="H974">
         <v>2</v>
       </c>
       <c r="I974" t="s">
-        <v>2852</v>
+        <v>2855</v>
       </c>
       <c r="J974" t="s">
         <v>2209</v>
@@ -49189,7 +49201,7 @@
         <v>21</v>
       </c>
       <c r="L974" t="s">
-        <v>116</v>
+        <v>2853</v>
       </c>
       <c r="M974" t="s">
         <v>625</v>
@@ -49212,16 +49224,16 @@
         <v>16</v>
       </c>
       <c r="F975" t="s">
-        <v>2849</v>
+        <v>2851</v>
       </c>
       <c r="G975" t="s">
-        <v>2850</v>
+        <v>2852</v>
       </c>
       <c r="H975">
         <v>2</v>
       </c>
       <c r="I975" t="s">
-        <v>2853</v>
+        <v>2856</v>
       </c>
       <c r="J975" t="s">
         <v>2213</v>
@@ -49230,7 +49242,7 @@
         <v>21</v>
       </c>
       <c r="L975" t="s">
-        <v>116</v>
+        <v>2853</v>
       </c>
       <c r="M975" t="s">
         <v>626</v>
@@ -49253,16 +49265,16 @@
         <v>16</v>
       </c>
       <c r="F976" t="s">
-        <v>2854</v>
+        <v>2857</v>
       </c>
       <c r="G976" t="s">
-        <v>2855</v>
+        <v>2858</v>
       </c>
       <c r="H976">
         <v>2</v>
       </c>
       <c r="I976" t="s">
-        <v>2852</v>
+        <v>2855</v>
       </c>
       <c r="J976" t="s">
         <v>2363</v>
@@ -49271,7 +49283,7 @@
         <v>21</v>
       </c>
       <c r="L976" t="s">
-        <v>116</v>
+        <v>2853</v>
       </c>
       <c r="M976" t="s">
         <v>23</v>
@@ -49294,25 +49306,25 @@
         <v>16</v>
       </c>
       <c r="F977" t="s">
-        <v>2856</v>
+        <v>2859</v>
       </c>
       <c r="G977" t="s">
-        <v>2857</v>
+        <v>2860</v>
       </c>
       <c r="H977">
         <v>2</v>
       </c>
       <c r="I977" t="s">
-        <v>2858</v>
+        <v>2861</v>
       </c>
       <c r="J977" t="s">
-        <v>2859</v>
+        <v>2862</v>
       </c>
       <c r="K977" t="s">
         <v>21</v>
       </c>
       <c r="L977" t="s">
-        <v>116</v>
+        <v>2853</v>
       </c>
       <c r="M977" t="s">
         <v>23</v>
@@ -49326,25 +49338,25 @@
         <v>2840</v>
       </c>
       <c r="C978" t="s">
-        <v>2860</v>
+        <v>2863</v>
       </c>
       <c r="D978" t="s">
-        <v>2861</v>
+        <v>2864</v>
       </c>
       <c r="E978" t="s">
         <v>16</v>
       </c>
       <c r="F978" t="s">
-        <v>2862</v>
+        <v>2865</v>
       </c>
       <c r="G978" t="s">
-        <v>2863</v>
+        <v>2866</v>
       </c>
       <c r="H978">
         <v>2</v>
       </c>
       <c r="I978" t="s">
-        <v>2852</v>
+        <v>2855</v>
       </c>
       <c r="J978" t="s">
         <v>2387</v>
@@ -49353,7 +49365,7 @@
         <v>21</v>
       </c>
       <c r="L978" t="s">
-        <v>116</v>
+        <v>2853</v>
       </c>
       <c r="M978" t="s">
         <v>23</v>
@@ -49367,25 +49379,25 @@
         <v>2840</v>
       </c>
       <c r="C979" t="s">
-        <v>2860</v>
+        <v>2863</v>
       </c>
       <c r="D979" t="s">
-        <v>2861</v>
+        <v>2864</v>
       </c>
       <c r="E979" t="s">
         <v>16</v>
       </c>
       <c r="F979" t="s">
-        <v>2864</v>
+        <v>2867</v>
       </c>
       <c r="G979" t="s">
-        <v>2865</v>
+        <v>2868</v>
       </c>
       <c r="H979">
         <v>2</v>
       </c>
       <c r="I979" t="s">
-        <v>2866</v>
+        <v>2869</v>
       </c>
       <c r="J979" t="s">
         <v>2218</v>
@@ -49394,7 +49406,7 @@
         <v>21</v>
       </c>
       <c r="L979" t="s">
-        <v>116</v>
+        <v>2549</v>
       </c>
       <c r="M979" t="s">
         <v>23</v>
@@ -49408,25 +49420,25 @@
         <v>2840</v>
       </c>
       <c r="C980" t="s">
-        <v>2860</v>
+        <v>2863</v>
       </c>
       <c r="D980" t="s">
-        <v>2861</v>
+        <v>2864</v>
       </c>
       <c r="E980" t="s">
         <v>16</v>
       </c>
       <c r="F980" t="s">
-        <v>2867</v>
+        <v>2870</v>
       </c>
       <c r="G980" t="s">
-        <v>2868</v>
+        <v>2871</v>
       </c>
       <c r="H980">
         <v>2</v>
       </c>
       <c r="I980" t="s">
-        <v>2869</v>
+        <v>2872</v>
       </c>
       <c r="J980" t="s">
         <v>2363</v>
@@ -49435,7 +49447,7 @@
         <v>21</v>
       </c>
       <c r="L980" t="s">
-        <v>116</v>
+        <v>2844</v>
       </c>
       <c r="M980" t="s">
         <v>23</v>
@@ -49449,25 +49461,25 @@
         <v>2840</v>
       </c>
       <c r="C981" t="s">
-        <v>2860</v>
+        <v>2863</v>
       </c>
       <c r="D981" t="s">
-        <v>2861</v>
+        <v>2864</v>
       </c>
       <c r="E981" t="s">
         <v>16</v>
       </c>
       <c r="F981" t="s">
-        <v>2870</v>
+        <v>2873</v>
       </c>
       <c r="G981" t="s">
-        <v>2871</v>
+        <v>2874</v>
       </c>
       <c r="H981">
         <v>2</v>
       </c>
       <c r="I981" t="s">
-        <v>2872</v>
+        <v>2875</v>
       </c>
       <c r="J981" t="s">
         <v>2387</v>
@@ -49476,7 +49488,7 @@
         <v>21</v>
       </c>
       <c r="L981" t="s">
-        <v>116</v>
+        <v>2549</v>
       </c>
       <c r="M981" t="s">
         <v>23</v>
@@ -49490,25 +49502,25 @@
         <v>2840</v>
       </c>
       <c r="C982" t="s">
-        <v>2860</v>
+        <v>2863</v>
       </c>
       <c r="D982" t="s">
-        <v>2861</v>
+        <v>2864</v>
       </c>
       <c r="E982" t="s">
         <v>16</v>
       </c>
       <c r="F982" t="s">
-        <v>2873</v>
+        <v>2876</v>
       </c>
       <c r="G982" t="s">
-        <v>2874</v>
+        <v>2877</v>
       </c>
       <c r="H982">
         <v>2</v>
       </c>
       <c r="I982" t="s">
-        <v>2875</v>
+        <v>2878</v>
       </c>
       <c r="J982" t="s">
         <v>2218</v>
@@ -49517,7 +49529,7 @@
         <v>21</v>
       </c>
       <c r="L982" t="s">
-        <v>116</v>
+        <v>2468</v>
       </c>
       <c r="M982" t="s">
         <v>23</v>
@@ -49531,25 +49543,25 @@
         <v>2840</v>
       </c>
       <c r="C983" t="s">
-        <v>2876</v>
+        <v>2879</v>
       </c>
       <c r="D983" t="s">
-        <v>2877</v>
+        <v>2880</v>
       </c>
       <c r="E983" t="s">
         <v>16</v>
       </c>
       <c r="F983" t="s">
-        <v>2878</v>
+        <v>2881</v>
       </c>
       <c r="G983" t="s">
-        <v>2879</v>
+        <v>2882</v>
       </c>
       <c r="H983">
         <v>2</v>
       </c>
       <c r="I983" t="s">
-        <v>2880</v>
+        <v>2883</v>
       </c>
       <c r="J983" t="s">
         <v>2387</v>
@@ -49558,7 +49570,7 @@
         <v>21</v>
       </c>
       <c r="L983" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="M983" t="s">
         <v>23</v>
@@ -49572,25 +49584,25 @@
         <v>2840</v>
       </c>
       <c r="C984" t="s">
-        <v>2876</v>
+        <v>2879</v>
       </c>
       <c r="D984" t="s">
-        <v>2877</v>
+        <v>2880</v>
       </c>
       <c r="E984" t="s">
         <v>16</v>
       </c>
       <c r="F984" t="s">
-        <v>2881</v>
+        <v>2884</v>
       </c>
       <c r="G984" t="s">
-        <v>2882</v>
+        <v>2885</v>
       </c>
       <c r="H984">
         <v>2</v>
       </c>
       <c r="I984" t="s">
-        <v>2846</v>
+        <v>2847</v>
       </c>
       <c r="J984" t="s">
         <v>2218</v>
@@ -49599,7 +49611,7 @@
         <v>21</v>
       </c>
       <c r="L984" t="s">
-        <v>116</v>
+        <v>2844</v>
       </c>
       <c r="M984" t="s">
         <v>23</v>
@@ -49613,25 +49625,25 @@
         <v>2840</v>
       </c>
       <c r="C985" t="s">
-        <v>2876</v>
+        <v>2879</v>
       </c>
       <c r="D985" t="s">
-        <v>2877</v>
+        <v>2880</v>
       </c>
       <c r="E985" t="s">
         <v>16</v>
       </c>
       <c r="F985" t="s">
-        <v>2883</v>
+        <v>2886</v>
       </c>
       <c r="G985" t="s">
-        <v>2884</v>
+        <v>2887</v>
       </c>
       <c r="H985">
         <v>2</v>
       </c>
       <c r="I985" t="s">
-        <v>2885</v>
+        <v>2888</v>
       </c>
       <c r="J985" t="s">
         <v>2387</v>
@@ -49640,7 +49652,7 @@
         <v>21</v>
       </c>
       <c r="L985" t="s">
-        <v>116</v>
+        <v>2468</v>
       </c>
       <c r="M985" t="s">
         <v>23</v>
@@ -49654,19 +49666,19 @@
         <v>2840</v>
       </c>
       <c r="C986" t="s">
-        <v>2876</v>
+        <v>2879</v>
       </c>
       <c r="D986" t="s">
-        <v>2877</v>
+        <v>2880</v>
       </c>
       <c r="E986" t="s">
         <v>16</v>
       </c>
       <c r="F986" t="s">
-        <v>2886</v>
+        <v>2889</v>
       </c>
       <c r="G986" t="s">
-        <v>2887</v>
+        <v>2890</v>
       </c>
       <c r="H986">
         <v>2</v>
@@ -49681,7 +49693,7 @@
         <v>21</v>
       </c>
       <c r="L986" t="s">
-        <v>116</v>
+        <v>2850</v>
       </c>
       <c r="M986" t="s">
         <v>23</v>
@@ -49695,16 +49707,16 @@
         <v>2840</v>
       </c>
       <c r="C987" t="s">
-        <v>2876</v>
+        <v>2879</v>
       </c>
       <c r="D987" t="s">
-        <v>2877</v>
+        <v>2880</v>
       </c>
       <c r="E987" t="s">
         <v>16</v>
       </c>
       <c r="F987" t="s">
-        <v>2888</v>
+        <v>2891</v>
       </c>
       <c r="G987" t="s">
         <v>452</v>
@@ -49713,7 +49725,7 @@
         <v>2</v>
       </c>
       <c r="I987" t="s">
-        <v>2889</v>
+        <v>2892</v>
       </c>
       <c r="J987" t="s">
         <v>2209</v>
@@ -49722,7 +49734,7 @@
         <v>21</v>
       </c>
       <c r="L987" t="s">
-        <v>116</v>
+        <v>2549</v>
       </c>
       <c r="M987" t="s">
         <v>23</v>
@@ -49736,25 +49748,25 @@
         <v>2840</v>
       </c>
       <c r="C988" t="s">
-        <v>2876</v>
+        <v>2879</v>
       </c>
       <c r="D988" t="s">
-        <v>2877</v>
+        <v>2880</v>
       </c>
       <c r="E988" t="s">
         <v>16</v>
       </c>
       <c r="F988" t="s">
-        <v>2890</v>
+        <v>2893</v>
       </c>
       <c r="G988" t="s">
-        <v>2891</v>
+        <v>2894</v>
       </c>
       <c r="H988">
         <v>2</v>
       </c>
       <c r="I988" t="s">
-        <v>2852</v>
+        <v>2855</v>
       </c>
       <c r="J988" t="s">
         <v>2218</v>
@@ -49763,7 +49775,7 @@
         <v>21</v>
       </c>
       <c r="L988" t="s">
-        <v>116</v>
+        <v>2853</v>
       </c>
       <c r="M988" t="s">
         <v>23</v>
@@ -49777,34 +49789,34 @@
         <v>2840</v>
       </c>
       <c r="C989" t="s">
-        <v>2892</v>
+        <v>2895</v>
       </c>
       <c r="D989" t="s">
-        <v>2893</v>
+        <v>2896</v>
       </c>
       <c r="E989" t="s">
         <v>16</v>
       </c>
       <c r="F989" t="s">
-        <v>2894</v>
+        <v>2897</v>
       </c>
       <c r="G989" t="s">
-        <v>2895</v>
+        <v>2898</v>
       </c>
       <c r="H989">
         <v>2</v>
       </c>
       <c r="I989" t="s">
-        <v>2885</v>
+        <v>2888</v>
       </c>
       <c r="J989" t="s">
-        <v>2896</v>
+        <v>2899</v>
       </c>
       <c r="K989" t="s">
         <v>21</v>
       </c>
       <c r="L989" t="s">
-        <v>116</v>
+        <v>2853</v>
       </c>
       <c r="M989" t="s">
         <v>23</v>
@@ -49818,34 +49830,34 @@
         <v>2840</v>
       </c>
       <c r="C990" t="s">
-        <v>2892</v>
+        <v>2895</v>
       </c>
       <c r="D990" t="s">
-        <v>2893</v>
+        <v>2896</v>
       </c>
       <c r="E990" t="s">
         <v>16</v>
       </c>
       <c r="F990" t="s">
-        <v>2897</v>
+        <v>2900</v>
       </c>
       <c r="G990" t="s">
-        <v>2898</v>
+        <v>2901</v>
       </c>
       <c r="H990">
         <v>2</v>
       </c>
       <c r="I990" t="s">
-        <v>2899</v>
+        <v>2902</v>
       </c>
       <c r="J990" t="s">
-        <v>2900</v>
+        <v>2903</v>
       </c>
       <c r="K990" t="s">
         <v>21</v>
       </c>
       <c r="L990" t="s">
-        <v>116</v>
+        <v>2853</v>
       </c>
       <c r="M990" t="s">
         <v>23</v>
@@ -49859,25 +49871,25 @@
         <v>2840</v>
       </c>
       <c r="C991" t="s">
-        <v>2892</v>
+        <v>2895</v>
       </c>
       <c r="D991" t="s">
-        <v>2893</v>
+        <v>2896</v>
       </c>
       <c r="E991" t="s">
         <v>16</v>
       </c>
       <c r="F991" t="s">
-        <v>2901</v>
+        <v>2904</v>
       </c>
       <c r="G991" t="s">
-        <v>2902</v>
+        <v>2905</v>
       </c>
       <c r="H991">
         <v>2</v>
       </c>
       <c r="I991" t="s">
-        <v>2880</v>
+        <v>2883</v>
       </c>
       <c r="J991" t="s">
         <v>2213</v>
@@ -49886,7 +49898,7 @@
         <v>21</v>
       </c>
       <c r="L991" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="M991" t="s">
         <v>23</v>
@@ -49900,25 +49912,25 @@
         <v>2840</v>
       </c>
       <c r="C992" t="s">
-        <v>2892</v>
+        <v>2895</v>
       </c>
       <c r="D992" t="s">
-        <v>2893</v>
+        <v>2896</v>
       </c>
       <c r="E992" t="s">
         <v>16</v>
       </c>
       <c r="F992" t="s">
-        <v>2903</v>
+        <v>2906</v>
       </c>
       <c r="G992" t="s">
-        <v>2904</v>
+        <v>2907</v>
       </c>
       <c r="H992">
         <v>2</v>
       </c>
       <c r="I992" t="s">
-        <v>2905</v>
+        <v>2908</v>
       </c>
       <c r="J992" t="s">
         <v>2363</v>
@@ -49927,7 +49939,7 @@
         <v>21</v>
       </c>
       <c r="L992" t="s">
-        <v>116</v>
+        <v>2909</v>
       </c>
       <c r="M992" t="s">
         <v>23</v>
@@ -49941,25 +49953,25 @@
         <v>2840</v>
       </c>
       <c r="C993" t="s">
-        <v>2892</v>
+        <v>2895</v>
       </c>
       <c r="D993" t="s">
-        <v>2893</v>
+        <v>2896</v>
       </c>
       <c r="E993" t="s">
         <v>16</v>
       </c>
       <c r="F993" t="s">
-        <v>2906</v>
+        <v>2910</v>
       </c>
       <c r="G993" t="s">
-        <v>2907</v>
+        <v>2911</v>
       </c>
       <c r="H993">
         <v>2</v>
       </c>
       <c r="I993" t="s">
-        <v>2899</v>
+        <v>2902</v>
       </c>
       <c r="J993" t="s">
         <v>2218</v>
@@ -49968,7 +49980,7 @@
         <v>21</v>
       </c>
       <c r="L993" t="s">
-        <v>116</v>
+        <v>2909</v>
       </c>
       <c r="M993" t="s">
         <v>23</v>
@@ -49982,25 +49994,25 @@
         <v>2840</v>
       </c>
       <c r="C994" t="s">
-        <v>2892</v>
+        <v>2895</v>
       </c>
       <c r="D994" t="s">
-        <v>2893</v>
+        <v>2896</v>
       </c>
       <c r="E994" t="s">
         <v>16</v>
       </c>
       <c r="F994" t="s">
-        <v>2908</v>
+        <v>2912</v>
       </c>
       <c r="G994" t="s">
-        <v>2909</v>
+        <v>2913</v>
       </c>
       <c r="H994">
         <v>2</v>
       </c>
       <c r="I994" t="s">
-        <v>2853</v>
+        <v>2856</v>
       </c>
       <c r="J994" t="s">
         <v>2363</v>
@@ -50009,7 +50021,7 @@
         <v>21</v>
       </c>
       <c r="L994" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="M994" t="s">
         <v>23</v>
@@ -50023,25 +50035,25 @@
         <v>2840</v>
       </c>
       <c r="C995" t="s">
-        <v>2892</v>
+        <v>2895</v>
       </c>
       <c r="D995" t="s">
-        <v>2893</v>
+        <v>2896</v>
       </c>
       <c r="E995" t="s">
         <v>16</v>
       </c>
       <c r="F995" t="s">
-        <v>2910</v>
+        <v>2914</v>
       </c>
       <c r="G995" t="s">
-        <v>2911</v>
+        <v>2915</v>
       </c>
       <c r="H995">
         <v>2</v>
       </c>
       <c r="I995" t="s">
-        <v>2912</v>
+        <v>2916</v>
       </c>
       <c r="J995" t="s">
         <v>2209</v>
@@ -50050,7 +50062,7 @@
         <v>21</v>
       </c>
       <c r="L995" t="s">
-        <v>116</v>
+        <v>2909</v>
       </c>
       <c r="M995" t="s">
         <v>23</v>
@@ -50064,25 +50076,25 @@
         <v>2840</v>
       </c>
       <c r="C996" t="s">
-        <v>2892</v>
+        <v>2895</v>
       </c>
       <c r="D996" t="s">
-        <v>2893</v>
+        <v>2896</v>
       </c>
       <c r="E996" t="s">
         <v>16</v>
       </c>
       <c r="F996" t="s">
-        <v>2913</v>
+        <v>2917</v>
       </c>
       <c r="G996" t="s">
-        <v>2914</v>
+        <v>2918</v>
       </c>
       <c r="H996">
         <v>2</v>
       </c>
       <c r="I996" t="s">
-        <v>2866</v>
+        <v>2869</v>
       </c>
       <c r="J996" t="s">
         <v>2209</v>
@@ -50091,7 +50103,7 @@
         <v>21</v>
       </c>
       <c r="L996" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="M996" t="s">
         <v>23</v>
@@ -50105,25 +50117,25 @@
         <v>2840</v>
       </c>
       <c r="C997" t="s">
-        <v>2892</v>
+        <v>2895</v>
       </c>
       <c r="D997" t="s">
-        <v>2893</v>
+        <v>2896</v>
       </c>
       <c r="E997" t="s">
         <v>16</v>
       </c>
       <c r="F997" t="s">
-        <v>2915</v>
+        <v>2919</v>
       </c>
       <c r="G997" t="s">
-        <v>2916</v>
+        <v>2920</v>
       </c>
       <c r="H997">
         <v>2</v>
       </c>
       <c r="I997" t="s">
-        <v>2853</v>
+        <v>2856</v>
       </c>
       <c r="J997" t="s">
         <v>2387</v>
@@ -50132,7 +50144,7 @@
         <v>21</v>
       </c>
       <c r="L997" t="s">
-        <v>116</v>
+        <v>2909</v>
       </c>
       <c r="M997" t="s">
         <v>23</v>
@@ -50140,13 +50152,13 @@
     </row>
     <row r="998" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
-        <v>2917</v>
+        <v>2921</v>
       </c>
       <c r="B998" t="s">
-        <v>2918</v>
+        <v>2922</v>
       </c>
       <c r="C998" t="s">
-        <v>2917</v>
+        <v>2921</v>
       </c>
       <c r="D998" t="s">
         <v>15</v>
@@ -50155,16 +50167,16 @@
         <v>1583</v>
       </c>
       <c r="F998" t="s">
-        <v>2919</v>
+        <v>2923</v>
       </c>
       <c r="G998" t="s">
-        <v>2920</v>
+        <v>2924</v>
       </c>
       <c r="H998">
         <v>2</v>
       </c>
       <c r="I998" t="s">
-        <v>2921</v>
+        <v>2925</v>
       </c>
       <c r="J998" t="s">
         <v>2218</v>
@@ -50181,34 +50193,34 @@
     </row>
     <row r="999" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
-        <v>2917</v>
+        <v>2921</v>
       </c>
       <c r="B999" t="s">
-        <v>2918</v>
+        <v>2922</v>
       </c>
       <c r="C999" t="s">
-        <v>2922</v>
+        <v>2926</v>
       </c>
       <c r="D999" t="s">
-        <v>2923</v>
+        <v>2927</v>
       </c>
       <c r="E999" t="s">
         <v>16</v>
       </c>
       <c r="F999" t="s">
-        <v>2924</v>
+        <v>2928</v>
       </c>
       <c r="G999" t="s">
-        <v>2925</v>
+        <v>2929</v>
       </c>
       <c r="H999">
         <v>2</v>
       </c>
       <c r="I999" t="s">
-        <v>2926</v>
+        <v>2930</v>
       </c>
       <c r="J999" t="s">
-        <v>2927</v>
+        <v>2931</v>
       </c>
       <c r="K999" t="s">
         <v>21</v>
@@ -50222,25 +50234,25 @@
     </row>
     <row r="1000" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
-        <v>2917</v>
+        <v>2921</v>
       </c>
       <c r="B1000" t="s">
-        <v>2918</v>
+        <v>2922</v>
       </c>
       <c r="C1000" t="s">
-        <v>2928</v>
+        <v>2932</v>
       </c>
       <c r="D1000" t="s">
-        <v>2929</v>
+        <v>2933</v>
       </c>
       <c r="E1000" t="s">
         <v>16</v>
       </c>
       <c r="F1000" t="s">
-        <v>2930</v>
+        <v>2934</v>
       </c>
       <c r="G1000" t="s">
-        <v>2931</v>
+        <v>2935</v>
       </c>
       <c r="H1000">
         <v>2</v>
@@ -50255,7 +50267,7 @@
         <v>21</v>
       </c>
       <c r="L1000" t="s">
-        <v>2932</v>
+        <v>2936</v>
       </c>
       <c r="M1000" t="s">
         <v>23</v>
@@ -50263,31 +50275,31 @@
     </row>
     <row r="1001" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
-        <v>2917</v>
+        <v>2921</v>
       </c>
       <c r="B1001" t="s">
-        <v>2918</v>
+        <v>2922</v>
       </c>
       <c r="C1001" t="s">
-        <v>2928</v>
+        <v>2932</v>
       </c>
       <c r="D1001" t="s">
-        <v>2929</v>
+        <v>2933</v>
       </c>
       <c r="E1001" t="s">
         <v>16</v>
       </c>
       <c r="F1001" t="s">
-        <v>2933</v>
+        <v>2937</v>
       </c>
       <c r="G1001" t="s">
-        <v>2934</v>
+        <v>2938</v>
       </c>
       <c r="H1001">
         <v>2</v>
       </c>
       <c r="I1001" t="s">
-        <v>2935</v>
+        <v>2939</v>
       </c>
       <c r="J1001" t="s">
         <v>2209</v>
@@ -50304,34 +50316,34 @@
     </row>
     <row r="1002" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
-        <v>2917</v>
+        <v>2921</v>
       </c>
       <c r="B1002" t="s">
-        <v>2918</v>
+        <v>2922</v>
       </c>
       <c r="C1002" t="s">
-        <v>2928</v>
+        <v>2932</v>
       </c>
       <c r="D1002" t="s">
-        <v>2929</v>
+        <v>2933</v>
       </c>
       <c r="E1002" t="s">
         <v>16</v>
       </c>
       <c r="F1002" t="s">
-        <v>2936</v>
+        <v>2940</v>
       </c>
       <c r="G1002" t="s">
-        <v>2937</v>
+        <v>2941</v>
       </c>
       <c r="H1002">
         <v>2</v>
       </c>
       <c r="I1002" t="s">
-        <v>2938</v>
+        <v>2942</v>
       </c>
       <c r="J1002" t="s">
-        <v>2927</v>
+        <v>2931</v>
       </c>
       <c r="K1002" t="s">
         <v>21</v>
@@ -50345,31 +50357,31 @@
     </row>
     <row r="1003" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
-        <v>2917</v>
+        <v>2921</v>
       </c>
       <c r="B1003" t="s">
-        <v>2918</v>
+        <v>2922</v>
       </c>
       <c r="C1003" t="s">
-        <v>2928</v>
+        <v>2932</v>
       </c>
       <c r="D1003" t="s">
-        <v>2929</v>
+        <v>2933</v>
       </c>
       <c r="E1003" t="s">
         <v>16</v>
       </c>
       <c r="F1003" t="s">
-        <v>2939</v>
+        <v>2943</v>
       </c>
       <c r="G1003" t="s">
-        <v>2940</v>
+        <v>2944</v>
       </c>
       <c r="H1003">
         <v>2</v>
       </c>
       <c r="I1003" t="s">
-        <v>2941</v>
+        <v>2945</v>
       </c>
       <c r="J1003" t="s">
         <v>1779</v>
@@ -50378,7 +50390,7 @@
         <v>21</v>
       </c>
       <c r="L1003" t="s">
-        <v>2942</v>
+        <v>2946</v>
       </c>
       <c r="M1003" t="s">
         <v>23</v>
@@ -50386,34 +50398,34 @@
     </row>
     <row r="1004" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
-        <v>2917</v>
+        <v>2921</v>
       </c>
       <c r="B1004" t="s">
-        <v>2918</v>
+        <v>2922</v>
       </c>
       <c r="C1004" t="s">
-        <v>2943</v>
+        <v>2947</v>
       </c>
       <c r="D1004" t="s">
-        <v>2944</v>
+        <v>2948</v>
       </c>
       <c r="E1004" t="s">
         <v>16</v>
       </c>
       <c r="F1004" t="s">
-        <v>2945</v>
+        <v>2949</v>
       </c>
       <c r="G1004" t="s">
-        <v>2946</v>
+        <v>2950</v>
       </c>
       <c r="H1004">
         <v>2</v>
       </c>
       <c r="I1004" t="s">
-        <v>2947</v>
+        <v>2951</v>
       </c>
       <c r="J1004" t="s">
-        <v>2948</v>
+        <v>2952</v>
       </c>
       <c r="K1004" t="s">
         <v>21</v>
@@ -50427,31 +50439,31 @@
     </row>
     <row r="1005" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
-        <v>2917</v>
+        <v>2921</v>
       </c>
       <c r="B1005" t="s">
-        <v>2918</v>
+        <v>2922</v>
       </c>
       <c r="C1005" t="s">
-        <v>2943</v>
+        <v>2947</v>
       </c>
       <c r="D1005" t="s">
-        <v>2944</v>
+        <v>2948</v>
       </c>
       <c r="E1005" t="s">
         <v>16</v>
       </c>
       <c r="F1005" t="s">
-        <v>2949</v>
+        <v>2953</v>
       </c>
       <c r="G1005" t="s">
-        <v>2950</v>
+        <v>2954</v>
       </c>
       <c r="H1005">
         <v>2</v>
       </c>
       <c r="I1005" t="s">
-        <v>2947</v>
+        <v>2951</v>
       </c>
       <c r="J1005" t="s">
         <v>1721</v>
@@ -50460,7 +50472,7 @@
         <v>21</v>
       </c>
       <c r="L1005" t="s">
-        <v>2942</v>
+        <v>2946</v>
       </c>
       <c r="M1005" t="s">
         <v>23</v>
@@ -50468,34 +50480,34 @@
     </row>
     <row r="1006" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
-        <v>2917</v>
+        <v>2921</v>
       </c>
       <c r="B1006" t="s">
-        <v>2918</v>
+        <v>2922</v>
       </c>
       <c r="C1006" t="s">
-        <v>2943</v>
+        <v>2947</v>
       </c>
       <c r="D1006" t="s">
-        <v>2944</v>
+        <v>2948</v>
       </c>
       <c r="E1006" t="s">
         <v>16</v>
       </c>
       <c r="F1006" t="s">
-        <v>2951</v>
+        <v>2955</v>
       </c>
       <c r="G1006" t="s">
-        <v>2952</v>
+        <v>2956</v>
       </c>
       <c r="H1006">
         <v>2</v>
       </c>
       <c r="I1006" t="s">
-        <v>2921</v>
+        <v>2925</v>
       </c>
       <c r="J1006" t="s">
-        <v>2953</v>
+        <v>2957</v>
       </c>
       <c r="K1006" t="s">
         <v>21</v>
@@ -50509,31 +50521,31 @@
     </row>
     <row r="1007" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
-        <v>2917</v>
+        <v>2921</v>
       </c>
       <c r="B1007" t="s">
-        <v>2918</v>
+        <v>2922</v>
       </c>
       <c r="C1007" t="s">
-        <v>2943</v>
+        <v>2947</v>
       </c>
       <c r="D1007" t="s">
-        <v>2944</v>
+        <v>2948</v>
       </c>
       <c r="E1007" t="s">
         <v>16</v>
       </c>
       <c r="F1007" t="s">
-        <v>2954</v>
+        <v>2958</v>
       </c>
       <c r="G1007" t="s">
-        <v>2955</v>
+        <v>2959</v>
       </c>
       <c r="H1007">
         <v>2</v>
       </c>
       <c r="I1007" t="s">
-        <v>2956</v>
+        <v>2960</v>
       </c>
       <c r="J1007" t="s">
         <v>2209</v>

--- a/actions_fetch/out/kookmin(2026-2).xlsx
+++ b/actions_fetch/out/kookmin(2026-2).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12229" uniqueCount="3006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12241" uniqueCount="3004">
   <si>
     <t>campusCode</t>
   </si>
@@ -8134,6 +8134,9 @@
     <t>전공실기1</t>
   </si>
   <si>
+    <t>목 09:00-11:00</t>
+  </si>
+  <si>
     <t>예술관1층3호실</t>
   </si>
   <si>
@@ -8143,30 +8146,24 @@
     <t>전공실기2</t>
   </si>
   <si>
+    <t>목 11:00-13:00</t>
+  </si>
+  <si>
     <t>이유선</t>
   </si>
   <si>
+    <t>예술관1층6호실</t>
+  </si>
+  <si>
     <t>695920a</t>
   </si>
   <si>
     <t>전공실기3</t>
   </si>
   <si>
-    <t>김진석</t>
-  </si>
-  <si>
-    <t>목 09:00-11:00</t>
-  </si>
-  <si>
-    <t>예술관1층6호실</t>
-  </si>
-  <si>
     <t>이옥재</t>
   </si>
   <si>
-    <t>목 11:00-13:00</t>
-  </si>
-  <si>
     <t>695930a</t>
   </si>
   <si>
@@ -8972,9 +8969,6 @@
   </si>
   <si>
     <t>스포츠문화 세미나</t>
-  </si>
-  <si>
-    <t>임상아</t>
   </si>
   <si>
     <t>7298401</t>
@@ -9405,7 +9399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M1019"/>
+  <dimension ref="A1:M1020"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -12058,16 +12052,16 @@
         <v>3</v>
       </c>
       <c r="I65" t="s">
-        <v>116</v>
+        <v>277</v>
       </c>
       <c r="J65" t="s">
-        <v>116</v>
+        <v>278</v>
       </c>
       <c r="K65" t="s">
         <v>21</v>
       </c>
       <c r="L65" t="s">
-        <v>116</v>
+        <v>279</v>
       </c>
       <c r="M65" t="s">
         <v>23</v>
@@ -46993,13 +46987,13 @@
         <v>2693</v>
       </c>
       <c r="J917" t="s">
-        <v>2665</v>
+        <v>2707</v>
       </c>
       <c r="K917" t="s">
         <v>21</v>
       </c>
       <c r="L917" t="s">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="M917" t="s">
         <v>23</v>
@@ -47022,10 +47016,10 @@
         <v>16</v>
       </c>
       <c r="F918" t="s">
-        <v>2708</v>
+        <v>2709</v>
       </c>
       <c r="G918" t="s">
-        <v>2709</v>
+        <v>2710</v>
       </c>
       <c r="H918">
         <v>2</v>
@@ -47034,13 +47028,13 @@
         <v>2693</v>
       </c>
       <c r="J918" t="s">
-        <v>2658</v>
+        <v>2711</v>
       </c>
       <c r="K918" t="s">
         <v>21</v>
       </c>
       <c r="L918" t="s">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="M918" t="s">
         <v>23</v>
@@ -47063,25 +47057,25 @@
         <v>16</v>
       </c>
       <c r="F919" t="s">
-        <v>2708</v>
+        <v>2709</v>
       </c>
       <c r="G919" t="s">
-        <v>2709</v>
+        <v>2710</v>
       </c>
       <c r="H919">
         <v>2</v>
       </c>
       <c r="I919" t="s">
-        <v>2710</v>
+        <v>2712</v>
       </c>
       <c r="J919" t="s">
-        <v>2653</v>
+        <v>2544</v>
       </c>
       <c r="K919" t="s">
         <v>21</v>
       </c>
       <c r="L919" t="s">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="M919" t="s">
         <v>630</v>
@@ -47104,28 +47098,28 @@
         <v>16</v>
       </c>
       <c r="F920" t="s">
-        <v>2711</v>
+        <v>2709</v>
       </c>
       <c r="G920" t="s">
-        <v>2712</v>
+        <v>2710</v>
       </c>
       <c r="H920">
         <v>2</v>
       </c>
       <c r="I920" t="s">
+        <v>2696</v>
+      </c>
+      <c r="J920" t="s">
+        <v>2547</v>
+      </c>
+      <c r="K920" t="s">
+        <v>21</v>
+      </c>
+      <c r="L920" t="s">
         <v>2713</v>
       </c>
-      <c r="J920" t="s">
-        <v>2714</v>
-      </c>
-      <c r="K920" t="s">
-        <v>21</v>
-      </c>
-      <c r="L920" t="s">
-        <v>2715</v>
-      </c>
       <c r="M920" t="s">
-        <v>23</v>
+        <v>631</v>
       </c>
     </row>
     <row r="921" spans="1:13" x14ac:dyDescent="0.25">
@@ -47145,28 +47139,28 @@
         <v>16</v>
       </c>
       <c r="F921" t="s">
-        <v>2711</v>
+        <v>2714</v>
       </c>
       <c r="G921" t="s">
-        <v>2712</v>
+        <v>2715</v>
       </c>
       <c r="H921">
         <v>2</v>
       </c>
       <c r="I921" t="s">
-        <v>2716</v>
+        <v>2704</v>
       </c>
       <c r="J921" t="s">
-        <v>2714</v>
+        <v>2707</v>
       </c>
       <c r="K921" t="s">
         <v>21</v>
       </c>
       <c r="L921" t="s">
-        <v>2707</v>
+        <v>2713</v>
       </c>
       <c r="M921" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
     </row>
     <row r="922" spans="1:13" x14ac:dyDescent="0.25">
@@ -47186,28 +47180,28 @@
         <v>16</v>
       </c>
       <c r="F922" t="s">
-        <v>2711</v>
+        <v>2714</v>
       </c>
       <c r="G922" t="s">
-        <v>2712</v>
+        <v>2715</v>
       </c>
       <c r="H922">
         <v>2</v>
       </c>
       <c r="I922" t="s">
-        <v>2701</v>
+        <v>2716</v>
       </c>
       <c r="J922" t="s">
-        <v>2717</v>
+        <v>2707</v>
       </c>
       <c r="K922" t="s">
         <v>21</v>
       </c>
       <c r="L922" t="s">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="M922" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="923" spans="1:13" x14ac:dyDescent="0.25">
@@ -47227,28 +47221,28 @@
         <v>16</v>
       </c>
       <c r="F923" t="s">
-        <v>2711</v>
+        <v>2714</v>
       </c>
       <c r="G923" t="s">
-        <v>2712</v>
+        <v>2715</v>
       </c>
       <c r="H923">
         <v>2</v>
       </c>
       <c r="I923" t="s">
-        <v>2693</v>
+        <v>2701</v>
       </c>
       <c r="J923" t="s">
-        <v>2544</v>
+        <v>2658</v>
       </c>
       <c r="K923" t="s">
         <v>21</v>
       </c>
       <c r="L923" t="s">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="M923" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="924" spans="1:13" x14ac:dyDescent="0.25">
@@ -47268,28 +47262,28 @@
         <v>16</v>
       </c>
       <c r="F924" t="s">
-        <v>2718</v>
+        <v>2714</v>
       </c>
       <c r="G924" t="s">
-        <v>2719</v>
+        <v>2715</v>
       </c>
       <c r="H924">
         <v>2</v>
       </c>
       <c r="I924" t="s">
-        <v>2720</v>
+        <v>2693</v>
       </c>
       <c r="J924" t="s">
-        <v>2460</v>
+        <v>2653</v>
       </c>
       <c r="K924" t="s">
         <v>21</v>
       </c>
       <c r="L924" t="s">
-        <v>763</v>
+        <v>2708</v>
       </c>
       <c r="M924" t="s">
-        <v>23</v>
+        <v>632</v>
       </c>
     </row>
     <row r="925" spans="1:13" x14ac:dyDescent="0.25">
@@ -47309,25 +47303,25 @@
         <v>16</v>
       </c>
       <c r="F925" t="s">
-        <v>2721</v>
+        <v>2717</v>
       </c>
       <c r="G925" t="s">
-        <v>2722</v>
+        <v>2718</v>
       </c>
       <c r="H925">
         <v>2</v>
       </c>
       <c r="I925" t="s">
-        <v>2693</v>
+        <v>2719</v>
       </c>
       <c r="J925" t="s">
-        <v>2468</v>
+        <v>2460</v>
       </c>
       <c r="K925" t="s">
         <v>21</v>
       </c>
       <c r="L925" t="s">
-        <v>721</v>
+        <v>763</v>
       </c>
       <c r="M925" t="s">
         <v>23</v>
@@ -47341,34 +47335,34 @@
         <v>2645</v>
       </c>
       <c r="C926" t="s">
-        <v>2723</v>
+        <v>2689</v>
       </c>
       <c r="D926" t="s">
-        <v>2724</v>
+        <v>2690</v>
       </c>
       <c r="E926" t="s">
         <v>16</v>
       </c>
       <c r="F926" t="s">
-        <v>2725</v>
+        <v>2720</v>
       </c>
       <c r="G926" t="s">
-        <v>2726</v>
+        <v>2721</v>
       </c>
       <c r="H926">
         <v>2</v>
       </c>
       <c r="I926" t="s">
-        <v>2727</v>
+        <v>2693</v>
       </c>
       <c r="J926" t="s">
-        <v>2151</v>
+        <v>2468</v>
       </c>
       <c r="K926" t="s">
         <v>21</v>
       </c>
       <c r="L926" t="s">
-        <v>2728</v>
+        <v>721</v>
       </c>
       <c r="M926" t="s">
         <v>23</v>
@@ -47382,34 +47376,34 @@
         <v>2645</v>
       </c>
       <c r="C927" t="s">
+        <v>2722</v>
+      </c>
+      <c r="D927" t="s">
         <v>2723</v>
-      </c>
-      <c r="D927" t="s">
-        <v>2724</v>
       </c>
       <c r="E927" t="s">
         <v>16</v>
       </c>
       <c r="F927" t="s">
-        <v>2729</v>
+        <v>2724</v>
       </c>
       <c r="G927" t="s">
-        <v>2730</v>
+        <v>2725</v>
       </c>
       <c r="H927">
         <v>2</v>
       </c>
       <c r="I927" t="s">
+        <v>2726</v>
+      </c>
+      <c r="J927" t="s">
+        <v>2151</v>
+      </c>
+      <c r="K927" t="s">
+        <v>21</v>
+      </c>
+      <c r="L927" t="s">
         <v>2727</v>
-      </c>
-      <c r="J927" t="s">
-        <v>2731</v>
-      </c>
-      <c r="K927" t="s">
-        <v>21</v>
-      </c>
-      <c r="L927" t="s">
-        <v>2728</v>
       </c>
       <c r="M927" t="s">
         <v>23</v>
@@ -47423,34 +47417,34 @@
         <v>2645</v>
       </c>
       <c r="C928" t="s">
+        <v>2722</v>
+      </c>
+      <c r="D928" t="s">
         <v>2723</v>
-      </c>
-      <c r="D928" t="s">
-        <v>2724</v>
       </c>
       <c r="E928" t="s">
         <v>16</v>
       </c>
       <c r="F928" t="s">
-        <v>2732</v>
+        <v>2728</v>
       </c>
       <c r="G928" t="s">
-        <v>2733</v>
+        <v>2729</v>
       </c>
       <c r="H928">
         <v>2</v>
       </c>
       <c r="I928" t="s">
+        <v>2726</v>
+      </c>
+      <c r="J928" t="s">
+        <v>2730</v>
+      </c>
+      <c r="K928" t="s">
+        <v>21</v>
+      </c>
+      <c r="L928" t="s">
         <v>2727</v>
-      </c>
-      <c r="J928" t="s">
-        <v>2734</v>
-      </c>
-      <c r="K928" t="s">
-        <v>21</v>
-      </c>
-      <c r="L928" t="s">
-        <v>2654</v>
       </c>
       <c r="M928" t="s">
         <v>23</v>
@@ -47464,28 +47458,28 @@
         <v>2645</v>
       </c>
       <c r="C929" t="s">
+        <v>2722</v>
+      </c>
+      <c r="D929" t="s">
         <v>2723</v>
-      </c>
-      <c r="D929" t="s">
-        <v>2724</v>
       </c>
       <c r="E929" t="s">
         <v>16</v>
       </c>
       <c r="F929" t="s">
-        <v>2735</v>
+        <v>2731</v>
       </c>
       <c r="G929" t="s">
-        <v>2736</v>
+        <v>2732</v>
       </c>
       <c r="H929">
         <v>2</v>
       </c>
       <c r="I929" t="s">
-        <v>2727</v>
+        <v>2726</v>
       </c>
       <c r="J929" t="s">
-        <v>2737</v>
+        <v>2733</v>
       </c>
       <c r="K929" t="s">
         <v>21</v>
@@ -47505,34 +47499,34 @@
         <v>2645</v>
       </c>
       <c r="C930" t="s">
+        <v>2722</v>
+      </c>
+      <c r="D930" t="s">
         <v>2723</v>
-      </c>
-      <c r="D930" t="s">
-        <v>2724</v>
       </c>
       <c r="E930" t="s">
         <v>16</v>
       </c>
       <c r="F930" t="s">
-        <v>2738</v>
+        <v>2734</v>
       </c>
       <c r="G930" t="s">
-        <v>2739</v>
+        <v>2735</v>
       </c>
       <c r="H930">
         <v>2</v>
       </c>
       <c r="I930" t="s">
-        <v>2740</v>
+        <v>2726</v>
       </c>
       <c r="J930" t="s">
-        <v>2741</v>
+        <v>2736</v>
       </c>
       <c r="K930" t="s">
         <v>21</v>
       </c>
       <c r="L930" t="s">
-        <v>2742</v>
+        <v>2654</v>
       </c>
       <c r="M930" t="s">
         <v>23</v>
@@ -47546,34 +47540,34 @@
         <v>2645</v>
       </c>
       <c r="C931" t="s">
-        <v>2743</v>
+        <v>2722</v>
       </c>
       <c r="D931" t="s">
-        <v>2744</v>
+        <v>2723</v>
       </c>
       <c r="E931" t="s">
         <v>16</v>
       </c>
       <c r="F931" t="s">
-        <v>2745</v>
+        <v>2737</v>
       </c>
       <c r="G931" t="s">
-        <v>2706</v>
+        <v>2738</v>
       </c>
       <c r="H931">
         <v>2</v>
       </c>
       <c r="I931" t="s">
-        <v>2746</v>
+        <v>2739</v>
       </c>
       <c r="J931" t="s">
-        <v>2747</v>
+        <v>2740</v>
       </c>
       <c r="K931" t="s">
         <v>21</v>
       </c>
       <c r="L931" t="s">
-        <v>2728</v>
+        <v>2741</v>
       </c>
       <c r="M931" t="s">
         <v>23</v>
@@ -47587,34 +47581,34 @@
         <v>2645</v>
       </c>
       <c r="C932" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D932" t="s">
         <v>2743</v>
-      </c>
-      <c r="D932" t="s">
-        <v>2744</v>
       </c>
       <c r="E932" t="s">
         <v>16</v>
       </c>
       <c r="F932" t="s">
-        <v>2748</v>
+        <v>2744</v>
       </c>
       <c r="G932" t="s">
-        <v>2749</v>
+        <v>2706</v>
       </c>
       <c r="H932">
         <v>2</v>
       </c>
       <c r="I932" t="s">
-        <v>2750</v>
+        <v>2745</v>
       </c>
       <c r="J932" t="s">
-        <v>2751</v>
+        <v>2746</v>
       </c>
       <c r="K932" t="s">
         <v>21</v>
       </c>
       <c r="L932" t="s">
-        <v>721</v>
+        <v>2727</v>
       </c>
       <c r="M932" t="s">
         <v>23</v>
@@ -47628,34 +47622,34 @@
         <v>2645</v>
       </c>
       <c r="C933" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D933" t="s">
         <v>2743</v>
-      </c>
-      <c r="D933" t="s">
-        <v>2744</v>
       </c>
       <c r="E933" t="s">
         <v>16</v>
       </c>
       <c r="F933" t="s">
-        <v>2752</v>
+        <v>2747</v>
       </c>
       <c r="G933" t="s">
-        <v>2709</v>
+        <v>2748</v>
       </c>
       <c r="H933">
         <v>2</v>
       </c>
       <c r="I933" t="s">
-        <v>2746</v>
+        <v>2749</v>
       </c>
       <c r="J933" t="s">
-        <v>2753</v>
+        <v>2750</v>
       </c>
       <c r="K933" t="s">
         <v>21</v>
       </c>
       <c r="L933" t="s">
-        <v>2728</v>
+        <v>721</v>
       </c>
       <c r="M933" t="s">
         <v>23</v>
@@ -47669,34 +47663,34 @@
         <v>2645</v>
       </c>
       <c r="C934" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D934" t="s">
         <v>2743</v>
-      </c>
-      <c r="D934" t="s">
-        <v>2744</v>
       </c>
       <c r="E934" t="s">
         <v>16</v>
       </c>
       <c r="F934" t="s">
-        <v>2754</v>
+        <v>2751</v>
       </c>
       <c r="G934" t="s">
-        <v>2712</v>
+        <v>2710</v>
       </c>
       <c r="H934">
         <v>2</v>
       </c>
       <c r="I934" t="s">
-        <v>2755</v>
+        <v>2745</v>
       </c>
       <c r="J934" t="s">
-        <v>2756</v>
+        <v>2752</v>
       </c>
       <c r="K934" t="s">
         <v>21</v>
       </c>
       <c r="L934" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="M934" t="s">
         <v>23</v>
@@ -47710,34 +47704,34 @@
         <v>2645</v>
       </c>
       <c r="C935" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D935" t="s">
         <v>2743</v>
-      </c>
-      <c r="D935" t="s">
-        <v>2744</v>
       </c>
       <c r="E935" t="s">
         <v>16</v>
       </c>
       <c r="F935" t="s">
-        <v>2757</v>
+        <v>2753</v>
       </c>
       <c r="G935" t="s">
-        <v>2758</v>
+        <v>2715</v>
       </c>
       <c r="H935">
         <v>2</v>
       </c>
       <c r="I935" t="s">
-        <v>2750</v>
+        <v>2754</v>
       </c>
       <c r="J935" t="s">
-        <v>2759</v>
+        <v>2755</v>
       </c>
       <c r="K935" t="s">
         <v>21</v>
       </c>
       <c r="L935" t="s">
-        <v>763</v>
+        <v>2727</v>
       </c>
       <c r="M935" t="s">
         <v>23</v>
@@ -47751,34 +47745,34 @@
         <v>2645</v>
       </c>
       <c r="C936" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D936" t="s">
         <v>2743</v>
-      </c>
-      <c r="D936" t="s">
-        <v>2744</v>
       </c>
       <c r="E936" t="s">
         <v>16</v>
       </c>
       <c r="F936" t="s">
-        <v>2760</v>
+        <v>2756</v>
       </c>
       <c r="G936" t="s">
-        <v>2761</v>
+        <v>2757</v>
       </c>
       <c r="H936">
         <v>2</v>
       </c>
       <c r="I936" t="s">
-        <v>2746</v>
+        <v>2749</v>
       </c>
       <c r="J936" t="s">
-        <v>2762</v>
+        <v>2758</v>
       </c>
       <c r="K936" t="s">
         <v>21</v>
       </c>
       <c r="L936" t="s">
-        <v>737</v>
+        <v>763</v>
       </c>
       <c r="M936" t="s">
         <v>23</v>
@@ -47792,34 +47786,34 @@
         <v>2645</v>
       </c>
       <c r="C937" t="s">
-        <v>2763</v>
+        <v>2742</v>
       </c>
       <c r="D937" t="s">
-        <v>2764</v>
+        <v>2743</v>
       </c>
       <c r="E937" t="s">
         <v>16</v>
       </c>
       <c r="F937" t="s">
-        <v>2765</v>
+        <v>2759</v>
       </c>
       <c r="G937" t="s">
-        <v>2766</v>
+        <v>2760</v>
       </c>
       <c r="H937">
         <v>2</v>
       </c>
       <c r="I937" t="s">
-        <v>2767</v>
+        <v>2745</v>
       </c>
       <c r="J937" t="s">
-        <v>2400</v>
+        <v>2761</v>
       </c>
       <c r="K937" t="s">
         <v>21</v>
       </c>
       <c r="L937" t="s">
-        <v>759</v>
+        <v>737</v>
       </c>
       <c r="M937" t="s">
         <v>23</v>
@@ -47833,25 +47827,25 @@
         <v>2645</v>
       </c>
       <c r="C938" t="s">
+        <v>2762</v>
+      </c>
+      <c r="D938" t="s">
         <v>2763</v>
-      </c>
-      <c r="D938" t="s">
-        <v>2764</v>
       </c>
       <c r="E938" t="s">
         <v>16</v>
       </c>
       <c r="F938" t="s">
+        <v>2764</v>
+      </c>
+      <c r="G938" t="s">
         <v>2765</v>
-      </c>
-      <c r="G938" t="s">
-        <v>2766</v>
       </c>
       <c r="H938">
         <v>2</v>
       </c>
       <c r="I938" t="s">
-        <v>2768</v>
+        <v>2766</v>
       </c>
       <c r="J938" t="s">
         <v>2400</v>
@@ -47860,10 +47854,10 @@
         <v>21</v>
       </c>
       <c r="L938" t="s">
-        <v>721</v>
+        <v>759</v>
       </c>
       <c r="M938" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
     </row>
     <row r="939" spans="1:13" x14ac:dyDescent="0.25">
@@ -47874,19 +47868,19 @@
         <v>2645</v>
       </c>
       <c r="C939" t="s">
+        <v>2762</v>
+      </c>
+      <c r="D939" t="s">
         <v>2763</v>
-      </c>
-      <c r="D939" t="s">
-        <v>2764</v>
       </c>
       <c r="E939" t="s">
         <v>16</v>
       </c>
       <c r="F939" t="s">
-        <v>2769</v>
+        <v>2764</v>
       </c>
       <c r="G939" t="s">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="H939">
         <v>2</v>
@@ -47895,16 +47889,16 @@
         <v>2767</v>
       </c>
       <c r="J939" t="s">
-        <v>2771</v>
+        <v>2400</v>
       </c>
       <c r="K939" t="s">
         <v>21</v>
       </c>
       <c r="L939" t="s">
-        <v>2772</v>
+        <v>721</v>
       </c>
       <c r="M939" t="s">
-        <v>23</v>
+        <v>630</v>
       </c>
     </row>
     <row r="940" spans="1:13" x14ac:dyDescent="0.25">
@@ -47915,37 +47909,37 @@
         <v>2645</v>
       </c>
       <c r="C940" t="s">
+        <v>2762</v>
+      </c>
+      <c r="D940" t="s">
         <v>2763</v>
-      </c>
-      <c r="D940" t="s">
-        <v>2764</v>
       </c>
       <c r="E940" t="s">
         <v>16</v>
       </c>
       <c r="F940" t="s">
+        <v>2768</v>
+      </c>
+      <c r="G940" t="s">
         <v>2769</v>
-      </c>
-      <c r="G940" t="s">
-        <v>2770</v>
       </c>
       <c r="H940">
         <v>2</v>
       </c>
       <c r="I940" t="s">
-        <v>2773</v>
+        <v>2766</v>
       </c>
       <c r="J940" t="s">
-        <v>2774</v>
+        <v>2770</v>
       </c>
       <c r="K940" t="s">
         <v>21</v>
       </c>
       <c r="L940" t="s">
-        <v>721</v>
+        <v>2771</v>
       </c>
       <c r="M940" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
     </row>
     <row r="941" spans="1:13" x14ac:dyDescent="0.25">
@@ -47956,28 +47950,28 @@
         <v>2645</v>
       </c>
       <c r="C941" t="s">
+        <v>2762</v>
+      </c>
+      <c r="D941" t="s">
         <v>2763</v>
-      </c>
-      <c r="D941" t="s">
-        <v>2764</v>
       </c>
       <c r="E941" t="s">
         <v>16</v>
       </c>
       <c r="F941" t="s">
+        <v>2768</v>
+      </c>
+      <c r="G941" t="s">
         <v>2769</v>
-      </c>
-      <c r="G941" t="s">
-        <v>2770</v>
       </c>
       <c r="H941">
         <v>2</v>
       </c>
       <c r="I941" t="s">
+        <v>2772</v>
+      </c>
+      <c r="J941" t="s">
         <v>2773</v>
-      </c>
-      <c r="J941" t="s">
-        <v>2775</v>
       </c>
       <c r="K941" t="s">
         <v>21</v>
@@ -47986,7 +47980,7 @@
         <v>721</v>
       </c>
       <c r="M941" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="942" spans="1:13" x14ac:dyDescent="0.25">
@@ -47997,25 +47991,25 @@
         <v>2645</v>
       </c>
       <c r="C942" t="s">
+        <v>2762</v>
+      </c>
+      <c r="D942" t="s">
         <v>2763</v>
-      </c>
-      <c r="D942" t="s">
-        <v>2764</v>
       </c>
       <c r="E942" t="s">
         <v>16</v>
       </c>
       <c r="F942" t="s">
-        <v>2776</v>
+        <v>2768</v>
       </c>
       <c r="G942" t="s">
-        <v>2777</v>
+        <v>2769</v>
       </c>
       <c r="H942">
         <v>2</v>
       </c>
       <c r="I942" t="s">
-        <v>2768</v>
+        <v>2772</v>
       </c>
       <c r="J942" t="s">
         <v>2774</v>
@@ -48024,10 +48018,10 @@
         <v>21</v>
       </c>
       <c r="L942" t="s">
-        <v>763</v>
+        <v>721</v>
       </c>
       <c r="M942" t="s">
-        <v>23</v>
+        <v>631</v>
       </c>
     </row>
     <row r="943" spans="1:13" x14ac:dyDescent="0.25">
@@ -48038,34 +48032,34 @@
         <v>2645</v>
       </c>
       <c r="C943" t="s">
+        <v>2762</v>
+      </c>
+      <c r="D943" t="s">
         <v>2763</v>
-      </c>
-      <c r="D943" t="s">
-        <v>2764</v>
       </c>
       <c r="E943" t="s">
         <v>16</v>
       </c>
       <c r="F943" t="s">
-        <v>2778</v>
+        <v>2775</v>
       </c>
       <c r="G943" t="s">
-        <v>2779</v>
+        <v>2776</v>
       </c>
       <c r="H943">
         <v>2</v>
       </c>
       <c r="I943" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="J943" t="s">
-        <v>2376</v>
+        <v>2773</v>
       </c>
       <c r="K943" t="s">
         <v>21</v>
       </c>
       <c r="L943" t="s">
-        <v>721</v>
+        <v>763</v>
       </c>
       <c r="M943" t="s">
         <v>23</v>
@@ -48079,28 +48073,28 @@
         <v>2645</v>
       </c>
       <c r="C944" t="s">
+        <v>2762</v>
+      </c>
+      <c r="D944" t="s">
         <v>2763</v>
-      </c>
-      <c r="D944" t="s">
-        <v>2764</v>
       </c>
       <c r="E944" t="s">
         <v>16</v>
       </c>
       <c r="F944" t="s">
-        <v>2780</v>
+        <v>2777</v>
       </c>
       <c r="G944" t="s">
-        <v>2781</v>
+        <v>2778</v>
       </c>
       <c r="H944">
         <v>2</v>
       </c>
       <c r="I944" t="s">
-        <v>2773</v>
+        <v>2767</v>
       </c>
       <c r="J944" t="s">
-        <v>2782</v>
+        <v>2376</v>
       </c>
       <c r="K944" t="s">
         <v>21</v>
@@ -48120,34 +48114,34 @@
         <v>2645</v>
       </c>
       <c r="C945" t="s">
-        <v>2783</v>
+        <v>2762</v>
       </c>
       <c r="D945" t="s">
-        <v>2784</v>
+        <v>2763</v>
       </c>
       <c r="E945" t="s">
         <v>16</v>
       </c>
       <c r="F945" t="s">
-        <v>2785</v>
+        <v>2779</v>
       </c>
       <c r="G945" t="s">
-        <v>2786</v>
+        <v>2780</v>
       </c>
       <c r="H945">
         <v>2</v>
       </c>
       <c r="I945" t="s">
-        <v>964</v>
+        <v>2772</v>
       </c>
       <c r="J945" t="s">
-        <v>2787</v>
+        <v>2781</v>
       </c>
       <c r="K945" t="s">
         <v>21</v>
       </c>
       <c r="L945" t="s">
-        <v>2788</v>
+        <v>721</v>
       </c>
       <c r="M945" t="s">
         <v>23</v>
@@ -48161,34 +48155,34 @@
         <v>2645</v>
       </c>
       <c r="C946" t="s">
+        <v>2782</v>
+      </c>
+      <c r="D946" t="s">
         <v>2783</v>
-      </c>
-      <c r="D946" t="s">
-        <v>2784</v>
       </c>
       <c r="E946" t="s">
         <v>16</v>
       </c>
       <c r="F946" t="s">
-        <v>2789</v>
+        <v>2784</v>
       </c>
       <c r="G946" t="s">
-        <v>2790</v>
+        <v>2785</v>
       </c>
       <c r="H946">
         <v>2</v>
       </c>
       <c r="I946" t="s">
-        <v>2791</v>
+        <v>964</v>
       </c>
       <c r="J946" t="s">
-        <v>2792</v>
+        <v>2786</v>
       </c>
       <c r="K946" t="s">
         <v>21</v>
       </c>
       <c r="L946" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="M946" t="s">
         <v>23</v>
@@ -48202,34 +48196,34 @@
         <v>2645</v>
       </c>
       <c r="C947" t="s">
+        <v>2782</v>
+      </c>
+      <c r="D947" t="s">
         <v>2783</v>
-      </c>
-      <c r="D947" t="s">
-        <v>2784</v>
       </c>
       <c r="E947" t="s">
         <v>16</v>
       </c>
       <c r="F947" t="s">
-        <v>2793</v>
+        <v>2788</v>
       </c>
       <c r="G947" t="s">
-        <v>2794</v>
+        <v>2789</v>
       </c>
       <c r="H947">
         <v>2</v>
       </c>
       <c r="I947" t="s">
-        <v>2795</v>
+        <v>2790</v>
       </c>
       <c r="J947" t="s">
-        <v>2679</v>
+        <v>2791</v>
       </c>
       <c r="K947" t="s">
         <v>21</v>
       </c>
       <c r="L947" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="M947" t="s">
         <v>23</v>
@@ -48237,40 +48231,40 @@
     </row>
     <row r="948" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
-        <v>2796</v>
+        <v>2644</v>
       </c>
       <c r="B948" t="s">
-        <v>2797</v>
+        <v>2645</v>
       </c>
       <c r="C948" t="s">
-        <v>2798</v>
+        <v>2782</v>
       </c>
       <c r="D948" t="s">
-        <v>2799</v>
+        <v>2783</v>
       </c>
       <c r="E948" t="s">
-        <v>2105</v>
+        <v>16</v>
       </c>
       <c r="F948" t="s">
-        <v>2800</v>
+        <v>2792</v>
       </c>
       <c r="G948" t="s">
-        <v>2801</v>
+        <v>2793</v>
       </c>
       <c r="H948">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I948" t="s">
-        <v>218</v>
+        <v>2794</v>
       </c>
       <c r="J948" t="s">
-        <v>2802</v>
+        <v>2679</v>
       </c>
       <c r="K948" t="s">
         <v>21</v>
       </c>
       <c r="L948" t="s">
-        <v>2803</v>
+        <v>2787</v>
       </c>
       <c r="M948" t="s">
         <v>23</v>
@@ -48278,25 +48272,25 @@
     </row>
     <row r="949" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B949" t="s">
         <v>2796</v>
       </c>
-      <c r="B949" t="s">
+      <c r="C949" t="s">
         <v>2797</v>
       </c>
-      <c r="C949" t="s">
+      <c r="D949" t="s">
         <v>2798</v>
       </c>
-      <c r="D949" t="s">
+      <c r="E949" t="s">
+        <v>2105</v>
+      </c>
+      <c r="F949" t="s">
         <v>2799</v>
       </c>
-      <c r="E949" t="s">
-        <v>16</v>
-      </c>
-      <c r="F949" t="s">
-        <v>2804</v>
-      </c>
       <c r="G949" t="s">
-        <v>2805</v>
+        <v>2800</v>
       </c>
       <c r="H949">
         <v>3</v>
@@ -48305,13 +48299,13 @@
         <v>218</v>
       </c>
       <c r="J949" t="s">
-        <v>2806</v>
+        <v>2801</v>
       </c>
       <c r="K949" t="s">
         <v>21</v>
       </c>
       <c r="L949" t="s">
-        <v>2081</v>
+        <v>2802</v>
       </c>
       <c r="M949" t="s">
         <v>23</v>
@@ -48319,34 +48313,34 @@
     </row>
     <row r="950" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B950" t="s">
         <v>2796</v>
       </c>
-      <c r="B950" t="s">
+      <c r="C950" t="s">
         <v>2797</v>
       </c>
-      <c r="C950" t="s">
+      <c r="D950" t="s">
         <v>2798</v>
-      </c>
-      <c r="D950" t="s">
-        <v>2799</v>
       </c>
       <c r="E950" t="s">
         <v>16</v>
       </c>
       <c r="F950" t="s">
-        <v>2807</v>
+        <v>2803</v>
       </c>
       <c r="G950" t="s">
-        <v>2808</v>
+        <v>2804</v>
       </c>
       <c r="H950">
         <v>3</v>
       </c>
       <c r="I950" t="s">
-        <v>2809</v>
+        <v>218</v>
       </c>
       <c r="J950" t="s">
-        <v>2810</v>
+        <v>2805</v>
       </c>
       <c r="K950" t="s">
         <v>21</v>
@@ -48360,40 +48354,40 @@
     </row>
     <row r="951" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B951" t="s">
         <v>2796</v>
       </c>
-      <c r="B951" t="s">
+      <c r="C951" t="s">
         <v>2797</v>
       </c>
-      <c r="C951" t="s">
+      <c r="D951" t="s">
         <v>2798</v>
       </c>
-      <c r="D951" t="s">
-        <v>2799</v>
-      </c>
       <c r="E951" t="s">
-        <v>2105</v>
+        <v>16</v>
       </c>
       <c r="F951" t="s">
-        <v>2811</v>
+        <v>2806</v>
       </c>
       <c r="G951" t="s">
-        <v>2812</v>
+        <v>2807</v>
       </c>
       <c r="H951">
         <v>3</v>
       </c>
       <c r="I951" t="s">
-        <v>2813</v>
+        <v>2808</v>
       </c>
       <c r="J951" t="s">
-        <v>2806</v>
+        <v>2809</v>
       </c>
       <c r="K951" t="s">
         <v>21</v>
       </c>
       <c r="L951" t="s">
-        <v>1982</v>
+        <v>2081</v>
       </c>
       <c r="M951" t="s">
         <v>23</v>
@@ -48401,40 +48395,40 @@
     </row>
     <row r="952" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B952" t="s">
         <v>2796</v>
       </c>
-      <c r="B952" t="s">
+      <c r="C952" t="s">
         <v>2797</v>
       </c>
-      <c r="C952" t="s">
+      <c r="D952" t="s">
         <v>2798</v>
       </c>
-      <c r="D952" t="s">
-        <v>2799</v>
-      </c>
       <c r="E952" t="s">
-        <v>16</v>
+        <v>2105</v>
       </c>
       <c r="F952" t="s">
-        <v>2814</v>
+        <v>2810</v>
       </c>
       <c r="G952" t="s">
-        <v>2815</v>
+        <v>2811</v>
       </c>
       <c r="H952">
         <v>3</v>
       </c>
       <c r="I952" t="s">
-        <v>2816</v>
+        <v>2812</v>
       </c>
       <c r="J952" t="s">
-        <v>2817</v>
+        <v>2805</v>
       </c>
       <c r="K952" t="s">
         <v>21</v>
       </c>
       <c r="L952" t="s">
-        <v>2081</v>
+        <v>1982</v>
       </c>
       <c r="M952" t="s">
         <v>23</v>
@@ -48442,40 +48436,40 @@
     </row>
     <row r="953" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B953" t="s">
         <v>2796</v>
       </c>
-      <c r="B953" t="s">
+      <c r="C953" t="s">
         <v>2797</v>
       </c>
-      <c r="C953" t="s">
+      <c r="D953" t="s">
         <v>2798</v>
-      </c>
-      <c r="D953" t="s">
-        <v>2799</v>
       </c>
       <c r="E953" t="s">
         <v>16</v>
       </c>
       <c r="F953" t="s">
-        <v>2818</v>
+        <v>2813</v>
       </c>
       <c r="G953" t="s">
-        <v>2819</v>
+        <v>2814</v>
       </c>
       <c r="H953">
         <v>3</v>
       </c>
       <c r="I953" t="s">
-        <v>215</v>
+        <v>2815</v>
       </c>
       <c r="J953" t="s">
-        <v>116</v>
+        <v>2816</v>
       </c>
       <c r="K953" t="s">
         <v>21</v>
       </c>
       <c r="L953" t="s">
-        <v>116</v>
+        <v>2081</v>
       </c>
       <c r="M953" t="s">
         <v>23</v>
@@ -48483,31 +48477,31 @@
     </row>
     <row r="954" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B954" t="s">
         <v>2796</v>
       </c>
-      <c r="B954" t="s">
+      <c r="C954" t="s">
         <v>2797</v>
       </c>
-      <c r="C954" t="s">
+      <c r="D954" t="s">
         <v>2798</v>
-      </c>
-      <c r="D954" t="s">
-        <v>2799</v>
       </c>
       <c r="E954" t="s">
         <v>16</v>
       </c>
       <c r="F954" t="s">
+        <v>2817</v>
+      </c>
+      <c r="G954" t="s">
         <v>2818</v>
       </c>
-      <c r="G954" t="s">
-        <v>2819</v>
-      </c>
       <c r="H954">
         <v>3</v>
       </c>
       <c r="I954" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J954" t="s">
         <v>116</v>
@@ -48519,36 +48513,36 @@
         <v>116</v>
       </c>
       <c r="M954" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
     </row>
     <row r="955" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B955" t="s">
         <v>2796</v>
       </c>
-      <c r="B955" t="s">
+      <c r="C955" t="s">
         <v>2797</v>
       </c>
-      <c r="C955" t="s">
+      <c r="D955" t="s">
         <v>2798</v>
-      </c>
-      <c r="D955" t="s">
-        <v>2799</v>
       </c>
       <c r="E955" t="s">
         <v>16</v>
       </c>
       <c r="F955" t="s">
+        <v>2817</v>
+      </c>
+      <c r="G955" t="s">
         <v>2818</v>
       </c>
-      <c r="G955" t="s">
-        <v>2819</v>
-      </c>
       <c r="H955">
         <v>3</v>
       </c>
       <c r="I955" t="s">
-        <v>2809</v>
+        <v>212</v>
       </c>
       <c r="J955" t="s">
         <v>116</v>
@@ -48560,36 +48554,36 @@
         <v>116</v>
       </c>
       <c r="M955" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="956" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B956" t="s">
         <v>2796</v>
       </c>
-      <c r="B956" t="s">
+      <c r="C956" t="s">
         <v>2797</v>
       </c>
-      <c r="C956" t="s">
+      <c r="D956" t="s">
         <v>2798</v>
-      </c>
-      <c r="D956" t="s">
-        <v>2799</v>
       </c>
       <c r="E956" t="s">
         <v>16</v>
       </c>
       <c r="F956" t="s">
+        <v>2817</v>
+      </c>
+      <c r="G956" t="s">
         <v>2818</v>
       </c>
-      <c r="G956" t="s">
-        <v>2819</v>
-      </c>
       <c r="H956">
         <v>3</v>
       </c>
       <c r="I956" t="s">
-        <v>2813</v>
+        <v>2808</v>
       </c>
       <c r="J956" t="s">
         <v>116</v>
@@ -48601,36 +48595,36 @@
         <v>116</v>
       </c>
       <c r="M956" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="957" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B957" t="s">
         <v>2796</v>
       </c>
-      <c r="B957" t="s">
+      <c r="C957" t="s">
         <v>2797</v>
       </c>
-      <c r="C957" t="s">
+      <c r="D957" t="s">
         <v>2798</v>
-      </c>
-      <c r="D957" t="s">
-        <v>2799</v>
       </c>
       <c r="E957" t="s">
         <v>16</v>
       </c>
       <c r="F957" t="s">
+        <v>2817</v>
+      </c>
+      <c r="G957" t="s">
         <v>2818</v>
       </c>
-      <c r="G957" t="s">
-        <v>2819</v>
-      </c>
       <c r="H957">
         <v>3</v>
       </c>
       <c r="I957" t="s">
-        <v>218</v>
+        <v>2812</v>
       </c>
       <c r="J957" t="s">
         <v>116</v>
@@ -48642,30 +48636,30 @@
         <v>116</v>
       </c>
       <c r="M957" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="958" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B958" t="s">
         <v>2796</v>
       </c>
-      <c r="B958" t="s">
+      <c r="C958" t="s">
         <v>2797</v>
       </c>
-      <c r="C958" t="s">
+      <c r="D958" t="s">
         <v>2798</v>
-      </c>
-      <c r="D958" t="s">
-        <v>2799</v>
       </c>
       <c r="E958" t="s">
         <v>16</v>
       </c>
       <c r="F958" t="s">
-        <v>2820</v>
+        <v>2817</v>
       </c>
       <c r="G958" t="s">
-        <v>2821</v>
+        <v>2818</v>
       </c>
       <c r="H958">
         <v>3</v>
@@ -48674,54 +48668,54 @@
         <v>218</v>
       </c>
       <c r="J958" t="s">
-        <v>2822</v>
+        <v>116</v>
       </c>
       <c r="K958" t="s">
         <v>21</v>
       </c>
       <c r="L958" t="s">
-        <v>2081</v>
+        <v>116</v>
       </c>
       <c r="M958" t="s">
-        <v>23</v>
+        <v>633</v>
       </c>
     </row>
     <row r="959" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B959" t="s">
         <v>2796</v>
       </c>
-      <c r="B959" t="s">
+      <c r="C959" t="s">
         <v>2797</v>
       </c>
-      <c r="C959" t="s">
+      <c r="D959" t="s">
         <v>2798</v>
-      </c>
-      <c r="D959" t="s">
-        <v>2799</v>
       </c>
       <c r="E959" t="s">
         <v>16</v>
       </c>
       <c r="F959" t="s">
-        <v>2823</v>
+        <v>2819</v>
       </c>
       <c r="G959" t="s">
-        <v>2824</v>
+        <v>2820</v>
       </c>
       <c r="H959">
         <v>3</v>
       </c>
       <c r="I959" t="s">
-        <v>2813</v>
+        <v>218</v>
       </c>
       <c r="J959" t="s">
-        <v>2825</v>
+        <v>2821</v>
       </c>
       <c r="K959" t="s">
         <v>21</v>
       </c>
       <c r="L959" t="s">
-        <v>2803</v>
+        <v>2081</v>
       </c>
       <c r="M959" t="s">
         <v>23</v>
@@ -48729,40 +48723,40 @@
     </row>
     <row r="960" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B960" t="s">
         <v>2796</v>
       </c>
-      <c r="B960" t="s">
+      <c r="C960" t="s">
         <v>2797</v>
       </c>
-      <c r="C960" t="s">
+      <c r="D960" t="s">
         <v>2798</v>
-      </c>
-      <c r="D960" t="s">
-        <v>2799</v>
       </c>
       <c r="E960" t="s">
         <v>16</v>
       </c>
       <c r="F960" t="s">
-        <v>2826</v>
+        <v>2822</v>
       </c>
       <c r="G960" t="s">
-        <v>2827</v>
+        <v>2823</v>
       </c>
       <c r="H960">
         <v>3</v>
       </c>
       <c r="I960" t="s">
-        <v>2809</v>
+        <v>2812</v>
       </c>
       <c r="J960" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
       <c r="K960" t="s">
         <v>21</v>
       </c>
       <c r="L960" t="s">
-        <v>2828</v>
+        <v>2802</v>
       </c>
       <c r="M960" t="s">
         <v>23</v>
@@ -48770,40 +48764,40 @@
     </row>
     <row r="961" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B961" t="s">
         <v>2796</v>
       </c>
-      <c r="B961" t="s">
+      <c r="C961" t="s">
         <v>2797</v>
       </c>
-      <c r="C961" t="s">
+      <c r="D961" t="s">
         <v>2798</v>
-      </c>
-      <c r="D961" t="s">
-        <v>2799</v>
       </c>
       <c r="E961" t="s">
         <v>16</v>
       </c>
       <c r="F961" t="s">
-        <v>2829</v>
+        <v>2825</v>
       </c>
       <c r="G961" t="s">
-        <v>2830</v>
+        <v>2826</v>
       </c>
       <c r="H961">
         <v>3</v>
       </c>
       <c r="I961" t="s">
-        <v>212</v>
+        <v>2808</v>
       </c>
       <c r="J961" t="s">
-        <v>2802</v>
+        <v>2824</v>
       </c>
       <c r="K961" t="s">
         <v>21</v>
       </c>
       <c r="L961" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="M961" t="s">
         <v>23</v>
@@ -48811,40 +48805,40 @@
     </row>
     <row r="962" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B962" t="s">
         <v>2796</v>
       </c>
-      <c r="B962" t="s">
+      <c r="C962" t="s">
         <v>2797</v>
       </c>
-      <c r="C962" t="s">
+      <c r="D962" t="s">
         <v>2798</v>
-      </c>
-      <c r="D962" t="s">
-        <v>2799</v>
       </c>
       <c r="E962" t="s">
         <v>16</v>
       </c>
       <c r="F962" t="s">
-        <v>2831</v>
+        <v>2828</v>
       </c>
       <c r="G962" t="s">
-        <v>2832</v>
+        <v>2829</v>
       </c>
       <c r="H962">
         <v>3</v>
       </c>
       <c r="I962" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J962" t="s">
-        <v>2810</v>
+        <v>2801</v>
       </c>
       <c r="K962" t="s">
         <v>21</v>
       </c>
       <c r="L962" t="s">
-        <v>1982</v>
+        <v>2827</v>
       </c>
       <c r="M962" t="s">
         <v>23</v>
@@ -48852,40 +48846,40 @@
     </row>
     <row r="963" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B963" t="s">
         <v>2796</v>
       </c>
-      <c r="B963" t="s">
+      <c r="C963" t="s">
         <v>2797</v>
       </c>
-      <c r="C963" t="s">
+      <c r="D963" t="s">
         <v>2798</v>
-      </c>
-      <c r="D963" t="s">
-        <v>2799</v>
       </c>
       <c r="E963" t="s">
         <v>16</v>
       </c>
       <c r="F963" t="s">
-        <v>2833</v>
+        <v>2830</v>
       </c>
       <c r="G963" t="s">
-        <v>2834</v>
+        <v>2831</v>
       </c>
       <c r="H963">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I963" t="s">
-        <v>116</v>
+        <v>215</v>
       </c>
       <c r="J963" t="s">
-        <v>116</v>
+        <v>2809</v>
       </c>
       <c r="K963" t="s">
         <v>21</v>
       </c>
       <c r="L963" t="s">
-        <v>116</v>
+        <v>1982</v>
       </c>
       <c r="M963" t="s">
         <v>23</v>
@@ -48893,25 +48887,25 @@
     </row>
     <row r="964" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B964" t="s">
         <v>2796</v>
       </c>
-      <c r="B964" t="s">
+      <c r="C964" t="s">
         <v>2797</v>
       </c>
-      <c r="C964" t="s">
+      <c r="D964" t="s">
         <v>2798</v>
-      </c>
-      <c r="D964" t="s">
-        <v>2799</v>
       </c>
       <c r="E964" t="s">
         <v>16</v>
       </c>
       <c r="F964" t="s">
-        <v>2835</v>
+        <v>2832</v>
       </c>
       <c r="G964" t="s">
-        <v>2836</v>
+        <v>2833</v>
       </c>
       <c r="H964">
         <v>6</v>
@@ -48934,40 +48928,40 @@
     </row>
     <row r="965" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B965" t="s">
         <v>2796</v>
       </c>
-      <c r="B965" t="s">
+      <c r="C965" t="s">
         <v>2797</v>
       </c>
-      <c r="C965" t="s">
+      <c r="D965" t="s">
         <v>2798</v>
-      </c>
-      <c r="D965" t="s">
-        <v>2799</v>
       </c>
       <c r="E965" t="s">
         <v>16</v>
       </c>
       <c r="F965" t="s">
-        <v>2837</v>
+        <v>2834</v>
       </c>
       <c r="G965" t="s">
-        <v>2838</v>
+        <v>2835</v>
       </c>
       <c r="H965">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I965" t="s">
-        <v>2839</v>
+        <v>116</v>
       </c>
       <c r="J965" t="s">
-        <v>2822</v>
+        <v>116</v>
       </c>
       <c r="K965" t="s">
         <v>21</v>
       </c>
       <c r="L965" t="s">
-        <v>1982</v>
+        <v>116</v>
       </c>
       <c r="M965" t="s">
         <v>23</v>
@@ -48975,40 +48969,40 @@
     </row>
     <row r="966" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B966" t="s">
         <v>2796</v>
       </c>
-      <c r="B966" t="s">
+      <c r="C966" t="s">
         <v>2797</v>
       </c>
-      <c r="C966" t="s">
-        <v>2840</v>
-      </c>
       <c r="D966" t="s">
-        <v>2841</v>
+        <v>2798</v>
       </c>
       <c r="E966" t="s">
-        <v>2105</v>
+        <v>16</v>
       </c>
       <c r="F966" t="s">
-        <v>2842</v>
+        <v>2836</v>
       </c>
       <c r="G966" t="s">
-        <v>2812</v>
+        <v>2837</v>
       </c>
       <c r="H966">
         <v>3</v>
       </c>
       <c r="I966" t="s">
-        <v>2843</v>
+        <v>2838</v>
       </c>
       <c r="J966" t="s">
-        <v>94</v>
+        <v>2821</v>
       </c>
       <c r="K966" t="s">
         <v>21</v>
       </c>
       <c r="L966" t="s">
-        <v>2081</v>
+        <v>1982</v>
       </c>
       <c r="M966" t="s">
         <v>23</v>
@@ -49016,34 +49010,34 @@
     </row>
     <row r="967" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B967" t="s">
         <v>2796</v>
       </c>
-      <c r="B967" t="s">
-        <v>2797</v>
-      </c>
       <c r="C967" t="s">
+        <v>2839</v>
+      </c>
+      <c r="D967" t="s">
         <v>2840</v>
       </c>
-      <c r="D967" t="s">
+      <c r="E967" t="s">
+        <v>2105</v>
+      </c>
+      <c r="F967" t="s">
         <v>2841</v>
       </c>
-      <c r="E967" t="s">
-        <v>16</v>
-      </c>
-      <c r="F967" t="s">
-        <v>2844</v>
-      </c>
       <c r="G967" t="s">
-        <v>2845</v>
+        <v>2811</v>
       </c>
       <c r="H967">
         <v>3</v>
       </c>
       <c r="I967" t="s">
-        <v>2846</v>
+        <v>2842</v>
       </c>
       <c r="J967" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K967" t="s">
         <v>21</v>
@@ -49057,34 +49051,34 @@
     </row>
     <row r="968" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B968" t="s">
         <v>2796</v>
       </c>
-      <c r="B968" t="s">
-        <v>2797</v>
-      </c>
       <c r="C968" t="s">
+        <v>2839</v>
+      </c>
+      <c r="D968" t="s">
         <v>2840</v>
-      </c>
-      <c r="D968" t="s">
-        <v>2841</v>
       </c>
       <c r="E968" t="s">
         <v>16</v>
       </c>
       <c r="F968" t="s">
-        <v>2847</v>
+        <v>2843</v>
       </c>
       <c r="G968" t="s">
-        <v>2848</v>
+        <v>2844</v>
       </c>
       <c r="H968">
         <v>3</v>
       </c>
       <c r="I968" t="s">
-        <v>215</v>
+        <v>2845</v>
       </c>
       <c r="J968" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="K968" t="s">
         <v>21</v>
@@ -49098,40 +49092,40 @@
     </row>
     <row r="969" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
-        <v>2849</v>
+        <v>2795</v>
       </c>
       <c r="B969" t="s">
-        <v>2850</v>
+        <v>2796</v>
       </c>
       <c r="C969" t="s">
-        <v>2849</v>
+        <v>2839</v>
       </c>
       <c r="D969" t="s">
-        <v>15</v>
+        <v>2840</v>
       </c>
       <c r="E969" t="s">
         <v>16</v>
       </c>
       <c r="F969" t="s">
-        <v>2851</v>
+        <v>2846</v>
       </c>
       <c r="G969" t="s">
-        <v>2852</v>
+        <v>2847</v>
       </c>
       <c r="H969">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I969" t="s">
-        <v>2853</v>
+        <v>215</v>
       </c>
       <c r="J969" t="s">
-        <v>2400</v>
+        <v>99</v>
       </c>
       <c r="K969" t="s">
         <v>21</v>
       </c>
       <c r="L969" t="s">
-        <v>2854</v>
+        <v>2081</v>
       </c>
       <c r="M969" t="s">
         <v>23</v>
@@ -49139,13 +49133,13 @@
     </row>
     <row r="970" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B970" t="s">
         <v>2849</v>
       </c>
-      <c r="B970" t="s">
-        <v>2850</v>
-      </c>
       <c r="C970" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="D970" t="s">
         <v>15</v>
@@ -49154,25 +49148,25 @@
         <v>16</v>
       </c>
       <c r="F970" t="s">
-        <v>2855</v>
+        <v>2850</v>
       </c>
       <c r="G970" t="s">
-        <v>2856</v>
+        <v>2851</v>
       </c>
       <c r="H970">
         <v>2</v>
       </c>
       <c r="I970" t="s">
-        <v>2857</v>
+        <v>2852</v>
       </c>
       <c r="J970" t="s">
-        <v>2218</v>
+        <v>2400</v>
       </c>
       <c r="K970" t="s">
         <v>21</v>
       </c>
       <c r="L970" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="M970" t="s">
         <v>23</v>
@@ -49180,13 +49174,13 @@
     </row>
     <row r="971" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B971" t="s">
         <v>2849</v>
       </c>
-      <c r="B971" t="s">
-        <v>2850</v>
-      </c>
       <c r="C971" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="D971" t="s">
         <v>15</v>
@@ -49195,25 +49189,25 @@
         <v>16</v>
       </c>
       <c r="F971" t="s">
-        <v>2858</v>
+        <v>2854</v>
       </c>
       <c r="G971" t="s">
-        <v>2859</v>
+        <v>2855</v>
       </c>
       <c r="H971">
         <v>2</v>
       </c>
       <c r="I971" t="s">
-        <v>35</v>
+        <v>2856</v>
       </c>
       <c r="J971" t="s">
-        <v>2400</v>
+        <v>2218</v>
       </c>
       <c r="K971" t="s">
         <v>21</v>
       </c>
       <c r="L971" t="s">
-        <v>2860</v>
+        <v>2853</v>
       </c>
       <c r="M971" t="s">
         <v>23</v>
@@ -49221,13 +49215,13 @@
     </row>
     <row r="972" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B972" t="s">
         <v>2849</v>
       </c>
-      <c r="B972" t="s">
-        <v>2850</v>
-      </c>
       <c r="C972" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="D972" t="s">
         <v>15</v>
@@ -49236,25 +49230,25 @@
         <v>16</v>
       </c>
       <c r="F972" t="s">
-        <v>2861</v>
+        <v>2857</v>
       </c>
       <c r="G972" t="s">
-        <v>2862</v>
+        <v>2858</v>
       </c>
       <c r="H972">
         <v>2</v>
       </c>
       <c r="I972" t="s">
-        <v>1227</v>
+        <v>35</v>
       </c>
       <c r="J972" t="s">
-        <v>2218</v>
+        <v>2400</v>
       </c>
       <c r="K972" t="s">
         <v>21</v>
       </c>
       <c r="L972" t="s">
-        <v>2863</v>
+        <v>2859</v>
       </c>
       <c r="M972" t="s">
         <v>23</v>
@@ -49262,13 +49256,13 @@
     </row>
     <row r="973" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B973" t="s">
         <v>2849</v>
       </c>
-      <c r="B973" t="s">
-        <v>2850</v>
-      </c>
       <c r="C973" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="D973" t="s">
         <v>15</v>
@@ -49277,39 +49271,39 @@
         <v>16</v>
       </c>
       <c r="F973" t="s">
+        <v>2860</v>
+      </c>
+      <c r="G973" t="s">
         <v>2861</v>
-      </c>
-      <c r="G973" t="s">
-        <v>2862</v>
       </c>
       <c r="H973">
         <v>2</v>
       </c>
       <c r="I973" t="s">
-        <v>1691</v>
+        <v>1227</v>
       </c>
       <c r="J973" t="s">
-        <v>2227</v>
+        <v>2218</v>
       </c>
       <c r="K973" t="s">
         <v>21</v>
       </c>
       <c r="L973" t="s">
-        <v>37</v>
+        <v>2862</v>
       </c>
       <c r="M973" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
     </row>
     <row r="974" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B974" t="s">
         <v>2849</v>
       </c>
-      <c r="B974" t="s">
-        <v>2850</v>
-      </c>
       <c r="C974" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="D974" t="s">
         <v>15</v>
@@ -49318,16 +49312,16 @@
         <v>16</v>
       </c>
       <c r="F974" t="s">
+        <v>2860</v>
+      </c>
+      <c r="G974" t="s">
         <v>2861</v>
-      </c>
-      <c r="G974" t="s">
-        <v>2862</v>
       </c>
       <c r="H974">
         <v>2</v>
       </c>
       <c r="I974" t="s">
-        <v>2864</v>
+        <v>1691</v>
       </c>
       <c r="J974" t="s">
         <v>2227</v>
@@ -49339,18 +49333,18 @@
         <v>37</v>
       </c>
       <c r="M974" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="975" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B975" t="s">
         <v>2849</v>
       </c>
-      <c r="B975" t="s">
-        <v>2850</v>
-      </c>
       <c r="C975" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="D975" t="s">
         <v>15</v>
@@ -49359,39 +49353,39 @@
         <v>16</v>
       </c>
       <c r="F975" t="s">
+        <v>2860</v>
+      </c>
+      <c r="G975" t="s">
         <v>2861</v>
-      </c>
-      <c r="G975" t="s">
-        <v>2862</v>
       </c>
       <c r="H975">
         <v>2</v>
       </c>
       <c r="I975" t="s">
-        <v>2865</v>
+        <v>2863</v>
       </c>
       <c r="J975" t="s">
-        <v>2218</v>
+        <v>2227</v>
       </c>
       <c r="K975" t="s">
         <v>21</v>
       </c>
       <c r="L975" t="s">
-        <v>2863</v>
+        <v>37</v>
       </c>
       <c r="M975" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="976" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B976" t="s">
         <v>2849</v>
       </c>
-      <c r="B976" t="s">
-        <v>2850</v>
-      </c>
       <c r="C976" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="D976" t="s">
         <v>15</v>
@@ -49400,39 +49394,39 @@
         <v>16</v>
       </c>
       <c r="F976" t="s">
+        <v>2860</v>
+      </c>
+      <c r="G976" t="s">
         <v>2861</v>
-      </c>
-      <c r="G976" t="s">
-        <v>2862</v>
       </c>
       <c r="H976">
         <v>2</v>
       </c>
       <c r="I976" t="s">
-        <v>2866</v>
+        <v>2864</v>
       </c>
       <c r="J976" t="s">
-        <v>2222</v>
+        <v>2218</v>
       </c>
       <c r="K976" t="s">
         <v>21</v>
       </c>
       <c r="L976" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="M976" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="977" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B977" t="s">
         <v>2849</v>
       </c>
-      <c r="B977" t="s">
-        <v>2850</v>
-      </c>
       <c r="C977" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="D977" t="s">
         <v>15</v>
@@ -49441,10 +49435,10 @@
         <v>16</v>
       </c>
       <c r="F977" t="s">
-        <v>2867</v>
+        <v>2860</v>
       </c>
       <c r="G977" t="s">
-        <v>2868</v>
+        <v>2861</v>
       </c>
       <c r="H977">
         <v>2</v>
@@ -49453,27 +49447,27 @@
         <v>2865</v>
       </c>
       <c r="J977" t="s">
-        <v>2376</v>
+        <v>2222</v>
       </c>
       <c r="K977" t="s">
         <v>21</v>
       </c>
       <c r="L977" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="M977" t="s">
-        <v>23</v>
+        <v>633</v>
       </c>
     </row>
     <row r="978" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B978" t="s">
         <v>2849</v>
       </c>
-      <c r="B978" t="s">
-        <v>2850</v>
-      </c>
       <c r="C978" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="D978" t="s">
         <v>15</v>
@@ -49482,25 +49476,25 @@
         <v>16</v>
       </c>
       <c r="F978" t="s">
-        <v>2869</v>
+        <v>2866</v>
       </c>
       <c r="G978" t="s">
-        <v>2870</v>
+        <v>2867</v>
       </c>
       <c r="H978">
         <v>2</v>
       </c>
       <c r="I978" t="s">
-        <v>2871</v>
+        <v>2864</v>
       </c>
       <c r="J978" t="s">
-        <v>2872</v>
+        <v>2376</v>
       </c>
       <c r="K978" t="s">
         <v>21</v>
       </c>
       <c r="L978" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="M978" t="s">
         <v>23</v>
@@ -49508,40 +49502,40 @@
     </row>
     <row r="979" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B979" t="s">
         <v>2849</v>
       </c>
-      <c r="B979" t="s">
-        <v>2850</v>
-      </c>
       <c r="C979" t="s">
-        <v>2873</v>
+        <v>2848</v>
       </c>
       <c r="D979" t="s">
-        <v>2874</v>
+        <v>15</v>
       </c>
       <c r="E979" t="s">
         <v>16</v>
       </c>
       <c r="F979" t="s">
-        <v>2875</v>
+        <v>2868</v>
       </c>
       <c r="G979" t="s">
-        <v>2876</v>
+        <v>2869</v>
       </c>
       <c r="H979">
         <v>2</v>
       </c>
       <c r="I979" t="s">
-        <v>2865</v>
+        <v>2870</v>
       </c>
       <c r="J979" t="s">
-        <v>2400</v>
+        <v>2871</v>
       </c>
       <c r="K979" t="s">
         <v>21</v>
       </c>
       <c r="L979" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="M979" t="s">
         <v>23</v>
@@ -49549,40 +49543,40 @@
     </row>
     <row r="980" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B980" t="s">
         <v>2849</v>
       </c>
-      <c r="B980" t="s">
-        <v>2850</v>
-      </c>
       <c r="C980" t="s">
+        <v>2872</v>
+      </c>
+      <c r="D980" t="s">
         <v>2873</v>
-      </c>
-      <c r="D980" t="s">
-        <v>2874</v>
       </c>
       <c r="E980" t="s">
         <v>16</v>
       </c>
       <c r="F980" t="s">
-        <v>2877</v>
+        <v>2874</v>
       </c>
       <c r="G980" t="s">
-        <v>2878</v>
+        <v>2875</v>
       </c>
       <c r="H980">
         <v>2</v>
       </c>
       <c r="I980" t="s">
-        <v>2879</v>
+        <v>2864</v>
       </c>
       <c r="J980" t="s">
-        <v>2227</v>
+        <v>2400</v>
       </c>
       <c r="K980" t="s">
         <v>21</v>
       </c>
       <c r="L980" t="s">
-        <v>2562</v>
+        <v>2862</v>
       </c>
       <c r="M980" t="s">
         <v>23</v>
@@ -49590,40 +49584,40 @@
     </row>
     <row r="981" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B981" t="s">
         <v>2849</v>
       </c>
-      <c r="B981" t="s">
-        <v>2850</v>
-      </c>
       <c r="C981" t="s">
+        <v>2872</v>
+      </c>
+      <c r="D981" t="s">
         <v>2873</v>
-      </c>
-      <c r="D981" t="s">
-        <v>2874</v>
       </c>
       <c r="E981" t="s">
         <v>16</v>
       </c>
       <c r="F981" t="s">
-        <v>2880</v>
+        <v>2876</v>
       </c>
       <c r="G981" t="s">
-        <v>2881</v>
+        <v>2877</v>
       </c>
       <c r="H981">
         <v>2</v>
       </c>
       <c r="I981" t="s">
-        <v>2882</v>
+        <v>2878</v>
       </c>
       <c r="J981" t="s">
-        <v>2376</v>
+        <v>2227</v>
       </c>
       <c r="K981" t="s">
         <v>21</v>
       </c>
       <c r="L981" t="s">
-        <v>2854</v>
+        <v>2562</v>
       </c>
       <c r="M981" t="s">
         <v>23</v>
@@ -49631,40 +49625,40 @@
     </row>
     <row r="982" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B982" t="s">
         <v>2849</v>
       </c>
-      <c r="B982" t="s">
-        <v>2850</v>
-      </c>
       <c r="C982" t="s">
+        <v>2872</v>
+      </c>
+      <c r="D982" t="s">
         <v>2873</v>
-      </c>
-      <c r="D982" t="s">
-        <v>2874</v>
       </c>
       <c r="E982" t="s">
         <v>16</v>
       </c>
       <c r="F982" t="s">
-        <v>2883</v>
+        <v>2879</v>
       </c>
       <c r="G982" t="s">
-        <v>2884</v>
+        <v>2880</v>
       </c>
       <c r="H982">
         <v>2</v>
       </c>
       <c r="I982" t="s">
-        <v>2885</v>
+        <v>2881</v>
       </c>
       <c r="J982" t="s">
-        <v>2400</v>
+        <v>2376</v>
       </c>
       <c r="K982" t="s">
         <v>21</v>
       </c>
       <c r="L982" t="s">
-        <v>2562</v>
+        <v>2853</v>
       </c>
       <c r="M982" t="s">
         <v>23</v>
@@ -49672,40 +49666,40 @@
     </row>
     <row r="983" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B983" t="s">
         <v>2849</v>
       </c>
-      <c r="B983" t="s">
-        <v>2850</v>
-      </c>
       <c r="C983" t="s">
+        <v>2872</v>
+      </c>
+      <c r="D983" t="s">
         <v>2873</v>
-      </c>
-      <c r="D983" t="s">
-        <v>2874</v>
       </c>
       <c r="E983" t="s">
         <v>16</v>
       </c>
       <c r="F983" t="s">
-        <v>2886</v>
+        <v>2882</v>
       </c>
       <c r="G983" t="s">
-        <v>2887</v>
+        <v>2883</v>
       </c>
       <c r="H983">
         <v>2</v>
       </c>
       <c r="I983" t="s">
-        <v>2888</v>
+        <v>2884</v>
       </c>
       <c r="J983" t="s">
-        <v>2227</v>
+        <v>2400</v>
       </c>
       <c r="K983" t="s">
         <v>21</v>
       </c>
       <c r="L983" t="s">
-        <v>2481</v>
+        <v>2562</v>
       </c>
       <c r="M983" t="s">
         <v>23</v>
@@ -49713,40 +49707,40 @@
     </row>
     <row r="984" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B984" t="s">
         <v>2849</v>
       </c>
-      <c r="B984" t="s">
-        <v>2850</v>
-      </c>
       <c r="C984" t="s">
-        <v>2889</v>
+        <v>2872</v>
       </c>
       <c r="D984" t="s">
-        <v>2890</v>
+        <v>2873</v>
       </c>
       <c r="E984" t="s">
         <v>16</v>
       </c>
       <c r="F984" t="s">
-        <v>2891</v>
+        <v>2885</v>
       </c>
       <c r="G984" t="s">
-        <v>2892</v>
+        <v>2886</v>
       </c>
       <c r="H984">
         <v>2</v>
       </c>
       <c r="I984" t="s">
-        <v>2893</v>
+        <v>2887</v>
       </c>
       <c r="J984" t="s">
-        <v>2400</v>
+        <v>2227</v>
       </c>
       <c r="K984" t="s">
         <v>21</v>
       </c>
       <c r="L984" t="s">
-        <v>37</v>
+        <v>2481</v>
       </c>
       <c r="M984" t="s">
         <v>23</v>
@@ -49754,40 +49748,40 @@
     </row>
     <row r="985" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B985" t="s">
         <v>2849</v>
       </c>
-      <c r="B985" t="s">
-        <v>2850</v>
-      </c>
       <c r="C985" t="s">
+        <v>2888</v>
+      </c>
+      <c r="D985" t="s">
         <v>2889</v>
-      </c>
-      <c r="D985" t="s">
-        <v>2890</v>
       </c>
       <c r="E985" t="s">
         <v>16</v>
       </c>
       <c r="F985" t="s">
-        <v>2894</v>
+        <v>2890</v>
       </c>
       <c r="G985" t="s">
-        <v>2895</v>
+        <v>2891</v>
       </c>
       <c r="H985">
         <v>2</v>
       </c>
       <c r="I985" t="s">
-        <v>2857</v>
+        <v>2892</v>
       </c>
       <c r="J985" t="s">
-        <v>2227</v>
+        <v>2400</v>
       </c>
       <c r="K985" t="s">
         <v>21</v>
       </c>
       <c r="L985" t="s">
-        <v>2854</v>
+        <v>37</v>
       </c>
       <c r="M985" t="s">
         <v>23</v>
@@ -49795,40 +49789,40 @@
     </row>
     <row r="986" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B986" t="s">
         <v>2849</v>
       </c>
-      <c r="B986" t="s">
-        <v>2850</v>
-      </c>
       <c r="C986" t="s">
+        <v>2888</v>
+      </c>
+      <c r="D986" t="s">
         <v>2889</v>
-      </c>
-      <c r="D986" t="s">
-        <v>2890</v>
       </c>
       <c r="E986" t="s">
         <v>16</v>
       </c>
       <c r="F986" t="s">
-        <v>2896</v>
+        <v>2893</v>
       </c>
       <c r="G986" t="s">
-        <v>2897</v>
+        <v>2894</v>
       </c>
       <c r="H986">
         <v>2</v>
       </c>
       <c r="I986" t="s">
-        <v>2898</v>
+        <v>2856</v>
       </c>
       <c r="J986" t="s">
-        <v>2400</v>
+        <v>2227</v>
       </c>
       <c r="K986" t="s">
         <v>21</v>
       </c>
       <c r="L986" t="s">
-        <v>2481</v>
+        <v>2853</v>
       </c>
       <c r="M986" t="s">
         <v>23</v>
@@ -49836,40 +49830,40 @@
     </row>
     <row r="987" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B987" t="s">
         <v>2849</v>
       </c>
-      <c r="B987" t="s">
-        <v>2850</v>
-      </c>
       <c r="C987" t="s">
+        <v>2888</v>
+      </c>
+      <c r="D987" t="s">
         <v>2889</v>
-      </c>
-      <c r="D987" t="s">
-        <v>2890</v>
       </c>
       <c r="E987" t="s">
         <v>16</v>
       </c>
       <c r="F987" t="s">
-        <v>2899</v>
+        <v>2895</v>
       </c>
       <c r="G987" t="s">
-        <v>2900</v>
+        <v>2896</v>
       </c>
       <c r="H987">
         <v>2</v>
       </c>
       <c r="I987" t="s">
-        <v>35</v>
+        <v>2897</v>
       </c>
       <c r="J987" t="s">
-        <v>2376</v>
+        <v>2400</v>
       </c>
       <c r="K987" t="s">
         <v>21</v>
       </c>
       <c r="L987" t="s">
-        <v>2860</v>
+        <v>2481</v>
       </c>
       <c r="M987" t="s">
         <v>23</v>
@@ -49877,40 +49871,40 @@
     </row>
     <row r="988" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B988" t="s">
         <v>2849</v>
       </c>
-      <c r="B988" t="s">
-        <v>2850</v>
-      </c>
       <c r="C988" t="s">
+        <v>2888</v>
+      </c>
+      <c r="D988" t="s">
         <v>2889</v>
-      </c>
-      <c r="D988" t="s">
-        <v>2890</v>
       </c>
       <c r="E988" t="s">
         <v>16</v>
       </c>
       <c r="F988" t="s">
-        <v>2901</v>
+        <v>2898</v>
       </c>
       <c r="G988" t="s">
-        <v>459</v>
+        <v>2899</v>
       </c>
       <c r="H988">
         <v>2</v>
       </c>
       <c r="I988" t="s">
-        <v>2902</v>
+        <v>35</v>
       </c>
       <c r="J988" t="s">
-        <v>2218</v>
+        <v>2376</v>
       </c>
       <c r="K988" t="s">
         <v>21</v>
       </c>
       <c r="L988" t="s">
-        <v>2562</v>
+        <v>2859</v>
       </c>
       <c r="M988" t="s">
         <v>23</v>
@@ -49918,40 +49912,40 @@
     </row>
     <row r="989" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B989" t="s">
         <v>2849</v>
       </c>
-      <c r="B989" t="s">
-        <v>2850</v>
-      </c>
       <c r="C989" t="s">
+        <v>2888</v>
+      </c>
+      <c r="D989" t="s">
         <v>2889</v>
-      </c>
-      <c r="D989" t="s">
-        <v>2890</v>
       </c>
       <c r="E989" t="s">
         <v>16</v>
       </c>
       <c r="F989" t="s">
-        <v>2903</v>
+        <v>2900</v>
       </c>
       <c r="G989" t="s">
-        <v>2904</v>
+        <v>459</v>
       </c>
       <c r="H989">
         <v>2</v>
       </c>
       <c r="I989" t="s">
-        <v>2865</v>
+        <v>2901</v>
       </c>
       <c r="J989" t="s">
-        <v>2227</v>
+        <v>2218</v>
       </c>
       <c r="K989" t="s">
         <v>21</v>
       </c>
       <c r="L989" t="s">
-        <v>2863</v>
+        <v>2562</v>
       </c>
       <c r="M989" t="s">
         <v>23</v>
@@ -49959,40 +49953,40 @@
     </row>
     <row r="990" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B990" t="s">
         <v>2849</v>
       </c>
-      <c r="B990" t="s">
-        <v>2850</v>
-      </c>
       <c r="C990" t="s">
-        <v>2905</v>
+        <v>2888</v>
       </c>
       <c r="D990" t="s">
-        <v>2906</v>
+        <v>2889</v>
       </c>
       <c r="E990" t="s">
         <v>16</v>
       </c>
       <c r="F990" t="s">
-        <v>2907</v>
+        <v>2902</v>
       </c>
       <c r="G990" t="s">
-        <v>2908</v>
+        <v>2903</v>
       </c>
       <c r="H990">
         <v>2</v>
       </c>
       <c r="I990" t="s">
-        <v>2898</v>
+        <v>2864</v>
       </c>
       <c r="J990" t="s">
-        <v>2909</v>
+        <v>2227</v>
       </c>
       <c r="K990" t="s">
         <v>21</v>
       </c>
       <c r="L990" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="M990" t="s">
         <v>23</v>
@@ -50000,40 +49994,40 @@
     </row>
     <row r="991" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B991" t="s">
         <v>2849</v>
       </c>
-      <c r="B991" t="s">
-        <v>2850</v>
-      </c>
       <c r="C991" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D991" t="s">
         <v>2905</v>
-      </c>
-      <c r="D991" t="s">
-        <v>2906</v>
       </c>
       <c r="E991" t="s">
         <v>16</v>
       </c>
       <c r="F991" t="s">
-        <v>2910</v>
+        <v>2906</v>
       </c>
       <c r="G991" t="s">
-        <v>2911</v>
+        <v>2907</v>
       </c>
       <c r="H991">
         <v>2</v>
       </c>
       <c r="I991" t="s">
-        <v>2912</v>
+        <v>2897</v>
       </c>
       <c r="J991" t="s">
-        <v>2913</v>
+        <v>2908</v>
       </c>
       <c r="K991" t="s">
         <v>21</v>
       </c>
       <c r="L991" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="M991" t="s">
         <v>23</v>
@@ -50041,40 +50035,40 @@
     </row>
     <row r="992" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B992" t="s">
         <v>2849</v>
       </c>
-      <c r="B992" t="s">
-        <v>2850</v>
-      </c>
       <c r="C992" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D992" t="s">
         <v>2905</v>
-      </c>
-      <c r="D992" t="s">
-        <v>2906</v>
       </c>
       <c r="E992" t="s">
         <v>16</v>
       </c>
       <c r="F992" t="s">
-        <v>2914</v>
+        <v>2909</v>
       </c>
       <c r="G992" t="s">
-        <v>2915</v>
+        <v>2910</v>
       </c>
       <c r="H992">
         <v>2</v>
       </c>
       <c r="I992" t="s">
-        <v>2893</v>
+        <v>2911</v>
       </c>
       <c r="J992" t="s">
-        <v>2222</v>
+        <v>2912</v>
       </c>
       <c r="K992" t="s">
         <v>21</v>
       </c>
       <c r="L992" t="s">
-        <v>37</v>
+        <v>2862</v>
       </c>
       <c r="M992" t="s">
         <v>23</v>
@@ -50082,40 +50076,40 @@
     </row>
     <row r="993" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B993" t="s">
         <v>2849</v>
       </c>
-      <c r="B993" t="s">
-        <v>2850</v>
-      </c>
       <c r="C993" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D993" t="s">
         <v>2905</v>
-      </c>
-      <c r="D993" t="s">
-        <v>2906</v>
       </c>
       <c r="E993" t="s">
         <v>16</v>
       </c>
       <c r="F993" t="s">
-        <v>2916</v>
+        <v>2913</v>
       </c>
       <c r="G993" t="s">
-        <v>2917</v>
+        <v>2914</v>
       </c>
       <c r="H993">
         <v>2</v>
       </c>
       <c r="I993" t="s">
-        <v>2918</v>
+        <v>2892</v>
       </c>
       <c r="J993" t="s">
-        <v>2376</v>
+        <v>2222</v>
       </c>
       <c r="K993" t="s">
         <v>21</v>
       </c>
       <c r="L993" t="s">
-        <v>2919</v>
+        <v>37</v>
       </c>
       <c r="M993" t="s">
         <v>23</v>
@@ -50123,40 +50117,40 @@
     </row>
     <row r="994" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B994" t="s">
         <v>2849</v>
       </c>
-      <c r="B994" t="s">
-        <v>2850</v>
-      </c>
       <c r="C994" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D994" t="s">
         <v>2905</v>
-      </c>
-      <c r="D994" t="s">
-        <v>2906</v>
       </c>
       <c r="E994" t="s">
         <v>16</v>
       </c>
       <c r="F994" t="s">
-        <v>2920</v>
+        <v>2915</v>
       </c>
       <c r="G994" t="s">
-        <v>2921</v>
+        <v>2916</v>
       </c>
       <c r="H994">
         <v>2</v>
       </c>
       <c r="I994" t="s">
-        <v>2912</v>
+        <v>2917</v>
       </c>
       <c r="J994" t="s">
-        <v>2227</v>
+        <v>2376</v>
       </c>
       <c r="K994" t="s">
         <v>21</v>
       </c>
       <c r="L994" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="M994" t="s">
         <v>23</v>
@@ -50164,40 +50158,40 @@
     </row>
     <row r="995" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B995" t="s">
         <v>2849</v>
       </c>
-      <c r="B995" t="s">
-        <v>2850</v>
-      </c>
       <c r="C995" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D995" t="s">
         <v>2905</v>
-      </c>
-      <c r="D995" t="s">
-        <v>2906</v>
       </c>
       <c r="E995" t="s">
         <v>16</v>
       </c>
       <c r="F995" t="s">
-        <v>2922</v>
+        <v>2919</v>
       </c>
       <c r="G995" t="s">
-        <v>2923</v>
+        <v>2920</v>
       </c>
       <c r="H995">
         <v>2</v>
       </c>
       <c r="I995" t="s">
-        <v>2866</v>
+        <v>2911</v>
       </c>
       <c r="J995" t="s">
-        <v>2376</v>
+        <v>2227</v>
       </c>
       <c r="K995" t="s">
         <v>21</v>
       </c>
       <c r="L995" t="s">
-        <v>37</v>
+        <v>2918</v>
       </c>
       <c r="M995" t="s">
         <v>23</v>
@@ -50205,40 +50199,40 @@
     </row>
     <row r="996" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B996" t="s">
         <v>2849</v>
       </c>
-      <c r="B996" t="s">
-        <v>2850</v>
-      </c>
       <c r="C996" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D996" t="s">
         <v>2905</v>
-      </c>
-      <c r="D996" t="s">
-        <v>2906</v>
       </c>
       <c r="E996" t="s">
         <v>16</v>
       </c>
       <c r="F996" t="s">
-        <v>2924</v>
+        <v>2921</v>
       </c>
       <c r="G996" t="s">
-        <v>2925</v>
+        <v>2922</v>
       </c>
       <c r="H996">
         <v>2</v>
       </c>
       <c r="I996" t="s">
-        <v>2926</v>
+        <v>2865</v>
       </c>
       <c r="J996" t="s">
-        <v>2218</v>
+        <v>2376</v>
       </c>
       <c r="K996" t="s">
         <v>21</v>
       </c>
       <c r="L996" t="s">
-        <v>2919</v>
+        <v>37</v>
       </c>
       <c r="M996" t="s">
         <v>23</v>
@@ -50246,31 +50240,31 @@
     </row>
     <row r="997" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B997" t="s">
         <v>2849</v>
       </c>
-      <c r="B997" t="s">
-        <v>2850</v>
-      </c>
       <c r="C997" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D997" t="s">
         <v>2905</v>
-      </c>
-      <c r="D997" t="s">
-        <v>2906</v>
       </c>
       <c r="E997" t="s">
         <v>16</v>
       </c>
       <c r="F997" t="s">
-        <v>2927</v>
+        <v>2923</v>
       </c>
       <c r="G997" t="s">
-        <v>2928</v>
+        <v>2924</v>
       </c>
       <c r="H997">
         <v>2</v>
       </c>
       <c r="I997" t="s">
-        <v>2879</v>
+        <v>2925</v>
       </c>
       <c r="J997" t="s">
         <v>2218</v>
@@ -50279,7 +50273,7 @@
         <v>21</v>
       </c>
       <c r="L997" t="s">
-        <v>37</v>
+        <v>2918</v>
       </c>
       <c r="M997" t="s">
         <v>23</v>
@@ -50287,40 +50281,40 @@
     </row>
     <row r="998" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B998" t="s">
         <v>2849</v>
       </c>
-      <c r="B998" t="s">
-        <v>2850</v>
-      </c>
       <c r="C998" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D998" t="s">
         <v>2905</v>
-      </c>
-      <c r="D998" t="s">
-        <v>2906</v>
       </c>
       <c r="E998" t="s">
         <v>16</v>
       </c>
       <c r="F998" t="s">
-        <v>2929</v>
+        <v>2926</v>
       </c>
       <c r="G998" t="s">
-        <v>2930</v>
+        <v>2927</v>
       </c>
       <c r="H998">
         <v>2</v>
       </c>
       <c r="I998" t="s">
-        <v>2866</v>
+        <v>2878</v>
       </c>
       <c r="J998" t="s">
-        <v>2400</v>
+        <v>2218</v>
       </c>
       <c r="K998" t="s">
         <v>21</v>
       </c>
       <c r="L998" t="s">
-        <v>2919</v>
+        <v>37</v>
       </c>
       <c r="M998" t="s">
         <v>23</v>
@@ -50328,40 +50322,40 @@
     </row>
     <row r="999" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
-        <v>2931</v>
+        <v>2848</v>
       </c>
       <c r="B999" t="s">
-        <v>2932</v>
+        <v>2849</v>
       </c>
       <c r="C999" t="s">
-        <v>2931</v>
+        <v>2904</v>
       </c>
       <c r="D999" t="s">
-        <v>15</v>
+        <v>2905</v>
       </c>
       <c r="E999" t="s">
-        <v>1594</v>
+        <v>16</v>
       </c>
       <c r="F999" t="s">
-        <v>2933</v>
+        <v>2928</v>
       </c>
       <c r="G999" t="s">
-        <v>2934</v>
+        <v>2929</v>
       </c>
       <c r="H999">
         <v>2</v>
       </c>
       <c r="I999" t="s">
-        <v>2935</v>
+        <v>2865</v>
       </c>
       <c r="J999" t="s">
-        <v>2227</v>
+        <v>2400</v>
       </c>
       <c r="K999" t="s">
         <v>21</v>
       </c>
       <c r="L999" t="s">
-        <v>457</v>
+        <v>2918</v>
       </c>
       <c r="M999" t="s">
         <v>23</v>
@@ -50369,40 +50363,40 @@
     </row>
     <row r="1000" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B1000" t="s">
         <v>2931</v>
       </c>
-      <c r="B1000" t="s">
+      <c r="C1000" t="s">
+        <v>2930</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1000" t="s">
+        <v>1594</v>
+      </c>
+      <c r="F1000" t="s">
         <v>2932</v>
       </c>
-      <c r="C1000" t="s">
-        <v>2936</v>
-      </c>
-      <c r="D1000" t="s">
-        <v>2937</v>
-      </c>
-      <c r="E1000" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1000" t="s">
-        <v>2938</v>
-      </c>
       <c r="G1000" t="s">
-        <v>2939</v>
+        <v>2933</v>
       </c>
       <c r="H1000">
         <v>2</v>
       </c>
       <c r="I1000" t="s">
-        <v>2940</v>
+        <v>2934</v>
       </c>
       <c r="J1000" t="s">
-        <v>2941</v>
+        <v>2227</v>
       </c>
       <c r="K1000" t="s">
         <v>21</v>
       </c>
       <c r="L1000" t="s">
-        <v>410</v>
+        <v>457</v>
       </c>
       <c r="M1000" t="s">
         <v>23</v>
@@ -50410,40 +50404,40 @@
     </row>
     <row r="1001" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B1001" t="s">
         <v>2931</v>
       </c>
-      <c r="B1001" t="s">
-        <v>2932</v>
-      </c>
       <c r="C1001" t="s">
-        <v>2942</v>
+        <v>2935</v>
       </c>
       <c r="D1001" t="s">
-        <v>2943</v>
+        <v>2936</v>
       </c>
       <c r="E1001" t="s">
         <v>16</v>
       </c>
       <c r="F1001" t="s">
-        <v>2944</v>
+        <v>2937</v>
       </c>
       <c r="G1001" t="s">
-        <v>2945</v>
+        <v>2938</v>
       </c>
       <c r="H1001">
         <v>2</v>
       </c>
       <c r="I1001" t="s">
-        <v>2137</v>
+        <v>2939</v>
       </c>
       <c r="J1001" t="s">
-        <v>1732</v>
+        <v>2940</v>
       </c>
       <c r="K1001" t="s">
         <v>21</v>
       </c>
       <c r="L1001" t="s">
-        <v>2946</v>
+        <v>410</v>
       </c>
       <c r="M1001" t="s">
         <v>23</v>
@@ -50451,40 +50445,40 @@
     </row>
     <row r="1002" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B1002" t="s">
         <v>2931</v>
       </c>
-      <c r="B1002" t="s">
-        <v>2932</v>
-      </c>
       <c r="C1002" t="s">
+        <v>2941</v>
+      </c>
+      <c r="D1002" t="s">
         <v>2942</v>
-      </c>
-      <c r="D1002" t="s">
-        <v>2943</v>
       </c>
       <c r="E1002" t="s">
         <v>16</v>
       </c>
       <c r="F1002" t="s">
-        <v>2947</v>
+        <v>2943</v>
       </c>
       <c r="G1002" t="s">
-        <v>2948</v>
+        <v>2944</v>
       </c>
       <c r="H1002">
         <v>2</v>
       </c>
       <c r="I1002" t="s">
-        <v>2949</v>
+        <v>2137</v>
       </c>
       <c r="J1002" t="s">
-        <v>2218</v>
+        <v>1732</v>
       </c>
       <c r="K1002" t="s">
         <v>21</v>
       </c>
       <c r="L1002" t="s">
-        <v>410</v>
+        <v>2945</v>
       </c>
       <c r="M1002" t="s">
         <v>23</v>
@@ -50492,40 +50486,40 @@
     </row>
     <row r="1003" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B1003" t="s">
         <v>2931</v>
       </c>
-      <c r="B1003" t="s">
-        <v>2932</v>
-      </c>
       <c r="C1003" t="s">
+        <v>2941</v>
+      </c>
+      <c r="D1003" t="s">
         <v>2942</v>
-      </c>
-      <c r="D1003" t="s">
-        <v>2943</v>
       </c>
       <c r="E1003" t="s">
         <v>16</v>
       </c>
       <c r="F1003" t="s">
-        <v>2950</v>
+        <v>2946</v>
       </c>
       <c r="G1003" t="s">
-        <v>2951</v>
+        <v>2947</v>
       </c>
       <c r="H1003">
         <v>2</v>
       </c>
       <c r="I1003" t="s">
-        <v>2952</v>
+        <v>2948</v>
       </c>
       <c r="J1003" t="s">
-        <v>2941</v>
+        <v>2218</v>
       </c>
       <c r="K1003" t="s">
         <v>21</v>
       </c>
       <c r="L1003" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="M1003" t="s">
         <v>23</v>
@@ -50533,40 +50527,40 @@
     </row>
     <row r="1004" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B1004" t="s">
         <v>2931</v>
       </c>
-      <c r="B1004" t="s">
-        <v>2932</v>
-      </c>
       <c r="C1004" t="s">
+        <v>2941</v>
+      </c>
+      <c r="D1004" t="s">
         <v>2942</v>
-      </c>
-      <c r="D1004" t="s">
-        <v>2943</v>
       </c>
       <c r="E1004" t="s">
         <v>16</v>
       </c>
       <c r="F1004" t="s">
-        <v>2953</v>
+        <v>2949</v>
       </c>
       <c r="G1004" t="s">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="H1004">
         <v>2</v>
       </c>
       <c r="I1004" t="s">
-        <v>2955</v>
+        <v>2951</v>
       </c>
       <c r="J1004" t="s">
-        <v>1789</v>
+        <v>2940</v>
       </c>
       <c r="K1004" t="s">
         <v>21</v>
       </c>
       <c r="L1004" t="s">
-        <v>2956</v>
+        <v>457</v>
       </c>
       <c r="M1004" t="s">
         <v>23</v>
@@ -50574,40 +50568,40 @@
     </row>
     <row r="1005" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B1005" t="s">
         <v>2931</v>
       </c>
-      <c r="B1005" t="s">
-        <v>2932</v>
-      </c>
       <c r="C1005" t="s">
-        <v>2957</v>
+        <v>2941</v>
       </c>
       <c r="D1005" t="s">
-        <v>2958</v>
+        <v>2942</v>
       </c>
       <c r="E1005" t="s">
         <v>16</v>
       </c>
       <c r="F1005" t="s">
-        <v>2959</v>
+        <v>2952</v>
       </c>
       <c r="G1005" t="s">
-        <v>2960</v>
+        <v>2953</v>
       </c>
       <c r="H1005">
         <v>2</v>
       </c>
       <c r="I1005" t="s">
-        <v>2961</v>
+        <v>2954</v>
       </c>
       <c r="J1005" t="s">
-        <v>2962</v>
+        <v>1789</v>
       </c>
       <c r="K1005" t="s">
         <v>21</v>
       </c>
       <c r="L1005" t="s">
-        <v>457</v>
+        <v>2955</v>
       </c>
       <c r="M1005" t="s">
         <v>23</v>
@@ -50615,40 +50609,40 @@
     </row>
     <row r="1006" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B1006" t="s">
         <v>2931</v>
       </c>
-      <c r="B1006" t="s">
-        <v>2932</v>
-      </c>
       <c r="C1006" t="s">
+        <v>2956</v>
+      </c>
+      <c r="D1006" t="s">
         <v>2957</v>
-      </c>
-      <c r="D1006" t="s">
-        <v>2958</v>
       </c>
       <c r="E1006" t="s">
         <v>16</v>
       </c>
       <c r="F1006" t="s">
-        <v>2963</v>
+        <v>2958</v>
       </c>
       <c r="G1006" t="s">
-        <v>2964</v>
+        <v>2959</v>
       </c>
       <c r="H1006">
         <v>2</v>
       </c>
       <c r="I1006" t="s">
+        <v>2960</v>
+      </c>
+      <c r="J1006" t="s">
         <v>2961</v>
       </c>
-      <c r="J1006" t="s">
-        <v>1732</v>
-      </c>
       <c r="K1006" t="s">
         <v>21</v>
       </c>
       <c r="L1006" t="s">
-        <v>2956</v>
+        <v>457</v>
       </c>
       <c r="M1006" t="s">
         <v>23</v>
@@ -50656,40 +50650,40 @@
     </row>
     <row r="1007" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B1007" t="s">
         <v>2931</v>
       </c>
-      <c r="B1007" t="s">
-        <v>2932</v>
-      </c>
       <c r="C1007" t="s">
+        <v>2956</v>
+      </c>
+      <c r="D1007" t="s">
         <v>2957</v>
-      </c>
-      <c r="D1007" t="s">
-        <v>2958</v>
       </c>
       <c r="E1007" t="s">
         <v>16</v>
       </c>
       <c r="F1007" t="s">
-        <v>2965</v>
+        <v>2962</v>
       </c>
       <c r="G1007" t="s">
-        <v>2966</v>
+        <v>2963</v>
       </c>
       <c r="H1007">
         <v>2</v>
       </c>
       <c r="I1007" t="s">
-        <v>2935</v>
+        <v>2960</v>
       </c>
       <c r="J1007" t="s">
-        <v>2967</v>
+        <v>1732</v>
       </c>
       <c r="K1007" t="s">
         <v>21</v>
       </c>
       <c r="L1007" t="s">
-        <v>410</v>
+        <v>2955</v>
       </c>
       <c r="M1007" t="s">
         <v>23</v>
@@ -50697,40 +50691,40 @@
     </row>
     <row r="1008" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B1008" t="s">
         <v>2931</v>
       </c>
-      <c r="B1008" t="s">
-        <v>2932</v>
-      </c>
       <c r="C1008" t="s">
+        <v>2956</v>
+      </c>
+      <c r="D1008" t="s">
         <v>2957</v>
-      </c>
-      <c r="D1008" t="s">
-        <v>2958</v>
       </c>
       <c r="E1008" t="s">
         <v>16</v>
       </c>
       <c r="F1008" t="s">
-        <v>2968</v>
+        <v>2964</v>
       </c>
       <c r="G1008" t="s">
-        <v>2969</v>
+        <v>2965</v>
       </c>
       <c r="H1008">
         <v>2</v>
       </c>
       <c r="I1008" t="s">
-        <v>2970</v>
+        <v>2934</v>
       </c>
       <c r="J1008" t="s">
-        <v>2218</v>
+        <v>2966</v>
       </c>
       <c r="K1008" t="s">
         <v>21</v>
       </c>
       <c r="L1008" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="M1008" t="s">
         <v>23</v>
@@ -50738,40 +50732,40 @@
     </row>
     <row r="1009" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
-        <v>2971</v>
+        <v>2930</v>
       </c>
       <c r="B1009" t="s">
-        <v>2972</v>
+        <v>2931</v>
       </c>
       <c r="C1009" t="s">
-        <v>2971</v>
+        <v>2956</v>
       </c>
       <c r="D1009" t="s">
-        <v>15</v>
+        <v>2957</v>
       </c>
       <c r="E1009" t="s">
-        <v>1594</v>
+        <v>16</v>
       </c>
       <c r="F1009" t="s">
-        <v>2973</v>
+        <v>2967</v>
       </c>
       <c r="G1009" t="s">
-        <v>2974</v>
+        <v>2968</v>
       </c>
       <c r="H1009">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I1009" t="s">
-        <v>2975</v>
+        <v>2969</v>
       </c>
       <c r="J1009" t="s">
-        <v>1623</v>
+        <v>2218</v>
       </c>
       <c r="K1009" t="s">
         <v>21</v>
       </c>
       <c r="L1009" t="s">
-        <v>2976</v>
+        <v>457</v>
       </c>
       <c r="M1009" t="s">
         <v>23</v>
@@ -50779,40 +50773,40 @@
     </row>
     <row r="1010" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1010" t="s">
         <v>2971</v>
       </c>
-      <c r="B1010" t="s">
-        <v>2972</v>
-      </c>
       <c r="C1010" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="D1010" t="s">
         <v>15</v>
       </c>
       <c r="E1010" t="s">
-        <v>16</v>
+        <v>1594</v>
       </c>
       <c r="F1010" t="s">
-        <v>2977</v>
+        <v>2972</v>
       </c>
       <c r="G1010" t="s">
-        <v>2978</v>
+        <v>2973</v>
       </c>
       <c r="H1010">
         <v>3</v>
       </c>
       <c r="I1010" t="s">
-        <v>1020</v>
+        <v>2974</v>
       </c>
       <c r="J1010" t="s">
-        <v>2248</v>
+        <v>1623</v>
       </c>
       <c r="K1010" t="s">
         <v>21</v>
       </c>
       <c r="L1010" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="M1010" t="s">
         <v>23</v>
@@ -50820,13 +50814,13 @@
     </row>
     <row r="1011" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1011" t="s">
         <v>2971</v>
       </c>
-      <c r="B1011" t="s">
-        <v>2972</v>
-      </c>
       <c r="C1011" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="D1011" t="s">
         <v>15</v>
@@ -50835,16 +50829,16 @@
         <v>16</v>
       </c>
       <c r="F1011" t="s">
-        <v>2979</v>
+        <v>2976</v>
       </c>
       <c r="G1011" t="s">
-        <v>2980</v>
+        <v>2977</v>
       </c>
       <c r="H1011">
         <v>3</v>
       </c>
       <c r="I1011" t="s">
-        <v>1295</v>
+        <v>1020</v>
       </c>
       <c r="J1011" t="s">
         <v>2248</v>
@@ -50853,7 +50847,7 @@
         <v>21</v>
       </c>
       <c r="L1011" t="s">
-        <v>2981</v>
+        <v>2975</v>
       </c>
       <c r="M1011" t="s">
         <v>23</v>
@@ -50861,40 +50855,40 @@
     </row>
     <row r="1012" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1012" t="s">
         <v>2971</v>
       </c>
-      <c r="B1012" t="s">
-        <v>2972</v>
-      </c>
       <c r="C1012" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="D1012" t="s">
         <v>15</v>
       </c>
       <c r="E1012" t="s">
-        <v>1594</v>
+        <v>16</v>
       </c>
       <c r="F1012" t="s">
-        <v>2982</v>
+        <v>2978</v>
       </c>
       <c r="G1012" t="s">
-        <v>2983</v>
+        <v>2979</v>
       </c>
       <c r="H1012">
         <v>3</v>
       </c>
       <c r="I1012" t="s">
-        <v>1020</v>
+        <v>1295</v>
       </c>
       <c r="J1012" t="s">
-        <v>162</v>
+        <v>2248</v>
       </c>
       <c r="K1012" t="s">
-        <v>324</v>
+        <v>21</v>
       </c>
       <c r="L1012" t="s">
-        <v>2984</v>
+        <v>2980</v>
       </c>
       <c r="M1012" t="s">
         <v>23</v>
@@ -50902,40 +50896,40 @@
     </row>
     <row r="1013" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1013" t="s">
         <v>2971</v>
       </c>
-      <c r="B1013" t="s">
-        <v>2972</v>
-      </c>
       <c r="C1013" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="D1013" t="s">
         <v>15</v>
       </c>
       <c r="E1013" t="s">
-        <v>2366</v>
+        <v>1594</v>
       </c>
       <c r="F1013" t="s">
-        <v>2985</v>
+        <v>2981</v>
       </c>
       <c r="G1013" t="s">
-        <v>2986</v>
+        <v>2982</v>
       </c>
       <c r="H1013">
         <v>3</v>
       </c>
       <c r="I1013" t="s">
-        <v>2987</v>
+        <v>1020</v>
       </c>
       <c r="J1013" t="s">
-        <v>288</v>
+        <v>162</v>
       </c>
       <c r="K1013" t="s">
         <v>324</v>
       </c>
       <c r="L1013" t="s">
-        <v>1296</v>
+        <v>2983</v>
       </c>
       <c r="M1013" t="s">
         <v>23</v>
@@ -50943,34 +50937,34 @@
     </row>
     <row r="1014" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1014" t="s">
         <v>2971</v>
       </c>
-      <c r="B1014" t="s">
-        <v>2972</v>
-      </c>
       <c r="C1014" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="D1014" t="s">
         <v>15</v>
       </c>
       <c r="E1014" t="s">
-        <v>1594</v>
+        <v>2366</v>
       </c>
       <c r="F1014" t="s">
-        <v>2988</v>
+        <v>2984</v>
       </c>
       <c r="G1014" t="s">
-        <v>2989</v>
+        <v>2985</v>
       </c>
       <c r="H1014">
         <v>3</v>
       </c>
       <c r="I1014" t="s">
-        <v>1295</v>
+        <v>1020</v>
       </c>
       <c r="J1014" t="s">
-        <v>70</v>
+        <v>288</v>
       </c>
       <c r="K1014" t="s">
         <v>324</v>
@@ -50984,13 +50978,13 @@
     </row>
     <row r="1015" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1015" t="s">
         <v>2971</v>
       </c>
-      <c r="B1015" t="s">
-        <v>2972</v>
-      </c>
       <c r="C1015" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="D1015" t="s">
         <v>15</v>
@@ -50999,19 +50993,19 @@
         <v>1594</v>
       </c>
       <c r="F1015" t="s">
-        <v>2990</v>
+        <v>2986</v>
       </c>
       <c r="G1015" t="s">
-        <v>2991</v>
+        <v>2987</v>
       </c>
       <c r="H1015">
         <v>3</v>
       </c>
       <c r="I1015" t="s">
-        <v>1668</v>
+        <v>1295</v>
       </c>
       <c r="J1015" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="K1015" t="s">
         <v>324</v>
@@ -51025,25 +51019,25 @@
     </row>
     <row r="1016" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1016" t="s">
         <v>2971</v>
       </c>
-      <c r="B1016" t="s">
-        <v>2972</v>
-      </c>
       <c r="C1016" t="s">
-        <v>2992</v>
+        <v>2970</v>
       </c>
       <c r="D1016" t="s">
-        <v>2993</v>
+        <v>15</v>
       </c>
       <c r="E1016" t="s">
-        <v>16</v>
+        <v>1594</v>
       </c>
       <c r="F1016" t="s">
-        <v>2994</v>
+        <v>2988</v>
       </c>
       <c r="G1016" t="s">
-        <v>2995</v>
+        <v>2989</v>
       </c>
       <c r="H1016">
         <v>3</v>
@@ -51052,13 +51046,13 @@
         <v>1668</v>
       </c>
       <c r="J1016" t="s">
-        <v>1215</v>
+        <v>86</v>
       </c>
       <c r="K1016" t="s">
-        <v>21</v>
+        <v>324</v>
       </c>
       <c r="L1016" t="s">
-        <v>2981</v>
+        <v>1296</v>
       </c>
       <c r="M1016" t="s">
         <v>23</v>
@@ -51066,40 +51060,40 @@
     </row>
     <row r="1017" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1017" t="s">
         <v>2971</v>
       </c>
-      <c r="B1017" t="s">
-        <v>2972</v>
-      </c>
       <c r="C1017" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
       <c r="D1017" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="E1017" t="s">
         <v>16</v>
       </c>
       <c r="F1017" t="s">
-        <v>2996</v>
+        <v>2992</v>
       </c>
       <c r="G1017" t="s">
-        <v>2997</v>
+        <v>2993</v>
       </c>
       <c r="H1017">
         <v>3</v>
       </c>
       <c r="I1017" t="s">
-        <v>1020</v>
+        <v>1668</v>
       </c>
       <c r="J1017" t="s">
-        <v>1638</v>
+        <v>1215</v>
       </c>
       <c r="K1017" t="s">
         <v>21</v>
       </c>
       <c r="L1017" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="M1017" t="s">
         <v>23</v>
@@ -51107,40 +51101,40 @@
     </row>
     <row r="1018" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1018" t="s">
         <v>2971</v>
       </c>
-      <c r="B1018" t="s">
-        <v>2972</v>
-      </c>
       <c r="C1018" t="s">
-        <v>2998</v>
+        <v>2990</v>
       </c>
       <c r="D1018" t="s">
-        <v>2999</v>
+        <v>2991</v>
       </c>
       <c r="E1018" t="s">
         <v>16</v>
       </c>
       <c r="F1018" t="s">
-        <v>3000</v>
+        <v>2994</v>
       </c>
       <c r="G1018" t="s">
-        <v>3001</v>
+        <v>2995</v>
       </c>
       <c r="H1018">
         <v>3</v>
       </c>
       <c r="I1018" t="s">
-        <v>3002</v>
+        <v>1020</v>
       </c>
       <c r="J1018" t="s">
-        <v>1215</v>
+        <v>1638</v>
       </c>
       <c r="K1018" t="s">
         <v>21</v>
       </c>
       <c r="L1018" t="s">
-        <v>2976</v>
+        <v>2980</v>
       </c>
       <c r="M1018" t="s">
         <v>23</v>
@@ -51148,42 +51142,83 @@
     </row>
     <row r="1019" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1019" t="s">
         <v>2971</v>
       </c>
-      <c r="B1019" t="s">
-        <v>2972</v>
-      </c>
       <c r="C1019" t="s">
-        <v>2998</v>
+        <v>2996</v>
       </c>
       <c r="D1019" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="E1019" t="s">
         <v>16</v>
       </c>
       <c r="F1019" t="s">
+        <v>2998</v>
+      </c>
+      <c r="G1019" t="s">
+        <v>2999</v>
+      </c>
+      <c r="H1019">
+        <v>3</v>
+      </c>
+      <c r="I1019" t="s">
+        <v>3000</v>
+      </c>
+      <c r="J1019" t="s">
+        <v>1215</v>
+      </c>
+      <c r="K1019" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1019" t="s">
+        <v>2975</v>
+      </c>
+      <c r="M1019" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1020" t="s">
+        <v>2970</v>
+      </c>
+      <c r="B1020" t="s">
+        <v>2971</v>
+      </c>
+      <c r="C1020" t="s">
+        <v>2996</v>
+      </c>
+      <c r="D1020" t="s">
+        <v>2997</v>
+      </c>
+      <c r="E1020" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1020" t="s">
+        <v>3001</v>
+      </c>
+      <c r="G1020" t="s">
+        <v>3002</v>
+      </c>
+      <c r="H1020">
+        <v>3</v>
+      </c>
+      <c r="I1020" t="s">
         <v>3003</v>
       </c>
-      <c r="G1019" t="s">
-        <v>3004</v>
-      </c>
-      <c r="H1019">
-        <v>3</v>
-      </c>
-      <c r="I1019" t="s">
-        <v>3005</v>
-      </c>
-      <c r="J1019" t="s">
+      <c r="J1020" t="s">
         <v>1638</v>
       </c>
-      <c r="K1019" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1019" t="s">
-        <v>2976</v>
-      </c>
-      <c r="M1019" t="s">
+      <c r="K1020" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1020" t="s">
+        <v>2975</v>
+      </c>
+      <c r="M1020" t="s">
         <v>23</v>
       </c>
     </row>

--- a/actions_fetch/out/kookmin(2026-2).xlsx
+++ b/actions_fetch/out/kookmin(2026-2).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12241" uniqueCount="3004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12253" uniqueCount="3007">
   <si>
     <t>campusCode</t>
   </si>
@@ -457,6 +457,9 @@
     <t>김동명</t>
   </si>
   <si>
+    <t>금 14:00-17:00</t>
+  </si>
+  <si>
     <t>30009</t>
   </si>
   <si>
@@ -616,9 +619,6 @@
     <t>이형재</t>
   </si>
   <si>
-    <t>금 14:00-17:00</t>
-  </si>
-  <si>
     <t>경영관4층18호실</t>
   </si>
   <si>
@@ -4699,7 +4699,79 @@
     <t>시각언어연구4</t>
   </si>
   <si>
-    <t>7244701</t>
+    <t>7297001</t>
+  </si>
+  <si>
+    <t>캡스톤디자인2</t>
+  </si>
+  <si>
+    <t>천애리</t>
+  </si>
+  <si>
+    <t>수 18:00-20:40,토 14:00-17:00</t>
+  </si>
+  <si>
+    <t>7297101</t>
+  </si>
+  <si>
+    <t>AX디자인워크숍4</t>
+  </si>
+  <si>
+    <t>이준용</t>
+  </si>
+  <si>
+    <t>7297201</t>
+  </si>
+  <si>
+    <t>그래픽디자인워크숍4</t>
+  </si>
+  <si>
+    <t>김동환</t>
+  </si>
+  <si>
+    <t>7297301</t>
+  </si>
+  <si>
+    <t>모션디자인워크숍4</t>
+  </si>
+  <si>
+    <t>7297401</t>
+  </si>
+  <si>
+    <t>편집디자인워크숍4</t>
+  </si>
+  <si>
+    <t>7297501</t>
+  </si>
+  <si>
+    <t>브랜드커뮤니케이션4</t>
+  </si>
+  <si>
+    <t>7297601</t>
+  </si>
+  <si>
+    <t>아이덴티티디자인4</t>
+  </si>
+  <si>
+    <t>화 14:00-17:00,금 14:00-17:00</t>
+  </si>
+  <si>
+    <t>7297701</t>
+  </si>
+  <si>
+    <t>디지털미디어디자인4</t>
+  </si>
+  <si>
+    <t>박재완</t>
+  </si>
+  <si>
+    <t>7297801</t>
+  </si>
+  <si>
+    <t>엔터테인먼트미디어4</t>
+  </si>
+  <si>
+    <t>7297901</t>
   </si>
   <si>
     <t>지역사회ESG디자인4</t>
@@ -4711,78 +4783,6 @@
     <t>조형관2층5-1호실</t>
   </si>
   <si>
-    <t>7297001</t>
-  </si>
-  <si>
-    <t>캡스톤디자인2</t>
-  </si>
-  <si>
-    <t>천애리</t>
-  </si>
-  <si>
-    <t>수 18:00-20:40,토 14:00-17:00</t>
-  </si>
-  <si>
-    <t>7297101</t>
-  </si>
-  <si>
-    <t>AX디자인워크숍4</t>
-  </si>
-  <si>
-    <t>이준용</t>
-  </si>
-  <si>
-    <t>7297201</t>
-  </si>
-  <si>
-    <t>그래픽디자인워크숍4</t>
-  </si>
-  <si>
-    <t>김동환</t>
-  </si>
-  <si>
-    <t>7297301</t>
-  </si>
-  <si>
-    <t>모션디자인워크숍4</t>
-  </si>
-  <si>
-    <t>7297401</t>
-  </si>
-  <si>
-    <t>편집디자인워크숍4</t>
-  </si>
-  <si>
-    <t>7297501</t>
-  </si>
-  <si>
-    <t>브랜드커뮤니케이션4</t>
-  </si>
-  <si>
-    <t>7297601</t>
-  </si>
-  <si>
-    <t>아이덴티티디자인4</t>
-  </si>
-  <si>
-    <t>화 14:00-17:00,금 14:00-17:00</t>
-  </si>
-  <si>
-    <t>7297701</t>
-  </si>
-  <si>
-    <t>디지털미디어디자인4</t>
-  </si>
-  <si>
-    <t>박재완</t>
-  </si>
-  <si>
-    <t>7297801</t>
-  </si>
-  <si>
-    <t>엔터테인먼트미디어4</t>
-  </si>
-  <si>
     <t>36418</t>
   </si>
   <si>
@@ -7957,18 +7957,27 @@
     <t>스즈끼 재능 교육전공</t>
   </si>
   <si>
+    <t>625220a</t>
+  </si>
+  <si>
+    <t>스즈끼전공실기1</t>
+  </si>
+  <si>
+    <t>곽은수</t>
+  </si>
+  <si>
+    <t>월 17:00-18:50</t>
+  </si>
+  <si>
+    <t>예술관3층3호실</t>
+  </si>
+  <si>
     <t>625300a</t>
   </si>
   <si>
     <t>스즈끼전공실기2</t>
   </si>
   <si>
-    <t>곽은수</t>
-  </si>
-  <si>
-    <t>예술관3층3호실</t>
-  </si>
-  <si>
     <t>황선영</t>
   </si>
   <si>
@@ -8290,10 +8299,10 @@
     <t>금 12:00-14:00</t>
   </si>
   <si>
-    <t>722400a</t>
-  </si>
-  <si>
-    <t>현악기초연구1</t>
+    <t>722410a</t>
+  </si>
+  <si>
+    <t>현악기초연구2</t>
   </si>
   <si>
     <t>금 14:00-16:00</t>
@@ -9399,7 +9408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M1020"/>
+  <dimension ref="A1:M1021"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -10620,7 +10629,7 @@
         <v>147</v>
       </c>
       <c r="J30" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="K30" t="s">
         <v>21</v>
@@ -10640,34 +10649,34 @@
         <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E31" t="s">
         <v>52</v>
       </c>
       <c r="F31" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G31" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H31">
         <v>3</v>
       </c>
       <c r="I31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K31" t="s">
         <v>21</v>
       </c>
       <c r="L31" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M31" t="s">
         <v>23</v>
@@ -10681,28 +10690,28 @@
         <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E32" t="s">
         <v>52</v>
       </c>
       <c r="F32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H32">
         <v>3</v>
       </c>
       <c r="I32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J32" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K32" t="s">
         <v>21</v>
@@ -10722,34 +10731,34 @@
         <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E33" t="s">
         <v>52</v>
       </c>
       <c r="F33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H33">
         <v>3</v>
       </c>
       <c r="I33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K33" t="s">
         <v>21</v>
       </c>
       <c r="L33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M33" t="s">
         <v>23</v>
@@ -10763,25 +10772,25 @@
         <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E34" t="s">
         <v>52</v>
       </c>
       <c r="F34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G34" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H34">
         <v>3</v>
       </c>
       <c r="I34" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J34" t="s">
         <v>56</v>
@@ -10790,7 +10799,7 @@
         <v>21</v>
       </c>
       <c r="L34" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M34" t="s">
         <v>23</v>
@@ -10804,25 +10813,25 @@
         <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E35" t="s">
         <v>52</v>
       </c>
       <c r="F35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H35">
         <v>3</v>
       </c>
       <c r="I35" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J35" t="s">
         <v>121</v>
@@ -10845,25 +10854,25 @@
         <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E36" t="s">
         <v>52</v>
       </c>
       <c r="F36" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H36">
         <v>3</v>
       </c>
       <c r="I36" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J36" t="s">
         <v>20</v>
@@ -10872,7 +10881,7 @@
         <v>21</v>
       </c>
       <c r="L36" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M36" t="s">
         <v>23</v>
@@ -10886,34 +10895,34 @@
         <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D37" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E37" t="s">
         <v>52</v>
       </c>
       <c r="F37" t="s">
+        <v>180</v>
+      </c>
+      <c r="G37" t="s">
+        <v>181</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+      <c r="I37" t="s">
+        <v>182</v>
+      </c>
+      <c r="J37" t="s">
+        <v>183</v>
+      </c>
+      <c r="K37" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" t="s">
         <v>179</v>
-      </c>
-      <c r="G37" t="s">
-        <v>180</v>
-      </c>
-      <c r="H37">
-        <v>3</v>
-      </c>
-      <c r="I37" t="s">
-        <v>181</v>
-      </c>
-      <c r="J37" t="s">
-        <v>182</v>
-      </c>
-      <c r="K37" t="s">
-        <v>21</v>
-      </c>
-      <c r="L37" t="s">
-        <v>178</v>
       </c>
       <c r="M37" t="s">
         <v>23</v>
@@ -10927,25 +10936,25 @@
         <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D38" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E38" t="s">
         <v>52</v>
       </c>
       <c r="F38" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G38" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H38">
         <v>3</v>
       </c>
       <c r="I38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J38" t="s">
         <v>78</v>
@@ -10954,7 +10963,7 @@
         <v>21</v>
       </c>
       <c r="L38" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M38" t="s">
         <v>23</v>
@@ -10968,25 +10977,25 @@
         <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D39" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E39" t="s">
         <v>52</v>
       </c>
       <c r="F39" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G39" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H39">
         <v>3</v>
       </c>
       <c r="I39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J39" t="s">
         <v>56</v>
@@ -10995,7 +11004,7 @@
         <v>21</v>
       </c>
       <c r="L39" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M39" t="s">
         <v>23</v>
@@ -11009,34 +11018,34 @@
         <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E40" t="s">
         <v>52</v>
       </c>
       <c r="F40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G40" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H40">
         <v>3</v>
       </c>
       <c r="I40" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J40" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K40" t="s">
         <v>21</v>
       </c>
       <c r="L40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -11050,28 +11059,28 @@
         <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D41" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E41" t="s">
         <v>52</v>
       </c>
       <c r="F41" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G41" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H41">
         <v>3</v>
       </c>
       <c r="I41" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J41" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K41" t="s">
         <v>21</v>
@@ -11091,10 +11100,10 @@
         <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D42" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E42" t="s">
         <v>52</v>
@@ -11132,10 +11141,10 @@
         <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D43" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E43" t="s">
         <v>52</v>
@@ -11173,10 +11182,10 @@
         <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D44" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E44" t="s">
         <v>52</v>
@@ -11214,10 +11223,10 @@
         <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D45" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E45" t="s">
         <v>52</v>
@@ -11255,10 +11264,10 @@
         <v>14</v>
       </c>
       <c r="C46" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D46" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E46" t="s">
         <v>52</v>
@@ -11296,10 +11305,10 @@
         <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D47" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E47" t="s">
         <v>52</v>
@@ -11337,10 +11346,10 @@
         <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D48" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E48" t="s">
         <v>52</v>
@@ -11358,7 +11367,7 @@
         <v>221</v>
       </c>
       <c r="J48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K48" t="s">
         <v>21</v>
@@ -11378,10 +11387,10 @@
         <v>14</v>
       </c>
       <c r="C49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D49" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E49" t="s">
         <v>52</v>
@@ -11419,10 +11428,10 @@
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E50" t="s">
         <v>52</v>
@@ -11460,10 +11469,10 @@
         <v>14</v>
       </c>
       <c r="C51" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D51" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E51" t="s">
         <v>52</v>
@@ -11501,10 +11510,10 @@
         <v>14</v>
       </c>
       <c r="C52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D52" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E52" t="s">
         <v>52</v>
@@ -11542,10 +11551,10 @@
         <v>14</v>
       </c>
       <c r="C53" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D53" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E53" t="s">
         <v>52</v>
@@ -11583,10 +11592,10 @@
         <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D54" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E54" t="s">
         <v>52</v>
@@ -11624,10 +11633,10 @@
         <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D55" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E55" t="s">
         <v>52</v>
@@ -11665,10 +11674,10 @@
         <v>14</v>
       </c>
       <c r="C56" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E56" t="s">
         <v>52</v>
@@ -11706,10 +11715,10 @@
         <v>14</v>
       </c>
       <c r="C57" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D57" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E57" t="s">
         <v>52</v>
@@ -11774,7 +11783,7 @@
         <v>21</v>
       </c>
       <c r="L58" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M58" t="s">
         <v>23</v>
@@ -11809,7 +11818,7 @@
         <v>259</v>
       </c>
       <c r="J59" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K59" t="s">
         <v>21</v>
@@ -12260,7 +12269,7 @@
         <v>299</v>
       </c>
       <c r="J70" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K70" t="s">
         <v>21</v>
@@ -13613,7 +13622,7 @@
         <v>436</v>
       </c>
       <c r="J103" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K103" t="s">
         <v>21</v>
@@ -13654,7 +13663,7 @@
         <v>439</v>
       </c>
       <c r="J104" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K104" t="s">
         <v>21</v>
@@ -14105,7 +14114,7 @@
         <v>483</v>
       </c>
       <c r="J115" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K115" t="s">
         <v>21</v>
@@ -14228,7 +14237,7 @@
         <v>491</v>
       </c>
       <c r="J118" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K118" t="s">
         <v>324</v>
@@ -14310,7 +14319,7 @@
         <v>498</v>
       </c>
       <c r="J120" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K120" t="s">
         <v>21</v>
@@ -14644,7 +14653,7 @@
         <v>21</v>
       </c>
       <c r="L128" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M128" t="s">
         <v>23</v>
@@ -14925,7 +14934,7 @@
         <v>555</v>
       </c>
       <c r="J135" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K135" t="s">
         <v>21</v>
@@ -15089,7 +15098,7 @@
         <v>559</v>
       </c>
       <c r="J139" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K139" t="s">
         <v>21</v>
@@ -15376,7 +15385,7 @@
         <v>596</v>
       </c>
       <c r="J146" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K146" t="s">
         <v>21</v>
@@ -23740,7 +23749,7 @@
         <v>850</v>
       </c>
       <c r="J350" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K350" t="s">
         <v>21</v>
@@ -24191,7 +24200,7 @@
         <v>889</v>
       </c>
       <c r="J361" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K361" t="s">
         <v>21</v>
@@ -25421,7 +25430,7 @@
         <v>982</v>
       </c>
       <c r="J391" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K391" t="s">
         <v>21</v>
@@ -25831,7 +25840,7 @@
         <v>1024</v>
       </c>
       <c r="J401" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K401" t="s">
         <v>21</v>
@@ -26077,7 +26086,7 @@
         <v>1051</v>
       </c>
       <c r="J407" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K407" t="s">
         <v>21</v>
@@ -26282,7 +26291,7 @@
         <v>1068</v>
       </c>
       <c r="J412" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K412" t="s">
         <v>21</v>
@@ -26364,7 +26373,7 @@
         <v>1076</v>
       </c>
       <c r="J414" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K414" t="s">
         <v>21</v>
@@ -26651,7 +26660,7 @@
         <v>1086</v>
       </c>
       <c r="J421" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K421" t="s">
         <v>21</v>
@@ -26856,7 +26865,7 @@
         <v>1113</v>
       </c>
       <c r="J426" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K426" t="s">
         <v>21</v>
@@ -27184,7 +27193,7 @@
         <v>147</v>
       </c>
       <c r="J434" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K434" t="s">
         <v>21</v>
@@ -27430,7 +27439,7 @@
         <v>1166</v>
       </c>
       <c r="J440" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K440" t="s">
         <v>21</v>
@@ -27553,7 +27562,7 @@
         <v>1177</v>
       </c>
       <c r="J443" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K443" t="s">
         <v>21</v>
@@ -28865,7 +28874,7 @@
         <v>1282</v>
       </c>
       <c r="J475" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K475" t="s">
         <v>21</v>
@@ -29152,7 +29161,7 @@
         <v>1307</v>
       </c>
       <c r="J482" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K482" t="s">
         <v>324</v>
@@ -30300,7 +30309,7 @@
         <v>1414</v>
       </c>
       <c r="J510" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K510" t="s">
         <v>21</v>
@@ -31161,7 +31170,7 @@
         <v>1455</v>
       </c>
       <c r="J531" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K531" t="s">
         <v>21</v>
@@ -31489,7 +31498,7 @@
         <v>1508</v>
       </c>
       <c r="J539" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K539" t="s">
         <v>21</v>
@@ -31735,7 +31744,7 @@
         <v>1496</v>
       </c>
       <c r="J545" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="K545" t="s">
         <v>21</v>
@@ -32347,16 +32356,16 @@
         <v>6</v>
       </c>
       <c r="I560" t="s">
-        <v>1059</v>
+        <v>1564</v>
       </c>
       <c r="J560" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="K560" t="s">
         <v>21</v>
       </c>
       <c r="L560" t="s">
-        <v>1565</v>
+        <v>1489</v>
       </c>
       <c r="M560" t="s">
         <v>23</v>
@@ -32376,7 +32385,7 @@
         <v>1543</v>
       </c>
       <c r="E561" t="s">
-        <v>1424</v>
+        <v>52</v>
       </c>
       <c r="F561" t="s">
         <v>1566</v>
@@ -32385,19 +32394,19 @@
         <v>1567</v>
       </c>
       <c r="H561">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I561" t="s">
         <v>1568</v>
       </c>
       <c r="J561" t="s">
-        <v>1569</v>
+        <v>590</v>
       </c>
       <c r="K561" t="s">
         <v>21</v>
       </c>
       <c r="L561" t="s">
-        <v>1489</v>
+        <v>1415</v>
       </c>
       <c r="M561" t="s">
         <v>23</v>
@@ -32420,19 +32429,19 @@
         <v>52</v>
       </c>
       <c r="F562" t="s">
+        <v>1569</v>
+      </c>
+      <c r="G562" t="s">
         <v>1570</v>
       </c>
-      <c r="G562" t="s">
+      <c r="H562">
+        <v>3</v>
+      </c>
+      <c r="I562" t="s">
         <v>1571</v>
       </c>
-      <c r="H562">
-        <v>3</v>
-      </c>
-      <c r="I562" t="s">
-        <v>1572</v>
-      </c>
       <c r="J562" t="s">
-        <v>590</v>
+        <v>563</v>
       </c>
       <c r="K562" t="s">
         <v>21</v>
@@ -32461,25 +32470,25 @@
         <v>52</v>
       </c>
       <c r="F563" t="s">
+        <v>1572</v>
+      </c>
+      <c r="G563" t="s">
         <v>1573</v>
       </c>
-      <c r="G563" t="s">
-        <v>1574</v>
-      </c>
       <c r="H563">
         <v>3</v>
       </c>
       <c r="I563" t="s">
-        <v>1575</v>
+        <v>887</v>
       </c>
       <c r="J563" t="s">
-        <v>563</v>
+        <v>349</v>
       </c>
       <c r="K563" t="s">
         <v>21</v>
       </c>
       <c r="L563" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="M563" t="s">
         <v>23</v>
@@ -32502,19 +32511,19 @@
         <v>52</v>
       </c>
       <c r="F564" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="G564" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="H564">
         <v>3</v>
       </c>
       <c r="I564" t="s">
-        <v>887</v>
+        <v>1391</v>
       </c>
       <c r="J564" t="s">
-        <v>349</v>
+        <v>716</v>
       </c>
       <c r="K564" t="s">
         <v>21</v>
@@ -32543,25 +32552,25 @@
         <v>52</v>
       </c>
       <c r="F565" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="G565" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H565">
         <v>3</v>
       </c>
       <c r="I565" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
       <c r="J565" t="s">
-        <v>716</v>
+        <v>163</v>
       </c>
       <c r="K565" t="s">
         <v>21</v>
       </c>
       <c r="L565" t="s">
-        <v>1411</v>
+        <v>1553</v>
       </c>
       <c r="M565" t="s">
         <v>23</v>
@@ -32581,22 +32590,22 @@
         <v>1543</v>
       </c>
       <c r="E566" t="s">
-        <v>52</v>
+        <v>1424</v>
       </c>
       <c r="F566" t="s">
+        <v>1578</v>
+      </c>
+      <c r="G566" t="s">
+        <v>1579</v>
+      </c>
+      <c r="H566">
+        <v>6</v>
+      </c>
+      <c r="I566" t="s">
+        <v>116</v>
+      </c>
+      <c r="J566" t="s">
         <v>1580</v>
-      </c>
-      <c r="G566" t="s">
-        <v>1581</v>
-      </c>
-      <c r="H566">
-        <v>3</v>
-      </c>
-      <c r="I566" t="s">
-        <v>1383</v>
-      </c>
-      <c r="J566" t="s">
-        <v>162</v>
       </c>
       <c r="K566" t="s">
         <v>21</v>
@@ -32622,28 +32631,28 @@
         <v>1543</v>
       </c>
       <c r="E567" t="s">
-        <v>1424</v>
+        <v>52</v>
       </c>
       <c r="F567" t="s">
+        <v>1581</v>
+      </c>
+      <c r="G567" t="s">
         <v>1582</v>
       </c>
-      <c r="G567" t="s">
+      <c r="H567">
+        <v>3</v>
+      </c>
+      <c r="I567" t="s">
         <v>1583</v>
       </c>
-      <c r="H567">
-        <v>6</v>
-      </c>
-      <c r="I567" t="s">
-        <v>116</v>
-      </c>
       <c r="J567" t="s">
-        <v>1584</v>
+        <v>70</v>
       </c>
       <c r="K567" t="s">
         <v>21</v>
       </c>
       <c r="L567" t="s">
-        <v>1553</v>
+        <v>1411</v>
       </c>
       <c r="M567" t="s">
         <v>23</v>
@@ -32663,28 +32672,28 @@
         <v>1543</v>
       </c>
       <c r="E568" t="s">
-        <v>52</v>
+        <v>1424</v>
       </c>
       <c r="F568" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G568" t="s">
         <v>1585</v>
       </c>
-      <c r="G568" t="s">
-        <v>1586</v>
-      </c>
       <c r="H568">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I568" t="s">
-        <v>1587</v>
+        <v>1583</v>
       </c>
       <c r="J568" t="s">
-        <v>70</v>
+        <v>1379</v>
       </c>
       <c r="K568" t="s">
         <v>21</v>
       </c>
       <c r="L568" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="M568" t="s">
         <v>23</v>
@@ -32707,25 +32716,25 @@
         <v>1424</v>
       </c>
       <c r="F569" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="G569" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="H569">
         <v>6</v>
       </c>
       <c r="I569" t="s">
-        <v>1587</v>
+        <v>1059</v>
       </c>
       <c r="J569" t="s">
-        <v>1379</v>
+        <v>1588</v>
       </c>
       <c r="K569" t="s">
         <v>21</v>
       </c>
       <c r="L569" t="s">
-        <v>1407</v>
+        <v>1589</v>
       </c>
       <c r="M569" t="s">
         <v>23</v>
@@ -32801,7 +32810,7 @@
         <v>1601</v>
       </c>
       <c r="J571" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K571" t="s">
         <v>21</v>
@@ -34734,7 +34743,7 @@
         <v>21</v>
       </c>
       <c r="L618" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M618" t="s">
         <v>23</v>
@@ -34775,7 +34784,7 @@
         <v>21</v>
       </c>
       <c r="L619" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M619" t="s">
         <v>630</v>
@@ -37850,7 +37859,7 @@
         <v>21</v>
       </c>
       <c r="L694" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M694" t="s">
         <v>23</v>
@@ -37973,7 +37982,7 @@
         <v>21</v>
       </c>
       <c r="L697" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M697" t="s">
         <v>23</v>
@@ -39982,7 +39991,7 @@
         <v>21</v>
       </c>
       <c r="L746" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M746" t="s">
         <v>23</v>
@@ -40023,7 +40032,7 @@
         <v>21</v>
       </c>
       <c r="L747" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M747" t="s">
         <v>23</v>
@@ -40105,7 +40114,7 @@
         <v>21</v>
       </c>
       <c r="L749" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M749" t="s">
         <v>23</v>
@@ -40146,7 +40155,7 @@
         <v>21</v>
       </c>
       <c r="L750" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M750" t="s">
         <v>23</v>
@@ -40187,7 +40196,7 @@
         <v>21</v>
       </c>
       <c r="L751" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M751" t="s">
         <v>23</v>
@@ -40392,7 +40401,7 @@
         <v>21</v>
       </c>
       <c r="L756" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M756" t="s">
         <v>23</v>
@@ -46249,13 +46258,13 @@
         <v>2650</v>
       </c>
       <c r="J899" t="s">
-        <v>2522</v>
+        <v>2651</v>
       </c>
       <c r="K899" t="s">
         <v>21</v>
       </c>
       <c r="L899" t="s">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="M899" t="s">
         <v>23</v>
@@ -46278,28 +46287,28 @@
         <v>16</v>
       </c>
       <c r="F900" t="s">
-        <v>2648</v>
+        <v>2653</v>
       </c>
       <c r="G900" t="s">
-        <v>2649</v>
+        <v>2654</v>
       </c>
       <c r="H900">
         <v>2</v>
       </c>
       <c r="I900" t="s">
+        <v>2650</v>
+      </c>
+      <c r="J900" t="s">
+        <v>2522</v>
+      </c>
+      <c r="K900" t="s">
+        <v>21</v>
+      </c>
+      <c r="L900" t="s">
         <v>2652</v>
       </c>
-      <c r="J900" t="s">
-        <v>2653</v>
-      </c>
-      <c r="K900" t="s">
-        <v>21</v>
-      </c>
-      <c r="L900" t="s">
-        <v>2654</v>
-      </c>
       <c r="M900" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
     </row>
     <row r="901" spans="1:13" x14ac:dyDescent="0.25">
@@ -46319,28 +46328,28 @@
         <v>16</v>
       </c>
       <c r="F901" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
       <c r="G901" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="H901">
         <v>2</v>
       </c>
       <c r="I901" t="s">
+        <v>2655</v>
+      </c>
+      <c r="J901" t="s">
+        <v>2656</v>
+      </c>
+      <c r="K901" t="s">
+        <v>21</v>
+      </c>
+      <c r="L901" t="s">
         <v>2657</v>
       </c>
-      <c r="J901" t="s">
-        <v>2658</v>
-      </c>
-      <c r="K901" t="s">
-        <v>21</v>
-      </c>
-      <c r="L901" t="s">
-        <v>2659</v>
-      </c>
       <c r="M901" t="s">
-        <v>23</v>
+        <v>630</v>
       </c>
     </row>
     <row r="902" spans="1:13" x14ac:dyDescent="0.25">
@@ -46360,25 +46369,25 @@
         <v>16</v>
       </c>
       <c r="F902" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="G902" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="H902">
         <v>2</v>
       </c>
       <c r="I902" t="s">
-        <v>2657</v>
+        <v>2660</v>
       </c>
       <c r="J902" t="s">
+        <v>2661</v>
+      </c>
+      <c r="K902" t="s">
+        <v>21</v>
+      </c>
+      <c r="L902" t="s">
         <v>2662</v>
-      </c>
-      <c r="K902" t="s">
-        <v>21</v>
-      </c>
-      <c r="L902" t="s">
-        <v>2659</v>
       </c>
       <c r="M902" t="s">
         <v>23</v>
@@ -46410,7 +46419,7 @@
         <v>2</v>
       </c>
       <c r="I903" t="s">
-        <v>1455</v>
+        <v>2660</v>
       </c>
       <c r="J903" t="s">
         <v>2665</v>
@@ -46419,7 +46428,7 @@
         <v>21</v>
       </c>
       <c r="L903" t="s">
-        <v>2659</v>
+        <v>2662</v>
       </c>
       <c r="M903" t="s">
         <v>23</v>
@@ -46451,16 +46460,16 @@
         <v>2</v>
       </c>
       <c r="I904" t="s">
-        <v>2652</v>
+        <v>1455</v>
       </c>
       <c r="J904" t="s">
+        <v>2668</v>
+      </c>
+      <c r="K904" t="s">
+        <v>21</v>
+      </c>
+      <c r="L904" t="s">
         <v>2662</v>
-      </c>
-      <c r="K904" t="s">
-        <v>21</v>
-      </c>
-      <c r="L904" t="s">
-        <v>2654</v>
       </c>
       <c r="M904" t="s">
         <v>23</v>
@@ -46483,28 +46492,28 @@
         <v>16</v>
       </c>
       <c r="F905" t="s">
-        <v>2666</v>
+        <v>2669</v>
       </c>
       <c r="G905" t="s">
-        <v>2667</v>
+        <v>2670</v>
       </c>
       <c r="H905">
         <v>2</v>
       </c>
       <c r="I905" t="s">
+        <v>2655</v>
+      </c>
+      <c r="J905" t="s">
+        <v>2665</v>
+      </c>
+      <c r="K905" t="s">
+        <v>21</v>
+      </c>
+      <c r="L905" t="s">
         <v>2657</v>
       </c>
-      <c r="J905" t="s">
-        <v>2668</v>
-      </c>
-      <c r="K905" t="s">
-        <v>21</v>
-      </c>
-      <c r="L905" t="s">
-        <v>2669</v>
-      </c>
       <c r="M905" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
     </row>
     <row r="906" spans="1:13" x14ac:dyDescent="0.25">
@@ -46524,28 +46533,28 @@
         <v>16</v>
       </c>
       <c r="F906" t="s">
-        <v>2666</v>
+        <v>2669</v>
       </c>
       <c r="G906" t="s">
-        <v>2667</v>
+        <v>2670</v>
       </c>
       <c r="H906">
         <v>2</v>
       </c>
       <c r="I906" t="s">
-        <v>2652</v>
+        <v>2660</v>
       </c>
       <c r="J906" t="s">
-        <v>2668</v>
+        <v>2671</v>
       </c>
       <c r="K906" t="s">
         <v>21</v>
       </c>
       <c r="L906" t="s">
-        <v>2654</v>
+        <v>2672</v>
       </c>
       <c r="M906" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="907" spans="1:13" x14ac:dyDescent="0.25">
@@ -46565,28 +46574,28 @@
         <v>16</v>
       </c>
       <c r="F907" t="s">
+        <v>2669</v>
+      </c>
+      <c r="G907" t="s">
         <v>2670</v>
-      </c>
-      <c r="G907" t="s">
-        <v>2671</v>
       </c>
       <c r="H907">
         <v>2</v>
       </c>
       <c r="I907" t="s">
+        <v>2655</v>
+      </c>
+      <c r="J907" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K907" t="s">
+        <v>21</v>
+      </c>
+      <c r="L907" t="s">
         <v>2657</v>
       </c>
-      <c r="J907" t="s">
-        <v>2653</v>
-      </c>
-      <c r="K907" t="s">
-        <v>21</v>
-      </c>
-      <c r="L907" t="s">
-        <v>2659</v>
-      </c>
       <c r="M907" t="s">
-        <v>23</v>
+        <v>631</v>
       </c>
     </row>
     <row r="908" spans="1:13" x14ac:dyDescent="0.25">
@@ -46606,25 +46615,25 @@
         <v>16</v>
       </c>
       <c r="F908" t="s">
-        <v>2672</v>
+        <v>2673</v>
       </c>
       <c r="G908" t="s">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="H908">
         <v>2</v>
       </c>
       <c r="I908" t="s">
-        <v>2657</v>
+        <v>2660</v>
       </c>
       <c r="J908" t="s">
-        <v>2665</v>
+        <v>2656</v>
       </c>
       <c r="K908" t="s">
         <v>21</v>
       </c>
       <c r="L908" t="s">
-        <v>2654</v>
+        <v>2662</v>
       </c>
       <c r="M908" t="s">
         <v>23</v>
@@ -46638,34 +46647,34 @@
         <v>2645</v>
       </c>
       <c r="C909" t="s">
-        <v>2674</v>
+        <v>2646</v>
       </c>
       <c r="D909" t="s">
-        <v>2675</v>
+        <v>2647</v>
       </c>
       <c r="E909" t="s">
         <v>16</v>
       </c>
       <c r="F909" t="s">
+        <v>2675</v>
+      </c>
+      <c r="G909" t="s">
         <v>2676</v>
-      </c>
-      <c r="G909" t="s">
-        <v>2677</v>
       </c>
       <c r="H909">
         <v>2</v>
       </c>
       <c r="I909" t="s">
-        <v>2678</v>
+        <v>2660</v>
       </c>
       <c r="J909" t="s">
-        <v>2679</v>
+        <v>2668</v>
       </c>
       <c r="K909" t="s">
         <v>21</v>
       </c>
       <c r="L909" t="s">
-        <v>2680</v>
+        <v>2657</v>
       </c>
       <c r="M909" t="s">
         <v>23</v>
@@ -46679,34 +46688,34 @@
         <v>2645</v>
       </c>
       <c r="C910" t="s">
-        <v>2674</v>
+        <v>2677</v>
       </c>
       <c r="D910" t="s">
-        <v>2675</v>
+        <v>2678</v>
       </c>
       <c r="E910" t="s">
         <v>16</v>
       </c>
       <c r="F910" t="s">
-        <v>2681</v>
+        <v>2679</v>
       </c>
       <c r="G910" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="H910">
         <v>2</v>
       </c>
       <c r="I910" t="s">
+        <v>2681</v>
+      </c>
+      <c r="J910" t="s">
+        <v>2682</v>
+      </c>
+      <c r="K910" t="s">
+        <v>21</v>
+      </c>
+      <c r="L910" t="s">
         <v>2683</v>
-      </c>
-      <c r="J910" t="s">
-        <v>2684</v>
-      </c>
-      <c r="K910" t="s">
-        <v>21</v>
-      </c>
-      <c r="L910" t="s">
-        <v>2680</v>
       </c>
       <c r="M910" t="s">
         <v>23</v>
@@ -46720,34 +46729,34 @@
         <v>2645</v>
       </c>
       <c r="C911" t="s">
-        <v>2674</v>
+        <v>2677</v>
       </c>
       <c r="D911" t="s">
-        <v>2675</v>
+        <v>2678</v>
       </c>
       <c r="E911" t="s">
         <v>16</v>
       </c>
       <c r="F911" t="s">
+        <v>2684</v>
+      </c>
+      <c r="G911" t="s">
         <v>2685</v>
-      </c>
-      <c r="G911" t="s">
-        <v>2686</v>
       </c>
       <c r="H911">
         <v>2</v>
       </c>
       <c r="I911" t="s">
+        <v>2686</v>
+      </c>
+      <c r="J911" t="s">
         <v>2687</v>
       </c>
-      <c r="J911" t="s">
-        <v>2688</v>
-      </c>
       <c r="K911" t="s">
         <v>21</v>
       </c>
       <c r="L911" t="s">
-        <v>2680</v>
+        <v>2683</v>
       </c>
       <c r="M911" t="s">
         <v>23</v>
@@ -46761,34 +46770,34 @@
         <v>2645</v>
       </c>
       <c r="C912" t="s">
-        <v>2689</v>
+        <v>2677</v>
       </c>
       <c r="D912" t="s">
-        <v>2690</v>
+        <v>2678</v>
       </c>
       <c r="E912" t="s">
         <v>16</v>
       </c>
       <c r="F912" t="s">
-        <v>2691</v>
+        <v>2688</v>
       </c>
       <c r="G912" t="s">
-        <v>2692</v>
+        <v>2689</v>
       </c>
       <c r="H912">
         <v>2</v>
       </c>
       <c r="I912" t="s">
-        <v>2693</v>
+        <v>2690</v>
       </c>
       <c r="J912" t="s">
-        <v>2448</v>
+        <v>2691</v>
       </c>
       <c r="K912" t="s">
         <v>21</v>
       </c>
       <c r="L912" t="s">
-        <v>721</v>
+        <v>2683</v>
       </c>
       <c r="M912" t="s">
         <v>23</v>
@@ -46802,10 +46811,10 @@
         <v>2645</v>
       </c>
       <c r="C913" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D913" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E913" t="s">
         <v>16</v>
@@ -46823,13 +46832,13 @@
         <v>2696</v>
       </c>
       <c r="J913" t="s">
-        <v>2522</v>
+        <v>2448</v>
       </c>
       <c r="K913" t="s">
         <v>21</v>
       </c>
       <c r="L913" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="M913" t="s">
         <v>23</v>
@@ -46843,10 +46852,10 @@
         <v>2645</v>
       </c>
       <c r="C914" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D914" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E914" t="s">
         <v>16</v>
@@ -46861,16 +46870,16 @@
         <v>2</v>
       </c>
       <c r="I914" t="s">
-        <v>1414</v>
+        <v>2699</v>
       </c>
       <c r="J914" t="s">
-        <v>2460</v>
+        <v>2522</v>
       </c>
       <c r="K914" t="s">
         <v>21</v>
       </c>
       <c r="L914" t="s">
-        <v>797</v>
+        <v>717</v>
       </c>
       <c r="M914" t="s">
         <v>23</v>
@@ -46884,34 +46893,34 @@
         <v>2645</v>
       </c>
       <c r="C915" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D915" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E915" t="s">
         <v>16</v>
       </c>
       <c r="F915" t="s">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="G915" t="s">
-        <v>2700</v>
+        <v>2701</v>
       </c>
       <c r="H915">
         <v>2</v>
       </c>
       <c r="I915" t="s">
-        <v>2701</v>
+        <v>1414</v>
       </c>
       <c r="J915" t="s">
-        <v>2468</v>
+        <v>2460</v>
       </c>
       <c r="K915" t="s">
         <v>21</v>
       </c>
       <c r="L915" t="s">
-        <v>749</v>
+        <v>797</v>
       </c>
       <c r="M915" t="s">
         <v>23</v>
@@ -46925,10 +46934,10 @@
         <v>2645</v>
       </c>
       <c r="C916" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D916" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E916" t="s">
         <v>16</v>
@@ -46946,13 +46955,13 @@
         <v>2704</v>
       </c>
       <c r="J916" t="s">
-        <v>2449</v>
+        <v>2468</v>
       </c>
       <c r="K916" t="s">
         <v>21</v>
       </c>
       <c r="L916" t="s">
-        <v>721</v>
+        <v>749</v>
       </c>
       <c r="M916" t="s">
         <v>23</v>
@@ -46966,10 +46975,10 @@
         <v>2645</v>
       </c>
       <c r="C917" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D917" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E917" t="s">
         <v>16</v>
@@ -46984,16 +46993,16 @@
         <v>2</v>
       </c>
       <c r="I917" t="s">
-        <v>2693</v>
+        <v>2707</v>
       </c>
       <c r="J917" t="s">
-        <v>2707</v>
+        <v>2449</v>
       </c>
       <c r="K917" t="s">
         <v>21</v>
       </c>
       <c r="L917" t="s">
-        <v>2708</v>
+        <v>721</v>
       </c>
       <c r="M917" t="s">
         <v>23</v>
@@ -47007,34 +47016,34 @@
         <v>2645</v>
       </c>
       <c r="C918" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D918" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E918" t="s">
         <v>16</v>
       </c>
       <c r="F918" t="s">
+        <v>2708</v>
+      </c>
+      <c r="G918" t="s">
         <v>2709</v>
-      </c>
-      <c r="G918" t="s">
-        <v>2710</v>
       </c>
       <c r="H918">
         <v>2</v>
       </c>
       <c r="I918" t="s">
-        <v>2693</v>
+        <v>2696</v>
       </c>
       <c r="J918" t="s">
+        <v>2710</v>
+      </c>
+      <c r="K918" t="s">
+        <v>21</v>
+      </c>
+      <c r="L918" t="s">
         <v>2711</v>
-      </c>
-      <c r="K918" t="s">
-        <v>21</v>
-      </c>
-      <c r="L918" t="s">
-        <v>2708</v>
       </c>
       <c r="M918" t="s">
         <v>23</v>
@@ -47048,37 +47057,37 @@
         <v>2645</v>
       </c>
       <c r="C919" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D919" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E919" t="s">
         <v>16</v>
       </c>
       <c r="F919" t="s">
-        <v>2709</v>
+        <v>2712</v>
       </c>
       <c r="G919" t="s">
-        <v>2710</v>
+        <v>2713</v>
       </c>
       <c r="H919">
         <v>2</v>
       </c>
       <c r="I919" t="s">
-        <v>2712</v>
+        <v>2696</v>
       </c>
       <c r="J919" t="s">
-        <v>2544</v>
+        <v>2714</v>
       </c>
       <c r="K919" t="s">
         <v>21</v>
       </c>
       <c r="L919" t="s">
-        <v>2708</v>
+        <v>2711</v>
       </c>
       <c r="M919" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
     </row>
     <row r="920" spans="1:13" x14ac:dyDescent="0.25">
@@ -47089,37 +47098,37 @@
         <v>2645</v>
       </c>
       <c r="C920" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D920" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E920" t="s">
         <v>16</v>
       </c>
       <c r="F920" t="s">
-        <v>2709</v>
+        <v>2712</v>
       </c>
       <c r="G920" t="s">
-        <v>2710</v>
+        <v>2713</v>
       </c>
       <c r="H920">
         <v>2</v>
       </c>
       <c r="I920" t="s">
-        <v>2696</v>
+        <v>2715</v>
       </c>
       <c r="J920" t="s">
-        <v>2547</v>
+        <v>2544</v>
       </c>
       <c r="K920" t="s">
         <v>21</v>
       </c>
       <c r="L920" t="s">
-        <v>2713</v>
+        <v>2711</v>
       </c>
       <c r="M920" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="921" spans="1:13" x14ac:dyDescent="0.25">
@@ -47130,37 +47139,37 @@
         <v>2645</v>
       </c>
       <c r="C921" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D921" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E921" t="s">
         <v>16</v>
       </c>
       <c r="F921" t="s">
-        <v>2714</v>
+        <v>2712</v>
       </c>
       <c r="G921" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
       <c r="H921">
         <v>2</v>
       </c>
       <c r="I921" t="s">
-        <v>2704</v>
+        <v>2699</v>
       </c>
       <c r="J921" t="s">
-        <v>2707</v>
+        <v>2547</v>
       </c>
       <c r="K921" t="s">
         <v>21</v>
       </c>
       <c r="L921" t="s">
-        <v>2713</v>
+        <v>2716</v>
       </c>
       <c r="M921" t="s">
-        <v>23</v>
+        <v>631</v>
       </c>
     </row>
     <row r="922" spans="1:13" x14ac:dyDescent="0.25">
@@ -47171,37 +47180,37 @@
         <v>2645</v>
       </c>
       <c r="C922" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D922" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E922" t="s">
         <v>16</v>
       </c>
       <c r="F922" t="s">
-        <v>2714</v>
+        <v>2717</v>
       </c>
       <c r="G922" t="s">
-        <v>2715</v>
+        <v>2718</v>
       </c>
       <c r="H922">
         <v>2</v>
       </c>
       <c r="I922" t="s">
+        <v>2707</v>
+      </c>
+      <c r="J922" t="s">
+        <v>2710</v>
+      </c>
+      <c r="K922" t="s">
+        <v>21</v>
+      </c>
+      <c r="L922" t="s">
         <v>2716</v>
       </c>
-      <c r="J922" t="s">
-        <v>2707</v>
-      </c>
-      <c r="K922" t="s">
-        <v>21</v>
-      </c>
-      <c r="L922" t="s">
-        <v>2708</v>
-      </c>
       <c r="M922" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
     </row>
     <row r="923" spans="1:13" x14ac:dyDescent="0.25">
@@ -47212,37 +47221,37 @@
         <v>2645</v>
       </c>
       <c r="C923" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D923" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E923" t="s">
         <v>16</v>
       </c>
       <c r="F923" t="s">
-        <v>2714</v>
+        <v>2717</v>
       </c>
       <c r="G923" t="s">
-        <v>2715</v>
+        <v>2718</v>
       </c>
       <c r="H923">
         <v>2</v>
       </c>
       <c r="I923" t="s">
-        <v>2701</v>
+        <v>2719</v>
       </c>
       <c r="J923" t="s">
-        <v>2658</v>
+        <v>2710</v>
       </c>
       <c r="K923" t="s">
         <v>21</v>
       </c>
       <c r="L923" t="s">
-        <v>2708</v>
+        <v>2711</v>
       </c>
       <c r="M923" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="924" spans="1:13" x14ac:dyDescent="0.25">
@@ -47253,37 +47262,37 @@
         <v>2645</v>
       </c>
       <c r="C924" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D924" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E924" t="s">
         <v>16</v>
       </c>
       <c r="F924" t="s">
-        <v>2714</v>
+        <v>2717</v>
       </c>
       <c r="G924" t="s">
-        <v>2715</v>
+        <v>2718</v>
       </c>
       <c r="H924">
         <v>2</v>
       </c>
       <c r="I924" t="s">
-        <v>2693</v>
+        <v>2704</v>
       </c>
       <c r="J924" t="s">
-        <v>2653</v>
+        <v>2661</v>
       </c>
       <c r="K924" t="s">
         <v>21</v>
       </c>
       <c r="L924" t="s">
-        <v>2708</v>
+        <v>2711</v>
       </c>
       <c r="M924" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="925" spans="1:13" x14ac:dyDescent="0.25">
@@ -47294,10 +47303,10 @@
         <v>2645</v>
       </c>
       <c r="C925" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D925" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E925" t="s">
         <v>16</v>
@@ -47312,19 +47321,19 @@
         <v>2</v>
       </c>
       <c r="I925" t="s">
-        <v>2719</v>
+        <v>2696</v>
       </c>
       <c r="J925" t="s">
-        <v>2460</v>
+        <v>2656</v>
       </c>
       <c r="K925" t="s">
         <v>21</v>
       </c>
       <c r="L925" t="s">
-        <v>763</v>
+        <v>2711</v>
       </c>
       <c r="M925" t="s">
-        <v>23</v>
+        <v>632</v>
       </c>
     </row>
     <row r="926" spans="1:13" x14ac:dyDescent="0.25">
@@ -47335,10 +47344,10 @@
         <v>2645</v>
       </c>
       <c r="C926" t="s">
-        <v>2689</v>
+        <v>2692</v>
       </c>
       <c r="D926" t="s">
-        <v>2690</v>
+        <v>2693</v>
       </c>
       <c r="E926" t="s">
         <v>16</v>
@@ -47353,16 +47362,16 @@
         <v>2</v>
       </c>
       <c r="I926" t="s">
-        <v>2693</v>
+        <v>2722</v>
       </c>
       <c r="J926" t="s">
-        <v>2468</v>
+        <v>2460</v>
       </c>
       <c r="K926" t="s">
         <v>21</v>
       </c>
       <c r="L926" t="s">
-        <v>721</v>
+        <v>763</v>
       </c>
       <c r="M926" t="s">
         <v>23</v>
@@ -47376,34 +47385,34 @@
         <v>2645</v>
       </c>
       <c r="C927" t="s">
-        <v>2722</v>
+        <v>2692</v>
       </c>
       <c r="D927" t="s">
-        <v>2723</v>
+        <v>2693</v>
       </c>
       <c r="E927" t="s">
         <v>16</v>
       </c>
       <c r="F927" t="s">
+        <v>2723</v>
+      </c>
+      <c r="G927" t="s">
         <v>2724</v>
-      </c>
-      <c r="G927" t="s">
-        <v>2725</v>
       </c>
       <c r="H927">
         <v>2</v>
       </c>
       <c r="I927" t="s">
-        <v>2726</v>
+        <v>2696</v>
       </c>
       <c r="J927" t="s">
-        <v>2151</v>
+        <v>2468</v>
       </c>
       <c r="K927" t="s">
         <v>21</v>
       </c>
       <c r="L927" t="s">
-        <v>2727</v>
+        <v>721</v>
       </c>
       <c r="M927" t="s">
         <v>23</v>
@@ -47417,34 +47426,34 @@
         <v>2645</v>
       </c>
       <c r="C928" t="s">
-        <v>2722</v>
+        <v>2725</v>
       </c>
       <c r="D928" t="s">
-        <v>2723</v>
+        <v>2726</v>
       </c>
       <c r="E928" t="s">
         <v>16</v>
       </c>
       <c r="F928" t="s">
+        <v>2727</v>
+      </c>
+      <c r="G928" t="s">
         <v>2728</v>
-      </c>
-      <c r="G928" t="s">
-        <v>2729</v>
       </c>
       <c r="H928">
         <v>2</v>
       </c>
       <c r="I928" t="s">
-        <v>2726</v>
+        <v>2729</v>
       </c>
       <c r="J928" t="s">
+        <v>2151</v>
+      </c>
+      <c r="K928" t="s">
+        <v>21</v>
+      </c>
+      <c r="L928" t="s">
         <v>2730</v>
-      </c>
-      <c r="K928" t="s">
-        <v>21</v>
-      </c>
-      <c r="L928" t="s">
-        <v>2727</v>
       </c>
       <c r="M928" t="s">
         <v>23</v>
@@ -47458,10 +47467,10 @@
         <v>2645</v>
       </c>
       <c r="C929" t="s">
-        <v>2722</v>
+        <v>2725</v>
       </c>
       <c r="D929" t="s">
-        <v>2723</v>
+        <v>2726</v>
       </c>
       <c r="E929" t="s">
         <v>16</v>
@@ -47476,7 +47485,7 @@
         <v>2</v>
       </c>
       <c r="I929" t="s">
-        <v>2726</v>
+        <v>2729</v>
       </c>
       <c r="J929" t="s">
         <v>2733</v>
@@ -47485,7 +47494,7 @@
         <v>21</v>
       </c>
       <c r="L929" t="s">
-        <v>2654</v>
+        <v>2730</v>
       </c>
       <c r="M929" t="s">
         <v>23</v>
@@ -47499,10 +47508,10 @@
         <v>2645</v>
       </c>
       <c r="C930" t="s">
-        <v>2722</v>
+        <v>2725</v>
       </c>
       <c r="D930" t="s">
-        <v>2723</v>
+        <v>2726</v>
       </c>
       <c r="E930" t="s">
         <v>16</v>
@@ -47517,7 +47526,7 @@
         <v>2</v>
       </c>
       <c r="I930" t="s">
-        <v>2726</v>
+        <v>2729</v>
       </c>
       <c r="J930" t="s">
         <v>2736</v>
@@ -47526,7 +47535,7 @@
         <v>21</v>
       </c>
       <c r="L930" t="s">
-        <v>2654</v>
+        <v>2657</v>
       </c>
       <c r="M930" t="s">
         <v>23</v>
@@ -47540,10 +47549,10 @@
         <v>2645</v>
       </c>
       <c r="C931" t="s">
-        <v>2722</v>
+        <v>2725</v>
       </c>
       <c r="D931" t="s">
-        <v>2723</v>
+        <v>2726</v>
       </c>
       <c r="E931" t="s">
         <v>16</v>
@@ -47558,16 +47567,16 @@
         <v>2</v>
       </c>
       <c r="I931" t="s">
+        <v>2729</v>
+      </c>
+      <c r="J931" t="s">
         <v>2739</v>
       </c>
-      <c r="J931" t="s">
-        <v>2740</v>
-      </c>
       <c r="K931" t="s">
         <v>21</v>
       </c>
       <c r="L931" t="s">
-        <v>2741</v>
+        <v>2657</v>
       </c>
       <c r="M931" t="s">
         <v>23</v>
@@ -47581,34 +47590,34 @@
         <v>2645</v>
       </c>
       <c r="C932" t="s">
-        <v>2742</v>
+        <v>2725</v>
       </c>
       <c r="D932" t="s">
-        <v>2743</v>
+        <v>2726</v>
       </c>
       <c r="E932" t="s">
         <v>16</v>
       </c>
       <c r="F932" t="s">
-        <v>2744</v>
+        <v>2740</v>
       </c>
       <c r="G932" t="s">
-        <v>2706</v>
+        <v>2741</v>
       </c>
       <c r="H932">
         <v>2</v>
       </c>
       <c r="I932" t="s">
-        <v>2745</v>
+        <v>2742</v>
       </c>
       <c r="J932" t="s">
-        <v>2746</v>
+        <v>2743</v>
       </c>
       <c r="K932" t="s">
         <v>21</v>
       </c>
       <c r="L932" t="s">
-        <v>2727</v>
+        <v>2744</v>
       </c>
       <c r="M932" t="s">
         <v>23</v>
@@ -47622,10 +47631,10 @@
         <v>2645</v>
       </c>
       <c r="C933" t="s">
-        <v>2742</v>
+        <v>2745</v>
       </c>
       <c r="D933" t="s">
-        <v>2743</v>
+        <v>2746</v>
       </c>
       <c r="E933" t="s">
         <v>16</v>
@@ -47634,22 +47643,22 @@
         <v>2747</v>
       </c>
       <c r="G933" t="s">
-        <v>2748</v>
+        <v>2709</v>
       </c>
       <c r="H933">
         <v>2</v>
       </c>
       <c r="I933" t="s">
+        <v>2748</v>
+      </c>
+      <c r="J933" t="s">
         <v>2749</v>
       </c>
-      <c r="J933" t="s">
-        <v>2750</v>
-      </c>
       <c r="K933" t="s">
         <v>21</v>
       </c>
       <c r="L933" t="s">
-        <v>721</v>
+        <v>2730</v>
       </c>
       <c r="M933" t="s">
         <v>23</v>
@@ -47663,34 +47672,34 @@
         <v>2645</v>
       </c>
       <c r="C934" t="s">
-        <v>2742</v>
+        <v>2745</v>
       </c>
       <c r="D934" t="s">
-        <v>2743</v>
+        <v>2746</v>
       </c>
       <c r="E934" t="s">
         <v>16</v>
       </c>
       <c r="F934" t="s">
+        <v>2750</v>
+      </c>
+      <c r="G934" t="s">
         <v>2751</v>
-      </c>
-      <c r="G934" t="s">
-        <v>2710</v>
       </c>
       <c r="H934">
         <v>2</v>
       </c>
       <c r="I934" t="s">
-        <v>2745</v>
+        <v>2752</v>
       </c>
       <c r="J934" t="s">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="K934" t="s">
         <v>21</v>
       </c>
       <c r="L934" t="s">
-        <v>2727</v>
+        <v>721</v>
       </c>
       <c r="M934" t="s">
         <v>23</v>
@@ -47704,25 +47713,25 @@
         <v>2645</v>
       </c>
       <c r="C935" t="s">
-        <v>2742</v>
+        <v>2745</v>
       </c>
       <c r="D935" t="s">
-        <v>2743</v>
+        <v>2746</v>
       </c>
       <c r="E935" t="s">
         <v>16</v>
       </c>
       <c r="F935" t="s">
-        <v>2753</v>
+        <v>2754</v>
       </c>
       <c r="G935" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
       <c r="H935">
         <v>2</v>
       </c>
       <c r="I935" t="s">
-        <v>2754</v>
+        <v>2748</v>
       </c>
       <c r="J935" t="s">
         <v>2755</v>
@@ -47731,7 +47740,7 @@
         <v>21</v>
       </c>
       <c r="L935" t="s">
-        <v>2727</v>
+        <v>2730</v>
       </c>
       <c r="M935" t="s">
         <v>23</v>
@@ -47745,10 +47754,10 @@
         <v>2645</v>
       </c>
       <c r="C936" t="s">
-        <v>2742</v>
+        <v>2745</v>
       </c>
       <c r="D936" t="s">
-        <v>2743</v>
+        <v>2746</v>
       </c>
       <c r="E936" t="s">
         <v>16</v>
@@ -47757,13 +47766,13 @@
         <v>2756</v>
       </c>
       <c r="G936" t="s">
-        <v>2757</v>
+        <v>2718</v>
       </c>
       <c r="H936">
         <v>2</v>
       </c>
       <c r="I936" t="s">
-        <v>2749</v>
+        <v>2757</v>
       </c>
       <c r="J936" t="s">
         <v>2758</v>
@@ -47772,7 +47781,7 @@
         <v>21</v>
       </c>
       <c r="L936" t="s">
-        <v>763</v>
+        <v>2730</v>
       </c>
       <c r="M936" t="s">
         <v>23</v>
@@ -47786,10 +47795,10 @@
         <v>2645</v>
       </c>
       <c r="C937" t="s">
-        <v>2742</v>
+        <v>2745</v>
       </c>
       <c r="D937" t="s">
-        <v>2743</v>
+        <v>2746</v>
       </c>
       <c r="E937" t="s">
         <v>16</v>
@@ -47804,7 +47813,7 @@
         <v>2</v>
       </c>
       <c r="I937" t="s">
-        <v>2745</v>
+        <v>2752</v>
       </c>
       <c r="J937" t="s">
         <v>2761</v>
@@ -47813,7 +47822,7 @@
         <v>21</v>
       </c>
       <c r="L937" t="s">
-        <v>737</v>
+        <v>763</v>
       </c>
       <c r="M937" t="s">
         <v>23</v>
@@ -47827,34 +47836,34 @@
         <v>2645</v>
       </c>
       <c r="C938" t="s">
-        <v>2762</v>
+        <v>2745</v>
       </c>
       <c r="D938" t="s">
-        <v>2763</v>
+        <v>2746</v>
       </c>
       <c r="E938" t="s">
         <v>16</v>
       </c>
       <c r="F938" t="s">
-        <v>2764</v>
+        <v>2762</v>
       </c>
       <c r="G938" t="s">
-        <v>2765</v>
+        <v>2763</v>
       </c>
       <c r="H938">
         <v>2</v>
       </c>
       <c r="I938" t="s">
-        <v>2766</v>
+        <v>2748</v>
       </c>
       <c r="J938" t="s">
-        <v>2400</v>
+        <v>2764</v>
       </c>
       <c r="K938" t="s">
         <v>21</v>
       </c>
       <c r="L938" t="s">
-        <v>759</v>
+        <v>737</v>
       </c>
       <c r="M938" t="s">
         <v>23</v>
@@ -47868,25 +47877,25 @@
         <v>2645</v>
       </c>
       <c r="C939" t="s">
-        <v>2762</v>
+        <v>2765</v>
       </c>
       <c r="D939" t="s">
-        <v>2763</v>
+        <v>2766</v>
       </c>
       <c r="E939" t="s">
         <v>16</v>
       </c>
       <c r="F939" t="s">
-        <v>2764</v>
+        <v>2767</v>
       </c>
       <c r="G939" t="s">
-        <v>2765</v>
+        <v>2768</v>
       </c>
       <c r="H939">
         <v>2</v>
       </c>
       <c r="I939" t="s">
-        <v>2767</v>
+        <v>2769</v>
       </c>
       <c r="J939" t="s">
         <v>2400</v>
@@ -47895,10 +47904,10 @@
         <v>21</v>
       </c>
       <c r="L939" t="s">
-        <v>721</v>
+        <v>759</v>
       </c>
       <c r="M939" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
     </row>
     <row r="940" spans="1:13" x14ac:dyDescent="0.25">
@@ -47909,37 +47918,37 @@
         <v>2645</v>
       </c>
       <c r="C940" t="s">
-        <v>2762</v>
+        <v>2765</v>
       </c>
       <c r="D940" t="s">
-        <v>2763</v>
+        <v>2766</v>
       </c>
       <c r="E940" t="s">
         <v>16</v>
       </c>
       <c r="F940" t="s">
+        <v>2767</v>
+      </c>
+      <c r="G940" t="s">
         <v>2768</v>
-      </c>
-      <c r="G940" t="s">
-        <v>2769</v>
       </c>
       <c r="H940">
         <v>2</v>
       </c>
       <c r="I940" t="s">
-        <v>2766</v>
+        <v>2770</v>
       </c>
       <c r="J940" t="s">
-        <v>2770</v>
+        <v>2400</v>
       </c>
       <c r="K940" t="s">
         <v>21</v>
       </c>
       <c r="L940" t="s">
-        <v>2771</v>
+        <v>721</v>
       </c>
       <c r="M940" t="s">
-        <v>23</v>
+        <v>630</v>
       </c>
     </row>
     <row r="941" spans="1:13" x14ac:dyDescent="0.25">
@@ -47950,25 +47959,25 @@
         <v>2645</v>
       </c>
       <c r="C941" t="s">
-        <v>2762</v>
+        <v>2765</v>
       </c>
       <c r="D941" t="s">
-        <v>2763</v>
+        <v>2766</v>
       </c>
       <c r="E941" t="s">
         <v>16</v>
       </c>
       <c r="F941" t="s">
-        <v>2768</v>
+        <v>2771</v>
       </c>
       <c r="G941" t="s">
-        <v>2769</v>
+        <v>2772</v>
       </c>
       <c r="H941">
         <v>2</v>
       </c>
       <c r="I941" t="s">
-        <v>2772</v>
+        <v>2769</v>
       </c>
       <c r="J941" t="s">
         <v>2773</v>
@@ -47977,10 +47986,10 @@
         <v>21</v>
       </c>
       <c r="L941" t="s">
-        <v>721</v>
+        <v>2774</v>
       </c>
       <c r="M941" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
     </row>
     <row r="942" spans="1:13" x14ac:dyDescent="0.25">
@@ -47991,28 +48000,28 @@
         <v>2645</v>
       </c>
       <c r="C942" t="s">
-        <v>2762</v>
+        <v>2765</v>
       </c>
       <c r="D942" t="s">
-        <v>2763</v>
+        <v>2766</v>
       </c>
       <c r="E942" t="s">
         <v>16</v>
       </c>
       <c r="F942" t="s">
-        <v>2768</v>
+        <v>2771</v>
       </c>
       <c r="G942" t="s">
-        <v>2769</v>
+        <v>2772</v>
       </c>
       <c r="H942">
         <v>2</v>
       </c>
       <c r="I942" t="s">
-        <v>2772</v>
+        <v>2775</v>
       </c>
       <c r="J942" t="s">
-        <v>2774</v>
+        <v>2776</v>
       </c>
       <c r="K942" t="s">
         <v>21</v>
@@ -48021,7 +48030,7 @@
         <v>721</v>
       </c>
       <c r="M942" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="943" spans="1:13" x14ac:dyDescent="0.25">
@@ -48032,37 +48041,37 @@
         <v>2645</v>
       </c>
       <c r="C943" t="s">
-        <v>2762</v>
+        <v>2765</v>
       </c>
       <c r="D943" t="s">
-        <v>2763</v>
+        <v>2766</v>
       </c>
       <c r="E943" t="s">
         <v>16</v>
       </c>
       <c r="F943" t="s">
-        <v>2775</v>
+        <v>2771</v>
       </c>
       <c r="G943" t="s">
-        <v>2776</v>
+        <v>2772</v>
       </c>
       <c r="H943">
         <v>2</v>
       </c>
       <c r="I943" t="s">
-        <v>2767</v>
+        <v>2775</v>
       </c>
       <c r="J943" t="s">
-        <v>2773</v>
+        <v>2777</v>
       </c>
       <c r="K943" t="s">
         <v>21</v>
       </c>
       <c r="L943" t="s">
-        <v>763</v>
+        <v>721</v>
       </c>
       <c r="M943" t="s">
-        <v>23</v>
+        <v>631</v>
       </c>
     </row>
     <row r="944" spans="1:13" x14ac:dyDescent="0.25">
@@ -48073,34 +48082,34 @@
         <v>2645</v>
       </c>
       <c r="C944" t="s">
-        <v>2762</v>
+        <v>2765</v>
       </c>
       <c r="D944" t="s">
-        <v>2763</v>
+        <v>2766</v>
       </c>
       <c r="E944" t="s">
         <v>16</v>
       </c>
       <c r="F944" t="s">
-        <v>2777</v>
+        <v>2778</v>
       </c>
       <c r="G944" t="s">
-        <v>2778</v>
+        <v>2779</v>
       </c>
       <c r="H944">
         <v>2</v>
       </c>
       <c r="I944" t="s">
-        <v>2767</v>
+        <v>2770</v>
       </c>
       <c r="J944" t="s">
-        <v>2376</v>
+        <v>2776</v>
       </c>
       <c r="K944" t="s">
         <v>21</v>
       </c>
       <c r="L944" t="s">
-        <v>721</v>
+        <v>763</v>
       </c>
       <c r="M944" t="s">
         <v>23</v>
@@ -48114,28 +48123,28 @@
         <v>2645</v>
       </c>
       <c r="C945" t="s">
-        <v>2762</v>
+        <v>2765</v>
       </c>
       <c r="D945" t="s">
-        <v>2763</v>
+        <v>2766</v>
       </c>
       <c r="E945" t="s">
         <v>16</v>
       </c>
       <c r="F945" t="s">
-        <v>2779</v>
+        <v>2780</v>
       </c>
       <c r="G945" t="s">
-        <v>2780</v>
+        <v>2781</v>
       </c>
       <c r="H945">
         <v>2</v>
       </c>
       <c r="I945" t="s">
-        <v>2772</v>
+        <v>2770</v>
       </c>
       <c r="J945" t="s">
-        <v>2781</v>
+        <v>2376</v>
       </c>
       <c r="K945" t="s">
         <v>21</v>
@@ -48155,34 +48164,34 @@
         <v>2645</v>
       </c>
       <c r="C946" t="s">
-        <v>2782</v>
+        <v>2765</v>
       </c>
       <c r="D946" t="s">
-        <v>2783</v>
+        <v>2766</v>
       </c>
       <c r="E946" t="s">
         <v>16</v>
       </c>
       <c r="F946" t="s">
-        <v>2784</v>
+        <v>2782</v>
       </c>
       <c r="G946" t="s">
-        <v>2785</v>
+        <v>2783</v>
       </c>
       <c r="H946">
         <v>2</v>
       </c>
       <c r="I946" t="s">
-        <v>964</v>
+        <v>2775</v>
       </c>
       <c r="J946" t="s">
-        <v>2786</v>
+        <v>2784</v>
       </c>
       <c r="K946" t="s">
         <v>21</v>
       </c>
       <c r="L946" t="s">
-        <v>2787</v>
+        <v>721</v>
       </c>
       <c r="M946" t="s">
         <v>23</v>
@@ -48196,34 +48205,34 @@
         <v>2645</v>
       </c>
       <c r="C947" t="s">
-        <v>2782</v>
+        <v>2785</v>
       </c>
       <c r="D947" t="s">
-        <v>2783</v>
+        <v>2786</v>
       </c>
       <c r="E947" t="s">
         <v>16</v>
       </c>
       <c r="F947" t="s">
+        <v>2787</v>
+      </c>
+      <c r="G947" t="s">
         <v>2788</v>
-      </c>
-      <c r="G947" t="s">
-        <v>2789</v>
       </c>
       <c r="H947">
         <v>2</v>
       </c>
       <c r="I947" t="s">
+        <v>964</v>
+      </c>
+      <c r="J947" t="s">
+        <v>2789</v>
+      </c>
+      <c r="K947" t="s">
+        <v>21</v>
+      </c>
+      <c r="L947" t="s">
         <v>2790</v>
-      </c>
-      <c r="J947" t="s">
-        <v>2791</v>
-      </c>
-      <c r="K947" t="s">
-        <v>21</v>
-      </c>
-      <c r="L947" t="s">
-        <v>2787</v>
       </c>
       <c r="M947" t="s">
         <v>23</v>
@@ -48237,34 +48246,34 @@
         <v>2645</v>
       </c>
       <c r="C948" t="s">
-        <v>2782</v>
+        <v>2785</v>
       </c>
       <c r="D948" t="s">
-        <v>2783</v>
+        <v>2786</v>
       </c>
       <c r="E948" t="s">
         <v>16</v>
       </c>
       <c r="F948" t="s">
+        <v>2791</v>
+      </c>
+      <c r="G948" t="s">
         <v>2792</v>
-      </c>
-      <c r="G948" t="s">
-        <v>2793</v>
       </c>
       <c r="H948">
         <v>2</v>
       </c>
       <c r="I948" t="s">
+        <v>2793</v>
+      </c>
+      <c r="J948" t="s">
         <v>2794</v>
       </c>
-      <c r="J948" t="s">
-        <v>2679</v>
-      </c>
       <c r="K948" t="s">
         <v>21</v>
       </c>
       <c r="L948" t="s">
-        <v>2787</v>
+        <v>2790</v>
       </c>
       <c r="M948" t="s">
         <v>23</v>
@@ -48272,40 +48281,40 @@
     </row>
     <row r="949" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
+        <v>2644</v>
+      </c>
+      <c r="B949" t="s">
+        <v>2645</v>
+      </c>
+      <c r="C949" t="s">
+        <v>2785</v>
+      </c>
+      <c r="D949" t="s">
+        <v>2786</v>
+      </c>
+      <c r="E949" t="s">
+        <v>16</v>
+      </c>
+      <c r="F949" t="s">
         <v>2795</v>
       </c>
-      <c r="B949" t="s">
+      <c r="G949" t="s">
         <v>2796</v>
       </c>
-      <c r="C949" t="s">
+      <c r="H949">
+        <v>2</v>
+      </c>
+      <c r="I949" t="s">
         <v>2797</v>
       </c>
-      <c r="D949" t="s">
-        <v>2798</v>
-      </c>
-      <c r="E949" t="s">
-        <v>2105</v>
-      </c>
-      <c r="F949" t="s">
-        <v>2799</v>
-      </c>
-      <c r="G949" t="s">
-        <v>2800</v>
-      </c>
-      <c r="H949">
-        <v>3</v>
-      </c>
-      <c r="I949" t="s">
-        <v>218</v>
-      </c>
       <c r="J949" t="s">
-        <v>2801</v>
+        <v>2682</v>
       </c>
       <c r="K949" t="s">
         <v>21</v>
       </c>
       <c r="L949" t="s">
-        <v>2802</v>
+        <v>2790</v>
       </c>
       <c r="M949" t="s">
         <v>23</v>
@@ -48313,25 +48322,25 @@
     </row>
     <row r="950" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B950" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C950" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D950" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E950" t="s">
-        <v>16</v>
+        <v>2105</v>
       </c>
       <c r="F950" t="s">
+        <v>2802</v>
+      </c>
+      <c r="G950" t="s">
         <v>2803</v>
-      </c>
-      <c r="G950" t="s">
-        <v>2804</v>
       </c>
       <c r="H950">
         <v>3</v>
@@ -48340,13 +48349,13 @@
         <v>218</v>
       </c>
       <c r="J950" t="s">
+        <v>2804</v>
+      </c>
+      <c r="K950" t="s">
+        <v>21</v>
+      </c>
+      <c r="L950" t="s">
         <v>2805</v>
-      </c>
-      <c r="K950" t="s">
-        <v>21</v>
-      </c>
-      <c r="L950" t="s">
-        <v>2081</v>
       </c>
       <c r="M950" t="s">
         <v>23</v>
@@ -48354,16 +48363,16 @@
     </row>
     <row r="951" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B951" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C951" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D951" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E951" t="s">
         <v>16</v>
@@ -48378,10 +48387,10 @@
         <v>3</v>
       </c>
       <c r="I951" t="s">
+        <v>218</v>
+      </c>
+      <c r="J951" t="s">
         <v>2808</v>
-      </c>
-      <c r="J951" t="s">
-        <v>2809</v>
       </c>
       <c r="K951" t="s">
         <v>21</v>
@@ -48395,40 +48404,40 @@
     </row>
     <row r="952" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B952" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C952" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D952" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E952" t="s">
-        <v>2105</v>
+        <v>16</v>
       </c>
       <c r="F952" t="s">
+        <v>2809</v>
+      </c>
+      <c r="G952" t="s">
         <v>2810</v>
       </c>
-      <c r="G952" t="s">
+      <c r="H952">
+        <v>3</v>
+      </c>
+      <c r="I952" t="s">
         <v>2811</v>
       </c>
-      <c r="H952">
-        <v>3</v>
-      </c>
-      <c r="I952" t="s">
+      <c r="J952" t="s">
         <v>2812</v>
       </c>
-      <c r="J952" t="s">
-        <v>2805</v>
-      </c>
       <c r="K952" t="s">
         <v>21</v>
       </c>
       <c r="L952" t="s">
-        <v>1982</v>
+        <v>2081</v>
       </c>
       <c r="M952" t="s">
         <v>23</v>
@@ -48436,19 +48445,19 @@
     </row>
     <row r="953" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B953" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C953" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D953" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E953" t="s">
-        <v>16</v>
+        <v>2105</v>
       </c>
       <c r="F953" t="s">
         <v>2813</v>
@@ -48463,13 +48472,13 @@
         <v>2815</v>
       </c>
       <c r="J953" t="s">
-        <v>2816</v>
+        <v>2808</v>
       </c>
       <c r="K953" t="s">
         <v>21</v>
       </c>
       <c r="L953" t="s">
-        <v>2081</v>
+        <v>1982</v>
       </c>
       <c r="M953" t="s">
         <v>23</v>
@@ -48477,40 +48486,40 @@
     </row>
     <row r="954" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B954" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C954" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D954" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E954" t="s">
         <v>16</v>
       </c>
       <c r="F954" t="s">
+        <v>2816</v>
+      </c>
+      <c r="G954" t="s">
         <v>2817</v>
       </c>
-      <c r="G954" t="s">
+      <c r="H954">
+        <v>3</v>
+      </c>
+      <c r="I954" t="s">
         <v>2818</v>
       </c>
-      <c r="H954">
-        <v>3</v>
-      </c>
-      <c r="I954" t="s">
-        <v>215</v>
-      </c>
       <c r="J954" t="s">
-        <v>116</v>
+        <v>2819</v>
       </c>
       <c r="K954" t="s">
         <v>21</v>
       </c>
       <c r="L954" t="s">
-        <v>116</v>
+        <v>2081</v>
       </c>
       <c r="M954" t="s">
         <v>23</v>
@@ -48518,31 +48527,31 @@
     </row>
     <row r="955" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B955" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C955" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D955" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E955" t="s">
         <v>16</v>
       </c>
       <c r="F955" t="s">
-        <v>2817</v>
+        <v>2820</v>
       </c>
       <c r="G955" t="s">
-        <v>2818</v>
+        <v>2821</v>
       </c>
       <c r="H955">
         <v>3</v>
       </c>
       <c r="I955" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="J955" t="s">
         <v>116</v>
@@ -48554,36 +48563,36 @@
         <v>116</v>
       </c>
       <c r="M955" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
     </row>
     <row r="956" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B956" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C956" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D956" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E956" t="s">
         <v>16</v>
       </c>
       <c r="F956" t="s">
-        <v>2817</v>
+        <v>2820</v>
       </c>
       <c r="G956" t="s">
-        <v>2818</v>
+        <v>2821</v>
       </c>
       <c r="H956">
         <v>3</v>
       </c>
       <c r="I956" t="s">
-        <v>2808</v>
+        <v>212</v>
       </c>
       <c r="J956" t="s">
         <v>116</v>
@@ -48595,36 +48604,36 @@
         <v>116</v>
       </c>
       <c r="M956" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="957" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B957" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C957" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D957" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E957" t="s">
         <v>16</v>
       </c>
       <c r="F957" t="s">
-        <v>2817</v>
+        <v>2820</v>
       </c>
       <c r="G957" t="s">
-        <v>2818</v>
+        <v>2821</v>
       </c>
       <c r="H957">
         <v>3</v>
       </c>
       <c r="I957" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="J957" t="s">
         <v>116</v>
@@ -48636,36 +48645,36 @@
         <v>116</v>
       </c>
       <c r="M957" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="958" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B958" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C958" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D958" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E958" t="s">
         <v>16</v>
       </c>
       <c r="F958" t="s">
-        <v>2817</v>
+        <v>2820</v>
       </c>
       <c r="G958" t="s">
-        <v>2818</v>
+        <v>2821</v>
       </c>
       <c r="H958">
         <v>3</v>
       </c>
       <c r="I958" t="s">
-        <v>218</v>
+        <v>2815</v>
       </c>
       <c r="J958" t="s">
         <v>116</v>
@@ -48677,30 +48686,30 @@
         <v>116</v>
       </c>
       <c r="M958" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="959" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B959" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C959" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D959" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E959" t="s">
         <v>16</v>
       </c>
       <c r="F959" t="s">
-        <v>2819</v>
+        <v>2820</v>
       </c>
       <c r="G959" t="s">
-        <v>2820</v>
+        <v>2821</v>
       </c>
       <c r="H959">
         <v>3</v>
@@ -48709,30 +48718,30 @@
         <v>218</v>
       </c>
       <c r="J959" t="s">
-        <v>2821</v>
+        <v>116</v>
       </c>
       <c r="K959" t="s">
         <v>21</v>
       </c>
       <c r="L959" t="s">
-        <v>2081</v>
+        <v>116</v>
       </c>
       <c r="M959" t="s">
-        <v>23</v>
+        <v>633</v>
       </c>
     </row>
     <row r="960" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B960" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C960" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D960" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E960" t="s">
         <v>16</v>
@@ -48747,7 +48756,7 @@
         <v>3</v>
       </c>
       <c r="I960" t="s">
-        <v>2812</v>
+        <v>218</v>
       </c>
       <c r="J960" t="s">
         <v>2824</v>
@@ -48756,7 +48765,7 @@
         <v>21</v>
       </c>
       <c r="L960" t="s">
-        <v>2802</v>
+        <v>2081</v>
       </c>
       <c r="M960" t="s">
         <v>23</v>
@@ -48764,16 +48773,16 @@
     </row>
     <row r="961" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B961" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C961" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D961" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E961" t="s">
         <v>16</v>
@@ -48788,16 +48797,16 @@
         <v>3</v>
       </c>
       <c r="I961" t="s">
-        <v>2808</v>
+        <v>2815</v>
       </c>
       <c r="J961" t="s">
-        <v>2824</v>
+        <v>2827</v>
       </c>
       <c r="K961" t="s">
         <v>21</v>
       </c>
       <c r="L961" t="s">
-        <v>2827</v>
+        <v>2805</v>
       </c>
       <c r="M961" t="s">
         <v>23</v>
@@ -48805,16 +48814,16 @@
     </row>
     <row r="962" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B962" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C962" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D962" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E962" t="s">
         <v>16</v>
@@ -48829,16 +48838,16 @@
         <v>3</v>
       </c>
       <c r="I962" t="s">
-        <v>212</v>
+        <v>2811</v>
       </c>
       <c r="J962" t="s">
-        <v>2801</v>
+        <v>2827</v>
       </c>
       <c r="K962" t="s">
         <v>21</v>
       </c>
       <c r="L962" t="s">
-        <v>2827</v>
+        <v>2830</v>
       </c>
       <c r="M962" t="s">
         <v>23</v>
@@ -48846,40 +48855,40 @@
     </row>
     <row r="963" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B963" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C963" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D963" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E963" t="s">
         <v>16</v>
       </c>
       <c r="F963" t="s">
+        <v>2831</v>
+      </c>
+      <c r="G963" t="s">
+        <v>2832</v>
+      </c>
+      <c r="H963">
+        <v>3</v>
+      </c>
+      <c r="I963" t="s">
+        <v>212</v>
+      </c>
+      <c r="J963" t="s">
+        <v>2804</v>
+      </c>
+      <c r="K963" t="s">
+        <v>21</v>
+      </c>
+      <c r="L963" t="s">
         <v>2830</v>
-      </c>
-      <c r="G963" t="s">
-        <v>2831</v>
-      </c>
-      <c r="H963">
-        <v>3</v>
-      </c>
-      <c r="I963" t="s">
-        <v>215</v>
-      </c>
-      <c r="J963" t="s">
-        <v>2809</v>
-      </c>
-      <c r="K963" t="s">
-        <v>21</v>
-      </c>
-      <c r="L963" t="s">
-        <v>1982</v>
       </c>
       <c r="M963" t="s">
         <v>23</v>
@@ -48887,40 +48896,40 @@
     </row>
     <row r="964" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B964" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C964" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D964" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E964" t="s">
         <v>16</v>
       </c>
       <c r="F964" t="s">
-        <v>2832</v>
+        <v>2833</v>
       </c>
       <c r="G964" t="s">
-        <v>2833</v>
+        <v>2834</v>
       </c>
       <c r="H964">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I964" t="s">
-        <v>116</v>
+        <v>215</v>
       </c>
       <c r="J964" t="s">
-        <v>116</v>
+        <v>2812</v>
       </c>
       <c r="K964" t="s">
         <v>21</v>
       </c>
       <c r="L964" t="s">
-        <v>116</v>
+        <v>1982</v>
       </c>
       <c r="M964" t="s">
         <v>23</v>
@@ -48928,25 +48937,25 @@
     </row>
     <row r="965" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B965" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C965" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D965" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E965" t="s">
         <v>16</v>
       </c>
       <c r="F965" t="s">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="G965" t="s">
-        <v>2835</v>
+        <v>2836</v>
       </c>
       <c r="H965">
         <v>6</v>
@@ -48969,40 +48978,40 @@
     </row>
     <row r="966" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B966" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C966" t="s">
-        <v>2797</v>
+        <v>2800</v>
       </c>
       <c r="D966" t="s">
-        <v>2798</v>
+        <v>2801</v>
       </c>
       <c r="E966" t="s">
         <v>16</v>
       </c>
       <c r="F966" t="s">
-        <v>2836</v>
+        <v>2837</v>
       </c>
       <c r="G966" t="s">
-        <v>2837</v>
+        <v>2838</v>
       </c>
       <c r="H966">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I966" t="s">
-        <v>2838</v>
+        <v>116</v>
       </c>
       <c r="J966" t="s">
-        <v>2821</v>
+        <v>116</v>
       </c>
       <c r="K966" t="s">
         <v>21</v>
       </c>
       <c r="L966" t="s">
-        <v>1982</v>
+        <v>116</v>
       </c>
       <c r="M966" t="s">
         <v>23</v>
@@ -49010,40 +49019,40 @@
     </row>
     <row r="967" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B967" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C967" t="s">
+        <v>2800</v>
+      </c>
+      <c r="D967" t="s">
+        <v>2801</v>
+      </c>
+      <c r="E967" t="s">
+        <v>16</v>
+      </c>
+      <c r="F967" t="s">
         <v>2839</v>
       </c>
-      <c r="D967" t="s">
+      <c r="G967" t="s">
         <v>2840</v>
       </c>
-      <c r="E967" t="s">
-        <v>2105</v>
-      </c>
-      <c r="F967" t="s">
+      <c r="H967">
+        <v>3</v>
+      </c>
+      <c r="I967" t="s">
         <v>2841</v>
       </c>
-      <c r="G967" t="s">
-        <v>2811</v>
-      </c>
-      <c r="H967">
-        <v>3</v>
-      </c>
-      <c r="I967" t="s">
-        <v>2842</v>
-      </c>
       <c r="J967" t="s">
-        <v>94</v>
+        <v>2824</v>
       </c>
       <c r="K967" t="s">
         <v>21</v>
       </c>
       <c r="L967" t="s">
-        <v>2081</v>
+        <v>1982</v>
       </c>
       <c r="M967" t="s">
         <v>23</v>
@@ -49051,25 +49060,25 @@
     </row>
     <row r="968" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B968" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C968" t="s">
-        <v>2839</v>
+        <v>2842</v>
       </c>
       <c r="D968" t="s">
-        <v>2840</v>
+        <v>2843</v>
       </c>
       <c r="E968" t="s">
-        <v>16</v>
+        <v>2105</v>
       </c>
       <c r="F968" t="s">
-        <v>2843</v>
+        <v>2844</v>
       </c>
       <c r="G968" t="s">
-        <v>2844</v>
+        <v>2814</v>
       </c>
       <c r="H968">
         <v>3</v>
@@ -49078,7 +49087,7 @@
         <v>2845</v>
       </c>
       <c r="J968" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K968" t="s">
         <v>21</v>
@@ -49092,16 +49101,16 @@
     </row>
     <row r="969" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
-        <v>2795</v>
+        <v>2798</v>
       </c>
       <c r="B969" t="s">
-        <v>2796</v>
+        <v>2799</v>
       </c>
       <c r="C969" t="s">
-        <v>2839</v>
+        <v>2842</v>
       </c>
       <c r="D969" t="s">
-        <v>2840</v>
+        <v>2843</v>
       </c>
       <c r="E969" t="s">
         <v>16</v>
@@ -49116,10 +49125,10 @@
         <v>3</v>
       </c>
       <c r="I969" t="s">
-        <v>215</v>
+        <v>2848</v>
       </c>
       <c r="J969" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="K969" t="s">
         <v>21</v>
@@ -49133,40 +49142,40 @@
     </row>
     <row r="970" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
-        <v>2848</v>
+        <v>2798</v>
       </c>
       <c r="B970" t="s">
-        <v>2849</v>
+        <v>2799</v>
       </c>
       <c r="C970" t="s">
-        <v>2848</v>
+        <v>2842</v>
       </c>
       <c r="D970" t="s">
-        <v>15</v>
+        <v>2843</v>
       </c>
       <c r="E970" t="s">
         <v>16</v>
       </c>
       <c r="F970" t="s">
+        <v>2849</v>
+      </c>
+      <c r="G970" t="s">
         <v>2850</v>
       </c>
-      <c r="G970" t="s">
-        <v>2851</v>
-      </c>
       <c r="H970">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I970" t="s">
-        <v>2852</v>
+        <v>215</v>
       </c>
       <c r="J970" t="s">
-        <v>2400</v>
+        <v>99</v>
       </c>
       <c r="K970" t="s">
         <v>21</v>
       </c>
       <c r="L970" t="s">
-        <v>2853</v>
+        <v>2081</v>
       </c>
       <c r="M970" t="s">
         <v>23</v>
@@ -49174,13 +49183,13 @@
     </row>
     <row r="971" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B971" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C971" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="D971" t="s">
         <v>15</v>
@@ -49189,25 +49198,25 @@
         <v>16</v>
       </c>
       <c r="F971" t="s">
+        <v>2853</v>
+      </c>
+      <c r="G971" t="s">
         <v>2854</v>
-      </c>
-      <c r="G971" t="s">
-        <v>2855</v>
       </c>
       <c r="H971">
         <v>2</v>
       </c>
       <c r="I971" t="s">
+        <v>2855</v>
+      </c>
+      <c r="J971" t="s">
+        <v>2400</v>
+      </c>
+      <c r="K971" t="s">
+        <v>21</v>
+      </c>
+      <c r="L971" t="s">
         <v>2856</v>
-      </c>
-      <c r="J971" t="s">
-        <v>2218</v>
-      </c>
-      <c r="K971" t="s">
-        <v>21</v>
-      </c>
-      <c r="L971" t="s">
-        <v>2853</v>
       </c>
       <c r="M971" t="s">
         <v>23</v>
@@ -49215,13 +49224,13 @@
     </row>
     <row r="972" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B972" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C972" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="D972" t="s">
         <v>15</v>
@@ -49239,16 +49248,16 @@
         <v>2</v>
       </c>
       <c r="I972" t="s">
-        <v>35</v>
+        <v>2859</v>
       </c>
       <c r="J972" t="s">
-        <v>2400</v>
+        <v>2218</v>
       </c>
       <c r="K972" t="s">
         <v>21</v>
       </c>
       <c r="L972" t="s">
-        <v>2859</v>
+        <v>2856</v>
       </c>
       <c r="M972" t="s">
         <v>23</v>
@@ -49256,13 +49265,13 @@
     </row>
     <row r="973" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B973" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C973" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="D973" t="s">
         <v>15</v>
@@ -49280,10 +49289,10 @@
         <v>2</v>
       </c>
       <c r="I973" t="s">
-        <v>1227</v>
+        <v>35</v>
       </c>
       <c r="J973" t="s">
-        <v>2218</v>
+        <v>2400</v>
       </c>
       <c r="K973" t="s">
         <v>21</v>
@@ -49297,13 +49306,13 @@
     </row>
     <row r="974" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B974" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C974" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="D974" t="s">
         <v>15</v>
@@ -49312,39 +49321,39 @@
         <v>16</v>
       </c>
       <c r="F974" t="s">
-        <v>2860</v>
+        <v>2863</v>
       </c>
       <c r="G974" t="s">
-        <v>2861</v>
+        <v>2864</v>
       </c>
       <c r="H974">
         <v>2</v>
       </c>
       <c r="I974" t="s">
-        <v>1691</v>
+        <v>1227</v>
       </c>
       <c r="J974" t="s">
-        <v>2227</v>
+        <v>2218</v>
       </c>
       <c r="K974" t="s">
         <v>21</v>
       </c>
       <c r="L974" t="s">
-        <v>37</v>
+        <v>2865</v>
       </c>
       <c r="M974" t="s">
-        <v>630</v>
+        <v>23</v>
       </c>
     </row>
     <row r="975" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B975" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C975" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="D975" t="s">
         <v>15</v>
@@ -49353,16 +49362,16 @@
         <v>16</v>
       </c>
       <c r="F975" t="s">
-        <v>2860</v>
+        <v>2863</v>
       </c>
       <c r="G975" t="s">
-        <v>2861</v>
+        <v>2864</v>
       </c>
       <c r="H975">
         <v>2</v>
       </c>
       <c r="I975" t="s">
-        <v>2863</v>
+        <v>1691</v>
       </c>
       <c r="J975" t="s">
         <v>2227</v>
@@ -49374,18 +49383,18 @@
         <v>37</v>
       </c>
       <c r="M975" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="976" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B976" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C976" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="D976" t="s">
         <v>15</v>
@@ -49394,39 +49403,39 @@
         <v>16</v>
       </c>
       <c r="F976" t="s">
-        <v>2860</v>
+        <v>2863</v>
       </c>
       <c r="G976" t="s">
-        <v>2861</v>
+        <v>2864</v>
       </c>
       <c r="H976">
         <v>2</v>
       </c>
       <c r="I976" t="s">
-        <v>2864</v>
+        <v>2866</v>
       </c>
       <c r="J976" t="s">
-        <v>2218</v>
+        <v>2227</v>
       </c>
       <c r="K976" t="s">
         <v>21</v>
       </c>
       <c r="L976" t="s">
-        <v>2862</v>
+        <v>37</v>
       </c>
       <c r="M976" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="977" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B977" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C977" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="D977" t="s">
         <v>15</v>
@@ -49435,39 +49444,39 @@
         <v>16</v>
       </c>
       <c r="F977" t="s">
-        <v>2860</v>
+        <v>2863</v>
       </c>
       <c r="G977" t="s">
-        <v>2861</v>
+        <v>2864</v>
       </c>
       <c r="H977">
         <v>2</v>
       </c>
       <c r="I977" t="s">
+        <v>2867</v>
+      </c>
+      <c r="J977" t="s">
+        <v>2218</v>
+      </c>
+      <c r="K977" t="s">
+        <v>21</v>
+      </c>
+      <c r="L977" t="s">
         <v>2865</v>
       </c>
-      <c r="J977" t="s">
-        <v>2222</v>
-      </c>
-      <c r="K977" t="s">
-        <v>21</v>
-      </c>
-      <c r="L977" t="s">
-        <v>2862</v>
-      </c>
       <c r="M977" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="978" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B978" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C978" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="D978" t="s">
         <v>15</v>
@@ -49476,39 +49485,39 @@
         <v>16</v>
       </c>
       <c r="F978" t="s">
-        <v>2866</v>
+        <v>2863</v>
       </c>
       <c r="G978" t="s">
-        <v>2867</v>
+        <v>2864</v>
       </c>
       <c r="H978">
         <v>2</v>
       </c>
       <c r="I978" t="s">
-        <v>2864</v>
+        <v>2868</v>
       </c>
       <c r="J978" t="s">
-        <v>2376</v>
+        <v>2222</v>
       </c>
       <c r="K978" t="s">
         <v>21</v>
       </c>
       <c r="L978" t="s">
-        <v>2862</v>
+        <v>2865</v>
       </c>
       <c r="M978" t="s">
-        <v>23</v>
+        <v>633</v>
       </c>
     </row>
     <row r="979" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B979" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C979" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="D979" t="s">
         <v>15</v>
@@ -49517,25 +49526,25 @@
         <v>16</v>
       </c>
       <c r="F979" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="G979" t="s">
-        <v>2869</v>
+        <v>2870</v>
       </c>
       <c r="H979">
         <v>2</v>
       </c>
       <c r="I979" t="s">
-        <v>2870</v>
+        <v>2867</v>
       </c>
       <c r="J979" t="s">
-        <v>2871</v>
+        <v>2376</v>
       </c>
       <c r="K979" t="s">
         <v>21</v>
       </c>
       <c r="L979" t="s">
-        <v>2862</v>
+        <v>2865</v>
       </c>
       <c r="M979" t="s">
         <v>23</v>
@@ -49543,40 +49552,40 @@
     </row>
     <row r="980" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B980" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C980" t="s">
-        <v>2872</v>
+        <v>2851</v>
       </c>
       <c r="D980" t="s">
-        <v>2873</v>
+        <v>15</v>
       </c>
       <c r="E980" t="s">
         <v>16</v>
       </c>
       <c r="F980" t="s">
-        <v>2874</v>
+        <v>2871</v>
       </c>
       <c r="G980" t="s">
-        <v>2875</v>
+        <v>2872</v>
       </c>
       <c r="H980">
         <v>2</v>
       </c>
       <c r="I980" t="s">
-        <v>2864</v>
+        <v>2873</v>
       </c>
       <c r="J980" t="s">
-        <v>2400</v>
+        <v>2874</v>
       </c>
       <c r="K980" t="s">
         <v>21</v>
       </c>
       <c r="L980" t="s">
-        <v>2862</v>
+        <v>2865</v>
       </c>
       <c r="M980" t="s">
         <v>23</v>
@@ -49584,40 +49593,40 @@
     </row>
     <row r="981" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B981" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C981" t="s">
-        <v>2872</v>
+        <v>2875</v>
       </c>
       <c r="D981" t="s">
-        <v>2873</v>
+        <v>2876</v>
       </c>
       <c r="E981" t="s">
         <v>16</v>
       </c>
       <c r="F981" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="G981" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="H981">
         <v>2</v>
       </c>
       <c r="I981" t="s">
-        <v>2878</v>
+        <v>2867</v>
       </c>
       <c r="J981" t="s">
-        <v>2227</v>
+        <v>2400</v>
       </c>
       <c r="K981" t="s">
         <v>21</v>
       </c>
       <c r="L981" t="s">
-        <v>2562</v>
+        <v>2865</v>
       </c>
       <c r="M981" t="s">
         <v>23</v>
@@ -49625,16 +49634,16 @@
     </row>
     <row r="982" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B982" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C982" t="s">
-        <v>2872</v>
+        <v>2875</v>
       </c>
       <c r="D982" t="s">
-        <v>2873</v>
+        <v>2876</v>
       </c>
       <c r="E982" t="s">
         <v>16</v>
@@ -49652,13 +49661,13 @@
         <v>2881</v>
       </c>
       <c r="J982" t="s">
-        <v>2376</v>
+        <v>2227</v>
       </c>
       <c r="K982" t="s">
         <v>21</v>
       </c>
       <c r="L982" t="s">
-        <v>2853</v>
+        <v>2562</v>
       </c>
       <c r="M982" t="s">
         <v>23</v>
@@ -49666,16 +49675,16 @@
     </row>
     <row r="983" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B983" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C983" t="s">
-        <v>2872</v>
+        <v>2875</v>
       </c>
       <c r="D983" t="s">
-        <v>2873</v>
+        <v>2876</v>
       </c>
       <c r="E983" t="s">
         <v>16</v>
@@ -49693,13 +49702,13 @@
         <v>2884</v>
       </c>
       <c r="J983" t="s">
-        <v>2400</v>
+        <v>2376</v>
       </c>
       <c r="K983" t="s">
         <v>21</v>
       </c>
       <c r="L983" t="s">
-        <v>2562</v>
+        <v>2856</v>
       </c>
       <c r="M983" t="s">
         <v>23</v>
@@ -49707,16 +49716,16 @@
     </row>
     <row r="984" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B984" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C984" t="s">
-        <v>2872</v>
+        <v>2875</v>
       </c>
       <c r="D984" t="s">
-        <v>2873</v>
+        <v>2876</v>
       </c>
       <c r="E984" t="s">
         <v>16</v>
@@ -49734,13 +49743,13 @@
         <v>2887</v>
       </c>
       <c r="J984" t="s">
-        <v>2227</v>
+        <v>2400</v>
       </c>
       <c r="K984" t="s">
         <v>21</v>
       </c>
       <c r="L984" t="s">
-        <v>2481</v>
+        <v>2562</v>
       </c>
       <c r="M984" t="s">
         <v>23</v>
@@ -49748,40 +49757,40 @@
     </row>
     <row r="985" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B985" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C985" t="s">
-        <v>2888</v>
+        <v>2875</v>
       </c>
       <c r="D985" t="s">
-        <v>2889</v>
+        <v>2876</v>
       </c>
       <c r="E985" t="s">
         <v>16</v>
       </c>
       <c r="F985" t="s">
-        <v>2890</v>
+        <v>2888</v>
       </c>
       <c r="G985" t="s">
-        <v>2891</v>
+        <v>2889</v>
       </c>
       <c r="H985">
         <v>2</v>
       </c>
       <c r="I985" t="s">
-        <v>2892</v>
+        <v>2890</v>
       </c>
       <c r="J985" t="s">
-        <v>2400</v>
+        <v>2227</v>
       </c>
       <c r="K985" t="s">
         <v>21</v>
       </c>
       <c r="L985" t="s">
-        <v>37</v>
+        <v>2481</v>
       </c>
       <c r="M985" t="s">
         <v>23</v>
@@ -49789,16 +49798,16 @@
     </row>
     <row r="986" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B986" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C986" t="s">
-        <v>2888</v>
+        <v>2891</v>
       </c>
       <c r="D986" t="s">
-        <v>2889</v>
+        <v>2892</v>
       </c>
       <c r="E986" t="s">
         <v>16</v>
@@ -49813,16 +49822,16 @@
         <v>2</v>
       </c>
       <c r="I986" t="s">
-        <v>2856</v>
+        <v>2895</v>
       </c>
       <c r="J986" t="s">
-        <v>2227</v>
+        <v>2400</v>
       </c>
       <c r="K986" t="s">
         <v>21</v>
       </c>
       <c r="L986" t="s">
-        <v>2853</v>
+        <v>37</v>
       </c>
       <c r="M986" t="s">
         <v>23</v>
@@ -49830,40 +49839,40 @@
     </row>
     <row r="987" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B987" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C987" t="s">
-        <v>2888</v>
+        <v>2891</v>
       </c>
       <c r="D987" t="s">
-        <v>2889</v>
+        <v>2892</v>
       </c>
       <c r="E987" t="s">
         <v>16</v>
       </c>
       <c r="F987" t="s">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="G987" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="H987">
         <v>2</v>
       </c>
       <c r="I987" t="s">
-        <v>2897</v>
+        <v>2859</v>
       </c>
       <c r="J987" t="s">
-        <v>2400</v>
+        <v>2227</v>
       </c>
       <c r="K987" t="s">
         <v>21</v>
       </c>
       <c r="L987" t="s">
-        <v>2481</v>
+        <v>2856</v>
       </c>
       <c r="M987" t="s">
         <v>23</v>
@@ -49871,16 +49880,16 @@
     </row>
     <row r="988" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B988" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C988" t="s">
-        <v>2888</v>
+        <v>2891</v>
       </c>
       <c r="D988" t="s">
-        <v>2889</v>
+        <v>2892</v>
       </c>
       <c r="E988" t="s">
         <v>16</v>
@@ -49895,16 +49904,16 @@
         <v>2</v>
       </c>
       <c r="I988" t="s">
-        <v>35</v>
+        <v>2900</v>
       </c>
       <c r="J988" t="s">
-        <v>2376</v>
+        <v>2400</v>
       </c>
       <c r="K988" t="s">
         <v>21</v>
       </c>
       <c r="L988" t="s">
-        <v>2859</v>
+        <v>2481</v>
       </c>
       <c r="M988" t="s">
         <v>23</v>
@@ -49912,40 +49921,40 @@
     </row>
     <row r="989" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B989" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C989" t="s">
-        <v>2888</v>
+        <v>2891</v>
       </c>
       <c r="D989" t="s">
-        <v>2889</v>
+        <v>2892</v>
       </c>
       <c r="E989" t="s">
         <v>16</v>
       </c>
       <c r="F989" t="s">
-        <v>2900</v>
+        <v>2901</v>
       </c>
       <c r="G989" t="s">
-        <v>459</v>
+        <v>2902</v>
       </c>
       <c r="H989">
         <v>2</v>
       </c>
       <c r="I989" t="s">
-        <v>2901</v>
+        <v>35</v>
       </c>
       <c r="J989" t="s">
-        <v>2218</v>
+        <v>2376</v>
       </c>
       <c r="K989" t="s">
         <v>21</v>
       </c>
       <c r="L989" t="s">
-        <v>2562</v>
+        <v>2862</v>
       </c>
       <c r="M989" t="s">
         <v>23</v>
@@ -49953,40 +49962,40 @@
     </row>
     <row r="990" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B990" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C990" t="s">
-        <v>2888</v>
+        <v>2891</v>
       </c>
       <c r="D990" t="s">
-        <v>2889</v>
+        <v>2892</v>
       </c>
       <c r="E990" t="s">
         <v>16</v>
       </c>
       <c r="F990" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="G990" t="s">
-        <v>2903</v>
+        <v>459</v>
       </c>
       <c r="H990">
         <v>2</v>
       </c>
       <c r="I990" t="s">
-        <v>2864</v>
+        <v>2904</v>
       </c>
       <c r="J990" t="s">
-        <v>2227</v>
+        <v>2218</v>
       </c>
       <c r="K990" t="s">
         <v>21</v>
       </c>
       <c r="L990" t="s">
-        <v>2862</v>
+        <v>2562</v>
       </c>
       <c r="M990" t="s">
         <v>23</v>
@@ -49994,40 +50003,40 @@
     </row>
     <row r="991" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B991" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C991" t="s">
-        <v>2904</v>
+        <v>2891</v>
       </c>
       <c r="D991" t="s">
-        <v>2905</v>
+        <v>2892</v>
       </c>
       <c r="E991" t="s">
         <v>16</v>
       </c>
       <c r="F991" t="s">
+        <v>2905</v>
+      </c>
+      <c r="G991" t="s">
         <v>2906</v>
-      </c>
-      <c r="G991" t="s">
-        <v>2907</v>
       </c>
       <c r="H991">
         <v>2</v>
       </c>
       <c r="I991" t="s">
-        <v>2897</v>
+        <v>2867</v>
       </c>
       <c r="J991" t="s">
-        <v>2908</v>
+        <v>2227</v>
       </c>
       <c r="K991" t="s">
         <v>21</v>
       </c>
       <c r="L991" t="s">
-        <v>2862</v>
+        <v>2865</v>
       </c>
       <c r="M991" t="s">
         <v>23</v>
@@ -50035,16 +50044,16 @@
     </row>
     <row r="992" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B992" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C992" t="s">
-        <v>2904</v>
+        <v>2907</v>
       </c>
       <c r="D992" t="s">
-        <v>2905</v>
+        <v>2908</v>
       </c>
       <c r="E992" t="s">
         <v>16</v>
@@ -50059,16 +50068,16 @@
         <v>2</v>
       </c>
       <c r="I992" t="s">
+        <v>2900</v>
+      </c>
+      <c r="J992" t="s">
         <v>2911</v>
       </c>
-      <c r="J992" t="s">
-        <v>2912</v>
-      </c>
       <c r="K992" t="s">
         <v>21</v>
       </c>
       <c r="L992" t="s">
-        <v>2862</v>
+        <v>2865</v>
       </c>
       <c r="M992" t="s">
         <v>23</v>
@@ -50076,40 +50085,40 @@
     </row>
     <row r="993" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B993" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C993" t="s">
-        <v>2904</v>
+        <v>2907</v>
       </c>
       <c r="D993" t="s">
-        <v>2905</v>
+        <v>2908</v>
       </c>
       <c r="E993" t="s">
         <v>16</v>
       </c>
       <c r="F993" t="s">
+        <v>2912</v>
+      </c>
+      <c r="G993" t="s">
         <v>2913</v>
-      </c>
-      <c r="G993" t="s">
-        <v>2914</v>
       </c>
       <c r="H993">
         <v>2</v>
       </c>
       <c r="I993" t="s">
-        <v>2892</v>
+        <v>2914</v>
       </c>
       <c r="J993" t="s">
-        <v>2222</v>
+        <v>2915</v>
       </c>
       <c r="K993" t="s">
         <v>21</v>
       </c>
       <c r="L993" t="s">
-        <v>37</v>
+        <v>2865</v>
       </c>
       <c r="M993" t="s">
         <v>23</v>
@@ -50117,40 +50126,40 @@
     </row>
     <row r="994" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B994" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C994" t="s">
-        <v>2904</v>
+        <v>2907</v>
       </c>
       <c r="D994" t="s">
-        <v>2905</v>
+        <v>2908</v>
       </c>
       <c r="E994" t="s">
         <v>16</v>
       </c>
       <c r="F994" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="G994" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="H994">
         <v>2</v>
       </c>
       <c r="I994" t="s">
-        <v>2917</v>
+        <v>2895</v>
       </c>
       <c r="J994" t="s">
-        <v>2376</v>
+        <v>2222</v>
       </c>
       <c r="K994" t="s">
         <v>21</v>
       </c>
       <c r="L994" t="s">
-        <v>2918</v>
+        <v>37</v>
       </c>
       <c r="M994" t="s">
         <v>23</v>
@@ -50158,40 +50167,40 @@
     </row>
     <row r="995" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B995" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C995" t="s">
-        <v>2904</v>
+        <v>2907</v>
       </c>
       <c r="D995" t="s">
-        <v>2905</v>
+        <v>2908</v>
       </c>
       <c r="E995" t="s">
         <v>16</v>
       </c>
       <c r="F995" t="s">
+        <v>2918</v>
+      </c>
+      <c r="G995" t="s">
         <v>2919</v>
-      </c>
-      <c r="G995" t="s">
-        <v>2920</v>
       </c>
       <c r="H995">
         <v>2</v>
       </c>
       <c r="I995" t="s">
-        <v>2911</v>
+        <v>2920</v>
       </c>
       <c r="J995" t="s">
-        <v>2227</v>
+        <v>2376</v>
       </c>
       <c r="K995" t="s">
         <v>21</v>
       </c>
       <c r="L995" t="s">
-        <v>2918</v>
+        <v>2921</v>
       </c>
       <c r="M995" t="s">
         <v>23</v>
@@ -50199,40 +50208,40 @@
     </row>
     <row r="996" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B996" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C996" t="s">
-        <v>2904</v>
+        <v>2907</v>
       </c>
       <c r="D996" t="s">
-        <v>2905</v>
+        <v>2908</v>
       </c>
       <c r="E996" t="s">
         <v>16</v>
       </c>
       <c r="F996" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="G996" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="H996">
         <v>2</v>
       </c>
       <c r="I996" t="s">
-        <v>2865</v>
+        <v>2914</v>
       </c>
       <c r="J996" t="s">
-        <v>2376</v>
+        <v>2227</v>
       </c>
       <c r="K996" t="s">
         <v>21</v>
       </c>
       <c r="L996" t="s">
-        <v>37</v>
+        <v>2921</v>
       </c>
       <c r="M996" t="s">
         <v>23</v>
@@ -50240,40 +50249,40 @@
     </row>
     <row r="997" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B997" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C997" t="s">
-        <v>2904</v>
+        <v>2907</v>
       </c>
       <c r="D997" t="s">
-        <v>2905</v>
+        <v>2908</v>
       </c>
       <c r="E997" t="s">
         <v>16</v>
       </c>
       <c r="F997" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="G997" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="H997">
         <v>2</v>
       </c>
       <c r="I997" t="s">
-        <v>2925</v>
+        <v>2868</v>
       </c>
       <c r="J997" t="s">
-        <v>2218</v>
+        <v>2376</v>
       </c>
       <c r="K997" t="s">
         <v>21</v>
       </c>
       <c r="L997" t="s">
-        <v>2918</v>
+        <v>37</v>
       </c>
       <c r="M997" t="s">
         <v>23</v>
@@ -50281,16 +50290,16 @@
     </row>
     <row r="998" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B998" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C998" t="s">
-        <v>2904</v>
+        <v>2907</v>
       </c>
       <c r="D998" t="s">
-        <v>2905</v>
+        <v>2908</v>
       </c>
       <c r="E998" t="s">
         <v>16</v>
@@ -50305,7 +50314,7 @@
         <v>2</v>
       </c>
       <c r="I998" t="s">
-        <v>2878</v>
+        <v>2928</v>
       </c>
       <c r="J998" t="s">
         <v>2218</v>
@@ -50314,7 +50323,7 @@
         <v>21</v>
       </c>
       <c r="L998" t="s">
-        <v>37</v>
+        <v>2921</v>
       </c>
       <c r="M998" t="s">
         <v>23</v>
@@ -50322,40 +50331,40 @@
     </row>
     <row r="999" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
-        <v>2848</v>
+        <v>2851</v>
       </c>
       <c r="B999" t="s">
-        <v>2849</v>
+        <v>2852</v>
       </c>
       <c r="C999" t="s">
-        <v>2904</v>
+        <v>2907</v>
       </c>
       <c r="D999" t="s">
-        <v>2905</v>
+        <v>2908</v>
       </c>
       <c r="E999" t="s">
         <v>16</v>
       </c>
       <c r="F999" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="G999" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="H999">
         <v>2</v>
       </c>
       <c r="I999" t="s">
-        <v>2865</v>
+        <v>2881</v>
       </c>
       <c r="J999" t="s">
-        <v>2400</v>
+        <v>2218</v>
       </c>
       <c r="K999" t="s">
         <v>21</v>
       </c>
       <c r="L999" t="s">
-        <v>2918</v>
+        <v>37</v>
       </c>
       <c r="M999" t="s">
         <v>23</v>
@@ -50363,40 +50372,40 @@
     </row>
     <row r="1000" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
-        <v>2930</v>
+        <v>2851</v>
       </c>
       <c r="B1000" t="s">
+        <v>2852</v>
+      </c>
+      <c r="C1000" t="s">
+        <v>2907</v>
+      </c>
+      <c r="D1000" t="s">
+        <v>2908</v>
+      </c>
+      <c r="E1000" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1000" t="s">
         <v>2931</v>
       </c>
-      <c r="C1000" t="s">
-        <v>2930</v>
-      </c>
-      <c r="D1000" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1000" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F1000" t="s">
+      <c r="G1000" t="s">
         <v>2932</v>
-      </c>
-      <c r="G1000" t="s">
-        <v>2933</v>
       </c>
       <c r="H1000">
         <v>2</v>
       </c>
       <c r="I1000" t="s">
-        <v>2934</v>
+        <v>2868</v>
       </c>
       <c r="J1000" t="s">
-        <v>2227</v>
+        <v>2400</v>
       </c>
       <c r="K1000" t="s">
         <v>21</v>
       </c>
       <c r="L1000" t="s">
-        <v>457</v>
+        <v>2921</v>
       </c>
       <c r="M1000" t="s">
         <v>23</v>
@@ -50404,40 +50413,40 @@
     </row>
     <row r="1001" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
-        <v>2930</v>
+        <v>2933</v>
       </c>
       <c r="B1001" t="s">
-        <v>2931</v>
+        <v>2934</v>
       </c>
       <c r="C1001" t="s">
+        <v>2933</v>
+      </c>
+      <c r="D1001" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1001" t="s">
+        <v>1594</v>
+      </c>
+      <c r="F1001" t="s">
         <v>2935</v>
       </c>
-      <c r="D1001" t="s">
+      <c r="G1001" t="s">
         <v>2936</v>
-      </c>
-      <c r="E1001" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1001" t="s">
-        <v>2937</v>
-      </c>
-      <c r="G1001" t="s">
-        <v>2938</v>
       </c>
       <c r="H1001">
         <v>2</v>
       </c>
       <c r="I1001" t="s">
-        <v>2939</v>
+        <v>2937</v>
       </c>
       <c r="J1001" t="s">
-        <v>2940</v>
+        <v>2227</v>
       </c>
       <c r="K1001" t="s">
         <v>21</v>
       </c>
       <c r="L1001" t="s">
-        <v>410</v>
+        <v>457</v>
       </c>
       <c r="M1001" t="s">
         <v>23</v>
@@ -50445,40 +50454,40 @@
     </row>
     <row r="1002" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
-        <v>2930</v>
+        <v>2933</v>
       </c>
       <c r="B1002" t="s">
-        <v>2931</v>
+        <v>2934</v>
       </c>
       <c r="C1002" t="s">
-        <v>2941</v>
+        <v>2938</v>
       </c>
       <c r="D1002" t="s">
-        <v>2942</v>
+        <v>2939</v>
       </c>
       <c r="E1002" t="s">
         <v>16</v>
       </c>
       <c r="F1002" t="s">
-        <v>2943</v>
+        <v>2940</v>
       </c>
       <c r="G1002" t="s">
-        <v>2944</v>
+        <v>2941</v>
       </c>
       <c r="H1002">
         <v>2</v>
       </c>
       <c r="I1002" t="s">
-        <v>2137</v>
+        <v>2942</v>
       </c>
       <c r="J1002" t="s">
-        <v>1732</v>
+        <v>2943</v>
       </c>
       <c r="K1002" t="s">
         <v>21</v>
       </c>
       <c r="L1002" t="s">
-        <v>2945</v>
+        <v>410</v>
       </c>
       <c r="M1002" t="s">
         <v>23</v>
@@ -50486,16 +50495,16 @@
     </row>
     <row r="1003" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
-        <v>2930</v>
+        <v>2933</v>
       </c>
       <c r="B1003" t="s">
-        <v>2931</v>
+        <v>2934</v>
       </c>
       <c r="C1003" t="s">
-        <v>2941</v>
+        <v>2944</v>
       </c>
       <c r="D1003" t="s">
-        <v>2942</v>
+        <v>2945</v>
       </c>
       <c r="E1003" t="s">
         <v>16</v>
@@ -50510,16 +50519,16 @@
         <v>2</v>
       </c>
       <c r="I1003" t="s">
+        <v>2137</v>
+      </c>
+      <c r="J1003" t="s">
+        <v>1732</v>
+      </c>
+      <c r="K1003" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1003" t="s">
         <v>2948</v>
-      </c>
-      <c r="J1003" t="s">
-        <v>2218</v>
-      </c>
-      <c r="K1003" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1003" t="s">
-        <v>410</v>
       </c>
       <c r="M1003" t="s">
         <v>23</v>
@@ -50527,16 +50536,16 @@
     </row>
     <row r="1004" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
-        <v>2930</v>
+        <v>2933</v>
       </c>
       <c r="B1004" t="s">
-        <v>2931</v>
+        <v>2934</v>
       </c>
       <c r="C1004" t="s">
-        <v>2941</v>
+        <v>2944</v>
       </c>
       <c r="D1004" t="s">
-        <v>2942</v>
+        <v>2945</v>
       </c>
       <c r="E1004" t="s">
         <v>16</v>
@@ -50554,13 +50563,13 @@
         <v>2951</v>
       </c>
       <c r="J1004" t="s">
-        <v>2940</v>
+        <v>2218</v>
       </c>
       <c r="K1004" t="s">
         <v>21</v>
       </c>
       <c r="L1004" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="M1004" t="s">
         <v>23</v>
@@ -50568,16 +50577,16 @@
     </row>
     <row r="1005" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
-        <v>2930</v>
+        <v>2933</v>
       </c>
       <c r="B1005" t="s">
-        <v>2931</v>
+        <v>2934</v>
       </c>
       <c r="C1005" t="s">
-        <v>2941</v>
+        <v>2944</v>
       </c>
       <c r="D1005" t="s">
-        <v>2942</v>
+        <v>2945</v>
       </c>
       <c r="E1005" t="s">
         <v>16</v>
@@ -50595,13 +50604,13 @@
         <v>2954</v>
       </c>
       <c r="J1005" t="s">
-        <v>1789</v>
+        <v>2943</v>
       </c>
       <c r="K1005" t="s">
         <v>21</v>
       </c>
       <c r="L1005" t="s">
-        <v>2955</v>
+        <v>457</v>
       </c>
       <c r="M1005" t="s">
         <v>23</v>
@@ -50609,40 +50618,40 @@
     </row>
     <row r="1006" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
-        <v>2930</v>
+        <v>2933</v>
       </c>
       <c r="B1006" t="s">
-        <v>2931</v>
+        <v>2934</v>
       </c>
       <c r="C1006" t="s">
-        <v>2956</v>
+        <v>2944</v>
       </c>
       <c r="D1006" t="s">
-        <v>2957</v>
+        <v>2945</v>
       </c>
       <c r="E1006" t="s">
         <v>16</v>
       </c>
       <c r="F1006" t="s">
-        <v>2958</v>
+        <v>2955</v>
       </c>
       <c r="G1006" t="s">
-        <v>2959</v>
+        <v>2956</v>
       </c>
       <c r="H1006">
         <v>2</v>
       </c>
       <c r="I1006" t="s">
-        <v>2960</v>
+        <v>2957</v>
       </c>
       <c r="J1006" t="s">
-        <v>2961</v>
+        <v>1789</v>
       </c>
       <c r="K1006" t="s">
         <v>21</v>
       </c>
       <c r="L1006" t="s">
-        <v>457</v>
+        <v>2958</v>
       </c>
       <c r="M1006" t="s">
         <v>23</v>
@@ -50650,40 +50659,40 @@
     </row>
     <row r="1007" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
-        <v>2930</v>
+        <v>2933</v>
       </c>
       <c r="B1007" t="s">
-        <v>2931</v>
+        <v>2934</v>
       </c>
       <c r="C1007" t="s">
-        <v>2956</v>
+        <v>2959</v>
       </c>
       <c r="D1007" t="s">
-        <v>2957</v>
+        <v>2960</v>
       </c>
       <c r="E1007" t="s">
         <v>16</v>
       </c>
       <c r="F1007" t="s">
+        <v>2961</v>
+      </c>
+      <c r="G1007" t="s">
         <v>2962</v>
-      </c>
-      <c r="G1007" t="s">
-        <v>2963</v>
       </c>
       <c r="H1007">
         <v>2</v>
       </c>
       <c r="I1007" t="s">
-        <v>2960</v>
+        <v>2963</v>
       </c>
       <c r="J1007" t="s">
-        <v>1732</v>
+        <v>2964</v>
       </c>
       <c r="K1007" t="s">
         <v>21</v>
       </c>
       <c r="L1007" t="s">
-        <v>2955</v>
+        <v>457</v>
       </c>
       <c r="M1007" t="s">
         <v>23</v>
@@ -50691,40 +50700,40 @@
     </row>
     <row r="1008" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
-        <v>2930</v>
+        <v>2933</v>
       </c>
       <c r="B1008" t="s">
-        <v>2931</v>
+        <v>2934</v>
       </c>
       <c r="C1008" t="s">
-        <v>2956</v>
+        <v>2959</v>
       </c>
       <c r="D1008" t="s">
-        <v>2957</v>
+        <v>2960</v>
       </c>
       <c r="E1008" t="s">
         <v>16</v>
       </c>
       <c r="F1008" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="G1008" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
       <c r="H1008">
         <v>2</v>
       </c>
       <c r="I1008" t="s">
-        <v>2934</v>
+        <v>2963</v>
       </c>
       <c r="J1008" t="s">
-        <v>2966</v>
+        <v>1732</v>
       </c>
       <c r="K1008" t="s">
         <v>21</v>
       </c>
       <c r="L1008" t="s">
-        <v>410</v>
+        <v>2958</v>
       </c>
       <c r="M1008" t="s">
         <v>23</v>
@@ -50732,16 +50741,16 @@
     </row>
     <row r="1009" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
-        <v>2930</v>
+        <v>2933</v>
       </c>
       <c r="B1009" t="s">
-        <v>2931</v>
+        <v>2934</v>
       </c>
       <c r="C1009" t="s">
-        <v>2956</v>
+        <v>2959</v>
       </c>
       <c r="D1009" t="s">
-        <v>2957</v>
+        <v>2960</v>
       </c>
       <c r="E1009" t="s">
         <v>16</v>
@@ -50756,16 +50765,16 @@
         <v>2</v>
       </c>
       <c r="I1009" t="s">
+        <v>2937</v>
+      </c>
+      <c r="J1009" t="s">
         <v>2969</v>
       </c>
-      <c r="J1009" t="s">
-        <v>2218</v>
-      </c>
       <c r="K1009" t="s">
         <v>21</v>
       </c>
       <c r="L1009" t="s">
-        <v>457</v>
+        <v>410</v>
       </c>
       <c r="M1009" t="s">
         <v>23</v>
@@ -50773,40 +50782,40 @@
     </row>
     <row r="1010" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
+        <v>2933</v>
+      </c>
+      <c r="B1010" t="s">
+        <v>2934</v>
+      </c>
+      <c r="C1010" t="s">
+        <v>2959</v>
+      </c>
+      <c r="D1010" t="s">
+        <v>2960</v>
+      </c>
+      <c r="E1010" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1010" t="s">
         <v>2970</v>
       </c>
-      <c r="B1010" t="s">
+      <c r="G1010" t="s">
         <v>2971</v>
       </c>
-      <c r="C1010" t="s">
-        <v>2970</v>
-      </c>
-      <c r="D1010" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1010" t="s">
-        <v>1594</v>
-      </c>
-      <c r="F1010" t="s">
+      <c r="H1010">
+        <v>2</v>
+      </c>
+      <c r="I1010" t="s">
         <v>2972</v>
       </c>
-      <c r="G1010" t="s">
-        <v>2973</v>
-      </c>
-      <c r="H1010">
-        <v>3</v>
-      </c>
-      <c r="I1010" t="s">
-        <v>2974</v>
-      </c>
       <c r="J1010" t="s">
-        <v>1623</v>
+        <v>2218</v>
       </c>
       <c r="K1010" t="s">
         <v>21</v>
       </c>
       <c r="L1010" t="s">
-        <v>2975</v>
+        <v>457</v>
       </c>
       <c r="M1010" t="s">
         <v>23</v>
@@ -50814,40 +50823,40 @@
     </row>
     <row r="1011" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="B1011" t="s">
-        <v>2971</v>
+        <v>2974</v>
       </c>
       <c r="C1011" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="D1011" t="s">
         <v>15</v>
       </c>
       <c r="E1011" t="s">
-        <v>16</v>
+        <v>1594</v>
       </c>
       <c r="F1011" t="s">
+        <v>2975</v>
+      </c>
+      <c r="G1011" t="s">
         <v>2976</v>
       </c>
-      <c r="G1011" t="s">
+      <c r="H1011">
+        <v>3</v>
+      </c>
+      <c r="I1011" t="s">
         <v>2977</v>
       </c>
-      <c r="H1011">
-        <v>3</v>
-      </c>
-      <c r="I1011" t="s">
-        <v>1020</v>
-      </c>
       <c r="J1011" t="s">
-        <v>2248</v>
+        <v>1623</v>
       </c>
       <c r="K1011" t="s">
         <v>21</v>
       </c>
       <c r="L1011" t="s">
-        <v>2975</v>
+        <v>2978</v>
       </c>
       <c r="M1011" t="s">
         <v>23</v>
@@ -50855,13 +50864,13 @@
     </row>
     <row r="1012" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="B1012" t="s">
-        <v>2971</v>
+        <v>2974</v>
       </c>
       <c r="C1012" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="D1012" t="s">
         <v>15</v>
@@ -50870,16 +50879,16 @@
         <v>16</v>
       </c>
       <c r="F1012" t="s">
-        <v>2978</v>
+        <v>2979</v>
       </c>
       <c r="G1012" t="s">
-        <v>2979</v>
+        <v>2980</v>
       </c>
       <c r="H1012">
         <v>3</v>
       </c>
       <c r="I1012" t="s">
-        <v>1295</v>
+        <v>1020</v>
       </c>
       <c r="J1012" t="s">
         <v>2248</v>
@@ -50888,7 +50897,7 @@
         <v>21</v>
       </c>
       <c r="L1012" t="s">
-        <v>2980</v>
+        <v>2978</v>
       </c>
       <c r="M1012" t="s">
         <v>23</v>
@@ -50896,19 +50905,19 @@
     </row>
     <row r="1013" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="B1013" t="s">
-        <v>2971</v>
+        <v>2974</v>
       </c>
       <c r="C1013" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="D1013" t="s">
         <v>15</v>
       </c>
       <c r="E1013" t="s">
-        <v>1594</v>
+        <v>16</v>
       </c>
       <c r="F1013" t="s">
         <v>2981</v>
@@ -50920,13 +50929,13 @@
         <v>3</v>
       </c>
       <c r="I1013" t="s">
-        <v>1020</v>
+        <v>1295</v>
       </c>
       <c r="J1013" t="s">
-        <v>162</v>
+        <v>2248</v>
       </c>
       <c r="K1013" t="s">
-        <v>324</v>
+        <v>21</v>
       </c>
       <c r="L1013" t="s">
         <v>2983</v>
@@ -50937,19 +50946,19 @@
     </row>
     <row r="1014" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="B1014" t="s">
-        <v>2971</v>
+        <v>2974</v>
       </c>
       <c r="C1014" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="D1014" t="s">
         <v>15</v>
       </c>
       <c r="E1014" t="s">
-        <v>2366</v>
+        <v>1594</v>
       </c>
       <c r="F1014" t="s">
         <v>2984</v>
@@ -50964,13 +50973,13 @@
         <v>1020</v>
       </c>
       <c r="J1014" t="s">
-        <v>288</v>
+        <v>163</v>
       </c>
       <c r="K1014" t="s">
         <v>324</v>
       </c>
       <c r="L1014" t="s">
-        <v>1296</v>
+        <v>2986</v>
       </c>
       <c r="M1014" t="s">
         <v>23</v>
@@ -50978,34 +50987,34 @@
     </row>
     <row r="1015" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="B1015" t="s">
-        <v>2971</v>
+        <v>2974</v>
       </c>
       <c r="C1015" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="D1015" t="s">
         <v>15</v>
       </c>
       <c r="E1015" t="s">
-        <v>1594</v>
+        <v>2366</v>
       </c>
       <c r="F1015" t="s">
-        <v>2986</v>
+        <v>2987</v>
       </c>
       <c r="G1015" t="s">
-        <v>2987</v>
+        <v>2988</v>
       </c>
       <c r="H1015">
         <v>3</v>
       </c>
       <c r="I1015" t="s">
-        <v>1295</v>
+        <v>1020</v>
       </c>
       <c r="J1015" t="s">
-        <v>70</v>
+        <v>288</v>
       </c>
       <c r="K1015" t="s">
         <v>324</v>
@@ -51019,13 +51028,13 @@
     </row>
     <row r="1016" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="B1016" t="s">
-        <v>2971</v>
+        <v>2974</v>
       </c>
       <c r="C1016" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="D1016" t="s">
         <v>15</v>
@@ -51034,19 +51043,19 @@
         <v>1594</v>
       </c>
       <c r="F1016" t="s">
-        <v>2988</v>
+        <v>2989</v>
       </c>
       <c r="G1016" t="s">
-        <v>2989</v>
+        <v>2990</v>
       </c>
       <c r="H1016">
         <v>3</v>
       </c>
       <c r="I1016" t="s">
-        <v>1668</v>
+        <v>1295</v>
       </c>
       <c r="J1016" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="K1016" t="s">
         <v>324</v>
@@ -51060,25 +51069,25 @@
     </row>
     <row r="1017" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="B1017" t="s">
-        <v>2971</v>
+        <v>2974</v>
       </c>
       <c r="C1017" t="s">
-        <v>2990</v>
+        <v>2973</v>
       </c>
       <c r="D1017" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1017" t="s">
+        <v>1594</v>
+      </c>
+      <c r="F1017" t="s">
         <v>2991</v>
       </c>
-      <c r="E1017" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1017" t="s">
+      <c r="G1017" t="s">
         <v>2992</v>
-      </c>
-      <c r="G1017" t="s">
-        <v>2993</v>
       </c>
       <c r="H1017">
         <v>3</v>
@@ -51087,13 +51096,13 @@
         <v>1668</v>
       </c>
       <c r="J1017" t="s">
-        <v>1215</v>
+        <v>86</v>
       </c>
       <c r="K1017" t="s">
-        <v>21</v>
+        <v>324</v>
       </c>
       <c r="L1017" t="s">
-        <v>2980</v>
+        <v>1296</v>
       </c>
       <c r="M1017" t="s">
         <v>23</v>
@@ -51101,40 +51110,40 @@
     </row>
     <row r="1018" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="B1018" t="s">
-        <v>2971</v>
+        <v>2974</v>
       </c>
       <c r="C1018" t="s">
-        <v>2990</v>
+        <v>2993</v>
       </c>
       <c r="D1018" t="s">
-        <v>2991</v>
+        <v>2994</v>
       </c>
       <c r="E1018" t="s">
         <v>16</v>
       </c>
       <c r="F1018" t="s">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="G1018" t="s">
-        <v>2995</v>
+        <v>2996</v>
       </c>
       <c r="H1018">
         <v>3</v>
       </c>
       <c r="I1018" t="s">
-        <v>1020</v>
+        <v>1668</v>
       </c>
       <c r="J1018" t="s">
-        <v>1638</v>
+        <v>1215</v>
       </c>
       <c r="K1018" t="s">
         <v>21</v>
       </c>
       <c r="L1018" t="s">
-        <v>2980</v>
+        <v>2983</v>
       </c>
       <c r="M1018" t="s">
         <v>23</v>
@@ -51142,40 +51151,40 @@
     </row>
     <row r="1019" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="B1019" t="s">
-        <v>2971</v>
+        <v>2974</v>
       </c>
       <c r="C1019" t="s">
-        <v>2996</v>
+        <v>2993</v>
       </c>
       <c r="D1019" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="E1019" t="s">
         <v>16</v>
       </c>
       <c r="F1019" t="s">
+        <v>2997</v>
+      </c>
+      <c r="G1019" t="s">
         <v>2998</v>
       </c>
-      <c r="G1019" t="s">
-        <v>2999</v>
-      </c>
       <c r="H1019">
         <v>3</v>
       </c>
       <c r="I1019" t="s">
-        <v>3000</v>
+        <v>1020</v>
       </c>
       <c r="J1019" t="s">
-        <v>1215</v>
+        <v>1638</v>
       </c>
       <c r="K1019" t="s">
         <v>21</v>
       </c>
       <c r="L1019" t="s">
-        <v>2975</v>
+        <v>2983</v>
       </c>
       <c r="M1019" t="s">
         <v>23</v>
@@ -51183,16 +51192,16 @@
     </row>
     <row r="1020" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
-        <v>2970</v>
+        <v>2973</v>
       </c>
       <c r="B1020" t="s">
-        <v>2971</v>
+        <v>2974</v>
       </c>
       <c r="C1020" t="s">
-        <v>2996</v>
+        <v>2999</v>
       </c>
       <c r="D1020" t="s">
-        <v>2997</v>
+        <v>3000</v>
       </c>
       <c r="E1020" t="s">
         <v>16</v>
@@ -51210,15 +51219,56 @@
         <v>3003</v>
       </c>
       <c r="J1020" t="s">
+        <v>1215</v>
+      </c>
+      <c r="K1020" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1020" t="s">
+        <v>2978</v>
+      </c>
+      <c r="M1020" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1021" t="s">
+        <v>2973</v>
+      </c>
+      <c r="B1021" t="s">
+        <v>2974</v>
+      </c>
+      <c r="C1021" t="s">
+        <v>2999</v>
+      </c>
+      <c r="D1021" t="s">
+        <v>3000</v>
+      </c>
+      <c r="E1021" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1021" t="s">
+        <v>3004</v>
+      </c>
+      <c r="G1021" t="s">
+        <v>3005</v>
+      </c>
+      <c r="H1021">
+        <v>3</v>
+      </c>
+      <c r="I1021" t="s">
+        <v>3006</v>
+      </c>
+      <c r="J1021" t="s">
         <v>1638</v>
       </c>
-      <c r="K1020" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1020" t="s">
-        <v>2975</v>
-      </c>
-      <c r="M1020" t="s">
+      <c r="K1021" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1021" t="s">
+        <v>2978</v>
+      </c>
+      <c r="M1021" t="s">
         <v>23</v>
       </c>
     </row>

--- a/actions_fetch/out/kookmin(2026-2).xlsx
+++ b/actions_fetch/out/kookmin(2026-2).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12469" uniqueCount="3161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12469" uniqueCount="3162">
   <si>
     <t>campusCode</t>
   </si>
@@ -2272,6 +2272,9 @@
     <t>09</t>
   </si>
   <si>
+    <t>화 15:00-16:00</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
@@ -3433,9 +3436,6 @@
     <t>강석민</t>
   </si>
   <si>
-    <t>형설관4층1호실</t>
-  </si>
-  <si>
     <t>36255</t>
   </si>
   <si>
@@ -8677,15 +8677,18 @@
     <t>국성화</t>
   </si>
   <si>
+    <t>예술관3층10호실,예술관3층17호실</t>
+  </si>
+  <si>
+    <t>697810a</t>
+  </si>
+  <si>
+    <t>플루트 전공실기Ⅱ</t>
+  </si>
+  <si>
     <t>예술관3층17호실</t>
   </si>
   <si>
-    <t>697810a</t>
-  </si>
-  <si>
-    <t>플루트 전공실기Ⅱ</t>
-  </si>
-  <si>
     <t>697850a</t>
   </si>
   <si>
@@ -8971,7 +8974,7 @@
     <t>사회적기업가정신과임팩트비즈니스</t>
   </si>
   <si>
-    <t>월 18:00-18:25,토 16:00-18:25</t>
+    <t>월 18:55-19:20,토 16:00-18:25</t>
   </si>
   <si>
     <t>7245802</t>
@@ -18714,19 +18717,19 @@
         <v>1</v>
       </c>
       <c r="I216" t="s">
-        <v>116</v>
+        <v>661</v>
       </c>
       <c r="J216" t="s">
-        <v>116</v>
+        <v>753</v>
       </c>
       <c r="K216" t="s">
         <v>21</v>
       </c>
       <c r="L216" t="s">
-        <v>116</v>
+        <v>663</v>
       </c>
       <c r="M216" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.25">
@@ -18746,25 +18749,25 @@
         <v>52</v>
       </c>
       <c r="F217" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="G217" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H217">
         <v>1</v>
       </c>
       <c r="I217" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="J217" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="K217" t="s">
         <v>21</v>
       </c>
       <c r="L217" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M217" t="s">
         <v>23</v>
@@ -18787,25 +18790,25 @@
         <v>52</v>
       </c>
       <c r="F218" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="G218" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H218">
         <v>1</v>
       </c>
       <c r="I218" t="s">
+        <v>760</v>
+      </c>
+      <c r="J218" t="s">
+        <v>761</v>
+      </c>
+      <c r="K218" t="s">
+        <v>21</v>
+      </c>
+      <c r="L218" t="s">
         <v>759</v>
-      </c>
-      <c r="J218" t="s">
-        <v>760</v>
-      </c>
-      <c r="K218" t="s">
-        <v>21</v>
-      </c>
-      <c r="L218" t="s">
-        <v>758</v>
       </c>
       <c r="M218" t="s">
         <v>635</v>
@@ -18828,10 +18831,10 @@
         <v>52</v>
       </c>
       <c r="F219" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="G219" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H219">
         <v>1</v>
@@ -18869,10 +18872,10 @@
         <v>52</v>
       </c>
       <c r="F220" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="G220" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H220">
         <v>1</v>
@@ -18910,10 +18913,10 @@
         <v>52</v>
       </c>
       <c r="F221" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="G221" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H221">
         <v>1</v>
@@ -18951,10 +18954,10 @@
         <v>52</v>
       </c>
       <c r="F222" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="G222" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H222">
         <v>1</v>
@@ -18992,10 +18995,10 @@
         <v>52</v>
       </c>
       <c r="F223" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="G223" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H223">
         <v>1</v>
@@ -19004,7 +19007,7 @@
         <v>692</v>
       </c>
       <c r="J223" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="K223" t="s">
         <v>21</v>
@@ -19033,10 +19036,10 @@
         <v>52</v>
       </c>
       <c r="F224" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="G224" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H224">
         <v>1</v>
@@ -19045,7 +19048,7 @@
         <v>692</v>
       </c>
       <c r="J224" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="K224" t="s">
         <v>21</v>
@@ -19074,25 +19077,25 @@
         <v>52</v>
       </c>
       <c r="F225" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G225" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H225">
         <v>2</v>
       </c>
       <c r="I225" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="J225" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K225" t="s">
         <v>21</v>
       </c>
       <c r="L225" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M225" t="s">
         <v>23</v>
@@ -19115,16 +19118,16 @@
         <v>52</v>
       </c>
       <c r="F226" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G226" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H226">
         <v>2</v>
       </c>
       <c r="I226" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="J226" t="s">
         <v>652</v>
@@ -19156,10 +19159,10 @@
         <v>52</v>
       </c>
       <c r="F227" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G227" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H227">
         <v>2</v>
@@ -19168,7 +19171,7 @@
         <v>716</v>
       </c>
       <c r="J227" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="K227" t="s">
         <v>21</v>
@@ -19197,10 +19200,10 @@
         <v>52</v>
       </c>
       <c r="F228" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G228" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H228">
         <v>2</v>
@@ -19209,7 +19212,7 @@
         <v>644</v>
       </c>
       <c r="J228" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K228" t="s">
         <v>21</v>
@@ -19238,25 +19241,25 @@
         <v>52</v>
       </c>
       <c r="F229" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G229" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H229">
         <v>2</v>
       </c>
       <c r="I229" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="J229" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="K229" t="s">
         <v>21</v>
       </c>
       <c r="L229" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M229" t="s">
         <v>643</v>
@@ -19279,10 +19282,10 @@
         <v>52</v>
       </c>
       <c r="F230" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G230" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H230">
         <v>2</v>
@@ -19320,10 +19323,10 @@
         <v>52</v>
       </c>
       <c r="F231" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G231" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H231">
         <v>2</v>
@@ -19332,13 +19335,13 @@
         <v>651</v>
       </c>
       <c r="J231" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K231" t="s">
         <v>21</v>
       </c>
       <c r="L231" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M231" t="s">
         <v>23</v>
@@ -19361,10 +19364,10 @@
         <v>52</v>
       </c>
       <c r="F232" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G232" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H232">
         <v>2</v>
@@ -19373,13 +19376,13 @@
         <v>651</v>
       </c>
       <c r="J232" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K232" t="s">
         <v>21</v>
       </c>
       <c r="L232" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M232" t="s">
         <v>635</v>
@@ -19402,10 +19405,10 @@
         <v>52</v>
       </c>
       <c r="F233" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G233" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H233">
         <v>2</v>
@@ -19420,7 +19423,7 @@
         <v>21</v>
       </c>
       <c r="L233" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M233" t="s">
         <v>638</v>
@@ -19443,10 +19446,10 @@
         <v>52</v>
       </c>
       <c r="F234" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G234" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H234">
         <v>2</v>
@@ -19461,7 +19464,7 @@
         <v>21</v>
       </c>
       <c r="L234" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M234" t="s">
         <v>641</v>
@@ -19484,10 +19487,10 @@
         <v>52</v>
       </c>
       <c r="F235" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G235" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H235">
         <v>2</v>
@@ -19496,13 +19499,13 @@
         <v>644</v>
       </c>
       <c r="J235" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K235" t="s">
         <v>21</v>
       </c>
       <c r="L235" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M235" t="s">
         <v>643</v>
@@ -19525,10 +19528,10 @@
         <v>52</v>
       </c>
       <c r="F236" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="G236" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H236">
         <v>2</v>
@@ -19537,13 +19540,13 @@
         <v>630</v>
       </c>
       <c r="J236" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K236" t="s">
         <v>21</v>
       </c>
       <c r="L236" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M236" t="s">
         <v>23</v>
@@ -19566,10 +19569,10 @@
         <v>52</v>
       </c>
       <c r="F237" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="G237" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H237">
         <v>2</v>
@@ -19578,7 +19581,7 @@
         <v>716</v>
       </c>
       <c r="J237" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K237" t="s">
         <v>21</v>
@@ -19607,19 +19610,19 @@
         <v>52</v>
       </c>
       <c r="F238" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="G238" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H238">
         <v>2</v>
       </c>
       <c r="I238" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="J238" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K238" t="s">
         <v>21</v>
@@ -19648,10 +19651,10 @@
         <v>52</v>
       </c>
       <c r="F239" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="G239" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H239">
         <v>2</v>
@@ -19666,7 +19669,7 @@
         <v>21</v>
       </c>
       <c r="L239" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M239" t="s">
         <v>641</v>
@@ -19689,10 +19692,10 @@
         <v>52</v>
       </c>
       <c r="F240" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="G240" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H240">
         <v>2</v>
@@ -19707,7 +19710,7 @@
         <v>21</v>
       </c>
       <c r="L240" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M240" t="s">
         <v>643</v>
@@ -19730,10 +19733,10 @@
         <v>52</v>
       </c>
       <c r="F241" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="G241" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H241">
         <v>2</v>
@@ -19748,7 +19751,7 @@
         <v>21</v>
       </c>
       <c r="L241" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M241" t="s">
         <v>646</v>
@@ -19771,10 +19774,10 @@
         <v>52</v>
       </c>
       <c r="F242" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G242" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H242">
         <v>2</v>
@@ -19783,7 +19786,7 @@
         <v>651</v>
       </c>
       <c r="J242" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="K242" t="s">
         <v>21</v>
@@ -19812,25 +19815,25 @@
         <v>52</v>
       </c>
       <c r="F243" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G243" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H243">
         <v>2</v>
       </c>
       <c r="I243" t="s">
+        <v>785</v>
+      </c>
+      <c r="J243" t="s">
         <v>784</v>
       </c>
-      <c r="J243" t="s">
-        <v>783</v>
-      </c>
       <c r="K243" t="s">
         <v>21</v>
       </c>
       <c r="L243" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M243" t="s">
         <v>635</v>
@@ -19853,10 +19856,10 @@
         <v>52</v>
       </c>
       <c r="F244" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G244" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H244">
         <v>2</v>
@@ -19865,7 +19868,7 @@
         <v>651</v>
       </c>
       <c r="J244" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="K244" t="s">
         <v>21</v>
@@ -19894,25 +19897,25 @@
         <v>52</v>
       </c>
       <c r="F245" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G245" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H245">
         <v>2</v>
       </c>
       <c r="I245" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="J245" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="K245" t="s">
         <v>21</v>
       </c>
       <c r="L245" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M245" t="s">
         <v>641</v>
@@ -19935,10 +19938,10 @@
         <v>52</v>
       </c>
       <c r="F246" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G246" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H246">
         <v>2</v>
@@ -19953,7 +19956,7 @@
         <v>21</v>
       </c>
       <c r="L246" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M246" t="s">
         <v>23</v>
@@ -19976,10 +19979,10 @@
         <v>52</v>
       </c>
       <c r="F247" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G247" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H247">
         <v>2</v>
@@ -19994,7 +19997,7 @@
         <v>21</v>
       </c>
       <c r="L247" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M247" t="s">
         <v>635</v>
@@ -20017,16 +20020,16 @@
         <v>52</v>
       </c>
       <c r="F248" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G248" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H248">
         <v>2</v>
       </c>
       <c r="I248" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="J248" t="s">
         <v>633</v>
@@ -20058,10 +20061,10 @@
         <v>52</v>
       </c>
       <c r="F249" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G249" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H249">
         <v>2</v>
@@ -20099,10 +20102,10 @@
         <v>52</v>
       </c>
       <c r="F250" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G250" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H250">
         <v>2</v>
@@ -20111,13 +20114,13 @@
         <v>651</v>
       </c>
       <c r="J250" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="K250" t="s">
         <v>21</v>
       </c>
       <c r="L250" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M250" t="s">
         <v>643</v>
@@ -20140,10 +20143,10 @@
         <v>52</v>
       </c>
       <c r="F251" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G251" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H251">
         <v>2</v>
@@ -20181,10 +20184,10 @@
         <v>52</v>
       </c>
       <c r="F252" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="G252" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H252">
         <v>2</v>
@@ -20193,13 +20196,13 @@
         <v>651</v>
       </c>
       <c r="J252" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="K252" t="s">
         <v>21</v>
       </c>
       <c r="L252" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M252" t="s">
         <v>647</v>
@@ -20222,10 +20225,10 @@
         <v>52</v>
       </c>
       <c r="F253" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G253" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H253">
         <v>2</v>
@@ -20234,7 +20237,7 @@
         <v>732</v>
       </c>
       <c r="J253" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="K253" t="s">
         <v>21</v>
@@ -20263,10 +20266,10 @@
         <v>52</v>
       </c>
       <c r="F254" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G254" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H254">
         <v>2</v>
@@ -20304,16 +20307,16 @@
         <v>52</v>
       </c>
       <c r="F255" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G255" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H255">
         <v>2</v>
       </c>
       <c r="I255" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="J255" t="s">
         <v>668</v>
@@ -20322,7 +20325,7 @@
         <v>21</v>
       </c>
       <c r="L255" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="M255" t="s">
         <v>638</v>
@@ -20345,10 +20348,10 @@
         <v>52</v>
       </c>
       <c r="F256" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G256" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H256">
         <v>2</v>
@@ -20386,10 +20389,10 @@
         <v>52</v>
       </c>
       <c r="F257" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G257" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H257">
         <v>2</v>
@@ -20427,16 +20430,16 @@
         <v>52</v>
       </c>
       <c r="F258" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G258" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H258">
         <v>2</v>
       </c>
       <c r="I258" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="J258" t="s">
         <v>656</v>
@@ -20445,7 +20448,7 @@
         <v>21</v>
       </c>
       <c r="L258" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="M258" t="s">
         <v>23</v>
@@ -20468,10 +20471,10 @@
         <v>52</v>
       </c>
       <c r="F259" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G259" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H259">
         <v>2</v>
@@ -20480,7 +20483,7 @@
         <v>658</v>
       </c>
       <c r="J259" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="K259" t="s">
         <v>21</v>
@@ -20509,16 +20512,16 @@
         <v>52</v>
       </c>
       <c r="F260" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G260" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H260">
         <v>2</v>
       </c>
       <c r="I260" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="J260" t="s">
         <v>659</v>
@@ -20527,7 +20530,7 @@
         <v>21</v>
       </c>
       <c r="L260" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="M260" t="s">
         <v>638</v>
@@ -20550,25 +20553,25 @@
         <v>52</v>
       </c>
       <c r="F261" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="G261" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H261">
         <v>2</v>
       </c>
       <c r="I261" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J261" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="K261" t="s">
         <v>21</v>
       </c>
       <c r="L261" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M261" t="s">
         <v>641</v>
@@ -20591,10 +20594,10 @@
         <v>52</v>
       </c>
       <c r="F262" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G262" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H262">
         <v>2</v>
@@ -20603,7 +20606,7 @@
         <v>658</v>
       </c>
       <c r="J262" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="K262" t="s">
         <v>21</v>
@@ -20632,16 +20635,16 @@
         <v>52</v>
       </c>
       <c r="F263" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G263" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H263">
         <v>2</v>
       </c>
       <c r="I263" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J263" t="s">
         <v>668</v>
@@ -20650,7 +20653,7 @@
         <v>21</v>
       </c>
       <c r="L263" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M263" t="s">
         <v>635</v>
@@ -20673,16 +20676,16 @@
         <v>52</v>
       </c>
       <c r="F264" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G264" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H264">
         <v>2</v>
       </c>
       <c r="I264" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J264" t="s">
         <v>664</v>
@@ -20691,7 +20694,7 @@
         <v>21</v>
       </c>
       <c r="L264" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M264" t="s">
         <v>638</v>
@@ -20714,10 +20717,10 @@
         <v>52</v>
       </c>
       <c r="F265" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G265" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H265">
         <v>2</v>
@@ -20726,7 +20729,7 @@
         <v>661</v>
       </c>
       <c r="J265" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="K265" t="s">
         <v>21</v>
@@ -20755,10 +20758,10 @@
         <v>52</v>
       </c>
       <c r="F266" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G266" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H266">
         <v>2</v>
@@ -20767,7 +20770,7 @@
         <v>658</v>
       </c>
       <c r="J266" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="K266" t="s">
         <v>21</v>
@@ -20796,10 +20799,10 @@
         <v>52</v>
       </c>
       <c r="F267" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G267" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H267">
         <v>2</v>
@@ -20837,10 +20840,10 @@
         <v>52</v>
       </c>
       <c r="F268" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="G268" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H268">
         <v>2</v>
@@ -20849,7 +20852,7 @@
         <v>658</v>
       </c>
       <c r="J268" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="K268" t="s">
         <v>21</v>
@@ -20878,25 +20881,25 @@
         <v>52</v>
       </c>
       <c r="F269" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G269" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H269">
         <v>2</v>
       </c>
       <c r="I269" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="J269" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="K269" t="s">
         <v>21</v>
       </c>
       <c r="L269" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="M269" t="s">
         <v>23</v>
@@ -20919,25 +20922,25 @@
         <v>52</v>
       </c>
       <c r="F270" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G270" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H270">
         <v>2</v>
       </c>
       <c r="I270" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="J270" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="K270" t="s">
         <v>21</v>
       </c>
       <c r="L270" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="M270" t="s">
         <v>635</v>
@@ -20960,16 +20963,16 @@
         <v>52</v>
       </c>
       <c r="F271" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G271" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H271">
         <v>2</v>
       </c>
       <c r="I271" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J271" t="s">
         <v>640</v>
@@ -20978,7 +20981,7 @@
         <v>21</v>
       </c>
       <c r="L271" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M271" t="s">
         <v>638</v>
@@ -21001,16 +21004,16 @@
         <v>52</v>
       </c>
       <c r="F272" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G272" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H272">
         <v>2</v>
       </c>
       <c r="I272" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="J272" t="s">
         <v>637</v>
@@ -21019,7 +21022,7 @@
         <v>21</v>
       </c>
       <c r="L272" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="M272" t="s">
         <v>641</v>
@@ -21042,10 +21045,10 @@
         <v>52</v>
       </c>
       <c r="F273" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G273" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H273">
         <v>2</v>
@@ -21083,10 +21086,10 @@
         <v>52</v>
       </c>
       <c r="F274" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G274" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H274">
         <v>2</v>
@@ -21095,7 +21098,7 @@
         <v>658</v>
       </c>
       <c r="J274" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K274" t="s">
         <v>21</v>
@@ -21124,10 +21127,10 @@
         <v>52</v>
       </c>
       <c r="F275" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G275" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H275">
         <v>2</v>
@@ -21165,10 +21168,10 @@
         <v>52</v>
       </c>
       <c r="F276" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G276" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H276">
         <v>2</v>
@@ -21177,13 +21180,13 @@
         <v>658</v>
       </c>
       <c r="J276" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="K276" t="s">
         <v>21</v>
       </c>
       <c r="L276" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="M276" t="s">
         <v>648</v>
@@ -21206,10 +21209,10 @@
         <v>52</v>
       </c>
       <c r="F277" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G277" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H277">
         <v>2</v>
@@ -21247,10 +21250,10 @@
         <v>52</v>
       </c>
       <c r="F278" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G278" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H278">
         <v>2</v>
@@ -21288,10 +21291,10 @@
         <v>52</v>
       </c>
       <c r="F279" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G279" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H279">
         <v>2</v>
@@ -21300,7 +21303,7 @@
         <v>667</v>
       </c>
       <c r="J279" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="K279" t="s">
         <v>21</v>
@@ -21329,25 +21332,25 @@
         <v>52</v>
       </c>
       <c r="F280" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G280" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H280">
         <v>2</v>
       </c>
       <c r="I280" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="J280" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="K280" t="s">
         <v>21</v>
       </c>
       <c r="L280" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="M280" t="s">
         <v>641</v>
@@ -21370,10 +21373,10 @@
         <v>52</v>
       </c>
       <c r="F281" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G281" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H281">
         <v>2</v>
@@ -21411,10 +21414,10 @@
         <v>52</v>
       </c>
       <c r="F282" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G282" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H282">
         <v>2</v>
@@ -21452,10 +21455,10 @@
         <v>52</v>
       </c>
       <c r="F283" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G283" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H283">
         <v>2</v>
@@ -21493,10 +21496,10 @@
         <v>52</v>
       </c>
       <c r="F284" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G284" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H284">
         <v>2</v>
@@ -21534,16 +21537,16 @@
         <v>52</v>
       </c>
       <c r="F285" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="G285" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H285">
         <v>2</v>
       </c>
       <c r="I285" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="J285" t="s">
         <v>633</v>
@@ -21575,10 +21578,10 @@
         <v>52</v>
       </c>
       <c r="F286" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="G286" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H286">
         <v>2</v>
@@ -21616,10 +21619,10 @@
         <v>52</v>
       </c>
       <c r="F287" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G287" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H287">
         <v>2</v>
@@ -21657,10 +21660,10 @@
         <v>52</v>
       </c>
       <c r="F288" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G288" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H288">
         <v>2</v>
@@ -21698,16 +21701,16 @@
         <v>52</v>
       </c>
       <c r="F289" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G289" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H289">
         <v>2</v>
       </c>
       <c r="I289" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="J289" t="s">
         <v>633</v>
@@ -21739,10 +21742,10 @@
         <v>52</v>
       </c>
       <c r="F290" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G290" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H290">
         <v>2</v>
@@ -21780,16 +21783,16 @@
         <v>52</v>
       </c>
       <c r="F291" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G291" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H291">
         <v>2</v>
       </c>
       <c r="I291" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="J291" t="s">
         <v>637</v>
@@ -21821,16 +21824,16 @@
         <v>52</v>
       </c>
       <c r="F292" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G292" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H292">
         <v>2</v>
       </c>
       <c r="I292" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="J292" t="s">
         <v>637</v>
@@ -21839,7 +21842,7 @@
         <v>21</v>
       </c>
       <c r="L292" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M292" t="s">
         <v>635</v>
@@ -21862,10 +21865,10 @@
         <v>52</v>
       </c>
       <c r="F293" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G293" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H293">
         <v>2</v>
@@ -21874,7 +21877,7 @@
         <v>698</v>
       </c>
       <c r="J293" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K293" t="s">
         <v>21</v>
@@ -21903,10 +21906,10 @@
         <v>52</v>
       </c>
       <c r="F294" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G294" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H294">
         <v>2</v>
@@ -21944,10 +21947,10 @@
         <v>52</v>
       </c>
       <c r="F295" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G295" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H295">
         <v>2</v>
@@ -21985,19 +21988,19 @@
         <v>52</v>
       </c>
       <c r="F296" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G296" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H296">
         <v>2</v>
       </c>
       <c r="I296" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="J296" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="K296" t="s">
         <v>21</v>
@@ -22026,10 +22029,10 @@
         <v>52</v>
       </c>
       <c r="F297" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="G297" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H297">
         <v>2</v>
@@ -22067,10 +22070,10 @@
         <v>52</v>
       </c>
       <c r="F298" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G298" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H298">
         <v>2</v>
@@ -22079,7 +22082,7 @@
         <v>692</v>
       </c>
       <c r="J298" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="K298" t="s">
         <v>21</v>
@@ -22108,10 +22111,10 @@
         <v>52</v>
       </c>
       <c r="F299" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G299" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H299">
         <v>2</v>
@@ -22149,10 +22152,10 @@
         <v>52</v>
       </c>
       <c r="F300" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="G300" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H300">
         <v>2</v>
@@ -22161,7 +22164,7 @@
         <v>692</v>
       </c>
       <c r="J300" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="K300" t="s">
         <v>21</v>
@@ -22190,10 +22193,10 @@
         <v>52</v>
       </c>
       <c r="F301" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="G301" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H301">
         <v>2</v>
@@ -22202,7 +22205,7 @@
         <v>692</v>
       </c>
       <c r="J301" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="K301" t="s">
         <v>21</v>
@@ -22231,10 +22234,10 @@
         <v>52</v>
       </c>
       <c r="F302" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G302" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H302">
         <v>2</v>
@@ -22243,7 +22246,7 @@
         <v>692</v>
       </c>
       <c r="J302" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="K302" t="s">
         <v>21</v>
@@ -22272,10 +22275,10 @@
         <v>52</v>
       </c>
       <c r="F303" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G303" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H303">
         <v>2</v>
@@ -22284,7 +22287,7 @@
         <v>709</v>
       </c>
       <c r="J303" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="K303" t="s">
         <v>21</v>
@@ -22313,10 +22316,10 @@
         <v>52</v>
       </c>
       <c r="F304" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G304" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H304">
         <v>2</v>
@@ -22325,7 +22328,7 @@
         <v>692</v>
       </c>
       <c r="J304" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="K304" t="s">
         <v>21</v>
@@ -22354,10 +22357,10 @@
         <v>52</v>
       </c>
       <c r="F305" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G305" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H305">
         <v>2</v>
@@ -22395,10 +22398,10 @@
         <v>52</v>
       </c>
       <c r="F306" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G306" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H306">
         <v>2</v>
@@ -22407,7 +22410,7 @@
         <v>709</v>
       </c>
       <c r="J306" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="K306" t="s">
         <v>21</v>
@@ -22436,10 +22439,10 @@
         <v>52</v>
       </c>
       <c r="F307" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G307" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H307">
         <v>2</v>
@@ -22477,10 +22480,10 @@
         <v>52</v>
       </c>
       <c r="F308" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="G308" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H308">
         <v>2</v>
@@ -22489,7 +22492,7 @@
         <v>692</v>
       </c>
       <c r="J308" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="K308" t="s">
         <v>21</v>
@@ -22518,10 +22521,10 @@
         <v>52</v>
       </c>
       <c r="F309" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="G309" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H309">
         <v>3</v>
@@ -22559,10 +22562,10 @@
         <v>52</v>
       </c>
       <c r="F310" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G310" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H310">
         <v>3</v>
@@ -22600,10 +22603,10 @@
         <v>52</v>
       </c>
       <c r="F311" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G311" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H311">
         <v>1</v>
@@ -22641,10 +22644,10 @@
         <v>52</v>
       </c>
       <c r="F312" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G312" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H312">
         <v>3</v>
@@ -22653,7 +22656,7 @@
         <v>702</v>
       </c>
       <c r="J312" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K312" t="s">
         <v>21</v>
@@ -22682,10 +22685,10 @@
         <v>52</v>
       </c>
       <c r="F313" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="G313" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H313">
         <v>3</v>
@@ -22694,13 +22697,13 @@
         <v>667</v>
       </c>
       <c r="J313" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="K313" t="s">
         <v>21</v>
       </c>
       <c r="L313" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M313" t="s">
         <v>23</v>
@@ -22723,10 +22726,10 @@
         <v>52</v>
       </c>
       <c r="F314" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="G314" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H314">
         <v>3</v>
@@ -22741,7 +22744,7 @@
         <v>21</v>
       </c>
       <c r="L314" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M314" t="s">
         <v>23</v>
@@ -22764,10 +22767,10 @@
         <v>52</v>
       </c>
       <c r="F315" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="G315" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H315">
         <v>3</v>
@@ -22776,13 +22779,13 @@
         <v>661</v>
       </c>
       <c r="J315" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K315" t="s">
         <v>21</v>
       </c>
       <c r="L315" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M315" t="s">
         <v>23</v>
@@ -22805,10 +22808,10 @@
         <v>52</v>
       </c>
       <c r="F316" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G316" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H316">
         <v>3</v>
@@ -22846,10 +22849,10 @@
         <v>52</v>
       </c>
       <c r="F317" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G317" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H317">
         <v>3</v>
@@ -22864,7 +22867,7 @@
         <v>21</v>
       </c>
       <c r="L317" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="M317" t="s">
         <v>23</v>
@@ -22887,25 +22890,25 @@
         <v>52</v>
       </c>
       <c r="F318" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G318" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H318">
         <v>3</v>
       </c>
       <c r="I318" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="J318" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="K318" t="s">
         <v>21</v>
       </c>
       <c r="L318" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M318" t="s">
         <v>23</v>
@@ -22928,10 +22931,10 @@
         <v>52</v>
       </c>
       <c r="F319" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="G319" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H319">
         <v>3</v>
@@ -22946,7 +22949,7 @@
         <v>21</v>
       </c>
       <c r="L319" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M319" t="s">
         <v>23</v>
@@ -22969,10 +22972,10 @@
         <v>52</v>
       </c>
       <c r="F320" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="G320" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H320">
         <v>3</v>
@@ -22981,7 +22984,7 @@
         <v>661</v>
       </c>
       <c r="J320" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="K320" t="s">
         <v>21</v>
@@ -23010,16 +23013,16 @@
         <v>52</v>
       </c>
       <c r="F321" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G321" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H321">
         <v>3</v>
       </c>
       <c r="I321" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="J321" t="s">
         <v>27</v>
@@ -23028,7 +23031,7 @@
         <v>21</v>
       </c>
       <c r="L321" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M321" t="s">
         <v>23</v>
@@ -23051,16 +23054,16 @@
         <v>52</v>
       </c>
       <c r="F322" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="G322" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H322">
         <v>3</v>
       </c>
       <c r="I322" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="J322" t="s">
         <v>563</v>
@@ -23069,7 +23072,7 @@
         <v>21</v>
       </c>
       <c r="L322" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M322" t="s">
         <v>23</v>
@@ -23092,10 +23095,10 @@
         <v>52</v>
       </c>
       <c r="F323" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="G323" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H323">
         <v>3</v>
@@ -23104,13 +23107,13 @@
         <v>116</v>
       </c>
       <c r="J323" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="K323" t="s">
         <v>21</v>
       </c>
       <c r="L323" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M323" t="s">
         <v>23</v>
@@ -23133,16 +23136,16 @@
         <v>52</v>
       </c>
       <c r="F324" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G324" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H324">
         <v>3</v>
       </c>
       <c r="I324" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="J324" t="s">
         <v>36</v>
@@ -23174,10 +23177,10 @@
         <v>52</v>
       </c>
       <c r="F325" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="G325" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H325">
         <v>3</v>
@@ -23192,7 +23195,7 @@
         <v>21</v>
       </c>
       <c r="L325" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="M325" t="s">
         <v>23</v>
@@ -23215,10 +23218,10 @@
         <v>52</v>
       </c>
       <c r="F326" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="G326" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H326">
         <v>3</v>
@@ -23233,7 +23236,7 @@
         <v>21</v>
       </c>
       <c r="L326" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M326" t="s">
         <v>23</v>
@@ -23256,25 +23259,25 @@
         <v>52</v>
       </c>
       <c r="F327" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="G327" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H327">
         <v>3</v>
       </c>
       <c r="I327" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="J327" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="K327" t="s">
         <v>21</v>
       </c>
       <c r="L327" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="M327" t="s">
         <v>23</v>
@@ -23297,16 +23300,16 @@
         <v>52</v>
       </c>
       <c r="F328" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G328" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H328">
         <v>3</v>
       </c>
       <c r="I328" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="J328" t="s">
         <v>567</v>
@@ -23315,7 +23318,7 @@
         <v>21</v>
       </c>
       <c r="L328" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M328" t="s">
         <v>23</v>
@@ -23338,25 +23341,25 @@
         <v>52</v>
       </c>
       <c r="F329" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="G329" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H329">
         <v>3</v>
       </c>
       <c r="I329" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="J329" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="K329" t="s">
         <v>21</v>
       </c>
       <c r="L329" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M329" t="s">
         <v>23</v>
@@ -23379,25 +23382,25 @@
         <v>52</v>
       </c>
       <c r="F330" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="G330" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H330">
         <v>3</v>
       </c>
       <c r="I330" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="J330" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K330" t="s">
         <v>21</v>
       </c>
       <c r="L330" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M330" t="s">
         <v>23</v>
@@ -23420,16 +23423,16 @@
         <v>52</v>
       </c>
       <c r="F331" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G331" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H331">
         <v>3</v>
       </c>
       <c r="I331" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="J331" t="s">
         <v>61</v>
@@ -23438,7 +23441,7 @@
         <v>21</v>
       </c>
       <c r="L331" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M331" t="s">
         <v>23</v>
@@ -23461,25 +23464,25 @@
         <v>52</v>
       </c>
       <c r="F332" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="G332" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H332">
         <v>3</v>
       </c>
       <c r="I332" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="J332" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="K332" t="s">
         <v>21</v>
       </c>
       <c r="L332" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M332" t="s">
         <v>23</v>
@@ -23502,25 +23505,25 @@
         <v>52</v>
       </c>
       <c r="F333" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="G333" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H333">
         <v>3</v>
       </c>
       <c r="I333" t="s">
-        <v>116</v>
+        <v>909</v>
       </c>
       <c r="J333" t="s">
-        <v>121</v>
+        <v>859</v>
       </c>
       <c r="K333" t="s">
         <v>21</v>
       </c>
       <c r="L333" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M333" t="s">
         <v>23</v>
@@ -23543,10 +23546,10 @@
         <v>52</v>
       </c>
       <c r="F334" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="G334" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H334">
         <v>3</v>
@@ -23584,10 +23587,10 @@
         <v>52</v>
       </c>
       <c r="F335" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="G335" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H335">
         <v>3</v>
@@ -23596,13 +23599,13 @@
         <v>722</v>
       </c>
       <c r="J335" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="K335" t="s">
         <v>21</v>
       </c>
       <c r="L335" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M335" t="s">
         <v>23</v>
@@ -23625,25 +23628,25 @@
         <v>52</v>
       </c>
       <c r="F336" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="G336" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H336">
         <v>3</v>
       </c>
       <c r="I336" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="J336" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="K336" t="s">
         <v>21</v>
       </c>
       <c r="L336" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M336" t="s">
         <v>23</v>
@@ -23666,10 +23669,10 @@
         <v>52</v>
       </c>
       <c r="F337" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G337" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H337">
         <v>3</v>
@@ -23684,7 +23687,7 @@
         <v>21</v>
       </c>
       <c r="L337" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="M337" t="s">
         <v>23</v>
@@ -23698,34 +23701,34 @@
         <v>14</v>
       </c>
       <c r="C338" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D338" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E338" t="s">
         <v>52</v>
       </c>
       <c r="F338" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="G338" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H338">
         <v>3</v>
       </c>
       <c r="I338" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="J338" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="K338" t="s">
         <v>21</v>
       </c>
       <c r="L338" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M338" t="s">
         <v>23</v>
@@ -23739,25 +23742,25 @@
         <v>14</v>
       </c>
       <c r="C339" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D339" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E339" t="s">
         <v>52</v>
       </c>
       <c r="F339" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="G339" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H339">
         <v>3</v>
       </c>
       <c r="I339" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="J339" t="s">
         <v>86</v>
@@ -23766,7 +23769,7 @@
         <v>21</v>
       </c>
       <c r="L339" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M339" t="s">
         <v>23</v>
@@ -23780,25 +23783,25 @@
         <v>14</v>
       </c>
       <c r="C340" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D340" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E340" t="s">
         <v>52</v>
       </c>
       <c r="F340" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="G340" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H340">
         <v>3</v>
       </c>
       <c r="I340" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="J340" t="s">
         <v>349</v>
@@ -23807,7 +23810,7 @@
         <v>21</v>
       </c>
       <c r="L340" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="M340" t="s">
         <v>23</v>
@@ -23821,34 +23824,34 @@
         <v>14</v>
       </c>
       <c r="C341" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D341" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E341" t="s">
         <v>52</v>
       </c>
       <c r="F341" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="G341" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H341">
         <v>3</v>
       </c>
       <c r="I341" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="J341" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="K341" t="s">
         <v>21</v>
       </c>
       <c r="L341" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="M341" t="s">
         <v>23</v>
@@ -23862,34 +23865,34 @@
         <v>14</v>
       </c>
       <c r="C342" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D342" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E342" t="s">
         <v>52</v>
       </c>
       <c r="F342" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="G342" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H342">
         <v>3</v>
       </c>
       <c r="I342" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="J342" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K342" t="s">
         <v>21</v>
       </c>
       <c r="L342" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M342" t="s">
         <v>23</v>
@@ -23903,34 +23906,34 @@
         <v>14</v>
       </c>
       <c r="C343" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D343" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E343" t="s">
         <v>52</v>
       </c>
       <c r="F343" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="G343" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H343">
         <v>3</v>
       </c>
       <c r="I343" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="J343" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K343" t="s">
         <v>21</v>
       </c>
       <c r="L343" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="M343" t="s">
         <v>23</v>
@@ -23944,19 +23947,19 @@
         <v>14</v>
       </c>
       <c r="C344" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D344" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E344" t="s">
         <v>52</v>
       </c>
       <c r="F344" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="G344" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H344">
         <v>3</v>
@@ -23965,13 +23968,13 @@
         <v>116</v>
       </c>
       <c r="J344" t="s">
-        <v>121</v>
+        <v>256</v>
       </c>
       <c r="K344" t="s">
         <v>21</v>
       </c>
       <c r="L344" t="s">
-        <v>929</v>
+        <v>942</v>
       </c>
       <c r="M344" t="s">
         <v>23</v>
@@ -23985,25 +23988,25 @@
         <v>14</v>
       </c>
       <c r="C345" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D345" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E345" t="s">
         <v>52</v>
       </c>
       <c r="F345" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="G345" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H345">
         <v>3</v>
       </c>
       <c r="I345" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="J345" t="s">
         <v>32</v>
@@ -24012,7 +24015,7 @@
         <v>21</v>
       </c>
       <c r="L345" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="M345" t="s">
         <v>23</v>
@@ -24026,34 +24029,34 @@
         <v>14</v>
       </c>
       <c r="C346" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D346" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E346" t="s">
         <v>52</v>
       </c>
       <c r="F346" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="G346" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H346">
         <v>3</v>
       </c>
       <c r="I346" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="J346" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K346" t="s">
         <v>21</v>
       </c>
       <c r="L346" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M346" t="s">
         <v>23</v>
@@ -24067,25 +24070,25 @@
         <v>14</v>
       </c>
       <c r="C347" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D347" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E347" t="s">
         <v>52</v>
       </c>
       <c r="F347" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="G347" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H347">
         <v>3</v>
       </c>
       <c r="I347" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="J347" t="s">
         <v>32</v>
@@ -24094,7 +24097,7 @@
         <v>21</v>
       </c>
       <c r="L347" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M347" t="s">
         <v>23</v>
@@ -24108,34 +24111,34 @@
         <v>14</v>
       </c>
       <c r="C348" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D348" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E348" t="s">
         <v>52</v>
       </c>
       <c r="F348" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G348" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H348">
         <v>3</v>
       </c>
       <c r="I348" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="J348" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="K348" t="s">
         <v>21</v>
       </c>
       <c r="L348" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M348" t="s">
         <v>23</v>
@@ -24149,25 +24152,25 @@
         <v>14</v>
       </c>
       <c r="C349" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D349" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E349" t="s">
         <v>52</v>
       </c>
       <c r="F349" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="G349" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H349">
         <v>3</v>
       </c>
       <c r="I349" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="J349" t="s">
         <v>534</v>
@@ -24176,7 +24179,7 @@
         <v>21</v>
       </c>
       <c r="L349" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="M349" t="s">
         <v>23</v>
@@ -24190,25 +24193,25 @@
         <v>14</v>
       </c>
       <c r="C350" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D350" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E350" t="s">
         <v>52</v>
       </c>
       <c r="F350" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="G350" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H350">
         <v>3</v>
       </c>
       <c r="I350" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="J350" t="s">
         <v>563</v>
@@ -24217,7 +24220,7 @@
         <v>21</v>
       </c>
       <c r="L350" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="M350" t="s">
         <v>23</v>
@@ -24231,34 +24234,34 @@
         <v>14</v>
       </c>
       <c r="C351" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D351" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E351" t="s">
         <v>52</v>
       </c>
       <c r="F351" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="G351" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H351">
         <v>3</v>
       </c>
       <c r="I351" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="J351" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="K351" t="s">
         <v>21</v>
       </c>
       <c r="L351" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="M351" t="s">
         <v>23</v>
@@ -24272,25 +24275,25 @@
         <v>14</v>
       </c>
       <c r="C352" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D352" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E352" t="s">
         <v>52</v>
       </c>
       <c r="F352" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="G352" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H352">
         <v>3</v>
       </c>
       <c r="I352" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="J352" t="s">
         <v>163</v>
@@ -24299,7 +24302,7 @@
         <v>21</v>
       </c>
       <c r="L352" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M352" t="s">
         <v>23</v>
@@ -24313,25 +24316,25 @@
         <v>14</v>
       </c>
       <c r="C353" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D353" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E353" t="s">
         <v>52</v>
       </c>
       <c r="F353" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="G353" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H353">
         <v>3</v>
       </c>
       <c r="I353" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="J353" t="s">
         <v>379</v>
@@ -24340,7 +24343,7 @@
         <v>21</v>
       </c>
       <c r="L353" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M353" t="s">
         <v>23</v>
@@ -24354,34 +24357,34 @@
         <v>14</v>
       </c>
       <c r="C354" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D354" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E354" t="s">
         <v>52</v>
       </c>
       <c r="F354" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="G354" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H354">
         <v>3</v>
       </c>
       <c r="I354" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="J354" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="K354" t="s">
         <v>21</v>
       </c>
       <c r="L354" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="M354" t="s">
         <v>23</v>
@@ -24395,25 +24398,25 @@
         <v>14</v>
       </c>
       <c r="C355" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D355" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="E355" t="s">
         <v>52</v>
       </c>
       <c r="F355" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="G355" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H355">
         <v>3</v>
       </c>
       <c r="I355" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="J355" t="s">
         <v>541</v>
@@ -24422,7 +24425,7 @@
         <v>21</v>
       </c>
       <c r="L355" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M355" t="s">
         <v>23</v>
@@ -24436,25 +24439,25 @@
         <v>14</v>
       </c>
       <c r="C356" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D356" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E356" t="s">
         <v>52</v>
       </c>
       <c r="F356" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="G356" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H356">
         <v>3</v>
       </c>
       <c r="I356" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="J356" t="s">
         <v>70</v>
@@ -24463,7 +24466,7 @@
         <v>21</v>
       </c>
       <c r="L356" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M356" t="s">
         <v>23</v>
@@ -24477,25 +24480,25 @@
         <v>14</v>
       </c>
       <c r="C357" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D357" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E357" t="s">
         <v>52</v>
       </c>
       <c r="F357" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="G357" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H357">
         <v>3</v>
       </c>
       <c r="I357" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="J357" t="s">
         <v>379</v>
@@ -24518,25 +24521,25 @@
         <v>14</v>
       </c>
       <c r="C358" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D358" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E358" t="s">
         <v>52</v>
       </c>
       <c r="F358" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="G358" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H358">
         <v>3</v>
       </c>
       <c r="I358" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="J358" t="s">
         <v>142</v>
@@ -24559,25 +24562,25 @@
         <v>14</v>
       </c>
       <c r="C359" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D359" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="E359" t="s">
         <v>52</v>
       </c>
       <c r="F359" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="G359" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H359">
         <v>3</v>
       </c>
       <c r="I359" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="J359" t="s">
         <v>56</v>
@@ -24600,25 +24603,25 @@
         <v>14</v>
       </c>
       <c r="C360" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D360" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E360" t="s">
         <v>52</v>
       </c>
       <c r="F360" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="G360" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H360">
         <v>3</v>
       </c>
       <c r="I360" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="J360" t="s">
         <v>86</v>
@@ -24627,7 +24630,7 @@
         <v>21</v>
       </c>
       <c r="L360" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M360" t="s">
         <v>23</v>
@@ -24641,34 +24644,34 @@
         <v>14</v>
       </c>
       <c r="C361" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D361" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E361" t="s">
         <v>52</v>
       </c>
       <c r="F361" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G361" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H361">
+        <v>3</v>
+      </c>
+      <c r="I361" t="s">
+        <v>1009</v>
+      </c>
+      <c r="J361" t="s">
+        <v>850</v>
+      </c>
+      <c r="K361" t="s">
+        <v>21</v>
+      </c>
+      <c r="L361" t="s">
         <v>1006</v>
-      </c>
-      <c r="G361" t="s">
-        <v>1007</v>
-      </c>
-      <c r="H361">
-        <v>3</v>
-      </c>
-      <c r="I361" t="s">
-        <v>1008</v>
-      </c>
-      <c r="J361" t="s">
-        <v>849</v>
-      </c>
-      <c r="K361" t="s">
-        <v>21</v>
-      </c>
-      <c r="L361" t="s">
-        <v>1005</v>
       </c>
       <c r="M361" t="s">
         <v>23</v>
@@ -24682,25 +24685,25 @@
         <v>14</v>
       </c>
       <c r="C362" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D362" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E362" t="s">
         <v>52</v>
       </c>
       <c r="F362" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="G362" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H362">
         <v>3</v>
       </c>
       <c r="I362" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="J362" t="s">
         <v>70</v>
@@ -24709,7 +24712,7 @@
         <v>21</v>
       </c>
       <c r="L362" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M362" t="s">
         <v>23</v>
@@ -24723,16 +24726,16 @@
         <v>14</v>
       </c>
       <c r="C363" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D363" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E363" t="s">
         <v>52</v>
       </c>
       <c r="F363" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="G363" t="s">
         <v>574</v>
@@ -24741,7 +24744,7 @@
         <v>3</v>
       </c>
       <c r="I363" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="J363" t="s">
         <v>163</v>
@@ -24750,7 +24753,7 @@
         <v>21</v>
       </c>
       <c r="L363" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M363" t="s">
         <v>23</v>
@@ -24764,34 +24767,34 @@
         <v>14</v>
       </c>
       <c r="C364" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D364" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E364" t="s">
         <v>52</v>
       </c>
       <c r="F364" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="G364" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H364">
         <v>3</v>
       </c>
       <c r="I364" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="J364" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="K364" t="s">
         <v>21</v>
       </c>
       <c r="L364" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="M364" t="s">
         <v>23</v>
@@ -24805,34 +24808,34 @@
         <v>14</v>
       </c>
       <c r="C365" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D365" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E365" t="s">
         <v>52</v>
       </c>
       <c r="F365" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="G365" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H365">
         <v>3</v>
       </c>
       <c r="I365" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="J365" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K365" t="s">
         <v>21</v>
       </c>
       <c r="L365" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M365" t="s">
         <v>23</v>
@@ -24846,25 +24849,25 @@
         <v>14</v>
       </c>
       <c r="C366" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D366" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E366" t="s">
         <v>52</v>
       </c>
       <c r="F366" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="G366" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H366">
         <v>3</v>
       </c>
       <c r="I366" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="J366" t="s">
         <v>90</v>
@@ -24873,7 +24876,7 @@
         <v>21</v>
       </c>
       <c r="L366" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="M366" t="s">
         <v>635</v>
@@ -24887,34 +24890,34 @@
         <v>14</v>
       </c>
       <c r="C367" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D367" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E367" t="s">
         <v>52</v>
       </c>
       <c r="F367" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="G367" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H367">
         <v>2</v>
       </c>
       <c r="I367" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="J367" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="K367" t="s">
         <v>21</v>
       </c>
       <c r="L367" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="M367" t="s">
         <v>23</v>
@@ -24928,34 +24931,34 @@
         <v>14</v>
       </c>
       <c r="C368" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D368" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E368" t="s">
         <v>52</v>
       </c>
       <c r="F368" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="G368" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H368">
         <v>3</v>
       </c>
       <c r="I368" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="J368" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="K368" t="s">
         <v>21</v>
       </c>
       <c r="L368" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="M368" t="s">
         <v>23</v>
@@ -24969,25 +24972,25 @@
         <v>14</v>
       </c>
       <c r="C369" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D369" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E369" t="s">
         <v>52</v>
       </c>
       <c r="F369" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="G369" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H369">
         <v>3</v>
       </c>
       <c r="I369" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="J369" t="s">
         <v>142</v>
@@ -24996,7 +24999,7 @@
         <v>21</v>
       </c>
       <c r="L369" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="M369" t="s">
         <v>23</v>
@@ -25010,34 +25013,34 @@
         <v>14</v>
       </c>
       <c r="C370" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D370" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E370" t="s">
         <v>52</v>
       </c>
       <c r="F370" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="G370" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H370">
         <v>3</v>
       </c>
       <c r="I370" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="J370" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="K370" t="s">
         <v>21</v>
       </c>
       <c r="L370" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="M370" t="s">
         <v>23</v>
@@ -25051,25 +25054,25 @@
         <v>14</v>
       </c>
       <c r="C371" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D371" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E371" t="s">
         <v>52</v>
       </c>
       <c r="F371" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G371" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H371">
         <v>3</v>
       </c>
       <c r="I371" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="J371" t="s">
         <v>94</v>
@@ -25078,7 +25081,7 @@
         <v>21</v>
       </c>
       <c r="L371" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="M371" t="s">
         <v>23</v>
@@ -25092,34 +25095,34 @@
         <v>14</v>
       </c>
       <c r="C372" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D372" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E372" t="s">
         <v>52</v>
       </c>
       <c r="F372" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="G372" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H372">
         <v>3</v>
       </c>
       <c r="I372" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="J372" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="K372" t="s">
         <v>21</v>
       </c>
       <c r="L372" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="M372" t="s">
         <v>23</v>
@@ -25133,34 +25136,34 @@
         <v>14</v>
       </c>
       <c r="C373" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D373" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E373" t="s">
         <v>52</v>
       </c>
       <c r="F373" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="G373" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H373">
         <v>3</v>
       </c>
       <c r="I373" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="J373" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K373" t="s">
         <v>21</v>
       </c>
       <c r="L373" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="M373" t="s">
         <v>23</v>
@@ -25174,25 +25177,25 @@
         <v>14</v>
       </c>
       <c r="C374" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D374" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E374" t="s">
         <v>52</v>
       </c>
       <c r="F374" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="G374" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H374">
         <v>3</v>
       </c>
       <c r="I374" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="J374" t="s">
         <v>278</v>
@@ -25201,7 +25204,7 @@
         <v>21</v>
       </c>
       <c r="L374" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M374" t="s">
         <v>635</v>
@@ -25215,25 +25218,25 @@
         <v>14</v>
       </c>
       <c r="C375" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D375" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E375" t="s">
         <v>52</v>
       </c>
       <c r="F375" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="G375" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H375">
         <v>3</v>
       </c>
       <c r="I375" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="J375" t="s">
         <v>99</v>
@@ -25242,7 +25245,7 @@
         <v>21</v>
       </c>
       <c r="L375" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M375" t="s">
         <v>23</v>
@@ -25256,25 +25259,25 @@
         <v>14</v>
       </c>
       <c r="C376" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D376" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E376" t="s">
         <v>52</v>
       </c>
       <c r="F376" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="G376" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H376">
         <v>3</v>
       </c>
       <c r="I376" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="J376" t="s">
         <v>94</v>
@@ -25283,7 +25286,7 @@
         <v>21</v>
       </c>
       <c r="L376" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M376" t="s">
         <v>635</v>
@@ -25297,25 +25300,25 @@
         <v>14</v>
       </c>
       <c r="C377" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D377" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E377" t="s">
         <v>52</v>
       </c>
       <c r="F377" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G377" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H377">
         <v>3</v>
       </c>
       <c r="I377" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="J377" t="s">
         <v>61</v>
@@ -25324,7 +25327,7 @@
         <v>21</v>
       </c>
       <c r="L377" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="M377" t="s">
         <v>23</v>
@@ -25338,25 +25341,25 @@
         <v>14</v>
       </c>
       <c r="C378" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D378" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E378" t="s">
         <v>52</v>
       </c>
       <c r="F378" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G378" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H378">
         <v>3</v>
       </c>
       <c r="I378" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="J378" t="s">
         <v>27</v>
@@ -25365,7 +25368,7 @@
         <v>21</v>
       </c>
       <c r="L378" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M378" t="s">
         <v>635</v>
@@ -25379,34 +25382,34 @@
         <v>14</v>
       </c>
       <c r="C379" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D379" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E379" t="s">
         <v>52</v>
       </c>
       <c r="F379" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="G379" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H379">
         <v>3</v>
       </c>
       <c r="I379" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="J379" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="K379" t="s">
         <v>21</v>
       </c>
       <c r="L379" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M379" t="s">
         <v>23</v>
@@ -25420,25 +25423,25 @@
         <v>14</v>
       </c>
       <c r="C380" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D380" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E380" t="s">
         <v>52</v>
       </c>
       <c r="F380" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="G380" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H380">
         <v>3</v>
       </c>
       <c r="I380" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="J380" t="s">
         <v>563</v>
@@ -25447,7 +25450,7 @@
         <v>21</v>
       </c>
       <c r="L380" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="M380" t="s">
         <v>23</v>
@@ -25461,34 +25464,34 @@
         <v>14</v>
       </c>
       <c r="C381" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D381" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E381" t="s">
         <v>52</v>
       </c>
       <c r="F381" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G381" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H381">
         <v>3</v>
       </c>
       <c r="I381" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="J381" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="K381" t="s">
         <v>21</v>
       </c>
       <c r="L381" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M381" t="s">
         <v>23</v>
@@ -25502,34 +25505,34 @@
         <v>14</v>
       </c>
       <c r="C382" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D382" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E382" t="s">
         <v>52</v>
       </c>
       <c r="F382" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G382" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H382">
         <v>3</v>
       </c>
       <c r="I382" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="J382" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K382" t="s">
         <v>21</v>
       </c>
       <c r="L382" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M382" t="s">
         <v>635</v>
@@ -25543,25 +25546,25 @@
         <v>14</v>
       </c>
       <c r="C383" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D383" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E383" t="s">
         <v>52</v>
       </c>
       <c r="F383" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="G383" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H383">
         <v>3</v>
       </c>
       <c r="I383" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="J383" t="s">
         <v>142</v>
@@ -25570,7 +25573,7 @@
         <v>21</v>
       </c>
       <c r="L383" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="M383" t="s">
         <v>23</v>
@@ -25584,25 +25587,25 @@
         <v>14</v>
       </c>
       <c r="C384" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D384" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E384" t="s">
         <v>52</v>
       </c>
       <c r="F384" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="G384" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H384">
         <v>3</v>
       </c>
       <c r="I384" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="J384" t="s">
         <v>142</v>
@@ -25611,7 +25614,7 @@
         <v>21</v>
       </c>
       <c r="L384" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="M384" t="s">
         <v>23</v>
@@ -25625,34 +25628,34 @@
         <v>14</v>
       </c>
       <c r="C385" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D385" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E385" t="s">
         <v>52</v>
       </c>
       <c r="F385" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="G385" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H385">
         <v>3</v>
       </c>
       <c r="I385" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="J385" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K385" t="s">
         <v>21</v>
       </c>
       <c r="L385" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="M385" t="s">
         <v>23</v>
@@ -25666,19 +25669,19 @@
         <v>14</v>
       </c>
       <c r="C386" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D386" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E386" t="s">
         <v>52</v>
       </c>
       <c r="F386" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="G386" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H386">
         <v>3</v>
@@ -25687,13 +25690,13 @@
         <v>622</v>
       </c>
       <c r="J386" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="K386" t="s">
         <v>21</v>
       </c>
       <c r="L386" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="M386" t="s">
         <v>23</v>
@@ -25707,25 +25710,25 @@
         <v>14</v>
       </c>
       <c r="C387" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D387" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E387" t="s">
         <v>52</v>
       </c>
       <c r="F387" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="G387" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H387">
         <v>3</v>
       </c>
       <c r="I387" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="J387" t="s">
         <v>27</v>
@@ -25734,7 +25737,7 @@
         <v>21</v>
       </c>
       <c r="L387" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="M387" t="s">
         <v>23</v>
@@ -25748,25 +25751,25 @@
         <v>14</v>
       </c>
       <c r="C388" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D388" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E388" t="s">
         <v>52</v>
       </c>
       <c r="F388" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="G388" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H388">
         <v>3</v>
       </c>
       <c r="I388" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="J388" t="s">
         <v>121</v>
@@ -25775,7 +25778,7 @@
         <v>21</v>
       </c>
       <c r="L388" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="M388" t="s">
         <v>23</v>
@@ -25789,34 +25792,34 @@
         <v>14</v>
       </c>
       <c r="C389" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D389" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="E389" t="s">
         <v>52</v>
       </c>
       <c r="F389" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="G389" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H389">
         <v>3</v>
       </c>
       <c r="I389" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="J389" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K389" t="s">
         <v>21</v>
       </c>
       <c r="L389" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="M389" t="s">
         <v>23</v>
@@ -25830,25 +25833,25 @@
         <v>14</v>
       </c>
       <c r="C390" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D390" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="E390" t="s">
         <v>52</v>
       </c>
       <c r="F390" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G390" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H390">
         <v>3</v>
       </c>
       <c r="I390" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J390" t="s">
         <v>86</v>
@@ -25857,7 +25860,7 @@
         <v>21</v>
       </c>
       <c r="L390" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="M390" t="s">
         <v>23</v>
@@ -25871,25 +25874,25 @@
         <v>14</v>
       </c>
       <c r="C391" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D391" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="E391" t="s">
         <v>52</v>
       </c>
       <c r="F391" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="G391" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H391">
         <v>3</v>
       </c>
       <c r="I391" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="J391" t="s">
         <v>563</v>
@@ -25898,7 +25901,7 @@
         <v>21</v>
       </c>
       <c r="L391" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="M391" t="s">
         <v>23</v>
@@ -25912,25 +25915,25 @@
         <v>14</v>
       </c>
       <c r="C392" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D392" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="E392" t="s">
         <v>52</v>
       </c>
       <c r="F392" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="G392" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H392">
         <v>3</v>
       </c>
       <c r="I392" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="J392" t="s">
         <v>121</v>
@@ -25939,7 +25942,7 @@
         <v>21</v>
       </c>
       <c r="L392" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="M392" t="s">
         <v>23</v>
@@ -25953,25 +25956,25 @@
         <v>14</v>
       </c>
       <c r="C393" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D393" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="E393" t="s">
         <v>52</v>
       </c>
       <c r="F393" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G393" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H393">
         <v>3</v>
       </c>
       <c r="I393" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="J393" t="s">
         <v>163</v>
@@ -25980,7 +25983,7 @@
         <v>21</v>
       </c>
       <c r="L393" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="M393" t="s">
         <v>23</v>
@@ -25994,25 +25997,25 @@
         <v>14</v>
       </c>
       <c r="C394" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D394" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E394" t="s">
         <v>52</v>
       </c>
       <c r="F394" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="G394" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H394">
         <v>3</v>
       </c>
       <c r="I394" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="J394" t="s">
         <v>56</v>
@@ -26035,25 +26038,25 @@
         <v>14</v>
       </c>
       <c r="C395" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D395" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="E395" t="s">
         <v>52</v>
       </c>
       <c r="F395" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G395" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H395">
         <v>3</v>
       </c>
       <c r="I395" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="J395" t="s">
         <v>142</v>
@@ -26076,25 +26079,25 @@
         <v>14</v>
       </c>
       <c r="C396" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D396" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="E396" t="s">
         <v>52</v>
       </c>
       <c r="F396" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="G396" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="H396">
         <v>3</v>
       </c>
       <c r="I396" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="J396" t="s">
         <v>358</v>
@@ -26103,7 +26106,7 @@
         <v>21</v>
       </c>
       <c r="L396" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="M396" t="s">
         <v>23</v>
@@ -26117,25 +26120,25 @@
         <v>14</v>
       </c>
       <c r="C397" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D397" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="E397" t="s">
         <v>52</v>
       </c>
       <c r="F397" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="G397" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="H397">
         <v>3</v>
       </c>
       <c r="I397" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="J397" t="s">
         <v>117</v>
@@ -26144,7 +26147,7 @@
         <v>21</v>
       </c>
       <c r="L397" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="M397" t="s">
         <v>23</v>
@@ -26158,25 +26161,25 @@
         <v>14</v>
       </c>
       <c r="C398" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D398" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="E398" t="s">
         <v>52</v>
       </c>
       <c r="F398" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="G398" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="H398">
         <v>3</v>
       </c>
       <c r="I398" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="J398" t="s">
         <v>354</v>
@@ -26185,7 +26188,7 @@
         <v>21</v>
       </c>
       <c r="L398" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="M398" t="s">
         <v>23</v>
@@ -26199,25 +26202,25 @@
         <v>14</v>
       </c>
       <c r="C399" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D399" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="E399" t="s">
         <v>52</v>
       </c>
       <c r="F399" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="G399" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H399">
         <v>3</v>
       </c>
       <c r="I399" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="J399" t="s">
         <v>349</v>
@@ -26226,7 +26229,7 @@
         <v>324</v>
       </c>
       <c r="L399" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="M399" t="s">
         <v>23</v>
@@ -26240,25 +26243,25 @@
         <v>14</v>
       </c>
       <c r="C400" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D400" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="E400" t="s">
         <v>52</v>
       </c>
       <c r="F400" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="G400" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="H400">
         <v>3</v>
       </c>
       <c r="I400" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="J400" t="s">
         <v>32</v>
@@ -26267,7 +26270,7 @@
         <v>324</v>
       </c>
       <c r="L400" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="M400" t="s">
         <v>23</v>
@@ -26281,25 +26284,25 @@
         <v>14</v>
       </c>
       <c r="C401" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D401" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="E401" t="s">
         <v>52</v>
       </c>
       <c r="F401" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="G401" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H401">
         <v>3</v>
       </c>
       <c r="I401" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="J401" t="s">
         <v>86</v>
@@ -26308,7 +26311,7 @@
         <v>21</v>
       </c>
       <c r="L401" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="M401" t="s">
         <v>23</v>
@@ -26425,7 +26428,7 @@
         <v>1152</v>
       </c>
       <c r="J404" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="K404" t="s">
         <v>21</v>
@@ -26548,7 +26551,7 @@
         <v>1166</v>
       </c>
       <c r="J407" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="K407" t="s">
         <v>21</v>
@@ -27365,7 +27368,7 @@
         <v>3</v>
       </c>
       <c r="I427" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="J427" t="s">
         <v>74</v>
@@ -27450,7 +27453,7 @@
         <v>1243</v>
       </c>
       <c r="J429" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K429" t="s">
         <v>21</v>
@@ -27866,7 +27869,7 @@
         <v>21</v>
       </c>
       <c r="L439" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M439" t="s">
         <v>23</v>
@@ -27942,7 +27945,7 @@
         <v>1284</v>
       </c>
       <c r="J441" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="K441" t="s">
         <v>21</v>
@@ -27989,7 +27992,7 @@
         <v>21</v>
       </c>
       <c r="L442" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M442" t="s">
         <v>23</v>
@@ -28030,7 +28033,7 @@
         <v>21</v>
       </c>
       <c r="L443" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M443" t="s">
         <v>23</v>
@@ -28065,7 +28068,7 @@
         <v>1297</v>
       </c>
       <c r="J444" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K444" t="s">
         <v>21</v>
@@ -28317,7 +28320,7 @@
         <v>21</v>
       </c>
       <c r="L450" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M450" t="s">
         <v>23</v>
@@ -28393,7 +28396,7 @@
         <v>1326</v>
       </c>
       <c r="J452" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K452" t="s">
         <v>21</v>
@@ -28762,7 +28765,7 @@
         <v>1354</v>
       </c>
       <c r="J461" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K461" t="s">
         <v>21</v>
@@ -29664,7 +29667,7 @@
         <v>1431</v>
       </c>
       <c r="J483" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K483" t="s">
         <v>324</v>
@@ -29951,7 +29954,7 @@
         <v>1456</v>
       </c>
       <c r="J490" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="K490" t="s">
         <v>324</v>
@@ -30238,7 +30241,7 @@
         <v>1476</v>
       </c>
       <c r="J497" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K497" t="s">
         <v>21</v>
@@ -30361,7 +30364,7 @@
         <v>1472</v>
       </c>
       <c r="J500" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K500" t="s">
         <v>324</v>
@@ -30484,7 +30487,7 @@
         <v>1456</v>
       </c>
       <c r="J503" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="K503" t="s">
         <v>21</v>
@@ -30853,7 +30856,7 @@
         <v>1530</v>
       </c>
       <c r="J512" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K512" t="s">
         <v>21</v>
@@ -31263,7 +31266,7 @@
         <v>1549</v>
       </c>
       <c r="J522" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K522" t="s">
         <v>21</v>
@@ -31386,7 +31389,7 @@
         <v>1579</v>
       </c>
       <c r="J525" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="K525" t="s">
         <v>21</v>
@@ -31427,7 +31430,7 @@
         <v>1545</v>
       </c>
       <c r="J526" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K526" t="s">
         <v>21</v>
@@ -31916,7 +31919,7 @@
         <v>0</v>
       </c>
       <c r="I538" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J538" t="s">
         <v>117</v>
@@ -31998,7 +32001,7 @@
         <v>3</v>
       </c>
       <c r="I540" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="J540" t="s">
         <v>358</v>
@@ -32121,7 +32124,7 @@
         <v>3</v>
       </c>
       <c r="I543" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="J543" t="s">
         <v>563</v>
@@ -32165,7 +32168,7 @@
         <v>1639</v>
       </c>
       <c r="J544" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K544" t="s">
         <v>21</v>
@@ -32367,10 +32370,10 @@
         <v>3</v>
       </c>
       <c r="I549" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="J549" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="K549" t="s">
         <v>21</v>
@@ -32572,7 +32575,7 @@
         <v>3</v>
       </c>
       <c r="I554" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="J554" t="s">
         <v>590</v>
@@ -32613,10 +32616,10 @@
         <v>3</v>
       </c>
       <c r="I555" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="J555" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="K555" t="s">
         <v>21</v>
@@ -32654,10 +32657,10 @@
         <v>3</v>
       </c>
       <c r="I556" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="J556" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="K556" t="s">
         <v>21</v>
@@ -32698,7 +32701,7 @@
         <v>1626</v>
       </c>
       <c r="J557" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="K557" t="s">
         <v>21</v>
@@ -32739,7 +32742,7 @@
         <v>1604</v>
       </c>
       <c r="J558" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K558" t="s">
         <v>21</v>
@@ -32862,7 +32865,7 @@
         <v>116</v>
       </c>
       <c r="J561" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="K561" t="s">
         <v>21</v>
@@ -32985,7 +32988,7 @@
         <v>69</v>
       </c>
       <c r="J564" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="K564" t="s">
         <v>21</v>
@@ -33026,7 +33029,7 @@
         <v>1679</v>
       </c>
       <c r="J565" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="K565" t="s">
         <v>21</v>
@@ -33146,7 +33149,7 @@
         <v>3</v>
       </c>
       <c r="I568" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="J568" t="s">
         <v>563</v>
@@ -33187,7 +33190,7 @@
         <v>3</v>
       </c>
       <c r="I569" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="J569" t="s">
         <v>349</v>
@@ -33231,7 +33234,7 @@
         <v>1527</v>
       </c>
       <c r="J570" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="K570" t="s">
         <v>21</v>
@@ -33600,7 +33603,7 @@
         <v>1730</v>
       </c>
       <c r="J579" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="K579" t="s">
         <v>21</v>
@@ -34912,7 +34915,7 @@
         <v>1849</v>
       </c>
       <c r="J611" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K611" t="s">
         <v>21</v>
@@ -35199,7 +35202,7 @@
         <v>1863</v>
       </c>
       <c r="J618" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="K618" t="s">
         <v>21</v>
@@ -37123,7 +37126,7 @@
         <v>2</v>
       </c>
       <c r="I665" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="J665" t="s">
         <v>1895</v>
@@ -37164,7 +37167,7 @@
         <v>2</v>
       </c>
       <c r="I666" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="J666" t="s">
         <v>1927</v>
@@ -38731,7 +38734,7 @@
         <v>21</v>
       </c>
       <c r="L704" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="M704" t="s">
         <v>23</v>
@@ -38977,7 +38980,7 @@
         <v>21</v>
       </c>
       <c r="L710" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="M710" t="s">
         <v>23</v>
@@ -40403,7 +40406,7 @@
         <v>3</v>
       </c>
       <c r="I745" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="J745" t="s">
         <v>1339</v>
@@ -40412,7 +40415,7 @@
         <v>21</v>
       </c>
       <c r="L745" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="M745" t="s">
         <v>23</v>
@@ -40526,7 +40529,7 @@
         <v>1.5</v>
       </c>
       <c r="I748" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="J748" t="s">
         <v>2159</v>
@@ -40699,7 +40702,7 @@
         <v>21</v>
       </c>
       <c r="L752" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="M752" t="s">
         <v>23</v>
@@ -40740,7 +40743,7 @@
         <v>21</v>
       </c>
       <c r="L753" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="M753" t="s">
         <v>23</v>
@@ -41431,7 +41434,7 @@
         <v>2314</v>
       </c>
       <c r="J770" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="K770" t="s">
         <v>21</v>
@@ -42576,7 +42579,7 @@
         <v>3</v>
       </c>
       <c r="I798" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="J798" t="s">
         <v>117</v>
@@ -42749,7 +42752,7 @@
         <v>21</v>
       </c>
       <c r="L802" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="M802" t="s">
         <v>23</v>
@@ -42790,7 +42793,7 @@
         <v>21</v>
       </c>
       <c r="L803" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="M803" t="s">
         <v>23</v>
@@ -42822,7 +42825,7 @@
         <v>3</v>
       </c>
       <c r="I804" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="J804" t="s">
         <v>590</v>
@@ -42831,7 +42834,7 @@
         <v>21</v>
       </c>
       <c r="L804" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="M804" t="s">
         <v>23</v>
@@ -43446,7 +43449,7 @@
         <v>21</v>
       </c>
       <c r="L819" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="M819" t="s">
         <v>23</v>
@@ -43938,7 +43941,7 @@
         <v>21</v>
       </c>
       <c r="L831" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M831" t="s">
         <v>23</v>
@@ -43979,7 +43982,7 @@
         <v>21</v>
       </c>
       <c r="L832" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M832" t="s">
         <v>23</v>
@@ -44225,7 +44228,7 @@
         <v>21</v>
       </c>
       <c r="L838" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M838" t="s">
         <v>23</v>
@@ -44389,7 +44392,7 @@
         <v>21</v>
       </c>
       <c r="L842" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M842" t="s">
         <v>23</v>
@@ -44430,7 +44433,7 @@
         <v>21</v>
       </c>
       <c r="L843" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M843" t="s">
         <v>23</v>
@@ -44471,7 +44474,7 @@
         <v>21</v>
       </c>
       <c r="L844" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M844" t="s">
         <v>23</v>
@@ -44594,7 +44597,7 @@
         <v>21</v>
       </c>
       <c r="L847" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M847" t="s">
         <v>23</v>
@@ -44676,7 +44679,7 @@
         <v>21</v>
       </c>
       <c r="L849" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M849" t="s">
         <v>23</v>
@@ -45900,7 +45903,7 @@
         <v>2698</v>
       </c>
       <c r="J879" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="K879" t="s">
         <v>21</v>
@@ -46023,7 +46026,7 @@
         <v>2675</v>
       </c>
       <c r="J882" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="K882" t="s">
         <v>21</v>
@@ -46105,7 +46108,7 @@
         <v>2713</v>
       </c>
       <c r="J884" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="K884" t="s">
         <v>21</v>
@@ -46146,7 +46149,7 @@
         <v>2715</v>
       </c>
       <c r="J885" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K885" t="s">
         <v>21</v>
@@ -47704,7 +47707,7 @@
         <v>2827</v>
       </c>
       <c r="J923" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="K923" t="s">
         <v>21</v>
@@ -47745,7 +47748,7 @@
         <v>2823</v>
       </c>
       <c r="J924" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="K924" t="s">
         <v>21</v>
@@ -47997,7 +48000,7 @@
         <v>21</v>
       </c>
       <c r="L930" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M930" t="s">
         <v>23</v>
@@ -48079,7 +48082,7 @@
         <v>21</v>
       </c>
       <c r="L932" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="M932" t="s">
         <v>23</v>
@@ -48120,7 +48123,7 @@
         <v>21</v>
       </c>
       <c r="L933" t="s">
-        <v>878</v>
+        <v>891</v>
       </c>
       <c r="M933" t="s">
         <v>23</v>
@@ -48161,7 +48164,7 @@
         <v>21</v>
       </c>
       <c r="L934" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M934" t="s">
         <v>23</v>
@@ -48278,7 +48281,7 @@
         <v>2873</v>
       </c>
       <c r="J937" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="K937" t="s">
         <v>21</v>
@@ -48319,7 +48322,7 @@
         <v>2859</v>
       </c>
       <c r="J938" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="K938" t="s">
         <v>21</v>
@@ -48530,7 +48533,7 @@
         <v>21</v>
       </c>
       <c r="L943" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="M943" t="s">
         <v>23</v>
@@ -48571,7 +48574,7 @@
         <v>21</v>
       </c>
       <c r="L944" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M944" t="s">
         <v>23</v>
@@ -48606,7 +48609,7 @@
         <v>2887</v>
       </c>
       <c r="J945" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="K945" t="s">
         <v>21</v>
@@ -48647,13 +48650,13 @@
         <v>116</v>
       </c>
       <c r="J946" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="K946" t="s">
         <v>21</v>
       </c>
       <c r="L946" t="s">
-        <v>2888</v>
+        <v>2891</v>
       </c>
       <c r="M946" t="s">
         <v>23</v>
@@ -48676,10 +48679,10 @@
         <v>16</v>
       </c>
       <c r="F947" t="s">
-        <v>2891</v>
+        <v>2892</v>
       </c>
       <c r="G947" t="s">
-        <v>2892</v>
+        <v>2893</v>
       </c>
       <c r="H947">
         <v>2</v>
@@ -48688,7 +48691,7 @@
         <v>2887</v>
       </c>
       <c r="J947" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="K947" t="s">
         <v>21</v>
@@ -48717,10 +48720,10 @@
         <v>16</v>
       </c>
       <c r="F948" t="s">
-        <v>2893</v>
+        <v>2894</v>
       </c>
       <c r="G948" t="s">
-        <v>2894</v>
+        <v>2895</v>
       </c>
       <c r="H948">
         <v>2</v>
@@ -48729,7 +48732,7 @@
         <v>2887</v>
       </c>
       <c r="J948" t="s">
-        <v>2895</v>
+        <v>2896</v>
       </c>
       <c r="K948" t="s">
         <v>21</v>
@@ -48758,25 +48761,25 @@
         <v>16</v>
       </c>
       <c r="F949" t="s">
-        <v>2896</v>
+        <v>2897</v>
       </c>
       <c r="G949" t="s">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="H949">
         <v>2</v>
       </c>
       <c r="I949" t="s">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="J949" t="s">
-        <v>2899</v>
+        <v>2900</v>
       </c>
       <c r="K949" t="s">
         <v>21</v>
       </c>
       <c r="L949" t="s">
-        <v>2900</v>
+        <v>2901</v>
       </c>
       <c r="M949" t="s">
         <v>23</v>
@@ -48790,16 +48793,16 @@
         <v>2814</v>
       </c>
       <c r="C950" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="D950" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="E950" t="s">
         <v>16</v>
       </c>
       <c r="F950" t="s">
-        <v>2903</v>
+        <v>2904</v>
       </c>
       <c r="G950" t="s">
         <v>2869</v>
@@ -48808,16 +48811,16 @@
         <v>2</v>
       </c>
       <c r="I950" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="J950" t="s">
-        <v>2905</v>
+        <v>2906</v>
       </c>
       <c r="K950" t="s">
         <v>21</v>
       </c>
       <c r="L950" t="s">
-        <v>2888</v>
+        <v>2891</v>
       </c>
       <c r="M950" t="s">
         <v>23</v>
@@ -48831,34 +48834,34 @@
         <v>2814</v>
       </c>
       <c r="C951" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="D951" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="E951" t="s">
         <v>16</v>
       </c>
       <c r="F951" t="s">
-        <v>2906</v>
+        <v>2907</v>
       </c>
       <c r="G951" t="s">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="H951">
         <v>2</v>
       </c>
       <c r="I951" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="J951" t="s">
-        <v>2909</v>
+        <v>2910</v>
       </c>
       <c r="K951" t="s">
         <v>21</v>
       </c>
       <c r="L951" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M951" t="s">
         <v>23</v>
@@ -48872,16 +48875,16 @@
         <v>2814</v>
       </c>
       <c r="C952" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="D952" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="E952" t="s">
         <v>16</v>
       </c>
       <c r="F952" t="s">
-        <v>2910</v>
+        <v>2911</v>
       </c>
       <c r="G952" t="s">
         <v>2872</v>
@@ -48890,16 +48893,16 @@
         <v>2</v>
       </c>
       <c r="I952" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="J952" t="s">
-        <v>2911</v>
+        <v>2912</v>
       </c>
       <c r="K952" t="s">
         <v>21</v>
       </c>
       <c r="L952" t="s">
-        <v>2888</v>
+        <v>2891</v>
       </c>
       <c r="M952" t="s">
         <v>23</v>
@@ -48913,16 +48916,16 @@
         <v>2814</v>
       </c>
       <c r="C953" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="D953" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="E953" t="s">
         <v>16</v>
       </c>
       <c r="F953" t="s">
-        <v>2912</v>
+        <v>2913</v>
       </c>
       <c r="G953" t="s">
         <v>2876</v>
@@ -48931,16 +48934,16 @@
         <v>2</v>
       </c>
       <c r="I953" t="s">
-        <v>2913</v>
+        <v>2914</v>
       </c>
       <c r="J953" t="s">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="K953" t="s">
         <v>21</v>
       </c>
       <c r="L953" t="s">
-        <v>2888</v>
+        <v>2891</v>
       </c>
       <c r="M953" t="s">
         <v>23</v>
@@ -48954,34 +48957,34 @@
         <v>2814</v>
       </c>
       <c r="C954" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="D954" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="E954" t="s">
         <v>16</v>
       </c>
       <c r="F954" t="s">
-        <v>2915</v>
+        <v>2916</v>
       </c>
       <c r="G954" t="s">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="H954">
         <v>2</v>
       </c>
       <c r="I954" t="s">
-        <v>2908</v>
+        <v>2909</v>
       </c>
       <c r="J954" t="s">
-        <v>2917</v>
+        <v>2918</v>
       </c>
       <c r="K954" t="s">
         <v>21</v>
       </c>
       <c r="L954" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="M954" t="s">
         <v>23</v>
@@ -48995,34 +48998,34 @@
         <v>2814</v>
       </c>
       <c r="C955" t="s">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="D955" t="s">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="E955" t="s">
         <v>16</v>
       </c>
       <c r="F955" t="s">
-        <v>2918</v>
+        <v>2919</v>
       </c>
       <c r="G955" t="s">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="H955">
         <v>2</v>
       </c>
       <c r="I955" t="s">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="J955" t="s">
-        <v>2920</v>
+        <v>2921</v>
       </c>
       <c r="K955" t="s">
         <v>21</v>
       </c>
       <c r="L955" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M955" t="s">
         <v>23</v>
@@ -49036,25 +49039,25 @@
         <v>2814</v>
       </c>
       <c r="C956" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="D956" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="E956" t="s">
         <v>16</v>
       </c>
       <c r="F956" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="G956" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="H956">
         <v>2</v>
       </c>
       <c r="I956" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="J956" t="s">
         <v>2561</v>
@@ -49077,25 +49080,25 @@
         <v>2814</v>
       </c>
       <c r="C957" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="D957" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="E957" t="s">
         <v>16</v>
       </c>
       <c r="F957" t="s">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="G957" t="s">
-        <v>2924</v>
+        <v>2925</v>
       </c>
       <c r="H957">
         <v>2</v>
       </c>
       <c r="I957" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="J957" t="s">
         <v>2381</v>
@@ -49118,19 +49121,19 @@
         <v>2814</v>
       </c>
       <c r="C958" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="D958" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="E958" t="s">
         <v>16</v>
       </c>
       <c r="F958" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="G958" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="H958">
         <v>2</v>
@@ -49139,13 +49142,13 @@
         <v>116</v>
       </c>
       <c r="J958" t="s">
-        <v>2928</v>
+        <v>2929</v>
       </c>
       <c r="K958" t="s">
         <v>21</v>
       </c>
       <c r="L958" t="s">
-        <v>2929</v>
+        <v>2930</v>
       </c>
       <c r="M958" t="s">
         <v>23</v>
@@ -49159,25 +49162,25 @@
         <v>2814</v>
       </c>
       <c r="C959" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="D959" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="E959" t="s">
         <v>16</v>
       </c>
       <c r="F959" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="G959" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="H959">
         <v>2</v>
       </c>
       <c r="I959" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="J959" t="s">
         <v>2561</v>
@@ -49186,7 +49189,7 @@
         <v>21</v>
       </c>
       <c r="L959" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M959" t="s">
         <v>635</v>
@@ -49200,34 +49203,34 @@
         <v>2814</v>
       </c>
       <c r="C960" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="D960" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="E960" t="s">
         <v>16</v>
       </c>
       <c r="F960" t="s">
-        <v>2926</v>
+        <v>2927</v>
       </c>
       <c r="G960" t="s">
-        <v>2927</v>
+        <v>2928</v>
       </c>
       <c r="H960">
         <v>2</v>
       </c>
       <c r="I960" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="J960" t="s">
-        <v>2931</v>
+        <v>2932</v>
       </c>
       <c r="K960" t="s">
         <v>21</v>
       </c>
       <c r="L960" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M960" t="s">
         <v>638</v>
@@ -49241,34 +49244,34 @@
         <v>2814</v>
       </c>
       <c r="C961" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="D961" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="E961" t="s">
         <v>16</v>
       </c>
       <c r="F961" t="s">
-        <v>2932</v>
+        <v>2933</v>
       </c>
       <c r="G961" t="s">
-        <v>2933</v>
+        <v>2934</v>
       </c>
       <c r="H961">
         <v>2</v>
       </c>
       <c r="I961" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="J961" t="s">
-        <v>2934</v>
+        <v>2935</v>
       </c>
       <c r="K961" t="s">
         <v>21</v>
       </c>
       <c r="L961" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="M961" t="s">
         <v>23</v>
@@ -49282,25 +49285,25 @@
         <v>2814</v>
       </c>
       <c r="C962" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="D962" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="E962" t="s">
         <v>16</v>
       </c>
       <c r="F962" t="s">
-        <v>2935</v>
+        <v>2936</v>
       </c>
       <c r="G962" t="s">
-        <v>2936</v>
+        <v>2937</v>
       </c>
       <c r="H962">
         <v>2</v>
       </c>
       <c r="I962" t="s">
-        <v>2925</v>
+        <v>2926</v>
       </c>
       <c r="J962" t="s">
         <v>2537</v>
@@ -49309,7 +49312,7 @@
         <v>21</v>
       </c>
       <c r="L962" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="M962" t="s">
         <v>23</v>
@@ -49323,34 +49326,34 @@
         <v>2814</v>
       </c>
       <c r="C963" t="s">
-        <v>2921</v>
+        <v>2922</v>
       </c>
       <c r="D963" t="s">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="E963" t="s">
         <v>16</v>
       </c>
       <c r="F963" t="s">
-        <v>2937</v>
+        <v>2938</v>
       </c>
       <c r="G963" t="s">
-        <v>2938</v>
+        <v>2939</v>
       </c>
       <c r="H963">
         <v>2</v>
       </c>
       <c r="I963" t="s">
-        <v>2930</v>
+        <v>2931</v>
       </c>
       <c r="J963" t="s">
-        <v>2939</v>
+        <v>2940</v>
       </c>
       <c r="K963" t="s">
         <v>21</v>
       </c>
       <c r="L963" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M963" t="s">
         <v>23</v>
@@ -49364,25 +49367,25 @@
         <v>2814</v>
       </c>
       <c r="C964" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="D964" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="E964" t="s">
         <v>16</v>
       </c>
       <c r="F964" t="s">
-        <v>2942</v>
+        <v>2943</v>
       </c>
       <c r="G964" t="s">
-        <v>2943</v>
+        <v>2944</v>
       </c>
       <c r="H964">
         <v>2</v>
       </c>
       <c r="I964" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="J964" t="s">
         <v>706</v>
@@ -49391,7 +49394,7 @@
         <v>21</v>
       </c>
       <c r="L964" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="M964" t="s">
         <v>23</v>
@@ -49405,25 +49408,25 @@
         <v>2814</v>
       </c>
       <c r="C965" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="D965" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="E965" t="s">
         <v>16</v>
       </c>
       <c r="F965" t="s">
-        <v>2945</v>
+        <v>2946</v>
       </c>
       <c r="G965" t="s">
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="H965">
         <v>2</v>
       </c>
       <c r="I965" t="s">
-        <v>2947</v>
+        <v>2948</v>
       </c>
       <c r="J965" t="s">
         <v>705</v>
@@ -49432,7 +49435,7 @@
         <v>21</v>
       </c>
       <c r="L965" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="M965" t="s">
         <v>23</v>
@@ -49446,25 +49449,25 @@
         <v>2814</v>
       </c>
       <c r="C966" t="s">
-        <v>2940</v>
+        <v>2941</v>
       </c>
       <c r="D966" t="s">
-        <v>2941</v>
+        <v>2942</v>
       </c>
       <c r="E966" t="s">
         <v>16</v>
       </c>
       <c r="F966" t="s">
-        <v>2948</v>
+        <v>2949</v>
       </c>
       <c r="G966" t="s">
-        <v>2949</v>
+        <v>2950</v>
       </c>
       <c r="H966">
         <v>2</v>
       </c>
       <c r="I966" t="s">
-        <v>2950</v>
+        <v>2951</v>
       </c>
       <c r="J966" t="s">
         <v>701</v>
@@ -49473,7 +49476,7 @@
         <v>21</v>
       </c>
       <c r="L966" t="s">
-        <v>2944</v>
+        <v>2945</v>
       </c>
       <c r="M966" t="s">
         <v>23</v>
@@ -49481,25 +49484,25 @@
     </row>
     <row r="967" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B967" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C967" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D967" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E967" t="s">
         <v>2268</v>
       </c>
       <c r="F967" t="s">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="G967" t="s">
-        <v>2956</v>
+        <v>2957</v>
       </c>
       <c r="H967">
         <v>3</v>
@@ -49508,13 +49511,13 @@
         <v>218</v>
       </c>
       <c r="J967" t="s">
-        <v>2957</v>
+        <v>2958</v>
       </c>
       <c r="K967" t="s">
         <v>21</v>
       </c>
       <c r="L967" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="M967" t="s">
         <v>23</v>
@@ -49522,25 +49525,25 @@
     </row>
     <row r="968" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B968" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C968" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D968" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E968" t="s">
         <v>16</v>
       </c>
       <c r="F968" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="G968" t="s">
-        <v>2960</v>
+        <v>2961</v>
       </c>
       <c r="H968">
         <v>3</v>
@@ -49549,7 +49552,7 @@
         <v>218</v>
       </c>
       <c r="J968" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
       <c r="K968" t="s">
         <v>21</v>
@@ -49563,34 +49566,34 @@
     </row>
     <row r="969" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B969" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C969" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D969" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E969" t="s">
         <v>16</v>
       </c>
       <c r="F969" t="s">
-        <v>2962</v>
+        <v>2963</v>
       </c>
       <c r="G969" t="s">
-        <v>2963</v>
+        <v>2964</v>
       </c>
       <c r="H969">
         <v>3</v>
       </c>
       <c r="I969" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="J969" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
       <c r="K969" t="s">
         <v>21</v>
@@ -49604,34 +49607,34 @@
     </row>
     <row r="970" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B970" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C970" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D970" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E970" t="s">
         <v>2268</v>
       </c>
       <c r="F970" t="s">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="G970" t="s">
-        <v>2967</v>
+        <v>2968</v>
       </c>
       <c r="H970">
         <v>3</v>
       </c>
       <c r="I970" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="J970" t="s">
-        <v>2961</v>
+        <v>2962</v>
       </c>
       <c r="K970" t="s">
         <v>21</v>
@@ -49645,34 +49648,34 @@
     </row>
     <row r="971" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B971" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C971" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D971" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E971" t="s">
         <v>16</v>
       </c>
       <c r="F971" t="s">
-        <v>2969</v>
+        <v>2970</v>
       </c>
       <c r="G971" t="s">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="H971">
         <v>3</v>
       </c>
       <c r="I971" t="s">
-        <v>2971</v>
+        <v>2972</v>
       </c>
       <c r="J971" t="s">
-        <v>2972</v>
+        <v>2973</v>
       </c>
       <c r="K971" t="s">
         <v>21</v>
@@ -49686,25 +49689,25 @@
     </row>
     <row r="972" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B972" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C972" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D972" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E972" t="s">
         <v>16</v>
       </c>
       <c r="F972" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="G972" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="H972">
         <v>3</v>
@@ -49727,25 +49730,25 @@
     </row>
     <row r="973" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B973" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C973" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D973" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E973" t="s">
         <v>16</v>
       </c>
       <c r="F973" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="G973" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="H973">
         <v>3</v>
@@ -49768,31 +49771,31 @@
     </row>
     <row r="974" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B974" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C974" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D974" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E974" t="s">
         <v>16</v>
       </c>
       <c r="F974" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="G974" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="H974">
         <v>3</v>
       </c>
       <c r="I974" t="s">
-        <v>2964</v>
+        <v>2965</v>
       </c>
       <c r="J974" t="s">
         <v>116</v>
@@ -49809,31 +49812,31 @@
     </row>
     <row r="975" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B975" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C975" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D975" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E975" t="s">
         <v>16</v>
       </c>
       <c r="F975" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="G975" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="H975">
         <v>3</v>
       </c>
       <c r="I975" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="J975" t="s">
         <v>116</v>
@@ -49850,25 +49853,25 @@
     </row>
     <row r="976" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B976" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C976" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D976" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E976" t="s">
         <v>16</v>
       </c>
       <c r="F976" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="G976" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="H976">
         <v>3</v>
@@ -49891,25 +49894,25 @@
     </row>
     <row r="977" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B977" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C977" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D977" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E977" t="s">
         <v>16</v>
       </c>
       <c r="F977" t="s">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="G977" t="s">
-        <v>2976</v>
+        <v>2977</v>
       </c>
       <c r="H977">
         <v>3</v>
@@ -49918,7 +49921,7 @@
         <v>218</v>
       </c>
       <c r="J977" t="s">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="K977" t="s">
         <v>21</v>
@@ -49932,40 +49935,40 @@
     </row>
     <row r="978" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B978" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C978" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D978" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E978" t="s">
         <v>16</v>
       </c>
       <c r="F978" t="s">
-        <v>2978</v>
+        <v>2979</v>
       </c>
       <c r="G978" t="s">
-        <v>2979</v>
+        <v>2980</v>
       </c>
       <c r="H978">
         <v>3</v>
       </c>
       <c r="I978" t="s">
-        <v>2968</v>
+        <v>2969</v>
       </c>
       <c r="J978" t="s">
-        <v>2980</v>
+        <v>2981</v>
       </c>
       <c r="K978" t="s">
         <v>21</v>
       </c>
       <c r="L978" t="s">
-        <v>2958</v>
+        <v>2959</v>
       </c>
       <c r="M978" t="s">
         <v>23</v>
@@ -49973,40 +49976,40 @@
     </row>
     <row r="979" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B979" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C979" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D979" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E979" t="s">
         <v>16</v>
       </c>
       <c r="F979" t="s">
+        <v>2982</v>
+      </c>
+      <c r="G979" t="s">
+        <v>2983</v>
+      </c>
+      <c r="H979">
+        <v>3</v>
+      </c>
+      <c r="I979" t="s">
+        <v>2965</v>
+      </c>
+      <c r="J979" t="s">
         <v>2981</v>
       </c>
-      <c r="G979" t="s">
-        <v>2982</v>
-      </c>
-      <c r="H979">
-        <v>3</v>
-      </c>
-      <c r="I979" t="s">
-        <v>2964</v>
-      </c>
-      <c r="J979" t="s">
-        <v>2980</v>
-      </c>
       <c r="K979" t="s">
         <v>21</v>
       </c>
       <c r="L979" t="s">
-        <v>2983</v>
+        <v>2984</v>
       </c>
       <c r="M979" t="s">
         <v>23</v>
@@ -50014,25 +50017,25 @@
     </row>
     <row r="980" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B980" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C980" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D980" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E980" t="s">
         <v>16</v>
       </c>
       <c r="F980" t="s">
-        <v>2984</v>
+        <v>2985</v>
       </c>
       <c r="G980" t="s">
-        <v>2985</v>
+        <v>2986</v>
       </c>
       <c r="H980">
         <v>3</v>
@@ -50041,13 +50044,13 @@
         <v>212</v>
       </c>
       <c r="J980" t="s">
-        <v>2986</v>
+        <v>2987</v>
       </c>
       <c r="K980" t="s">
         <v>21</v>
       </c>
       <c r="L980" t="s">
-        <v>2983</v>
+        <v>2984</v>
       </c>
       <c r="M980" t="s">
         <v>23</v>
@@ -50055,25 +50058,25 @@
     </row>
     <row r="981" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B981" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C981" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D981" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E981" t="s">
         <v>16</v>
       </c>
       <c r="F981" t="s">
-        <v>2987</v>
+        <v>2988</v>
       </c>
       <c r="G981" t="s">
-        <v>2988</v>
+        <v>2989</v>
       </c>
       <c r="H981">
         <v>3</v>
@@ -50082,7 +50085,7 @@
         <v>215</v>
       </c>
       <c r="J981" t="s">
-        <v>2965</v>
+        <v>2966</v>
       </c>
       <c r="K981" t="s">
         <v>21</v>
@@ -50096,25 +50099,25 @@
     </row>
     <row r="982" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B982" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C982" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D982" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E982" t="s">
         <v>16</v>
       </c>
       <c r="F982" t="s">
-        <v>2989</v>
+        <v>2990</v>
       </c>
       <c r="G982" t="s">
-        <v>2990</v>
+        <v>2991</v>
       </c>
       <c r="H982">
         <v>6</v>
@@ -50137,25 +50140,25 @@
     </row>
     <row r="983" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B983" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C983" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D983" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E983" t="s">
         <v>16</v>
       </c>
       <c r="F983" t="s">
-        <v>2991</v>
+        <v>2992</v>
       </c>
       <c r="G983" t="s">
-        <v>2992</v>
+        <v>2993</v>
       </c>
       <c r="H983">
         <v>6</v>
@@ -50178,34 +50181,34 @@
     </row>
     <row r="984" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B984" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C984" t="s">
-        <v>2953</v>
+        <v>2954</v>
       </c>
       <c r="D984" t="s">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="E984" t="s">
         <v>16</v>
       </c>
       <c r="F984" t="s">
-        <v>2993</v>
+        <v>2994</v>
       </c>
       <c r="G984" t="s">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="H984">
         <v>3</v>
       </c>
       <c r="I984" t="s">
-        <v>2995</v>
+        <v>2996</v>
       </c>
       <c r="J984" t="s">
-        <v>2977</v>
+        <v>2978</v>
       </c>
       <c r="K984" t="s">
         <v>21</v>
@@ -50219,31 +50222,31 @@
     </row>
     <row r="985" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B985" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C985" t="s">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="D985" t="s">
-        <v>2997</v>
+        <v>2998</v>
       </c>
       <c r="E985" t="s">
         <v>2268</v>
       </c>
       <c r="F985" t="s">
-        <v>2998</v>
+        <v>2999</v>
       </c>
       <c r="G985" t="s">
-        <v>2967</v>
+        <v>2968</v>
       </c>
       <c r="H985">
         <v>3</v>
       </c>
       <c r="I985" t="s">
-        <v>2999</v>
+        <v>3000</v>
       </c>
       <c r="J985" t="s">
         <v>94</v>
@@ -50260,31 +50263,31 @@
     </row>
     <row r="986" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B986" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C986" t="s">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="D986" t="s">
-        <v>2997</v>
+        <v>2998</v>
       </c>
       <c r="E986" t="s">
         <v>16</v>
       </c>
       <c r="F986" t="s">
-        <v>3000</v>
+        <v>3001</v>
       </c>
       <c r="G986" t="s">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="H986">
         <v>3</v>
       </c>
       <c r="I986" t="s">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="J986" t="s">
         <v>90</v>
@@ -50301,25 +50304,25 @@
     </row>
     <row r="987" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="B987" t="s">
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="C987" t="s">
-        <v>2996</v>
+        <v>2997</v>
       </c>
       <c r="D987" t="s">
-        <v>2997</v>
+        <v>2998</v>
       </c>
       <c r="E987" t="s">
         <v>16</v>
       </c>
       <c r="F987" t="s">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="G987" t="s">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="H987">
         <v>3</v>
@@ -50342,13 +50345,13 @@
     </row>
     <row r="988" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B988" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C988" t="s">
         <v>3006</v>
-      </c>
-      <c r="C988" t="s">
-        <v>3005</v>
       </c>
       <c r="D988" t="s">
         <v>15</v>
@@ -50357,16 +50360,16 @@
         <v>16</v>
       </c>
       <c r="F988" t="s">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="G988" t="s">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="H988">
         <v>2</v>
       </c>
       <c r="I988" t="s">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="J988" t="s">
         <v>2561</v>
@@ -50375,7 +50378,7 @@
         <v>21</v>
       </c>
       <c r="L988" t="s">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="M988" t="s">
         <v>23</v>
@@ -50383,13 +50386,13 @@
     </row>
     <row r="989" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B989" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C989" t="s">
         <v>3006</v>
-      </c>
-      <c r="C989" t="s">
-        <v>3005</v>
       </c>
       <c r="D989" t="s">
         <v>15</v>
@@ -50398,16 +50401,16 @@
         <v>16</v>
       </c>
       <c r="F989" t="s">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="G989" t="s">
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="H989">
         <v>2</v>
       </c>
       <c r="I989" t="s">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="J989" t="s">
         <v>2381</v>
@@ -50416,7 +50419,7 @@
         <v>21</v>
       </c>
       <c r="L989" t="s">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="M989" t="s">
         <v>23</v>
@@ -50424,13 +50427,13 @@
     </row>
     <row r="990" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B990" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C990" t="s">
         <v>3006</v>
-      </c>
-      <c r="C990" t="s">
-        <v>3005</v>
       </c>
       <c r="D990" t="s">
         <v>15</v>
@@ -50439,10 +50442,10 @@
         <v>16</v>
       </c>
       <c r="F990" t="s">
-        <v>3014</v>
+        <v>3015</v>
       </c>
       <c r="G990" t="s">
-        <v>3015</v>
+        <v>3016</v>
       </c>
       <c r="H990">
         <v>2</v>
@@ -50457,7 +50460,7 @@
         <v>21</v>
       </c>
       <c r="L990" t="s">
-        <v>3016</v>
+        <v>3017</v>
       </c>
       <c r="M990" t="s">
         <v>23</v>
@@ -50465,13 +50468,13 @@
     </row>
     <row r="991" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B991" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C991" t="s">
         <v>3006</v>
-      </c>
-      <c r="C991" t="s">
-        <v>3005</v>
       </c>
       <c r="D991" t="s">
         <v>15</v>
@@ -50480,10 +50483,10 @@
         <v>16</v>
       </c>
       <c r="F991" t="s">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="G991" t="s">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="H991">
         <v>2</v>
@@ -50498,7 +50501,7 @@
         <v>21</v>
       </c>
       <c r="L991" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="M991" t="s">
         <v>23</v>
@@ -50506,13 +50509,13 @@
     </row>
     <row r="992" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B992" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C992" t="s">
         <v>3006</v>
-      </c>
-      <c r="C992" t="s">
-        <v>3005</v>
       </c>
       <c r="D992" t="s">
         <v>15</v>
@@ -50521,10 +50524,10 @@
         <v>16</v>
       </c>
       <c r="F992" t="s">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="G992" t="s">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="H992">
         <v>2</v>
@@ -50547,13 +50550,13 @@
     </row>
     <row r="993" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B993" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C993" t="s">
         <v>3006</v>
-      </c>
-      <c r="C993" t="s">
-        <v>3005</v>
       </c>
       <c r="D993" t="s">
         <v>15</v>
@@ -50562,16 +50565,16 @@
         <v>16</v>
       </c>
       <c r="F993" t="s">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="G993" t="s">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="H993">
         <v>2</v>
       </c>
       <c r="I993" t="s">
-        <v>3020</v>
+        <v>3021</v>
       </c>
       <c r="J993" t="s">
         <v>2389</v>
@@ -50588,13 +50591,13 @@
     </row>
     <row r="994" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B994" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C994" t="s">
         <v>3006</v>
-      </c>
-      <c r="C994" t="s">
-        <v>3005</v>
       </c>
       <c r="D994" t="s">
         <v>15</v>
@@ -50603,16 +50606,16 @@
         <v>16</v>
       </c>
       <c r="F994" t="s">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="G994" t="s">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="H994">
         <v>2</v>
       </c>
       <c r="I994" t="s">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="J994" t="s">
         <v>2381</v>
@@ -50621,7 +50624,7 @@
         <v>21</v>
       </c>
       <c r="L994" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="M994" t="s">
         <v>641</v>
@@ -50629,13 +50632,13 @@
     </row>
     <row r="995" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B995" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C995" t="s">
         <v>3006</v>
-      </c>
-      <c r="C995" t="s">
-        <v>3005</v>
       </c>
       <c r="D995" t="s">
         <v>15</v>
@@ -50644,16 +50647,16 @@
         <v>16</v>
       </c>
       <c r="F995" t="s">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="G995" t="s">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="H995">
         <v>2</v>
       </c>
       <c r="I995" t="s">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="J995" t="s">
         <v>659</v>
@@ -50662,7 +50665,7 @@
         <v>21</v>
       </c>
       <c r="L995" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="M995" t="s">
         <v>643</v>
@@ -50670,13 +50673,13 @@
     </row>
     <row r="996" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B996" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C996" t="s">
         <v>3006</v>
-      </c>
-      <c r="C996" t="s">
-        <v>3005</v>
       </c>
       <c r="D996" t="s">
         <v>15</v>
@@ -50685,25 +50688,25 @@
         <v>16</v>
       </c>
       <c r="F996" t="s">
-        <v>3017</v>
+        <v>3018</v>
       </c>
       <c r="G996" t="s">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="H996">
         <v>2</v>
       </c>
       <c r="I996" t="s">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="J996" t="s">
-        <v>3024</v>
+        <v>3025</v>
       </c>
       <c r="K996" t="s">
         <v>21</v>
       </c>
       <c r="L996" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="M996" t="s">
         <v>646</v>
@@ -50711,13 +50714,13 @@
     </row>
     <row r="997" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B997" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C997" t="s">
         <v>3006</v>
-      </c>
-      <c r="C997" t="s">
-        <v>3005</v>
       </c>
       <c r="D997" t="s">
         <v>15</v>
@@ -50726,16 +50729,16 @@
         <v>16</v>
       </c>
       <c r="F997" t="s">
-        <v>3025</v>
+        <v>3026</v>
       </c>
       <c r="G997" t="s">
-        <v>3026</v>
+        <v>3027</v>
       </c>
       <c r="H997">
         <v>2</v>
       </c>
       <c r="I997" t="s">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="J997" t="s">
         <v>2537</v>
@@ -50744,7 +50747,7 @@
         <v>21</v>
       </c>
       <c r="L997" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="M997" t="s">
         <v>23</v>
@@ -50752,13 +50755,13 @@
     </row>
     <row r="998" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B998" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C998" t="s">
         <v>3006</v>
-      </c>
-      <c r="C998" t="s">
-        <v>3005</v>
       </c>
       <c r="D998" t="s">
         <v>15</v>
@@ -50767,25 +50770,25 @@
         <v>16</v>
       </c>
       <c r="F998" t="s">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="G998" t="s">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="H998">
         <v>2</v>
       </c>
       <c r="I998" t="s">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="J998" t="s">
-        <v>3029</v>
+        <v>3030</v>
       </c>
       <c r="K998" t="s">
         <v>21</v>
       </c>
       <c r="L998" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="M998" t="s">
         <v>23</v>
@@ -50793,31 +50796,31 @@
     </row>
     <row r="999" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B999" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C999" t="s">
-        <v>3030</v>
+        <v>3031</v>
       </c>
       <c r="D999" t="s">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="E999" t="s">
         <v>16</v>
       </c>
       <c r="F999" t="s">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="G999" t="s">
-        <v>3033</v>
+        <v>3034</v>
       </c>
       <c r="H999">
         <v>2</v>
       </c>
       <c r="I999" t="s">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="J999" t="s">
         <v>2561</v>
@@ -50826,7 +50829,7 @@
         <v>21</v>
       </c>
       <c r="L999" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="M999" t="s">
         <v>23</v>
@@ -50834,31 +50837,31 @@
     </row>
     <row r="1000" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1000" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1000" t="s">
-        <v>3030</v>
+        <v>3031</v>
       </c>
       <c r="D1000" t="s">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="E1000" t="s">
         <v>16</v>
       </c>
       <c r="F1000" t="s">
-        <v>3034</v>
+        <v>3035</v>
       </c>
       <c r="G1000" t="s">
-        <v>3035</v>
+        <v>3036</v>
       </c>
       <c r="H1000">
         <v>2</v>
       </c>
       <c r="I1000" t="s">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="J1000" t="s">
         <v>2389</v>
@@ -50875,31 +50878,31 @@
     </row>
     <row r="1001" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1001" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1001" t="s">
-        <v>3030</v>
+        <v>3031</v>
       </c>
       <c r="D1001" t="s">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="E1001" t="s">
         <v>16</v>
       </c>
       <c r="F1001" t="s">
-        <v>3037</v>
+        <v>3038</v>
       </c>
       <c r="G1001" t="s">
-        <v>3038</v>
+        <v>3039</v>
       </c>
       <c r="H1001">
         <v>2</v>
       </c>
       <c r="I1001" t="s">
-        <v>3039</v>
+        <v>3040</v>
       </c>
       <c r="J1001" t="s">
         <v>2537</v>
@@ -50908,7 +50911,7 @@
         <v>21</v>
       </c>
       <c r="L1001" t="s">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="M1001" t="s">
         <v>23</v>
@@ -50916,31 +50919,31 @@
     </row>
     <row r="1002" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1002" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1002" t="s">
-        <v>3030</v>
+        <v>3031</v>
       </c>
       <c r="D1002" t="s">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="E1002" t="s">
         <v>16</v>
       </c>
       <c r="F1002" t="s">
-        <v>3040</v>
+        <v>3041</v>
       </c>
       <c r="G1002" t="s">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="H1002">
         <v>2</v>
       </c>
       <c r="I1002" t="s">
-        <v>3042</v>
+        <v>3043</v>
       </c>
       <c r="J1002" t="s">
         <v>2561</v>
@@ -50957,31 +50960,31 @@
     </row>
     <row r="1003" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1003" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1003" t="s">
-        <v>3030</v>
+        <v>3031</v>
       </c>
       <c r="D1003" t="s">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="E1003" t="s">
         <v>16</v>
       </c>
       <c r="F1003" t="s">
-        <v>3043</v>
+        <v>3044</v>
       </c>
       <c r="G1003" t="s">
-        <v>3044</v>
+        <v>3045</v>
       </c>
       <c r="H1003">
         <v>2</v>
       </c>
       <c r="I1003" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
       <c r="J1003" t="s">
         <v>2389</v>
@@ -50998,31 +51001,31 @@
     </row>
     <row r="1004" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1004" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1004" t="s">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="D1004" t="s">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="E1004" t="s">
         <v>16</v>
       </c>
       <c r="F1004" t="s">
-        <v>3048</v>
+        <v>3049</v>
       </c>
       <c r="G1004" t="s">
-        <v>3049</v>
+        <v>3050</v>
       </c>
       <c r="H1004">
         <v>2</v>
       </c>
       <c r="I1004" t="s">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="J1004" t="s">
         <v>2561</v>
@@ -51039,31 +51042,31 @@
     </row>
     <row r="1005" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1005" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1005" t="s">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="D1005" t="s">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="E1005" t="s">
         <v>16</v>
       </c>
       <c r="F1005" t="s">
-        <v>3051</v>
+        <v>3052</v>
       </c>
       <c r="G1005" t="s">
-        <v>3052</v>
+        <v>3053</v>
       </c>
       <c r="H1005">
         <v>2</v>
       </c>
       <c r="I1005" t="s">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="J1005" t="s">
         <v>2389</v>
@@ -51072,7 +51075,7 @@
         <v>21</v>
       </c>
       <c r="L1005" t="s">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="M1005" t="s">
         <v>23</v>
@@ -51080,31 +51083,31 @@
     </row>
     <row r="1006" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1006" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1006" t="s">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="D1006" t="s">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="E1006" t="s">
         <v>16</v>
       </c>
       <c r="F1006" t="s">
-        <v>3053</v>
+        <v>3054</v>
       </c>
       <c r="G1006" t="s">
-        <v>3054</v>
+        <v>3055</v>
       </c>
       <c r="H1006">
         <v>2</v>
       </c>
       <c r="I1006" t="s">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="J1006" t="s">
         <v>2561</v>
@@ -51121,25 +51124,25 @@
     </row>
     <row r="1007" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1007" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1007" t="s">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="D1007" t="s">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="E1007" t="s">
         <v>16</v>
       </c>
       <c r="F1007" t="s">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="G1007" t="s">
-        <v>3057</v>
+        <v>3058</v>
       </c>
       <c r="H1007">
         <v>2</v>
@@ -51154,7 +51157,7 @@
         <v>21</v>
       </c>
       <c r="L1007" t="s">
-        <v>3016</v>
+        <v>3017</v>
       </c>
       <c r="M1007" t="s">
         <v>23</v>
@@ -51162,22 +51165,22 @@
     </row>
     <row r="1008" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1008" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1008" t="s">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="D1008" t="s">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="E1008" t="s">
         <v>16</v>
       </c>
       <c r="F1008" t="s">
-        <v>3058</v>
+        <v>3059</v>
       </c>
       <c r="G1008" t="s">
         <v>459</v>
@@ -51186,7 +51189,7 @@
         <v>2</v>
       </c>
       <c r="I1008" t="s">
-        <v>3059</v>
+        <v>3060</v>
       </c>
       <c r="J1008" t="s">
         <v>2381</v>
@@ -51203,31 +51206,31 @@
     </row>
     <row r="1009" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1009" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1009" t="s">
-        <v>3046</v>
+        <v>3047</v>
       </c>
       <c r="D1009" t="s">
-        <v>3047</v>
+        <v>3048</v>
       </c>
       <c r="E1009" t="s">
         <v>16</v>
       </c>
       <c r="F1009" t="s">
-        <v>3060</v>
+        <v>3061</v>
       </c>
       <c r="G1009" t="s">
-        <v>3061</v>
+        <v>3062</v>
       </c>
       <c r="H1009">
         <v>2</v>
       </c>
       <c r="I1009" t="s">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="J1009" t="s">
         <v>2389</v>
@@ -51236,7 +51239,7 @@
         <v>21</v>
       </c>
       <c r="L1009" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="M1009" t="s">
         <v>23</v>
@@ -51244,40 +51247,40 @@
     </row>
     <row r="1010" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1010" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1010" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="D1010" t="s">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="E1010" t="s">
         <v>16</v>
       </c>
       <c r="F1010" t="s">
-        <v>3064</v>
+        <v>3065</v>
       </c>
       <c r="G1010" t="s">
-        <v>3065</v>
+        <v>3066</v>
       </c>
       <c r="H1010">
         <v>2</v>
       </c>
       <c r="I1010" t="s">
-        <v>3055</v>
+        <v>3056</v>
       </c>
       <c r="J1010" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="K1010" t="s">
         <v>21</v>
       </c>
       <c r="L1010" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="M1010" t="s">
         <v>23</v>
@@ -51285,40 +51288,40 @@
     </row>
     <row r="1011" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1011" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1011" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="D1011" t="s">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="E1011" t="s">
         <v>16</v>
       </c>
       <c r="F1011" t="s">
-        <v>3066</v>
+        <v>3067</v>
       </c>
       <c r="G1011" t="s">
-        <v>3067</v>
+        <v>3068</v>
       </c>
       <c r="H1011">
         <v>2</v>
       </c>
       <c r="I1011" t="s">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="J1011" t="s">
-        <v>3069</v>
+        <v>3070</v>
       </c>
       <c r="K1011" t="s">
         <v>21</v>
       </c>
       <c r="L1011" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="M1011" t="s">
         <v>23</v>
@@ -51326,31 +51329,31 @@
     </row>
     <row r="1012" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1012" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1012" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="D1012" t="s">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="E1012" t="s">
         <v>16</v>
       </c>
       <c r="F1012" t="s">
-        <v>3070</v>
+        <v>3071</v>
       </c>
       <c r="G1012" t="s">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="H1012">
         <v>2</v>
       </c>
       <c r="I1012" t="s">
-        <v>3050</v>
+        <v>3051</v>
       </c>
       <c r="J1012" t="s">
         <v>659</v>
@@ -51367,31 +51370,31 @@
     </row>
     <row r="1013" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1013" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1013" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="D1013" t="s">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="E1013" t="s">
         <v>16</v>
       </c>
       <c r="F1013" t="s">
-        <v>3072</v>
+        <v>3073</v>
       </c>
       <c r="G1013" t="s">
-        <v>3073</v>
+        <v>3074</v>
       </c>
       <c r="H1013">
         <v>2</v>
       </c>
       <c r="I1013" t="s">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="J1013" t="s">
         <v>2537</v>
@@ -51400,7 +51403,7 @@
         <v>21</v>
       </c>
       <c r="L1013" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M1013" t="s">
         <v>23</v>
@@ -51408,31 +51411,31 @@
     </row>
     <row r="1014" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1014" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1014" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="D1014" t="s">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="E1014" t="s">
         <v>16</v>
       </c>
       <c r="F1014" t="s">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="G1014" t="s">
-        <v>3077</v>
+        <v>3078</v>
       </c>
       <c r="H1014">
         <v>2</v>
       </c>
       <c r="I1014" t="s">
-        <v>3068</v>
+        <v>3069</v>
       </c>
       <c r="J1014" t="s">
         <v>2389</v>
@@ -51441,7 +51444,7 @@
         <v>21</v>
       </c>
       <c r="L1014" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M1014" t="s">
         <v>23</v>
@@ -51449,31 +51452,31 @@
     </row>
     <row r="1015" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1015" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1015" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="D1015" t="s">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="E1015" t="s">
         <v>16</v>
       </c>
       <c r="F1015" t="s">
-        <v>3078</v>
+        <v>3079</v>
       </c>
       <c r="G1015" t="s">
-        <v>3079</v>
+        <v>3080</v>
       </c>
       <c r="H1015">
         <v>2</v>
       </c>
       <c r="I1015" t="s">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="J1015" t="s">
         <v>2537</v>
@@ -51490,31 +51493,31 @@
     </row>
     <row r="1016" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1016" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1016" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="D1016" t="s">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="E1016" t="s">
         <v>16</v>
       </c>
       <c r="F1016" t="s">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="G1016" t="s">
-        <v>3081</v>
+        <v>3082</v>
       </c>
       <c r="H1016">
         <v>2</v>
       </c>
       <c r="I1016" t="s">
-        <v>3082</v>
+        <v>3083</v>
       </c>
       <c r="J1016" t="s">
         <v>2381</v>
@@ -51523,7 +51526,7 @@
         <v>21</v>
       </c>
       <c r="L1016" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M1016" t="s">
         <v>23</v>
@@ -51531,31 +51534,31 @@
     </row>
     <row r="1017" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1017" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1017" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="D1017" t="s">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="E1017" t="s">
         <v>16</v>
       </c>
       <c r="F1017" t="s">
-        <v>3083</v>
+        <v>3084</v>
       </c>
       <c r="G1017" t="s">
-        <v>3084</v>
+        <v>3085</v>
       </c>
       <c r="H1017">
         <v>2</v>
       </c>
       <c r="I1017" t="s">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="J1017" t="s">
         <v>2381</v>
@@ -51572,31 +51575,31 @@
     </row>
     <row r="1018" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B1018" t="s">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="C1018" t="s">
-        <v>3062</v>
+        <v>3063</v>
       </c>
       <c r="D1018" t="s">
-        <v>3063</v>
+        <v>3064</v>
       </c>
       <c r="E1018" t="s">
         <v>16</v>
       </c>
       <c r="F1018" t="s">
-        <v>3085</v>
+        <v>3086</v>
       </c>
       <c r="G1018" t="s">
-        <v>3086</v>
+        <v>3087</v>
       </c>
       <c r="H1018">
         <v>2</v>
       </c>
       <c r="I1018" t="s">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="J1018" t="s">
         <v>2561</v>
@@ -51605,7 +51608,7 @@
         <v>21</v>
       </c>
       <c r="L1018" t="s">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="M1018" t="s">
         <v>23</v>
@@ -51613,13 +51616,13 @@
     </row>
     <row r="1019" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="B1019" t="s">
+        <v>3089</v>
+      </c>
+      <c r="C1019" t="s">
         <v>3088</v>
-      </c>
-      <c r="C1019" t="s">
-        <v>3087</v>
       </c>
       <c r="D1019" t="s">
         <v>15</v>
@@ -51628,16 +51631,16 @@
         <v>1727</v>
       </c>
       <c r="F1019" t="s">
-        <v>3089</v>
+        <v>3090</v>
       </c>
       <c r="G1019" t="s">
-        <v>3090</v>
+        <v>3091</v>
       </c>
       <c r="H1019">
         <v>2</v>
       </c>
       <c r="I1019" t="s">
-        <v>3091</v>
+        <v>3092</v>
       </c>
       <c r="J1019" t="s">
         <v>2389</v>
@@ -51654,34 +51657,34 @@
     </row>
     <row r="1020" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="B1020" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="C1020" t="s">
-        <v>3092</v>
+        <v>3093</v>
       </c>
       <c r="D1020" t="s">
-        <v>3093</v>
+        <v>3094</v>
       </c>
       <c r="E1020" t="s">
         <v>16</v>
       </c>
       <c r="F1020" t="s">
-        <v>3094</v>
+        <v>3095</v>
       </c>
       <c r="G1020" t="s">
-        <v>3095</v>
+        <v>3096</v>
       </c>
       <c r="H1020">
         <v>2</v>
       </c>
       <c r="I1020" t="s">
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="J1020" t="s">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="K1020" t="s">
         <v>21</v>
@@ -51695,25 +51698,25 @@
     </row>
     <row r="1021" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="B1021" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="C1021" t="s">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="D1021" t="s">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="E1021" t="s">
         <v>16</v>
       </c>
       <c r="F1021" t="s">
-        <v>3100</v>
+        <v>3101</v>
       </c>
       <c r="G1021" t="s">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="H1021">
         <v>2</v>
@@ -51728,7 +51731,7 @@
         <v>21</v>
       </c>
       <c r="L1021" t="s">
-        <v>3102</v>
+        <v>3103</v>
       </c>
       <c r="M1021" t="s">
         <v>23</v>
@@ -51736,31 +51739,31 @@
     </row>
     <row r="1022" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="B1022" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="C1022" t="s">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="D1022" t="s">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="E1022" t="s">
         <v>16</v>
       </c>
       <c r="F1022" t="s">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="G1022" t="s">
-        <v>3104</v>
+        <v>3105</v>
       </c>
       <c r="H1022">
         <v>2</v>
       </c>
       <c r="I1022" t="s">
-        <v>3105</v>
+        <v>3106</v>
       </c>
       <c r="J1022" t="s">
         <v>2381</v>
@@ -51777,34 +51780,34 @@
     </row>
     <row r="1023" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="B1023" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="C1023" t="s">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="D1023" t="s">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="E1023" t="s">
         <v>16</v>
       </c>
       <c r="F1023" t="s">
-        <v>3106</v>
+        <v>3107</v>
       </c>
       <c r="G1023" t="s">
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="H1023">
         <v>2</v>
       </c>
       <c r="I1023" t="s">
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="J1023" t="s">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="K1023" t="s">
         <v>21</v>
@@ -51818,31 +51821,31 @@
     </row>
     <row r="1024" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="B1024" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="C1024" t="s">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="D1024" t="s">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="E1024" t="s">
         <v>16</v>
       </c>
       <c r="F1024" t="s">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="G1024" t="s">
-        <v>3110</v>
+        <v>3111</v>
       </c>
       <c r="H1024">
         <v>2</v>
       </c>
       <c r="I1024" t="s">
-        <v>3111</v>
+        <v>3112</v>
       </c>
       <c r="J1024" t="s">
         <v>1952</v>
@@ -51851,7 +51854,7 @@
         <v>21</v>
       </c>
       <c r="L1024" t="s">
-        <v>3112</v>
+        <v>3113</v>
       </c>
       <c r="M1024" t="s">
         <v>23</v>
@@ -51859,34 +51862,34 @@
     </row>
     <row r="1025" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="B1025" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="C1025" t="s">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="D1025" t="s">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="E1025" t="s">
         <v>16</v>
       </c>
       <c r="F1025" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
       <c r="G1025" t="s">
-        <v>3116</v>
+        <v>3117</v>
       </c>
       <c r="H1025">
         <v>2</v>
       </c>
       <c r="I1025" t="s">
-        <v>3117</v>
+        <v>3118</v>
       </c>
       <c r="J1025" t="s">
-        <v>3118</v>
+        <v>3119</v>
       </c>
       <c r="K1025" t="s">
         <v>21</v>
@@ -51900,31 +51903,31 @@
     </row>
     <row r="1026" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="B1026" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="C1026" t="s">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="D1026" t="s">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="E1026" t="s">
         <v>16</v>
       </c>
       <c r="F1026" t="s">
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="G1026" t="s">
-        <v>3120</v>
+        <v>3121</v>
       </c>
       <c r="H1026">
         <v>2</v>
       </c>
       <c r="I1026" t="s">
-        <v>3117</v>
+        <v>3118</v>
       </c>
       <c r="J1026" t="s">
         <v>1895</v>
@@ -51933,7 +51936,7 @@
         <v>21</v>
       </c>
       <c r="L1026" t="s">
-        <v>3112</v>
+        <v>3113</v>
       </c>
       <c r="M1026" t="s">
         <v>23</v>
@@ -51941,34 +51944,34 @@
     </row>
     <row r="1027" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="B1027" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="C1027" t="s">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="D1027" t="s">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="E1027" t="s">
         <v>16</v>
       </c>
       <c r="F1027" t="s">
-        <v>3121</v>
+        <v>3122</v>
       </c>
       <c r="G1027" t="s">
-        <v>3122</v>
+        <v>3123</v>
       </c>
       <c r="H1027">
         <v>2</v>
       </c>
       <c r="I1027" t="s">
-        <v>3091</v>
+        <v>3092</v>
       </c>
       <c r="J1027" t="s">
-        <v>3123</v>
+        <v>3124</v>
       </c>
       <c r="K1027" t="s">
         <v>21</v>
@@ -51982,31 +51985,31 @@
     </row>
     <row r="1028" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
-        <v>3087</v>
+        <v>3088</v>
       </c>
       <c r="B1028" t="s">
-        <v>3088</v>
+        <v>3089</v>
       </c>
       <c r="C1028" t="s">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="D1028" t="s">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="E1028" t="s">
         <v>16</v>
       </c>
       <c r="F1028" t="s">
-        <v>3124</v>
+        <v>3125</v>
       </c>
       <c r="G1028" t="s">
-        <v>3125</v>
+        <v>3126</v>
       </c>
       <c r="H1028">
         <v>2</v>
       </c>
       <c r="I1028" t="s">
-        <v>3126</v>
+        <v>3127</v>
       </c>
       <c r="J1028" t="s">
         <v>2381</v>
@@ -52023,13 +52026,13 @@
     </row>
     <row r="1029" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="B1029" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1029" t="s">
         <v>3128</v>
-      </c>
-      <c r="C1029" t="s">
-        <v>3127</v>
       </c>
       <c r="D1029" t="s">
         <v>15</v>
@@ -52038,16 +52041,16 @@
         <v>1727</v>
       </c>
       <c r="F1029" t="s">
-        <v>3129</v>
+        <v>3130</v>
       </c>
       <c r="G1029" t="s">
-        <v>3130</v>
+        <v>3131</v>
       </c>
       <c r="H1029">
         <v>3</v>
       </c>
       <c r="I1029" t="s">
-        <v>3131</v>
+        <v>3132</v>
       </c>
       <c r="J1029" t="s">
         <v>1756</v>
@@ -52056,7 +52059,7 @@
         <v>21</v>
       </c>
       <c r="L1029" t="s">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="M1029" t="s">
         <v>23</v>
@@ -52064,13 +52067,13 @@
     </row>
     <row r="1030" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="B1030" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1030" t="s">
         <v>3128</v>
-      </c>
-      <c r="C1030" t="s">
-        <v>3127</v>
       </c>
       <c r="D1030" t="s">
         <v>15</v>
@@ -52079,10 +52082,10 @@
         <v>16</v>
       </c>
       <c r="F1030" t="s">
-        <v>3133</v>
+        <v>3134</v>
       </c>
       <c r="G1030" t="s">
-        <v>3134</v>
+        <v>3135</v>
       </c>
       <c r="H1030">
         <v>3</v>
@@ -52097,7 +52100,7 @@
         <v>21</v>
       </c>
       <c r="L1030" t="s">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="M1030" t="s">
         <v>23</v>
@@ -52105,13 +52108,13 @@
     </row>
     <row r="1031" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="B1031" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1031" t="s">
         <v>3128</v>
-      </c>
-      <c r="C1031" t="s">
-        <v>3127</v>
       </c>
       <c r="D1031" t="s">
         <v>15</v>
@@ -52120,10 +52123,10 @@
         <v>16</v>
       </c>
       <c r="F1031" t="s">
-        <v>3135</v>
+        <v>3136</v>
       </c>
       <c r="G1031" t="s">
-        <v>3136</v>
+        <v>3137</v>
       </c>
       <c r="H1031">
         <v>3</v>
@@ -52138,7 +52141,7 @@
         <v>21</v>
       </c>
       <c r="L1031" t="s">
-        <v>3137</v>
+        <v>3138</v>
       </c>
       <c r="M1031" t="s">
         <v>23</v>
@@ -52146,13 +52149,13 @@
     </row>
     <row r="1032" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="B1032" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1032" t="s">
         <v>3128</v>
-      </c>
-      <c r="C1032" t="s">
-        <v>3127</v>
       </c>
       <c r="D1032" t="s">
         <v>15</v>
@@ -52161,10 +52164,10 @@
         <v>1727</v>
       </c>
       <c r="F1032" t="s">
-        <v>3138</v>
+        <v>3139</v>
       </c>
       <c r="G1032" t="s">
-        <v>3139</v>
+        <v>3140</v>
       </c>
       <c r="H1032">
         <v>3</v>
@@ -52179,7 +52182,7 @@
         <v>324</v>
       </c>
       <c r="L1032" t="s">
-        <v>3140</v>
+        <v>3141</v>
       </c>
       <c r="M1032" t="s">
         <v>23</v>
@@ -52187,13 +52190,13 @@
     </row>
     <row r="1033" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="B1033" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1033" t="s">
         <v>3128</v>
-      </c>
-      <c r="C1033" t="s">
-        <v>3127</v>
       </c>
       <c r="D1033" t="s">
         <v>15</v>
@@ -52202,10 +52205,10 @@
         <v>2527</v>
       </c>
       <c r="F1033" t="s">
-        <v>3141</v>
+        <v>3142</v>
       </c>
       <c r="G1033" t="s">
-        <v>3142</v>
+        <v>3143</v>
       </c>
       <c r="H1033">
         <v>3</v>
@@ -52228,13 +52231,13 @@
     </row>
     <row r="1034" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="B1034" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1034" t="s">
         <v>3128</v>
-      </c>
-      <c r="C1034" t="s">
-        <v>3127</v>
       </c>
       <c r="D1034" t="s">
         <v>15</v>
@@ -52243,10 +52246,10 @@
         <v>1727</v>
       </c>
       <c r="F1034" t="s">
-        <v>3143</v>
+        <v>3144</v>
       </c>
       <c r="G1034" t="s">
-        <v>3144</v>
+        <v>3145</v>
       </c>
       <c r="H1034">
         <v>3</v>
@@ -52269,13 +52272,13 @@
     </row>
     <row r="1035" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="B1035" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1035" t="s">
         <v>3128</v>
-      </c>
-      <c r="C1035" t="s">
-        <v>3127</v>
       </c>
       <c r="D1035" t="s">
         <v>15</v>
@@ -52284,10 +52287,10 @@
         <v>1727</v>
       </c>
       <c r="F1035" t="s">
-        <v>3145</v>
+        <v>3146</v>
       </c>
       <c r="G1035" t="s">
-        <v>3146</v>
+        <v>3147</v>
       </c>
       <c r="H1035">
         <v>3</v>
@@ -52310,25 +52313,25 @@
     </row>
     <row r="1036" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="B1036" t="s">
-        <v>3128</v>
+        <v>3129</v>
       </c>
       <c r="C1036" t="s">
-        <v>3147</v>
+        <v>3148</v>
       </c>
       <c r="D1036" t="s">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="E1036" t="s">
         <v>16</v>
       </c>
       <c r="F1036" t="s">
-        <v>3149</v>
+        <v>3150</v>
       </c>
       <c r="G1036" t="s">
-        <v>3150</v>
+        <v>3151</v>
       </c>
       <c r="H1036">
         <v>3</v>
@@ -52343,7 +52346,7 @@
         <v>21</v>
       </c>
       <c r="L1036" t="s">
-        <v>3137</v>
+        <v>3138</v>
       </c>
       <c r="M1036" t="s">
         <v>23</v>
@@ -52351,25 +52354,25 @@
     </row>
     <row r="1037" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="B1037" t="s">
-        <v>3128</v>
+        <v>3129</v>
       </c>
       <c r="C1037" t="s">
-        <v>3147</v>
+        <v>3148</v>
       </c>
       <c r="D1037" t="s">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="E1037" t="s">
         <v>16</v>
       </c>
       <c r="F1037" t="s">
-        <v>3151</v>
+        <v>3152</v>
       </c>
       <c r="G1037" t="s">
-        <v>3152</v>
+        <v>3153</v>
       </c>
       <c r="H1037">
         <v>3</v>
@@ -52384,7 +52387,7 @@
         <v>21</v>
       </c>
       <c r="L1037" t="s">
-        <v>3137</v>
+        <v>3138</v>
       </c>
       <c r="M1037" t="s">
         <v>23</v>
@@ -52392,31 +52395,31 @@
     </row>
     <row r="1038" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="B1038" t="s">
-        <v>3128</v>
+        <v>3129</v>
       </c>
       <c r="C1038" t="s">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="D1038" t="s">
-        <v>3154</v>
+        <v>3155</v>
       </c>
       <c r="E1038" t="s">
         <v>16</v>
       </c>
       <c r="F1038" t="s">
-        <v>3155</v>
+        <v>3156</v>
       </c>
       <c r="G1038" t="s">
-        <v>3156</v>
+        <v>3157</v>
       </c>
       <c r="H1038">
         <v>3</v>
       </c>
       <c r="I1038" t="s">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="J1038" t="s">
         <v>1339</v>
@@ -52425,7 +52428,7 @@
         <v>21</v>
       </c>
       <c r="L1038" t="s">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="M1038" t="s">
         <v>23</v>
@@ -52433,31 +52436,31 @@
     </row>
     <row r="1039" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
-        <v>3127</v>
+        <v>3128</v>
       </c>
       <c r="B1039" t="s">
-        <v>3128</v>
+        <v>3129</v>
       </c>
       <c r="C1039" t="s">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="D1039" t="s">
-        <v>3154</v>
+        <v>3155</v>
       </c>
       <c r="E1039" t="s">
         <v>16</v>
       </c>
       <c r="F1039" t="s">
-        <v>3158</v>
+        <v>3159</v>
       </c>
       <c r="G1039" t="s">
-        <v>3159</v>
+        <v>3160</v>
       </c>
       <c r="H1039">
         <v>3</v>
       </c>
       <c r="I1039" t="s">
-        <v>3160</v>
+        <v>3161</v>
       </c>
       <c r="J1039" t="s">
         <v>1771</v>
@@ -52466,7 +52469,7 @@
         <v>21</v>
       </c>
       <c r="L1039" t="s">
-        <v>3132</v>
+        <v>3133</v>
       </c>
       <c r="M1039" t="s">
         <v>23</v>

--- a/actions_fetch/out/kookmin(2026-2).xlsx
+++ b/actions_fetch/out/kookmin(2026-2).xlsx
@@ -2089,6 +2089,9 @@
     <t>김성혜</t>
   </si>
   <si>
+    <t>월 09:00-11:00</t>
+  </si>
+  <si>
     <t>예술관3층3호실</t>
   </si>
   <si>
@@ -2135,9 +2138,6 @@
   </si>
   <si>
     <t>연효정</t>
-  </si>
-  <si>
-    <t>월 09:00-11:00</t>
   </si>
   <si>
     <t>예술관5층4호실</t>
@@ -15154,7 +15154,7 @@
         <v>21</v>
       </c>
       <c r="L128" t="s">
-        <v>164</v>
+        <v>519</v>
       </c>
       <c r="M128" t="s">
         <v>23</v>
@@ -17280,13 +17280,13 @@
         <v>691</v>
       </c>
       <c r="J180" t="s">
-        <v>678</v>
+        <v>692</v>
       </c>
       <c r="K180" t="s">
         <v>21</v>
       </c>
       <c r="L180" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M180" t="s">
         <v>643</v>
@@ -17391,16 +17391,16 @@
         <v>52</v>
       </c>
       <c r="F183" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G183" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H183">
         <v>2</v>
       </c>
       <c r="I183" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="J183" t="s">
         <v>669</v>
@@ -17409,7 +17409,7 @@
         <v>21</v>
       </c>
       <c r="L183" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M183" t="s">
         <v>23</v>
@@ -17432,25 +17432,25 @@
         <v>52</v>
       </c>
       <c r="F184" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G184" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H184">
         <v>2</v>
       </c>
       <c r="I184" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J184" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="K184" t="s">
         <v>21</v>
       </c>
       <c r="L184" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M184" t="s">
         <v>640</v>
@@ -17473,25 +17473,25 @@
         <v>52</v>
       </c>
       <c r="F185" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G185" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H185">
         <v>2</v>
       </c>
       <c r="I185" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J185" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="K185" t="s">
         <v>21</v>
       </c>
       <c r="L185" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M185" t="s">
         <v>23</v>
@@ -17514,25 +17514,25 @@
         <v>52</v>
       </c>
       <c r="F186" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G186" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H186">
         <v>2</v>
       </c>
       <c r="I186" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J186" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K186" t="s">
         <v>21</v>
       </c>
       <c r="L186" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M186" t="s">
         <v>640</v>
@@ -17555,25 +17555,25 @@
         <v>52</v>
       </c>
       <c r="F187" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G187" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H187">
         <v>2</v>
       </c>
       <c r="I187" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J187" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="K187" t="s">
         <v>21</v>
       </c>
       <c r="L187" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M187" t="s">
         <v>643</v>
@@ -17596,25 +17596,25 @@
         <v>52</v>
       </c>
       <c r="F188" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G188" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H188">
         <v>2</v>
       </c>
       <c r="I188" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J188" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="K188" t="s">
         <v>21</v>
       </c>
       <c r="L188" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M188" t="s">
         <v>646</v>
@@ -17637,19 +17637,19 @@
         <v>52</v>
       </c>
       <c r="F189" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G189" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H189">
         <v>2</v>
       </c>
       <c r="I189" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J189" t="s">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="K189" t="s">
         <v>21</v>
@@ -17678,16 +17678,16 @@
         <v>52</v>
       </c>
       <c r="F190" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G190" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H190">
         <v>2</v>
       </c>
       <c r="I190" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J190" t="s">
         <v>710</v>
@@ -17696,7 +17696,7 @@
         <v>21</v>
       </c>
       <c r="L190" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M190" t="s">
         <v>651</v>
@@ -17719,16 +17719,16 @@
         <v>52</v>
       </c>
       <c r="F191" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G191" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H191">
         <v>2</v>
       </c>
       <c r="I191" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J191" t="s">
         <v>711</v>
@@ -17737,7 +17737,7 @@
         <v>21</v>
       </c>
       <c r="L191" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M191" t="s">
         <v>652</v>
@@ -17778,7 +17778,7 @@
         <v>21</v>
       </c>
       <c r="L192" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M192" t="s">
         <v>23</v>
@@ -18999,7 +18999,7 @@
         <v>1</v>
       </c>
       <c r="I222" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J222" t="s">
         <v>754</v>
@@ -19008,7 +19008,7 @@
         <v>21</v>
       </c>
       <c r="L222" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M222" t="s">
         <v>23</v>
@@ -19040,7 +19040,7 @@
         <v>1</v>
       </c>
       <c r="I223" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J223" t="s">
         <v>763</v>
@@ -19049,7 +19049,7 @@
         <v>21</v>
       </c>
       <c r="L223" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M223" t="s">
         <v>640</v>
@@ -19081,7 +19081,7 @@
         <v>1</v>
       </c>
       <c r="I224" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J224" t="s">
         <v>769</v>
@@ -19090,7 +19090,7 @@
         <v>21</v>
       </c>
       <c r="L224" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M224" t="s">
         <v>643</v>
@@ -19658,7 +19658,7 @@
         <v>785</v>
       </c>
       <c r="J238" t="s">
-        <v>773</v>
+        <v>692</v>
       </c>
       <c r="K238" t="s">
         <v>21</v>
@@ -21910,7 +21910,7 @@
         <v>2</v>
       </c>
       <c r="I293" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J293" t="s">
         <v>815</v>
@@ -21951,7 +21951,7 @@
         <v>2</v>
       </c>
       <c r="I294" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J294" t="s">
         <v>638</v>
@@ -21960,7 +21960,7 @@
         <v>21</v>
       </c>
       <c r="L294" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M294" t="s">
         <v>640</v>
@@ -21992,7 +21992,7 @@
         <v>2</v>
       </c>
       <c r="I295" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J295" t="s">
         <v>642</v>
@@ -22001,7 +22001,7 @@
         <v>21</v>
       </c>
       <c r="L295" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M295" t="s">
         <v>643</v>
@@ -22115,7 +22115,7 @@
         <v>2</v>
       </c>
       <c r="I298" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J298" t="s">
         <v>837</v>
@@ -22124,7 +22124,7 @@
         <v>21</v>
       </c>
       <c r="L298" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M298" t="s">
         <v>23</v>
@@ -22197,7 +22197,7 @@
         <v>2</v>
       </c>
       <c r="I300" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J300" t="s">
         <v>840</v>
@@ -22206,7 +22206,7 @@
         <v>21</v>
       </c>
       <c r="L300" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M300" t="s">
         <v>23</v>
@@ -22238,7 +22238,7 @@
         <v>2</v>
       </c>
       <c r="I301" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J301" t="s">
         <v>841</v>
@@ -22247,7 +22247,7 @@
         <v>21</v>
       </c>
       <c r="L301" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M301" t="s">
         <v>640</v>
@@ -22279,7 +22279,7 @@
         <v>2</v>
       </c>
       <c r="I302" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J302" t="s">
         <v>844</v>
@@ -22288,7 +22288,7 @@
         <v>21</v>
       </c>
       <c r="L302" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M302" t="s">
         <v>23</v>
@@ -22361,7 +22361,7 @@
         <v>2</v>
       </c>
       <c r="I304" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J304" t="s">
         <v>845</v>
@@ -22370,7 +22370,7 @@
         <v>21</v>
       </c>
       <c r="L304" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M304" t="s">
         <v>643</v>
@@ -22402,7 +22402,7 @@
         <v>2</v>
       </c>
       <c r="I305" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J305" t="s">
         <v>669</v>
@@ -22411,7 +22411,7 @@
         <v>21</v>
       </c>
       <c r="L305" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M305" t="s">
         <v>646</v>
@@ -22484,16 +22484,16 @@
         <v>2</v>
       </c>
       <c r="I307" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J307" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="K307" t="s">
         <v>21</v>
       </c>
       <c r="L307" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M307" t="s">
         <v>651</v>
@@ -22525,7 +22525,7 @@
         <v>2</v>
       </c>
       <c r="I308" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="J308" t="s">
         <v>815</v>
@@ -22534,7 +22534,7 @@
         <v>21</v>
       </c>
       <c r="L308" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="M308" t="s">
         <v>652</v>
@@ -22689,7 +22689,7 @@
         <v>3</v>
       </c>
       <c r="I312" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J312" t="s">
         <v>854</v>
@@ -23190,7 +23190,7 @@
         <v>21</v>
       </c>
       <c r="L324" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M324" t="s">
         <v>23</v>
@@ -47462,7 +47462,7 @@
         <v>21</v>
       </c>
       <c r="L916" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M916" t="s">
         <v>23</v>
@@ -47503,7 +47503,7 @@
         <v>21</v>
       </c>
       <c r="L917" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M917" t="s">
         <v>23</v>
@@ -47907,7 +47907,7 @@
         <v>2854</v>
       </c>
       <c r="J927" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="K927" t="s">
         <v>21</v>
@@ -47948,7 +47948,7 @@
         <v>2858</v>
       </c>
       <c r="J928" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="K928" t="s">
         <v>21</v>
@@ -47989,7 +47989,7 @@
         <v>2861</v>
       </c>
       <c r="J929" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="K929" t="s">
         <v>21</v>
@@ -49102,7 +49102,7 @@
         <v>21</v>
       </c>
       <c r="L956" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M956" t="s">
         <v>23</v>
@@ -49143,7 +49143,7 @@
         <v>21</v>
       </c>
       <c r="L957" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M957" t="s">
         <v>640</v>
@@ -49506,7 +49506,7 @@
         <v>2961</v>
       </c>
       <c r="J966" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="K966" t="s">
         <v>21</v>

--- a/actions_fetch/out/kookmin(2026-2).xlsx
+++ b/actions_fetch/out/kookmin(2026-2).xlsx
@@ -40609,7 +40609,7 @@
         <v>21</v>
       </c>
       <c r="L749" t="s">
-        <v>2145</v>
+        <v>2238</v>
       </c>
       <c r="M749" t="s">
         <v>23</v>

--- a/actions_fetch/out/kookmin(2026-2).xlsx
+++ b/actions_fetch/out/kookmin(2026-2).xlsx
@@ -4528,7 +4528,7 @@
     <t>홍성지</t>
   </si>
   <si>
-    <t>월 10:00-12:00,수 10:00-12:00</t>
+    <t>월 10:30-12:00,수 10:00-12:00</t>
   </si>
   <si>
     <t>조형관별관1층1-1호실</t>
@@ -4540,7 +4540,7 @@
     <t>초급한국어2</t>
   </si>
   <si>
-    <t>화 10:00-12:00,목 10:00-12:00</t>
+    <t>화 10:30-12:00,목 10:00-12:00</t>
   </si>
   <si>
     <t>7233201</t>
@@ -30605,7 +30605,7 @@
         <v>21</v>
       </c>
       <c r="L505" t="s">
-        <v>536</v>
+        <v>580</v>
       </c>
       <c r="M505" t="s">
         <v>23</v>

--- a/actions_fetch/out/kookmin(2026-2).xlsx
+++ b/actions_fetch/out/kookmin(2026-2).xlsx
@@ -4531,559 +4531,559 @@
     <t>월 10:30-12:00,수 10:00-12:00</t>
   </si>
   <si>
+    <t>704670a</t>
+  </si>
+  <si>
+    <t>초급한국어2</t>
+  </si>
+  <si>
+    <t>화 10:30-12:00,목 10:00-12:00</t>
+  </si>
+  <si>
+    <t>7233201</t>
+  </si>
+  <si>
+    <t>디자인 한국어1</t>
+  </si>
+  <si>
+    <t>정은주</t>
+  </si>
+  <si>
+    <t>조형관별관3층8호실</t>
+  </si>
+  <si>
+    <t>7233701</t>
+  </si>
+  <si>
+    <t>디자인 한국어2</t>
+  </si>
+  <si>
+    <t>금 09:00-13:00</t>
+  </si>
+  <si>
+    <t>조형관별관3층10호실</t>
+  </si>
+  <si>
+    <t>7233801</t>
+  </si>
+  <si>
+    <t>디자인 프랙티스2</t>
+  </si>
+  <si>
+    <t>박윤정</t>
+  </si>
+  <si>
+    <t>화 15:00-18:00,금 15:00-18:00</t>
+  </si>
+  <si>
+    <t>글로벌센터4층8호실</t>
+  </si>
+  <si>
+    <t>7233901</t>
+  </si>
+  <si>
+    <t>디자인 프랙티스1</t>
+  </si>
+  <si>
+    <t>박소영</t>
+  </si>
+  <si>
+    <t>월 15:00-18:00,목 15:00-18:00</t>
+  </si>
+  <si>
+    <t>7266001</t>
+  </si>
+  <si>
+    <t>디자인 프랙티스3</t>
+  </si>
+  <si>
+    <t>신정민</t>
+  </si>
+  <si>
+    <t>글로벌센터4층9호실</t>
+  </si>
+  <si>
+    <t>7286601</t>
+  </si>
+  <si>
+    <t>DK워크숍1</t>
+  </si>
+  <si>
+    <t>김미애</t>
+  </si>
+  <si>
+    <t>7286701</t>
+  </si>
+  <si>
+    <t>DK워크숍2</t>
+  </si>
+  <si>
+    <t>진황가</t>
+  </si>
+  <si>
+    <t>조형관별관3층7호실</t>
+  </si>
+  <si>
+    <t>36277</t>
+  </si>
+  <si>
+    <t>스마트경험디자인학과</t>
+  </si>
+  <si>
+    <t>704140b</t>
+  </si>
+  <si>
+    <t>논문ㆍ작품지도</t>
+  </si>
+  <si>
+    <t>연명흠</t>
+  </si>
+  <si>
+    <t>수 18:55-21:35</t>
+  </si>
+  <si>
+    <t>조형관별관1층5호실</t>
+  </si>
+  <si>
+    <t>704150a</t>
+  </si>
+  <si>
+    <t>논문지도1</t>
+  </si>
+  <si>
+    <t>목 18:55-21:35</t>
+  </si>
+  <si>
+    <t>조형관별관3층4호실</t>
+  </si>
+  <si>
+    <t>704160a</t>
+  </si>
+  <si>
+    <t>논문지도2</t>
+  </si>
+  <si>
+    <t>임진호</t>
+  </si>
+  <si>
+    <t>조형관별관3층5호실</t>
+  </si>
+  <si>
+    <t>689070a</t>
+  </si>
+  <si>
+    <t>인터랙션디자인2</t>
+  </si>
+  <si>
+    <t>김수진</t>
+  </si>
+  <si>
+    <t>조형관별관3층3호실</t>
+  </si>
+  <si>
+    <t>689430a</t>
+  </si>
+  <si>
+    <t>서비스디자인2</t>
+  </si>
+  <si>
+    <t>정진열</t>
+  </si>
+  <si>
+    <t>화 18:55-21:35</t>
+  </si>
+  <si>
+    <t>696070a</t>
+  </si>
+  <si>
+    <t>디자인조사분석연습</t>
+  </si>
+  <si>
+    <t>조형관별관3층2호실</t>
+  </si>
+  <si>
+    <t>스튜디오</t>
+  </si>
+  <si>
+    <t>7204501</t>
+  </si>
+  <si>
+    <t>로컬플래닝 스튜디오 2</t>
+  </si>
+  <si>
+    <t>토 10:00-16:00</t>
+  </si>
+  <si>
+    <t>7204601</t>
+  </si>
+  <si>
+    <t>기술융합디자인논제 2</t>
+  </si>
+  <si>
+    <t>정치훈</t>
+  </si>
+  <si>
+    <t>7219501</t>
+  </si>
+  <si>
+    <t>도시공간론2</t>
+  </si>
+  <si>
+    <t>이용원</t>
+  </si>
+  <si>
+    <t>월 18:55-21:35</t>
+  </si>
+  <si>
+    <t>7231401</t>
+  </si>
+  <si>
+    <t>인공지능 활용 디자인</t>
+  </si>
+  <si>
+    <t>7244101</t>
+  </si>
+  <si>
+    <t>AI-XR 디자인</t>
+  </si>
+  <si>
+    <t>한주현</t>
+  </si>
+  <si>
+    <t>7249001</t>
+  </si>
+  <si>
+    <t>로컬혁신세미나2</t>
+  </si>
+  <si>
+    <t>7253701</t>
+  </si>
+  <si>
+    <t>기후변화와 서비스디자인</t>
+  </si>
+  <si>
+    <t>유채문</t>
+  </si>
+  <si>
+    <t>7260501</t>
+  </si>
+  <si>
+    <t>인클루시브 디자인</t>
+  </si>
+  <si>
+    <t>7286301</t>
+  </si>
+  <si>
+    <t>인간-인공지능 협업디자인 스튜디오2</t>
+  </si>
+  <si>
+    <t>허정윤</t>
+  </si>
+  <si>
+    <t>월 14:00-17:00,수 10:00-13:00</t>
+  </si>
+  <si>
+    <t>조형관별관3층10호실,조형관별관3층2호실</t>
+  </si>
+  <si>
+    <t>7295401</t>
+  </si>
+  <si>
+    <t>AI콘텐츠디자인스튜디오1</t>
+  </si>
+  <si>
+    <t>권주영</t>
+  </si>
+  <si>
+    <t>월 14:00-19:45</t>
+  </si>
+  <si>
+    <t>김진영</t>
+  </si>
+  <si>
+    <t>월 10:00-13:00,목 10:00-13:00</t>
+  </si>
+  <si>
+    <t>7295501</t>
+  </si>
+  <si>
+    <t>AI 시대의 인간이해</t>
+  </si>
+  <si>
+    <t>7295601</t>
+  </si>
+  <si>
+    <t>Agentic UX디자인</t>
+  </si>
+  <si>
+    <t>7295701</t>
+  </si>
+  <si>
+    <t>서비스디자인스튜디오2</t>
+  </si>
+  <si>
+    <t>조만수</t>
+  </si>
+  <si>
+    <t>월 10:00-13:00,수 10:00-13:00</t>
+  </si>
+  <si>
+    <t>7295901</t>
+  </si>
+  <si>
+    <t>사운드경험디자인</t>
+  </si>
+  <si>
+    <t>남궁기찬</t>
+  </si>
+  <si>
+    <t>월 11:00-14:00</t>
+  </si>
+  <si>
+    <t>7296001</t>
+  </si>
+  <si>
+    <t>제품서비스시스템디자인스튜디오2</t>
+  </si>
+  <si>
+    <t>심유리</t>
+  </si>
+  <si>
+    <t>월 10:00-17:00</t>
+  </si>
+  <si>
+    <t>7296101</t>
+  </si>
+  <si>
+    <t>정보디자인스튜디오2</t>
+  </si>
+  <si>
+    <t>허정현</t>
+  </si>
+  <si>
+    <t>월 18:00-20:40,수 14:30-17:30</t>
+  </si>
+  <si>
+    <t>조형관별관3층3호실,조형관별관3층10호실</t>
+  </si>
+  <si>
+    <t>7296201</t>
+  </si>
+  <si>
+    <t>공공서비스디자인</t>
+  </si>
+  <si>
+    <t>박순정</t>
+  </si>
+  <si>
+    <t>조형관별관3층9호실</t>
+  </si>
+  <si>
+    <t>7296301</t>
+  </si>
+  <si>
+    <t>정량연구방법</t>
+  </si>
+  <si>
+    <t>36320</t>
+  </si>
+  <si>
+    <t>공간ㆍ문화디자인학과</t>
+  </si>
+  <si>
+    <t>704200b</t>
+  </si>
+  <si>
+    <t>7243701</t>
+  </si>
+  <si>
+    <t>특수연구과제2</t>
+  </si>
+  <si>
+    <t>윤성호</t>
+  </si>
+  <si>
+    <t>조형관별관3층14호실</t>
+  </si>
+  <si>
+    <t>7294501</t>
+  </si>
+  <si>
+    <t>7295101</t>
+  </si>
+  <si>
+    <t>강민선</t>
+  </si>
+  <si>
+    <t>707590a</t>
+  </si>
+  <si>
+    <t>소재 융합 개발 연구</t>
+  </si>
+  <si>
+    <t>이순정</t>
+  </si>
+  <si>
+    <t>토 10:00-13:00</t>
+  </si>
+  <si>
+    <t>7129001</t>
+  </si>
+  <si>
+    <t>디자인리서치&amp;방법론</t>
+  </si>
+  <si>
+    <t>7192201</t>
+  </si>
+  <si>
+    <t>글로벌 디자인 워크샵</t>
+  </si>
+  <si>
+    <t>정상엽</t>
+  </si>
+  <si>
+    <t>7192301</t>
+  </si>
+  <si>
+    <t>공간디자인 리서치 1</t>
+  </si>
+  <si>
+    <t>고은주</t>
+  </si>
+  <si>
+    <t>7243801</t>
+  </si>
+  <si>
+    <t>현대도시디자인</t>
+  </si>
+  <si>
+    <t>김상호</t>
+  </si>
+  <si>
+    <t>7262401</t>
+  </si>
+  <si>
+    <t>사진과 문화공간</t>
+  </si>
+  <si>
+    <t>김규랑</t>
+  </si>
+  <si>
+    <t>7294101</t>
+  </si>
+  <si>
+    <t>미래디자인트렌드</t>
+  </si>
+  <si>
+    <t>박성미</t>
+  </si>
+  <si>
+    <t>7294201</t>
+  </si>
+  <si>
+    <t>리빙제품 및 신소재연구</t>
+  </si>
+  <si>
+    <t>7294301</t>
+  </si>
+  <si>
+    <t>리빙 및 가구 제품 기획</t>
+  </si>
+  <si>
+    <t>김상현</t>
+  </si>
+  <si>
+    <t>토 13:00-18:50</t>
+  </si>
+  <si>
+    <t>7294401</t>
+  </si>
+  <si>
+    <t>융합실내디자인스튜디오1</t>
+  </si>
+  <si>
+    <t>7294601</t>
+  </si>
+  <si>
+    <t>문화현장리서치</t>
+  </si>
+  <si>
+    <t>이상해</t>
+  </si>
+  <si>
+    <t>7294701</t>
+  </si>
+  <si>
+    <t>디지털공간디자인1</t>
+  </si>
+  <si>
+    <t>민세희</t>
+  </si>
+  <si>
+    <t>7294801</t>
+  </si>
+  <si>
+    <t>융합공간디자인세미나</t>
+  </si>
+  <si>
+    <t>7294901</t>
+  </si>
+  <si>
+    <t>인터렉티브 환경디자인 스튜디오1</t>
+  </si>
+  <si>
+    <t>7295001</t>
+  </si>
+  <si>
+    <t>공간디자인스튜디오2</t>
+  </si>
+  <si>
+    <t>7295201</t>
+  </si>
+  <si>
+    <t>크리에이티브스페이스스튜디오1</t>
+  </si>
+  <si>
+    <t>7295301</t>
+  </si>
+  <si>
+    <t>뉴미디어환경디자인스튜디오1</t>
+  </si>
+  <si>
+    <t>36378</t>
+  </si>
+  <si>
+    <t>융합디자인학과</t>
+  </si>
+  <si>
+    <t>689540b</t>
+  </si>
+  <si>
+    <t>성재혁</t>
+  </si>
+  <si>
+    <t>689260a</t>
+  </si>
+  <si>
+    <t>704700a</t>
+  </si>
+  <si>
+    <t>사회적책임과디자인4</t>
+  </si>
+  <si>
+    <t>최호랑</t>
+  </si>
+  <si>
+    <t>7130201</t>
+  </si>
+  <si>
+    <t>타이포그래픽 디자인4</t>
+  </si>
+  <si>
+    <t>화 10:00-13:00,금 10:00-13:00</t>
+  </si>
+  <si>
     <t>조형관별관1층1-1호실</t>
-  </si>
-  <si>
-    <t>704670a</t>
-  </si>
-  <si>
-    <t>초급한국어2</t>
-  </si>
-  <si>
-    <t>화 10:30-12:00,목 10:00-12:00</t>
-  </si>
-  <si>
-    <t>7233201</t>
-  </si>
-  <si>
-    <t>디자인 한국어1</t>
-  </si>
-  <si>
-    <t>정은주</t>
-  </si>
-  <si>
-    <t>조형관별관3층8호실</t>
-  </si>
-  <si>
-    <t>7233701</t>
-  </si>
-  <si>
-    <t>디자인 한국어2</t>
-  </si>
-  <si>
-    <t>금 09:00-13:00</t>
-  </si>
-  <si>
-    <t>7233801</t>
-  </si>
-  <si>
-    <t>디자인 프랙티스2</t>
-  </si>
-  <si>
-    <t>박윤정</t>
-  </si>
-  <si>
-    <t>화 15:00-18:00,금 15:00-18:00</t>
-  </si>
-  <si>
-    <t>글로벌센터4층8호실</t>
-  </si>
-  <si>
-    <t>7233901</t>
-  </si>
-  <si>
-    <t>디자인 프랙티스1</t>
-  </si>
-  <si>
-    <t>박소영</t>
-  </si>
-  <si>
-    <t>월 15:00-18:00,목 15:00-18:00</t>
-  </si>
-  <si>
-    <t>7266001</t>
-  </si>
-  <si>
-    <t>디자인 프랙티스3</t>
-  </si>
-  <si>
-    <t>신정민</t>
-  </si>
-  <si>
-    <t>글로벌센터4층9호실</t>
-  </si>
-  <si>
-    <t>7286601</t>
-  </si>
-  <si>
-    <t>DK워크숍1</t>
-  </si>
-  <si>
-    <t>김미애</t>
-  </si>
-  <si>
-    <t>7286701</t>
-  </si>
-  <si>
-    <t>DK워크숍2</t>
-  </si>
-  <si>
-    <t>진황가</t>
-  </si>
-  <si>
-    <t>조형관별관3층7호실</t>
-  </si>
-  <si>
-    <t>36277</t>
-  </si>
-  <si>
-    <t>스마트경험디자인학과</t>
-  </si>
-  <si>
-    <t>704140b</t>
-  </si>
-  <si>
-    <t>논문ㆍ작품지도</t>
-  </si>
-  <si>
-    <t>연명흠</t>
-  </si>
-  <si>
-    <t>수 18:55-21:35</t>
-  </si>
-  <si>
-    <t>조형관별관1층5호실</t>
-  </si>
-  <si>
-    <t>704150a</t>
-  </si>
-  <si>
-    <t>논문지도1</t>
-  </si>
-  <si>
-    <t>목 18:55-21:35</t>
-  </si>
-  <si>
-    <t>조형관별관3층4호실</t>
-  </si>
-  <si>
-    <t>704160a</t>
-  </si>
-  <si>
-    <t>논문지도2</t>
-  </si>
-  <si>
-    <t>임진호</t>
-  </si>
-  <si>
-    <t>조형관별관3층5호실</t>
-  </si>
-  <si>
-    <t>689070a</t>
-  </si>
-  <si>
-    <t>인터랙션디자인2</t>
-  </si>
-  <si>
-    <t>김수진</t>
-  </si>
-  <si>
-    <t>조형관별관3층3호실</t>
-  </si>
-  <si>
-    <t>689430a</t>
-  </si>
-  <si>
-    <t>서비스디자인2</t>
-  </si>
-  <si>
-    <t>정진열</t>
-  </si>
-  <si>
-    <t>화 18:55-21:35</t>
-  </si>
-  <si>
-    <t>696070a</t>
-  </si>
-  <si>
-    <t>디자인조사분석연습</t>
-  </si>
-  <si>
-    <t>조형관별관3층2호실</t>
-  </si>
-  <si>
-    <t>스튜디오</t>
-  </si>
-  <si>
-    <t>7204501</t>
-  </si>
-  <si>
-    <t>로컬플래닝 스튜디오 2</t>
-  </si>
-  <si>
-    <t>토 10:00-16:00</t>
-  </si>
-  <si>
-    <t>7204601</t>
-  </si>
-  <si>
-    <t>기술융합디자인논제 2</t>
-  </si>
-  <si>
-    <t>정치훈</t>
-  </si>
-  <si>
-    <t>7219501</t>
-  </si>
-  <si>
-    <t>도시공간론2</t>
-  </si>
-  <si>
-    <t>이용원</t>
-  </si>
-  <si>
-    <t>월 18:55-21:35</t>
-  </si>
-  <si>
-    <t>7231401</t>
-  </si>
-  <si>
-    <t>인공지능 활용 디자인</t>
-  </si>
-  <si>
-    <t>7244101</t>
-  </si>
-  <si>
-    <t>AI-XR 디자인</t>
-  </si>
-  <si>
-    <t>한주현</t>
-  </si>
-  <si>
-    <t>7249001</t>
-  </si>
-  <si>
-    <t>로컬혁신세미나2</t>
-  </si>
-  <si>
-    <t>7253701</t>
-  </si>
-  <si>
-    <t>기후변화와 서비스디자인</t>
-  </si>
-  <si>
-    <t>유채문</t>
-  </si>
-  <si>
-    <t>7260501</t>
-  </si>
-  <si>
-    <t>인클루시브 디자인</t>
-  </si>
-  <si>
-    <t>조형관별관3층10호실</t>
-  </si>
-  <si>
-    <t>7286301</t>
-  </si>
-  <si>
-    <t>인간-인공지능 협업디자인 스튜디오2</t>
-  </si>
-  <si>
-    <t>허정윤</t>
-  </si>
-  <si>
-    <t>월 14:00-17:00,수 10:00-13:00</t>
-  </si>
-  <si>
-    <t>조형관별관3층10호실,조형관별관3층2호실</t>
-  </si>
-  <si>
-    <t>7295401</t>
-  </si>
-  <si>
-    <t>AI콘텐츠디자인스튜디오1</t>
-  </si>
-  <si>
-    <t>권주영</t>
-  </si>
-  <si>
-    <t>월 14:00-19:45</t>
-  </si>
-  <si>
-    <t>김진영</t>
-  </si>
-  <si>
-    <t>월 10:00-13:00,목 10:00-13:00</t>
-  </si>
-  <si>
-    <t>7295501</t>
-  </si>
-  <si>
-    <t>AI 시대의 인간이해</t>
-  </si>
-  <si>
-    <t>7295601</t>
-  </si>
-  <si>
-    <t>Agentic UX디자인</t>
-  </si>
-  <si>
-    <t>7295701</t>
-  </si>
-  <si>
-    <t>서비스디자인스튜디오2</t>
-  </si>
-  <si>
-    <t>조만수</t>
-  </si>
-  <si>
-    <t>월 10:00-13:00,수 10:00-13:00</t>
-  </si>
-  <si>
-    <t>7295901</t>
-  </si>
-  <si>
-    <t>사운드경험디자인</t>
-  </si>
-  <si>
-    <t>남궁기찬</t>
-  </si>
-  <si>
-    <t>월 11:00-14:00</t>
-  </si>
-  <si>
-    <t>7296001</t>
-  </si>
-  <si>
-    <t>제품서비스시스템디자인스튜디오2</t>
-  </si>
-  <si>
-    <t>심유리</t>
-  </si>
-  <si>
-    <t>월 10:00-17:00</t>
-  </si>
-  <si>
-    <t>7296101</t>
-  </si>
-  <si>
-    <t>정보디자인스튜디오2</t>
-  </si>
-  <si>
-    <t>허정현</t>
-  </si>
-  <si>
-    <t>월 18:00-20:40,수 14:30-17:30</t>
-  </si>
-  <si>
-    <t>조형관별관3층3호실,조형관별관3층10호실</t>
-  </si>
-  <si>
-    <t>7296201</t>
-  </si>
-  <si>
-    <t>공공서비스디자인</t>
-  </si>
-  <si>
-    <t>박순정</t>
-  </si>
-  <si>
-    <t>조형관별관3층9호실</t>
-  </si>
-  <si>
-    <t>7296301</t>
-  </si>
-  <si>
-    <t>정량연구방법</t>
-  </si>
-  <si>
-    <t>36320</t>
-  </si>
-  <si>
-    <t>공간ㆍ문화디자인학과</t>
-  </si>
-  <si>
-    <t>704200b</t>
-  </si>
-  <si>
-    <t>7243701</t>
-  </si>
-  <si>
-    <t>특수연구과제2</t>
-  </si>
-  <si>
-    <t>윤성호</t>
-  </si>
-  <si>
-    <t>조형관별관3층14호실</t>
-  </si>
-  <si>
-    <t>7294501</t>
-  </si>
-  <si>
-    <t>7295101</t>
-  </si>
-  <si>
-    <t>강민선</t>
-  </si>
-  <si>
-    <t>707590a</t>
-  </si>
-  <si>
-    <t>소재 융합 개발 연구</t>
-  </si>
-  <si>
-    <t>이순정</t>
-  </si>
-  <si>
-    <t>토 10:00-13:00</t>
-  </si>
-  <si>
-    <t>7129001</t>
-  </si>
-  <si>
-    <t>디자인리서치&amp;방법론</t>
-  </si>
-  <si>
-    <t>7192201</t>
-  </si>
-  <si>
-    <t>글로벌 디자인 워크샵</t>
-  </si>
-  <si>
-    <t>정상엽</t>
-  </si>
-  <si>
-    <t>7192301</t>
-  </si>
-  <si>
-    <t>공간디자인 리서치 1</t>
-  </si>
-  <si>
-    <t>고은주</t>
-  </si>
-  <si>
-    <t>7243801</t>
-  </si>
-  <si>
-    <t>현대도시디자인</t>
-  </si>
-  <si>
-    <t>김상호</t>
-  </si>
-  <si>
-    <t>7262401</t>
-  </si>
-  <si>
-    <t>사진과 문화공간</t>
-  </si>
-  <si>
-    <t>김규랑</t>
-  </si>
-  <si>
-    <t>7294101</t>
-  </si>
-  <si>
-    <t>미래디자인트렌드</t>
-  </si>
-  <si>
-    <t>박성미</t>
-  </si>
-  <si>
-    <t>7294201</t>
-  </si>
-  <si>
-    <t>리빙제품 및 신소재연구</t>
-  </si>
-  <si>
-    <t>7294301</t>
-  </si>
-  <si>
-    <t>리빙 및 가구 제품 기획</t>
-  </si>
-  <si>
-    <t>김상현</t>
-  </si>
-  <si>
-    <t>토 13:00-18:50</t>
-  </si>
-  <si>
-    <t>7294401</t>
-  </si>
-  <si>
-    <t>융합실내디자인스튜디오1</t>
-  </si>
-  <si>
-    <t>7294601</t>
-  </si>
-  <si>
-    <t>문화현장리서치</t>
-  </si>
-  <si>
-    <t>이상해</t>
-  </si>
-  <si>
-    <t>7294701</t>
-  </si>
-  <si>
-    <t>디지털공간디자인1</t>
-  </si>
-  <si>
-    <t>민세희</t>
-  </si>
-  <si>
-    <t>7294801</t>
-  </si>
-  <si>
-    <t>융합공간디자인세미나</t>
-  </si>
-  <si>
-    <t>7294901</t>
-  </si>
-  <si>
-    <t>인터렉티브 환경디자인 스튜디오1</t>
-  </si>
-  <si>
-    <t>7295001</t>
-  </si>
-  <si>
-    <t>공간디자인스튜디오2</t>
-  </si>
-  <si>
-    <t>7295201</t>
-  </si>
-  <si>
-    <t>크리에이티브스페이스스튜디오1</t>
-  </si>
-  <si>
-    <t>7295301</t>
-  </si>
-  <si>
-    <t>뉴미디어환경디자인스튜디오1</t>
-  </si>
-  <si>
-    <t>36378</t>
-  </si>
-  <si>
-    <t>융합디자인학과</t>
-  </si>
-  <si>
-    <t>689540b</t>
-  </si>
-  <si>
-    <t>성재혁</t>
-  </si>
-  <si>
-    <t>689260a</t>
-  </si>
-  <si>
-    <t>704700a</t>
-  </si>
-  <si>
-    <t>사회적책임과디자인4</t>
-  </si>
-  <si>
-    <t>최호랑</t>
-  </si>
-  <si>
-    <t>7130201</t>
-  </si>
-  <si>
-    <t>타이포그래픽 디자인4</t>
-  </si>
-  <si>
-    <t>화 10:00-13:00,금 10:00-13:00</t>
   </si>
   <si>
     <t>7231901</t>
@@ -30564,7 +30564,7 @@
         <v>21</v>
       </c>
       <c r="L504" t="s">
-        <v>1506</v>
+        <v>536</v>
       </c>
       <c r="M504" t="s">
         <v>23</v>
@@ -30587,10 +30587,10 @@
         <v>1501</v>
       </c>
       <c r="F505" t="s">
+        <v>1506</v>
+      </c>
+      <c r="G505" t="s">
         <v>1507</v>
-      </c>
-      <c r="G505" t="s">
-        <v>1508</v>
       </c>
       <c r="H505">
         <v>3</v>
@@ -30599,7 +30599,7 @@
         <v>1504</v>
       </c>
       <c r="J505" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="K505" t="s">
         <v>21</v>
@@ -30628,16 +30628,16 @@
         <v>1501</v>
       </c>
       <c r="F506" t="s">
+        <v>1509</v>
+      </c>
+      <c r="G506" t="s">
         <v>1510</v>
       </c>
-      <c r="G506" t="s">
+      <c r="H506">
+        <v>3</v>
+      </c>
+      <c r="I506" t="s">
         <v>1511</v>
-      </c>
-      <c r="H506">
-        <v>3</v>
-      </c>
-      <c r="I506" t="s">
-        <v>1512</v>
       </c>
       <c r="J506" t="s">
         <v>531</v>
@@ -30646,7 +30646,7 @@
         <v>21</v>
       </c>
       <c r="L506" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="M506" t="s">
         <v>23</v>
@@ -30669,25 +30669,25 @@
         <v>1501</v>
       </c>
       <c r="F507" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G507" t="s">
         <v>1514</v>
       </c>
-      <c r="G507" t="s">
+      <c r="H507">
+        <v>3</v>
+      </c>
+      <c r="I507" t="s">
+        <v>1511</v>
+      </c>
+      <c r="J507" t="s">
         <v>1515</v>
       </c>
-      <c r="H507">
-        <v>3</v>
-      </c>
-      <c r="I507" t="s">
-        <v>1512</v>
-      </c>
-      <c r="J507" t="s">
+      <c r="K507" t="s">
+        <v>21</v>
+      </c>
+      <c r="L507" t="s">
         <v>1516</v>
-      </c>
-      <c r="K507" t="s">
-        <v>21</v>
-      </c>
-      <c r="L507" t="s">
-        <v>1513</v>
       </c>
       <c r="M507" t="s">
         <v>23</v>
@@ -30851,7 +30851,7 @@
         <v>21</v>
       </c>
       <c r="L511" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="M511" t="s">
         <v>23</v>
@@ -31302,7 +31302,7 @@
         <v>21</v>
       </c>
       <c r="L522" t="s">
-        <v>1547</v>
+        <v>1562</v>
       </c>
       <c r="M522" t="s">
         <v>23</v>
@@ -31466,7 +31466,7 @@
         <v>21</v>
       </c>
       <c r="L526" t="s">
-        <v>1586</v>
+        <v>1516</v>
       </c>
       <c r="M526" t="s">
         <v>23</v>
@@ -31489,25 +31489,25 @@
         <v>1563</v>
       </c>
       <c r="F527" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G527" t="s">
         <v>1587</v>
-      </c>
-      <c r="G527" t="s">
-        <v>1588</v>
       </c>
       <c r="H527">
         <v>6</v>
       </c>
       <c r="I527" t="s">
+        <v>1588</v>
+      </c>
+      <c r="J527" t="s">
         <v>1589</v>
       </c>
-      <c r="J527" t="s">
+      <c r="K527" t="s">
+        <v>21</v>
+      </c>
+      <c r="L527" t="s">
         <v>1590</v>
-      </c>
-      <c r="K527" t="s">
-        <v>21</v>
-      </c>
-      <c r="L527" t="s">
-        <v>1591</v>
       </c>
       <c r="M527" t="s">
         <v>23</v>
@@ -31530,19 +31530,19 @@
         <v>1563</v>
       </c>
       <c r="F528" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G528" t="s">
         <v>1592</v>
-      </c>
-      <c r="G528" t="s">
-        <v>1593</v>
       </c>
       <c r="H528">
         <v>6</v>
       </c>
       <c r="I528" t="s">
+        <v>1593</v>
+      </c>
+      <c r="J528" t="s">
         <v>1594</v>
-      </c>
-      <c r="J528" t="s">
-        <v>1595</v>
       </c>
       <c r="K528" t="s">
         <v>21</v>
@@ -31571,19 +31571,19 @@
         <v>1563</v>
       </c>
       <c r="F529" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G529" t="s">
         <v>1592</v>
-      </c>
-      <c r="G529" t="s">
-        <v>1593</v>
       </c>
       <c r="H529">
         <v>6</v>
       </c>
       <c r="I529" t="s">
+        <v>1595</v>
+      </c>
+      <c r="J529" t="s">
         <v>1596</v>
-      </c>
-      <c r="J529" t="s">
-        <v>1597</v>
       </c>
       <c r="K529" t="s">
         <v>21</v>
@@ -31612,16 +31612,16 @@
         <v>52</v>
       </c>
       <c r="F530" t="s">
+        <v>1597</v>
+      </c>
+      <c r="G530" t="s">
         <v>1598</v>
       </c>
-      <c r="G530" t="s">
-        <v>1599</v>
-      </c>
       <c r="H530">
         <v>3</v>
       </c>
       <c r="I530" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="J530" t="s">
         <v>86</v>
@@ -31630,7 +31630,7 @@
         <v>21</v>
       </c>
       <c r="L530" t="s">
-        <v>1586</v>
+        <v>1516</v>
       </c>
       <c r="M530" t="s">
         <v>23</v>
@@ -31653,16 +31653,16 @@
         <v>52</v>
       </c>
       <c r="F531" t="s">
+        <v>1599</v>
+      </c>
+      <c r="G531" t="s">
         <v>1600</v>
       </c>
-      <c r="G531" t="s">
-        <v>1601</v>
-      </c>
       <c r="H531">
         <v>3</v>
       </c>
       <c r="I531" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="J531" t="s">
         <v>117</v>
@@ -31671,7 +31671,7 @@
         <v>21</v>
       </c>
       <c r="L531" t="s">
-        <v>1586</v>
+        <v>1516</v>
       </c>
       <c r="M531" t="s">
         <v>23</v>
@@ -31694,19 +31694,19 @@
         <v>1563</v>
       </c>
       <c r="F532" t="s">
+        <v>1601</v>
+      </c>
+      <c r="G532" t="s">
         <v>1602</v>
-      </c>
-      <c r="G532" t="s">
-        <v>1603</v>
       </c>
       <c r="H532">
         <v>6</v>
       </c>
       <c r="I532" t="s">
+        <v>1603</v>
+      </c>
+      <c r="J532" t="s">
         <v>1604</v>
-      </c>
-      <c r="J532" t="s">
-        <v>1605</v>
       </c>
       <c r="K532" t="s">
         <v>21</v>
@@ -31735,19 +31735,19 @@
         <v>52</v>
       </c>
       <c r="F533" t="s">
+        <v>1605</v>
+      </c>
+      <c r="G533" t="s">
         <v>1606</v>
       </c>
-      <c r="G533" t="s">
+      <c r="H533">
+        <v>3</v>
+      </c>
+      <c r="I533" t="s">
         <v>1607</v>
       </c>
-      <c r="H533">
-        <v>3</v>
-      </c>
-      <c r="I533" t="s">
+      <c r="J533" t="s">
         <v>1608</v>
-      </c>
-      <c r="J533" t="s">
-        <v>1609</v>
       </c>
       <c r="K533" t="s">
         <v>21</v>
@@ -31776,19 +31776,19 @@
         <v>1563</v>
       </c>
       <c r="F534" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G534" t="s">
         <v>1610</v>
-      </c>
-      <c r="G534" t="s">
-        <v>1611</v>
       </c>
       <c r="H534">
         <v>6</v>
       </c>
       <c r="I534" t="s">
+        <v>1611</v>
+      </c>
+      <c r="J534" t="s">
         <v>1612</v>
-      </c>
-      <c r="J534" t="s">
-        <v>1613</v>
       </c>
       <c r="K534" t="s">
         <v>21</v>
@@ -31817,25 +31817,25 @@
         <v>1563</v>
       </c>
       <c r="F535" t="s">
+        <v>1613</v>
+      </c>
+      <c r="G535" t="s">
         <v>1614</v>
-      </c>
-      <c r="G535" t="s">
-        <v>1615</v>
       </c>
       <c r="H535">
         <v>6</v>
       </c>
       <c r="I535" t="s">
+        <v>1615</v>
+      </c>
+      <c r="J535" t="s">
         <v>1616</v>
       </c>
-      <c r="J535" t="s">
+      <c r="K535" t="s">
+        <v>21</v>
+      </c>
+      <c r="L535" t="s">
         <v>1617</v>
-      </c>
-      <c r="K535" t="s">
-        <v>21</v>
-      </c>
-      <c r="L535" t="s">
-        <v>1618</v>
       </c>
       <c r="M535" t="s">
         <v>23</v>
@@ -31858,16 +31858,16 @@
         <v>52</v>
       </c>
       <c r="F536" t="s">
+        <v>1618</v>
+      </c>
+      <c r="G536" t="s">
         <v>1619</v>
       </c>
-      <c r="G536" t="s">
+      <c r="H536">
+        <v>3</v>
+      </c>
+      <c r="I536" t="s">
         <v>1620</v>
-      </c>
-      <c r="H536">
-        <v>3</v>
-      </c>
-      <c r="I536" t="s">
-        <v>1621</v>
       </c>
       <c r="J536" t="s">
         <v>86</v>
@@ -31876,7 +31876,7 @@
         <v>21</v>
       </c>
       <c r="L536" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="M536" t="s">
         <v>23</v>
@@ -31899,16 +31899,16 @@
         <v>52</v>
       </c>
       <c r="F537" t="s">
+        <v>1622</v>
+      </c>
+      <c r="G537" t="s">
         <v>1623</v>
       </c>
-      <c r="G537" t="s">
-        <v>1624</v>
-      </c>
       <c r="H537">
         <v>3</v>
       </c>
       <c r="I537" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="J537" t="s">
         <v>163</v>
@@ -31931,16 +31931,16 @@
         <v>1500</v>
       </c>
       <c r="C538" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D538" t="s">
         <v>1625</v>
-      </c>
-      <c r="D538" t="s">
-        <v>1626</v>
       </c>
       <c r="E538" t="s">
         <v>52</v>
       </c>
       <c r="F538" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="G538" t="s">
         <v>1540</v>
@@ -31972,25 +31972,25 @@
         <v>1500</v>
       </c>
       <c r="C539" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D539" t="s">
         <v>1625</v>
-      </c>
-      <c r="D539" t="s">
-        <v>1626</v>
       </c>
       <c r="E539" t="s">
         <v>52</v>
       </c>
       <c r="F539" t="s">
+        <v>1627</v>
+      </c>
+      <c r="G539" t="s">
         <v>1628</v>
       </c>
-      <c r="G539" t="s">
+      <c r="H539">
+        <v>3</v>
+      </c>
+      <c r="I539" t="s">
         <v>1629</v>
-      </c>
-      <c r="H539">
-        <v>3</v>
-      </c>
-      <c r="I539" t="s">
-        <v>1630</v>
       </c>
       <c r="J539" t="s">
         <v>70</v>
@@ -31999,7 +31999,7 @@
         <v>21</v>
       </c>
       <c r="L539" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M539" t="s">
         <v>23</v>
@@ -32013,16 +32013,16 @@
         <v>1500</v>
       </c>
       <c r="C540" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D540" t="s">
         <v>1625</v>
-      </c>
-      <c r="D540" t="s">
-        <v>1626</v>
       </c>
       <c r="E540" t="s">
         <v>52</v>
       </c>
       <c r="F540" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="G540" t="s">
         <v>1549</v>
@@ -32040,7 +32040,7 @@
         <v>21</v>
       </c>
       <c r="L540" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="M540" t="s">
         <v>23</v>
@@ -32054,16 +32054,16 @@
         <v>1500</v>
       </c>
       <c r="C541" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D541" t="s">
         <v>1625</v>
-      </c>
-      <c r="D541" t="s">
-        <v>1626</v>
       </c>
       <c r="E541" t="s">
         <v>52</v>
       </c>
       <c r="F541" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="G541" t="s">
         <v>1545</v>
@@ -32072,7 +32072,7 @@
         <v>3</v>
       </c>
       <c r="I541" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="J541" t="s">
         <v>359</v>
@@ -32095,34 +32095,34 @@
         <v>1500</v>
       </c>
       <c r="C542" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D542" t="s">
         <v>1625</v>
-      </c>
-      <c r="D542" t="s">
-        <v>1626</v>
       </c>
       <c r="E542" t="s">
         <v>52</v>
       </c>
       <c r="F542" t="s">
+        <v>1634</v>
+      </c>
+      <c r="G542" t="s">
         <v>1635</v>
       </c>
-      <c r="G542" t="s">
+      <c r="H542">
+        <v>3</v>
+      </c>
+      <c r="I542" t="s">
         <v>1636</v>
       </c>
-      <c r="H542">
-        <v>3</v>
-      </c>
-      <c r="I542" t="s">
+      <c r="J542" t="s">
         <v>1637</v>
       </c>
-      <c r="J542" t="s">
-        <v>1638</v>
-      </c>
       <c r="K542" t="s">
         <v>21</v>
       </c>
       <c r="L542" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="M542" t="s">
         <v>23</v>
@@ -32136,19 +32136,19 @@
         <v>1500</v>
       </c>
       <c r="C543" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D543" t="s">
         <v>1625</v>
-      </c>
-      <c r="D543" t="s">
-        <v>1626</v>
       </c>
       <c r="E543" t="s">
         <v>52</v>
       </c>
       <c r="F543" t="s">
+        <v>1638</v>
+      </c>
+      <c r="G543" t="s">
         <v>1639</v>
-      </c>
-      <c r="G543" t="s">
-        <v>1640</v>
       </c>
       <c r="H543">
         <v>3</v>
@@ -32163,7 +32163,7 @@
         <v>21</v>
       </c>
       <c r="L543" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="M543" t="s">
         <v>23</v>
@@ -32177,25 +32177,25 @@
         <v>1500</v>
       </c>
       <c r="C544" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D544" t="s">
         <v>1625</v>
-      </c>
-      <c r="D544" t="s">
-        <v>1626</v>
       </c>
       <c r="E544" t="s">
         <v>1563</v>
       </c>
       <c r="F544" t="s">
+        <v>1640</v>
+      </c>
+      <c r="G544" t="s">
         <v>1641</v>
       </c>
-      <c r="G544" t="s">
+      <c r="H544">
+        <v>3</v>
+      </c>
+      <c r="I544" t="s">
         <v>1642</v>
-      </c>
-      <c r="H544">
-        <v>3</v>
-      </c>
-      <c r="I544" t="s">
-        <v>1643</v>
       </c>
       <c r="J544" t="s">
         <v>854</v>
@@ -32218,25 +32218,25 @@
         <v>1500</v>
       </c>
       <c r="C545" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D545" t="s">
         <v>1625</v>
-      </c>
-      <c r="D545" t="s">
-        <v>1626</v>
       </c>
       <c r="E545" t="s">
         <v>52</v>
       </c>
       <c r="F545" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G545" t="s">
         <v>1644</v>
       </c>
-      <c r="G545" t="s">
+      <c r="H545">
+        <v>3</v>
+      </c>
+      <c r="I545" t="s">
         <v>1645</v>
-      </c>
-      <c r="H545">
-        <v>3</v>
-      </c>
-      <c r="I545" t="s">
-        <v>1646</v>
       </c>
       <c r="J545" t="s">
         <v>163</v>
@@ -32245,7 +32245,7 @@
         <v>21</v>
       </c>
       <c r="L545" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="M545" t="s">
         <v>23</v>
@@ -32259,25 +32259,25 @@
         <v>1500</v>
       </c>
       <c r="C546" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D546" t="s">
         <v>1625</v>
-      </c>
-      <c r="D546" t="s">
-        <v>1626</v>
       </c>
       <c r="E546" t="s">
         <v>52</v>
       </c>
       <c r="F546" t="s">
+        <v>1646</v>
+      </c>
+      <c r="G546" t="s">
         <v>1647</v>
       </c>
-      <c r="G546" t="s">
+      <c r="H546">
+        <v>3</v>
+      </c>
+      <c r="I546" t="s">
         <v>1648</v>
-      </c>
-      <c r="H546">
-        <v>3</v>
-      </c>
-      <c r="I546" t="s">
-        <v>1649</v>
       </c>
       <c r="J546" t="s">
         <v>99</v>
@@ -32286,7 +32286,7 @@
         <v>21</v>
       </c>
       <c r="L546" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M546" t="s">
         <v>23</v>
@@ -32300,25 +32300,25 @@
         <v>1500</v>
       </c>
       <c r="C547" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D547" t="s">
         <v>1625</v>
-      </c>
-      <c r="D547" t="s">
-        <v>1626</v>
       </c>
       <c r="E547" t="s">
         <v>52</v>
       </c>
       <c r="F547" t="s">
+        <v>1649</v>
+      </c>
+      <c r="G547" t="s">
         <v>1650</v>
       </c>
-      <c r="G547" t="s">
+      <c r="H547">
+        <v>3</v>
+      </c>
+      <c r="I547" t="s">
         <v>1651</v>
-      </c>
-      <c r="H547">
-        <v>3</v>
-      </c>
-      <c r="I547" t="s">
-        <v>1652</v>
       </c>
       <c r="J547" t="s">
         <v>271</v>
@@ -32341,34 +32341,34 @@
         <v>1500</v>
       </c>
       <c r="C548" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D548" t="s">
         <v>1625</v>
-      </c>
-      <c r="D548" t="s">
-        <v>1626</v>
       </c>
       <c r="E548" t="s">
         <v>52</v>
       </c>
       <c r="F548" t="s">
+        <v>1652</v>
+      </c>
+      <c r="G548" t="s">
         <v>1653</v>
       </c>
-      <c r="G548" t="s">
+      <c r="H548">
+        <v>3</v>
+      </c>
+      <c r="I548" t="s">
         <v>1654</v>
       </c>
-      <c r="H548">
-        <v>3</v>
-      </c>
-      <c r="I548" t="s">
-        <v>1655</v>
-      </c>
       <c r="J548" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="K548" t="s">
         <v>21</v>
       </c>
       <c r="L548" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="M548" t="s">
         <v>23</v>
@@ -32382,19 +32382,19 @@
         <v>1500</v>
       </c>
       <c r="C549" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D549" t="s">
         <v>1625</v>
-      </c>
-      <c r="D549" t="s">
-        <v>1626</v>
       </c>
       <c r="E549" t="s">
         <v>52</v>
       </c>
       <c r="F549" t="s">
+        <v>1655</v>
+      </c>
+      <c r="G549" t="s">
         <v>1656</v>
-      </c>
-      <c r="G549" t="s">
-        <v>1657</v>
       </c>
       <c r="H549">
         <v>3</v>
@@ -32409,7 +32409,7 @@
         <v>21</v>
       </c>
       <c r="L549" t="s">
-        <v>1586</v>
+        <v>1516</v>
       </c>
       <c r="M549" t="s">
         <v>23</v>
@@ -32423,34 +32423,34 @@
         <v>1500</v>
       </c>
       <c r="C550" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D550" t="s">
         <v>1625</v>
-      </c>
-      <c r="D550" t="s">
-        <v>1626</v>
       </c>
       <c r="E550" t="s">
         <v>1563</v>
       </c>
       <c r="F550" t="s">
+        <v>1657</v>
+      </c>
+      <c r="G550" t="s">
         <v>1658</v>
-      </c>
-      <c r="G550" t="s">
-        <v>1659</v>
       </c>
       <c r="H550">
         <v>6</v>
       </c>
       <c r="I550" t="s">
+        <v>1659</v>
+      </c>
+      <c r="J550" t="s">
         <v>1660</v>
       </c>
-      <c r="J550" t="s">
-        <v>1661</v>
-      </c>
       <c r="K550" t="s">
         <v>21</v>
       </c>
       <c r="L550" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="M550" t="s">
         <v>23</v>
@@ -32464,25 +32464,25 @@
         <v>1500</v>
       </c>
       <c r="C551" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D551" t="s">
         <v>1625</v>
-      </c>
-      <c r="D551" t="s">
-        <v>1626</v>
       </c>
       <c r="E551" t="s">
         <v>1563</v>
       </c>
       <c r="F551" t="s">
+        <v>1661</v>
+      </c>
+      <c r="G551" t="s">
         <v>1662</v>
       </c>
-      <c r="G551" t="s">
-        <v>1663</v>
-      </c>
       <c r="H551">
         <v>3</v>
       </c>
       <c r="I551" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="J551" t="s">
         <v>148</v>
@@ -32505,25 +32505,25 @@
         <v>1500</v>
       </c>
       <c r="C552" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D552" t="s">
         <v>1625</v>
-      </c>
-      <c r="D552" t="s">
-        <v>1626</v>
       </c>
       <c r="E552" t="s">
         <v>52</v>
       </c>
       <c r="F552" t="s">
+        <v>1663</v>
+      </c>
+      <c r="G552" t="s">
         <v>1664</v>
       </c>
-      <c r="G552" t="s">
+      <c r="H552">
+        <v>3</v>
+      </c>
+      <c r="I552" t="s">
         <v>1665</v>
-      </c>
-      <c r="H552">
-        <v>3</v>
-      </c>
-      <c r="I552" t="s">
-        <v>1666</v>
       </c>
       <c r="J552" t="s">
         <v>271</v>
@@ -32546,25 +32546,25 @@
         <v>1500</v>
       </c>
       <c r="C553" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D553" t="s">
         <v>1625</v>
-      </c>
-      <c r="D553" t="s">
-        <v>1626</v>
       </c>
       <c r="E553" t="s">
         <v>1563</v>
       </c>
       <c r="F553" t="s">
+        <v>1666</v>
+      </c>
+      <c r="G553" t="s">
         <v>1667</v>
       </c>
-      <c r="G553" t="s">
+      <c r="H553">
+        <v>3</v>
+      </c>
+      <c r="I553" t="s">
         <v>1668</v>
-      </c>
-      <c r="H553">
-        <v>3</v>
-      </c>
-      <c r="I553" t="s">
-        <v>1669</v>
       </c>
       <c r="J553" t="s">
         <v>70</v>
@@ -32573,7 +32573,7 @@
         <v>21</v>
       </c>
       <c r="L553" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="M553" t="s">
         <v>23</v>
@@ -32587,19 +32587,19 @@
         <v>1500</v>
       </c>
       <c r="C554" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D554" t="s">
         <v>1625</v>
-      </c>
-      <c r="D554" t="s">
-        <v>1626</v>
       </c>
       <c r="E554" t="s">
         <v>52</v>
       </c>
       <c r="F554" t="s">
+        <v>1669</v>
+      </c>
+      <c r="G554" t="s">
         <v>1670</v>
-      </c>
-      <c r="G554" t="s">
-        <v>1671</v>
       </c>
       <c r="H554">
         <v>3</v>
@@ -32628,19 +32628,19 @@
         <v>1500</v>
       </c>
       <c r="C555" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D555" t="s">
         <v>1625</v>
-      </c>
-      <c r="D555" t="s">
-        <v>1626</v>
       </c>
       <c r="E555" t="s">
         <v>1563</v>
       </c>
       <c r="F555" t="s">
+        <v>1671</v>
+      </c>
+      <c r="G555" t="s">
         <v>1672</v>
-      </c>
-      <c r="G555" t="s">
-        <v>1673</v>
       </c>
       <c r="H555">
         <v>3</v>
@@ -32669,19 +32669,19 @@
         <v>1500</v>
       </c>
       <c r="C556" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D556" t="s">
         <v>1625</v>
-      </c>
-      <c r="D556" t="s">
-        <v>1626</v>
       </c>
       <c r="E556" t="s">
         <v>1563</v>
       </c>
       <c r="F556" t="s">
+        <v>1673</v>
+      </c>
+      <c r="G556" t="s">
         <v>1674</v>
-      </c>
-      <c r="G556" t="s">
-        <v>1675</v>
       </c>
       <c r="H556">
         <v>3</v>
@@ -32710,25 +32710,25 @@
         <v>1500</v>
       </c>
       <c r="C557" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D557" t="s">
         <v>1625</v>
-      </c>
-      <c r="D557" t="s">
-        <v>1626</v>
       </c>
       <c r="E557" t="s">
         <v>1563</v>
       </c>
       <c r="F557" t="s">
+        <v>1675</v>
+      </c>
+      <c r="G557" t="s">
         <v>1676</v>
       </c>
-      <c r="G557" t="s">
-        <v>1677</v>
-      </c>
       <c r="H557">
         <v>3</v>
       </c>
       <c r="I557" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="J557" t="s">
         <v>908</v>
@@ -32737,7 +32737,7 @@
         <v>21</v>
       </c>
       <c r="L557" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M557" t="s">
         <v>23</v>
@@ -32751,25 +32751,25 @@
         <v>1500</v>
       </c>
       <c r="C558" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D558" t="s">
         <v>1625</v>
-      </c>
-      <c r="D558" t="s">
-        <v>1626</v>
       </c>
       <c r="E558" t="s">
         <v>1563</v>
       </c>
       <c r="F558" t="s">
+        <v>1677</v>
+      </c>
+      <c r="G558" t="s">
         <v>1678</v>
       </c>
-      <c r="G558" t="s">
-        <v>1679</v>
-      </c>
       <c r="H558">
         <v>3</v>
       </c>
       <c r="I558" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="J558" t="s">
         <v>854</v>
@@ -32792,16 +32792,16 @@
         <v>1500</v>
       </c>
       <c r="C559" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D559" t="s">
         <v>1680</v>
-      </c>
-      <c r="D559" t="s">
-        <v>1681</v>
       </c>
       <c r="E559" t="s">
         <v>52</v>
       </c>
       <c r="F559" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="G559" t="s">
         <v>1540</v>
@@ -32810,7 +32810,7 @@
         <v>0</v>
       </c>
       <c r="I559" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J559" t="s">
         <v>571</v>
@@ -32819,7 +32819,7 @@
         <v>21</v>
       </c>
       <c r="L559" t="s">
-        <v>1586</v>
+        <v>1516</v>
       </c>
       <c r="M559" t="s">
         <v>23</v>
@@ -32833,16 +32833,16 @@
         <v>1500</v>
       </c>
       <c r="C560" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D560" t="s">
         <v>1680</v>
-      </c>
-      <c r="D560" t="s">
-        <v>1681</v>
       </c>
       <c r="E560" t="s">
         <v>52</v>
       </c>
       <c r="F560" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="G560" t="s">
         <v>1549</v>
@@ -32851,7 +32851,7 @@
         <v>3</v>
       </c>
       <c r="I560" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J560" t="s">
         <v>359</v>
@@ -32874,25 +32874,25 @@
         <v>1500</v>
       </c>
       <c r="C561" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D561" t="s">
         <v>1680</v>
-      </c>
-      <c r="D561" t="s">
-        <v>1681</v>
       </c>
       <c r="E561" t="s">
         <v>52</v>
       </c>
       <c r="F561" t="s">
+        <v>1684</v>
+      </c>
+      <c r="G561" t="s">
         <v>1685</v>
       </c>
-      <c r="G561" t="s">
+      <c r="H561">
+        <v>3</v>
+      </c>
+      <c r="I561" t="s">
         <v>1686</v>
-      </c>
-      <c r="H561">
-        <v>3</v>
-      </c>
-      <c r="I561" t="s">
-        <v>1687</v>
       </c>
       <c r="J561" t="s">
         <v>908</v>
@@ -32915,19 +32915,19 @@
         <v>1500</v>
       </c>
       <c r="C562" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D562" t="s">
         <v>1680</v>
-      </c>
-      <c r="D562" t="s">
-        <v>1681</v>
       </c>
       <c r="E562" t="s">
         <v>1563</v>
       </c>
       <c r="F562" t="s">
+        <v>1687</v>
+      </c>
+      <c r="G562" t="s">
         <v>1688</v>
-      </c>
-      <c r="G562" t="s">
-        <v>1689</v>
       </c>
       <c r="H562">
         <v>6</v>
@@ -32936,13 +32936,13 @@
         <v>1519</v>
       </c>
       <c r="J562" t="s">
+        <v>1689</v>
+      </c>
+      <c r="K562" t="s">
+        <v>21</v>
+      </c>
+      <c r="L562" t="s">
         <v>1690</v>
-      </c>
-      <c r="K562" t="s">
-        <v>21</v>
-      </c>
-      <c r="L562" t="s">
-        <v>1506</v>
       </c>
       <c r="M562" t="s">
         <v>23</v>
@@ -32956,10 +32956,10 @@
         <v>1500</v>
       </c>
       <c r="C563" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D563" t="s">
         <v>1680</v>
-      </c>
-      <c r="D563" t="s">
-        <v>1681</v>
       </c>
       <c r="E563" t="s">
         <v>1563</v>
@@ -32983,7 +32983,7 @@
         <v>21</v>
       </c>
       <c r="L563" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="M563" t="s">
         <v>23</v>
@@ -32997,10 +32997,10 @@
         <v>1500</v>
       </c>
       <c r="C564" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D564" t="s">
         <v>1680</v>
-      </c>
-      <c r="D564" t="s">
-        <v>1681</v>
       </c>
       <c r="E564" t="s">
         <v>52</v>
@@ -33038,10 +33038,10 @@
         <v>1500</v>
       </c>
       <c r="C565" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D565" t="s">
         <v>1680</v>
-      </c>
-      <c r="D565" t="s">
-        <v>1681</v>
       </c>
       <c r="E565" t="s">
         <v>52</v>
@@ -33056,7 +33056,7 @@
         <v>3</v>
       </c>
       <c r="I565" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="J565" t="s">
         <v>908</v>
@@ -33079,10 +33079,10 @@
         <v>1500</v>
       </c>
       <c r="C566" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D566" t="s">
         <v>1680</v>
-      </c>
-      <c r="D566" t="s">
-        <v>1681</v>
       </c>
       <c r="E566" t="s">
         <v>1563</v>
@@ -33120,10 +33120,10 @@
         <v>1500</v>
       </c>
       <c r="C567" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D567" t="s">
         <v>1680</v>
-      </c>
-      <c r="D567" t="s">
-        <v>1681</v>
       </c>
       <c r="E567" t="s">
         <v>52</v>
@@ -33161,10 +33161,10 @@
         <v>1500</v>
       </c>
       <c r="C568" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D568" t="s">
         <v>1680</v>
-      </c>
-      <c r="D568" t="s">
-        <v>1681</v>
       </c>
       <c r="E568" t="s">
         <v>52</v>
@@ -33202,10 +33202,10 @@
         <v>1500</v>
       </c>
       <c r="C569" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D569" t="s">
         <v>1680</v>
-      </c>
-      <c r="D569" t="s">
-        <v>1681</v>
       </c>
       <c r="E569" t="s">
         <v>52</v>
@@ -33243,10 +33243,10 @@
         <v>1500</v>
       </c>
       <c r="C570" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D570" t="s">
         <v>1680</v>
-      </c>
-      <c r="D570" t="s">
-        <v>1681</v>
       </c>
       <c r="E570" t="s">
         <v>52</v>
@@ -33270,7 +33270,7 @@
         <v>21</v>
       </c>
       <c r="L570" t="s">
-        <v>1506</v>
+        <v>1690</v>
       </c>
       <c r="M570" t="s">
         <v>23</v>
@@ -33284,10 +33284,10 @@
         <v>1500</v>
       </c>
       <c r="C571" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D571" t="s">
         <v>1680</v>
-      </c>
-      <c r="D571" t="s">
-        <v>1681</v>
       </c>
       <c r="E571" t="s">
         <v>52</v>
@@ -33311,7 +33311,7 @@
         <v>21</v>
       </c>
       <c r="L571" t="s">
-        <v>1506</v>
+        <v>1690</v>
       </c>
       <c r="M571" t="s">
         <v>23</v>
@@ -33325,10 +33325,10 @@
         <v>1500</v>
       </c>
       <c r="C572" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D572" t="s">
         <v>1680</v>
-      </c>
-      <c r="D572" t="s">
-        <v>1681</v>
       </c>
       <c r="E572" t="s">
         <v>1563</v>
@@ -33352,7 +33352,7 @@
         <v>21</v>
       </c>
       <c r="L572" t="s">
-        <v>1506</v>
+        <v>1690</v>
       </c>
       <c r="M572" t="s">
         <v>23</v>
@@ -33366,10 +33366,10 @@
         <v>1500</v>
       </c>
       <c r="C573" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D573" t="s">
         <v>1680</v>
-      </c>
-      <c r="D573" t="s">
-        <v>1681</v>
       </c>
       <c r="E573" t="s">
         <v>52</v>
@@ -33407,10 +33407,10 @@
         <v>1500</v>
       </c>
       <c r="C574" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D574" t="s">
         <v>1680</v>
-      </c>
-      <c r="D574" t="s">
-        <v>1681</v>
       </c>
       <c r="E574" t="s">
         <v>1563</v>
@@ -33448,10 +33448,10 @@
         <v>1500</v>
       </c>
       <c r="C575" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D575" t="s">
         <v>1680</v>
-      </c>
-      <c r="D575" t="s">
-        <v>1681</v>
       </c>
       <c r="E575" t="s">
         <v>1563</v>
@@ -42773,7 +42773,7 @@
         <v>3</v>
       </c>
       <c r="I802" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="J802" t="s">
         <v>355</v>
@@ -42814,7 +42814,7 @@
         <v>3</v>
       </c>
       <c r="I803" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="J803" t="s">
         <v>2415</v>
@@ -43511,7 +43511,7 @@
         <v>3</v>
       </c>
       <c r="I820" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="J820" t="s">
         <v>355</v>
@@ -43520,7 +43520,7 @@
         <v>21</v>
       </c>
       <c r="L820" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="M820" t="s">
         <v>23</v>
@@ -43552,7 +43552,7 @@
         <v>3</v>
       </c>
       <c r="I821" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="J821" t="s">
         <v>2415</v>
@@ -45110,7 +45110,7 @@
         <v>2</v>
       </c>
       <c r="I859" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="J859" t="s">
         <v>2638</v>
@@ -47652,7 +47652,7 @@
         <v>2</v>
       </c>
       <c r="I921" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="J921" t="s">
         <v>678</v>
